--- a/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
+++ b/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="295">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="298">
   <si>
     <t>DATA RADAR ANOMALI KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 5 Sep 2026, 06.52</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 6 Sep 2026, 07.59</t>
   </si>
   <si>
     <t>Kode</t>
@@ -298,559 +298,571 @@
     <t>0,01</t>
   </si>
   <si>
-    <t>4,21</t>
-  </si>
-  <si>
-    <t>0,59</t>
+    <t>4,29</t>
+  </si>
+  <si>
+    <t>0,58</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>21,11</t>
+    <t>21,44</t>
+  </si>
+  <si>
+    <t>0,12</t>
+  </si>
+  <si>
+    <t>0,63</t>
+  </si>
+  <si>
+    <t>2,27</t>
+  </si>
+  <si>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>2,92</t>
+  </si>
+  <si>
+    <t>0,52</t>
+  </si>
+  <si>
+    <t>0,32</t>
+  </si>
+  <si>
+    <t>43,69</t>
+  </si>
+  <si>
+    <t>0,91</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>16,13</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>LAMPUNG BARAT</t>
+  </si>
+  <si>
+    <t>4,23</t>
+  </si>
+  <si>
+    <t>0,67</t>
+  </si>
+  <si>
+    <t>28,4</t>
+  </si>
+  <si>
+    <t>0,17</t>
+  </si>
+  <si>
+    <t>0,46</t>
+  </si>
+  <si>
+    <t>4,12</t>
+  </si>
+  <si>
+    <t>0,44</t>
+  </si>
+  <si>
+    <t>39,65</t>
+  </si>
+  <si>
+    <t>0,08</t>
+  </si>
+  <si>
+    <t>12,81</t>
+  </si>
+  <si>
+    <t>7,97</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>TANGGAMUS</t>
+  </si>
+  <si>
+    <t>6,64</t>
+  </si>
+  <si>
+    <t>19,74</t>
+  </si>
+  <si>
+    <t>0,06</t>
+  </si>
+  <si>
+    <t>0,87</t>
+  </si>
+  <si>
+    <t>3,44</t>
+  </si>
+  <si>
+    <t>3,32</t>
+  </si>
+  <si>
+    <t>0,29</t>
+  </si>
+  <si>
+    <t>41,88</t>
+  </si>
+  <si>
+    <t>22,89</t>
+  </si>
+  <si>
+    <t>0,41</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>LAMPUNG SELATAN</t>
+  </si>
+  <si>
+    <t>5,74</t>
+  </si>
+  <si>
+    <t>0,33</t>
+  </si>
+  <si>
+    <t>20,57</t>
+  </si>
+  <si>
+    <t>0,51</t>
+  </si>
+  <si>
+    <t>2,89</t>
+  </si>
+  <si>
+    <t>3,27</t>
+  </si>
+  <si>
+    <t>44,09</t>
+  </si>
+  <si>
+    <t>3,57</t>
+  </si>
+  <si>
+    <t>17,28</t>
+  </si>
+  <si>
+    <t>1,02</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>4,16</t>
+  </si>
+  <si>
+    <t>26,42</t>
+  </si>
+  <si>
+    <t>0,23</t>
+  </si>
+  <si>
+    <t>0,92</t>
+  </si>
+  <si>
+    <t>2,17</t>
+  </si>
+  <si>
+    <t>0,21</t>
+  </si>
+  <si>
+    <t>3,04</t>
+  </si>
+  <si>
+    <t>0,27</t>
+  </si>
+  <si>
+    <t>1,29</t>
+  </si>
+  <si>
+    <t>43,43</t>
+  </si>
+  <si>
+    <t>0,34</t>
+  </si>
+  <si>
+    <t>15,68</t>
+  </si>
+  <si>
+    <t>1,39</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
+    <t>4,22</t>
+  </si>
+  <si>
+    <t>0,09</t>
+  </si>
+  <si>
+    <t>22,49</t>
+  </si>
+  <si>
+    <t>0,43</t>
+  </si>
+  <si>
+    <t>5,91</t>
+  </si>
+  <si>
+    <t>4,2</t>
+  </si>
+  <si>
+    <t>0,45</t>
+  </si>
+  <si>
+    <t>0,14</t>
+  </si>
+  <si>
+    <t>45,07</t>
+  </si>
+  <si>
+    <t>1,13</t>
+  </si>
+  <si>
+    <t>14,92</t>
+  </si>
+  <si>
+    <t>0,61</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>2,57</t>
+  </si>
+  <si>
+    <t>2,29</t>
+  </si>
+  <si>
+    <t>14,5</t>
+  </si>
+  <si>
+    <t>2,49</t>
+  </si>
+  <si>
+    <t>0,56</t>
+  </si>
+  <si>
+    <t>44,41</t>
+  </si>
+  <si>
+    <t>0,78</t>
+  </si>
+  <si>
+    <t>16,73</t>
+  </si>
+  <si>
+    <t>12,82</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>4,18</t>
+  </si>
+  <si>
+    <t>20,3</t>
+  </si>
+  <si>
+    <t>2,38</t>
+  </si>
+  <si>
+    <t>2,88</t>
+  </si>
+  <si>
+    <t>1,8</t>
+  </si>
+  <si>
+    <t>40,43</t>
+  </si>
+  <si>
+    <t>0,35</t>
+  </si>
+  <si>
+    <t>25,18</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG</t>
+  </si>
+  <si>
+    <t>4,35</t>
+  </si>
+  <si>
+    <t>0,71</t>
+  </si>
+  <si>
+    <t>23,43</t>
+  </si>
+  <si>
+    <t>0,25</t>
+  </si>
+  <si>
+    <t>1,17</t>
+  </si>
+  <si>
+    <t>2,51</t>
   </si>
   <si>
     <t>0,13</t>
   </si>
   <si>
-    <t>0,64</t>
-  </si>
-  <si>
-    <t>2,31</t>
-  </si>
-  <si>
-    <t>0,1</t>
-  </si>
-  <si>
-    <t>2,86</t>
-  </si>
-  <si>
-    <t>0,53</t>
-  </si>
-  <si>
-    <t>0,32</t>
-  </si>
-  <si>
-    <t>43,83</t>
-  </si>
-  <si>
-    <t>0,93</t>
-  </si>
-  <si>
-    <t>0,03</t>
-  </si>
-  <si>
-    <t>16,26</t>
-  </si>
-  <si>
-    <t>6,1</t>
-  </si>
-  <si>
-    <t>0,04</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>LAMPUNG BARAT</t>
-  </si>
-  <si>
-    <t>4,23</t>
-  </si>
-  <si>
-    <t>0,67</t>
-  </si>
-  <si>
-    <t>28,4</t>
-  </si>
-  <si>
-    <t>0,17</t>
-  </si>
-  <si>
-    <t>0,46</t>
-  </si>
-  <si>
-    <t>4,12</t>
-  </si>
-  <si>
-    <t>0,44</t>
-  </si>
-  <si>
-    <t>39,65</t>
-  </si>
-  <si>
-    <t>0,08</t>
-  </si>
-  <si>
-    <t>12,81</t>
-  </si>
-  <si>
-    <t>7,97</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>TANGGAMUS</t>
-  </si>
-  <si>
-    <t>6,56</t>
-  </si>
-  <si>
-    <t>19,68</t>
-  </si>
-  <si>
-    <t>0,06</t>
+    <t>2,3</t>
+  </si>
+  <si>
+    <t>45,98</t>
+  </si>
+  <si>
+    <t>14,69</t>
+  </si>
+  <si>
+    <t>4,14</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>3,3</t>
+  </si>
+  <si>
+    <t>1,14</t>
+  </si>
+  <si>
+    <t>13,47</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>1,41</t>
+  </si>
+  <si>
+    <t>1,28</t>
+  </si>
+  <si>
+    <t>40,66</t>
+  </si>
+  <si>
+    <t>0,85</t>
+  </si>
+  <si>
+    <t>14,7</t>
+  </si>
+  <si>
+    <t>21,94</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>4,92</t>
+  </si>
+  <si>
+    <t>0,26</t>
+  </si>
+  <si>
+    <t>16,95</t>
+  </si>
+  <si>
+    <t>1,32</t>
+  </si>
+  <si>
+    <t>4</t>
   </si>
   <si>
     <t>0,88</t>
   </si>
   <si>
-    <t>3,46</t>
-  </si>
-  <si>
-    <t>3,22</t>
-  </si>
-  <si>
-    <t>0,29</t>
-  </si>
-  <si>
     <t>0,18</t>
   </si>
   <si>
-    <t>42,06</t>
-  </si>
-  <si>
-    <t>0,12</t>
-  </si>
-  <si>
-    <t>22,91</t>
-  </si>
-  <si>
-    <t>0,41</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>LAMPUNG SELATAN</t>
-  </si>
-  <si>
-    <t>5,7</t>
-  </si>
-  <si>
-    <t>0,33</t>
-  </si>
-  <si>
-    <t>20,06</t>
-  </si>
-  <si>
-    <t>0,51</t>
-  </si>
-  <si>
-    <t>2,92</t>
-  </si>
-  <si>
-    <t>3,28</t>
-  </si>
-  <si>
-    <t>0,68</t>
-  </si>
-  <si>
-    <t>44,39</t>
-  </si>
-  <si>
-    <t>3,61</t>
-  </si>
-  <si>
-    <t>17,43</t>
-  </si>
-  <si>
-    <t>1,03</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>4,06</t>
-  </si>
-  <si>
-    <t>0,3</t>
-  </si>
-  <si>
-    <t>25,96</t>
+    <t>43,35</t>
+  </si>
+  <si>
+    <t>1,54</t>
+  </si>
+  <si>
+    <t>19,02</t>
+  </si>
+  <si>
+    <t>2,5</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
+  </si>
+  <si>
+    <t>0,02</t>
+  </si>
+  <si>
+    <t>4,63</t>
+  </si>
+  <si>
+    <t>0,6</t>
+  </si>
+  <si>
+    <t>23,33</t>
+  </si>
+  <si>
+    <t>0,5</t>
+  </si>
+  <si>
+    <t>0,66</t>
+  </si>
+  <si>
+    <t>0,69</t>
+  </si>
+  <si>
+    <t>1,72</t>
+  </si>
+  <si>
+    <t>49,93</t>
+  </si>
+  <si>
+    <t>0,96</t>
+  </si>
+  <si>
+    <t>0,07</t>
+  </si>
+  <si>
+    <t>11,5</t>
+  </si>
+  <si>
+    <t>5,04</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>4,27</t>
+  </si>
+  <si>
+    <t>22,73</t>
+  </si>
+  <si>
+    <t>0,42</t>
+  </si>
+  <si>
+    <t>1,61</t>
+  </si>
+  <si>
+    <t>1,83</t>
+  </si>
+  <si>
+    <t>0,28</t>
+  </si>
+  <si>
+    <t>45,53</t>
   </si>
   <si>
     <t>0,24</t>
   </si>
   <si>
-    <t>0,94</t>
-  </si>
-  <si>
-    <t>2,2</t>
-  </si>
-  <si>
-    <t>0,21</t>
-  </si>
-  <si>
-    <t>3,04</t>
-  </si>
-  <si>
-    <t>0,27</t>
-  </si>
-  <si>
-    <t>1,32</t>
-  </si>
-  <si>
-    <t>43,69</t>
-  </si>
-  <si>
-    <t>0,35</t>
-  </si>
-  <si>
-    <t>0,07</t>
-  </si>
-  <si>
-    <t>15,83</t>
-  </si>
-  <si>
-    <t>1,42</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>4,17</t>
-  </si>
-  <si>
-    <t>0,09</t>
-  </si>
-  <si>
-    <t>22,34</t>
-  </si>
-  <si>
-    <t>0,23</t>
-  </si>
-  <si>
-    <t>5,95</t>
-  </si>
-  <si>
-    <t>4,22</t>
-  </si>
-  <si>
-    <t>0,45</t>
-  </si>
-  <si>
-    <t>0,14</t>
-  </si>
-  <si>
-    <t>45,13</t>
-  </si>
-  <si>
-    <t>1,14</t>
-  </si>
-  <si>
-    <t>14,98</t>
-  </si>
-  <si>
-    <t>0,61</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>2,58</t>
-  </si>
-  <si>
-    <t>2,29</t>
-  </si>
-  <si>
-    <t>14,46</t>
-  </si>
-  <si>
-    <t>2,46</t>
-  </si>
-  <si>
-    <t>0,56</t>
-  </si>
-  <si>
-    <t>44,45</t>
-  </si>
-  <si>
-    <t>0,78</t>
-  </si>
-  <si>
-    <t>16,75</t>
-  </si>
-  <si>
-    <t>12,83</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>4,2</t>
-  </si>
-  <si>
-    <t>20,12</t>
-  </si>
-  <si>
-    <t>0,58</t>
-  </si>
-  <si>
-    <t>2,39</t>
-  </si>
-  <si>
-    <t>2,89</t>
-  </si>
-  <si>
-    <t>1,81</t>
-  </si>
-  <si>
-    <t>40,54</t>
-  </si>
-  <si>
-    <t>25,28</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG</t>
-  </si>
-  <si>
-    <t>4,38</t>
-  </si>
-  <si>
-    <t>0,72</t>
-  </si>
-  <si>
-    <t>23,27</t>
-  </si>
-  <si>
-    <t>1,18</t>
-  </si>
-  <si>
-    <t>2,48</t>
-  </si>
-  <si>
-    <t>0,25</t>
-  </si>
-  <si>
-    <t>2,15</t>
-  </si>
-  <si>
-    <t>46,13</t>
-  </si>
-  <si>
-    <t>14,69</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>3,3</t>
-  </si>
-  <si>
-    <t>13,47</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>1,01</t>
-  </si>
-  <si>
-    <t>1,41</t>
-  </si>
-  <si>
-    <t>1,28</t>
-  </si>
-  <si>
-    <t>40,66</t>
-  </si>
-  <si>
-    <t>0,85</t>
-  </si>
-  <si>
-    <t>14,7</t>
-  </si>
-  <si>
-    <t>21,95</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>4,96</t>
-  </si>
-  <si>
-    <t>16,73</t>
-  </si>
-  <si>
-    <t>1,33</t>
-  </si>
-  <si>
-    <t>4,03</t>
-  </si>
-  <si>
-    <t>43,45</t>
-  </si>
-  <si>
-    <t>1,55</t>
-  </si>
-  <si>
-    <t>18,98</t>
-  </si>
-  <si>
-    <t>2,52</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>0,02</t>
-  </si>
-  <si>
-    <t>4,57</t>
-  </si>
-  <si>
-    <t>0,6</t>
-  </si>
-  <si>
-    <t>22,96</t>
-  </si>
-  <si>
-    <t>0,69</t>
-  </si>
-  <si>
-    <t>1,71</t>
-  </si>
-  <si>
-    <t>50,23</t>
-  </si>
-  <si>
-    <t>0,97</t>
-  </si>
-  <si>
-    <t>11,58</t>
-  </si>
-  <si>
-    <t>5,08</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>22,56</t>
-  </si>
-  <si>
-    <t>0,16</t>
-  </si>
-  <si>
-    <t>0,42</t>
-  </si>
-  <si>
-    <t>1,62</t>
-  </si>
-  <si>
-    <t>0,28</t>
-  </si>
-  <si>
-    <t>45,65</t>
-  </si>
-  <si>
-    <t>22,02</t>
+    <t>21,98</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>4,93</t>
+  </si>
+  <si>
+    <t>28,66</t>
+  </si>
+  <si>
+    <t>3,5</t>
+  </si>
+  <si>
+    <t>44,86</t>
+  </si>
+  <si>
+    <t>0,4</t>
+  </si>
+  <si>
+    <t>14,45</t>
+  </si>
+  <si>
+    <t>1871</t>
+  </si>
+  <si>
+    <t>BANDAR LAMPUNG</t>
+  </si>
+  <si>
+    <t>6,89</t>
   </si>
   <si>
     <t>0,86</t>
   </si>
   <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>4,35</t>
-  </si>
-  <si>
-    <t>27,95</t>
-  </si>
-  <si>
-    <t>3,16</t>
-  </si>
-  <si>
-    <t>45,3</t>
-  </si>
-  <si>
-    <t>15,17</t>
-  </si>
-  <si>
-    <t>2,56</t>
-  </si>
-  <si>
-    <t>1871</t>
-  </si>
-  <si>
-    <t>BANDAR LAMPUNG</t>
-  </si>
-  <si>
-    <t>6,85</t>
-  </si>
-  <si>
-    <t>0,87</t>
-  </si>
-  <si>
-    <t>9,62</t>
-  </si>
-  <si>
-    <t>5,98</t>
-  </si>
-  <si>
-    <t>1,17</t>
-  </si>
-  <si>
-    <t>6,71</t>
-  </si>
-  <si>
-    <t>13,12</t>
-  </si>
-  <si>
-    <t>39,8</t>
-  </si>
-  <si>
-    <t>1,75</t>
-  </si>
-  <si>
-    <t>9,33</t>
-  </si>
-  <si>
-    <t>2,77</t>
+    <t>10,04</t>
+  </si>
+  <si>
+    <t>0,57</t>
+  </si>
+  <si>
+    <t>5,88</t>
+  </si>
+  <si>
+    <t>1,15</t>
+  </si>
+  <si>
+    <t>7,46</t>
+  </si>
+  <si>
+    <t>12,91</t>
+  </si>
+  <si>
+    <t>39,17</t>
+  </si>
+  <si>
+    <t>9,18</t>
+  </si>
+  <si>
+    <t>2,73</t>
   </si>
   <si>
     <t>1872</t>
@@ -860,9 +872,6 @@
   </si>
   <si>
     <t>2,67</t>
-  </si>
-  <si>
-    <t>0,4</t>
   </si>
   <si>
     <t>11,6</t>
@@ -1815,7 +1824,7 @@
         <v>93</v>
       </c>
       <c r="C6" s="6">
-        <v>66820</v>
+        <v>67943</v>
       </c>
       <c r="D6" s="6">
         <v>6</v>
@@ -1824,7 +1833,7 @@
         <v>94</v>
       </c>
       <c r="F6" s="6">
-        <v>2811</v>
+        <v>2916</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>95</v>
@@ -1842,7 +1851,7 @@
         <v>97</v>
       </c>
       <c r="L6" s="6">
-        <v>14103</v>
+        <v>14570</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>98</v>
@@ -1854,49 +1863,49 @@
         <v>97</v>
       </c>
       <c r="P6" s="6">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q6" s="7" t="s">
         <v>99</v>
       </c>
       <c r="R6" s="6">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="S6" s="7" t="s">
         <v>100</v>
       </c>
       <c r="T6" s="6">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="U6" s="7" t="s">
         <v>101</v>
       </c>
       <c r="V6" s="6">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="W6" s="7" t="s">
         <v>102</v>
       </c>
       <c r="X6" s="6">
-        <v>1912</v>
+        <v>1981</v>
       </c>
       <c r="Y6" s="7" t="s">
         <v>103</v>
       </c>
       <c r="Z6" s="6">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AA6" s="7" t="s">
         <v>104</v>
       </c>
       <c r="AB6" s="6">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AC6" s="7" t="s">
         <v>105</v>
       </c>
       <c r="AD6" s="6">
-        <v>29290</v>
+        <v>29682</v>
       </c>
       <c r="AE6" s="7" t="s">
         <v>106</v>
@@ -1908,19 +1917,19 @@
         <v>107</v>
       </c>
       <c r="AH6" s="6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI6" s="7" t="s">
         <v>108</v>
       </c>
       <c r="AJ6" s="6">
-        <v>10867</v>
+        <v>10959</v>
       </c>
       <c r="AK6" s="7" t="s">
         <v>109</v>
       </c>
       <c r="AL6" s="6">
-        <v>4074</v>
+        <v>4075</v>
       </c>
       <c r="AM6" s="7" t="s">
         <v>110</v>
@@ -2089,7 +2098,7 @@
         <v>126</v>
       </c>
       <c r="C8" s="9">
-        <v>1707</v>
+        <v>1717</v>
       </c>
       <c r="D8" s="9">
         <v>0</v>
@@ -2098,7 +2107,7 @@
         <v>97</v>
       </c>
       <c r="F8" s="9">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>127</v>
@@ -2116,7 +2125,7 @@
         <v>97</v>
       </c>
       <c r="L8" s="9">
-        <v>336</v>
+        <v>339</v>
       </c>
       <c r="M8" s="10" t="s">
         <v>128</v>
@@ -2152,7 +2161,7 @@
         <v>97</v>
       </c>
       <c r="X8" s="9">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="Y8" s="10" t="s">
         <v>132</v>
@@ -2167,19 +2176,19 @@
         <v>3</v>
       </c>
       <c r="AC8" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="AD8" s="9">
+        <v>719</v>
+      </c>
+      <c r="AE8" s="10" t="s">
         <v>134</v>
-      </c>
-      <c r="AD8" s="9">
-        <v>718</v>
-      </c>
-      <c r="AE8" s="10" t="s">
-        <v>135</v>
       </c>
       <c r="AF8" s="9">
         <v>2</v>
       </c>
       <c r="AG8" s="10" t="s">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="AH8" s="9">
         <v>1</v>
@@ -2188,16 +2197,16 @@
         <v>129</v>
       </c>
       <c r="AJ8" s="9">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="AK8" s="10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AL8" s="9">
         <v>7</v>
       </c>
       <c r="AM8" s="10" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AN8" s="9">
         <v>0</v>
@@ -2215,36 +2224,36 @@
         <v>2</v>
       </c>
       <c r="AS8" s="10" t="s">
-        <v>136</v>
+        <v>99</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="9">
+        <v>6689</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F9" s="9">
+        <v>384</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>139</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C9" s="9">
-        <v>6616</v>
-      </c>
-      <c r="D9" s="9">
-        <v>0</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="F9" s="9">
-        <v>377</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>141</v>
       </c>
       <c r="H9" s="9">
         <v>22</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="J9" s="9">
         <v>0</v>
@@ -2253,10 +2262,10 @@
         <v>97</v>
       </c>
       <c r="L9" s="9">
-        <v>1327</v>
+        <v>1376</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="N9" s="9">
         <v>0</v>
@@ -2274,13 +2283,13 @@
         <v>34</v>
       </c>
       <c r="S9" s="10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="T9" s="9">
         <v>193</v>
       </c>
       <c r="U9" s="10" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="V9" s="9">
         <v>0</v>
@@ -2289,16 +2298,16 @@
         <v>97</v>
       </c>
       <c r="X9" s="9">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="Z9" s="9">
         <v>45</v>
       </c>
       <c r="AA9" s="10" t="s">
-        <v>147</v>
+        <v>115</v>
       </c>
       <c r="AB9" s="9">
         <v>0</v>
@@ -2307,16 +2316,16 @@
         <v>97</v>
       </c>
       <c r="AD9" s="9">
-        <v>2937</v>
+        <v>2949</v>
       </c>
       <c r="AE9" s="10" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
       <c r="AF9" s="9">
         <v>239</v>
       </c>
       <c r="AG9" s="10" t="s">
-        <v>149</v>
+        <v>146</v>
       </c>
       <c r="AH9" s="9">
         <v>0</v>
@@ -2325,16 +2334,16 @@
         <v>97</v>
       </c>
       <c r="AJ9" s="9">
-        <v>1153</v>
+        <v>1156</v>
       </c>
       <c r="AK9" s="10" t="s">
-        <v>150</v>
+        <v>147</v>
       </c>
       <c r="AL9" s="9">
         <v>68</v>
       </c>
       <c r="AM9" s="10" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
       <c r="AN9" s="9">
         <v>0</v>
@@ -2357,13 +2366,13 @@
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="C10" s="9">
-        <v>8397</v>
+        <v>8542</v>
       </c>
       <c r="D10" s="9">
         <v>3</v>
@@ -2372,16 +2381,16 @@
         <v>111</v>
       </c>
       <c r="F10" s="9">
-        <v>341</v>
+        <v>355</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="H10" s="9">
         <v>25</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>155</v>
+        <v>133</v>
       </c>
       <c r="J10" s="9">
         <v>0</v>
@@ -2390,10 +2399,10 @@
         <v>97</v>
       </c>
       <c r="L10" s="9">
-        <v>2180</v>
+        <v>2257</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="N10" s="9">
         <v>1</v>
@@ -2405,73 +2414,73 @@
         <v>20</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="R10" s="9">
         <v>79</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>158</v>
+        <v>154</v>
       </c>
       <c r="T10" s="9">
         <v>185</v>
       </c>
       <c r="U10" s="10" t="s">
-        <v>159</v>
+        <v>155</v>
       </c>
       <c r="V10" s="9">
         <v>18</v>
       </c>
       <c r="W10" s="10" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="X10" s="9">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>161</v>
+        <v>157</v>
       </c>
       <c r="Z10" s="9">
         <v>23</v>
       </c>
       <c r="AA10" s="10" t="s">
-        <v>162</v>
+        <v>158</v>
       </c>
       <c r="AB10" s="9">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="AC10" s="10" t="s">
-        <v>163</v>
+        <v>159</v>
       </c>
       <c r="AD10" s="9">
-        <v>3669</v>
+        <v>3710</v>
       </c>
       <c r="AE10" s="10" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="AF10" s="9">
         <v>29</v>
       </c>
       <c r="AG10" s="10" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="AH10" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AI10" s="10" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="AJ10" s="9">
-        <v>1329</v>
+        <v>1339</v>
       </c>
       <c r="AK10" s="10" t="s">
-        <v>167</v>
+        <v>162</v>
       </c>
       <c r="AL10" s="9">
         <v>119</v>
       </c>
       <c r="AM10" s="10" t="s">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="AN10" s="9">
         <v>1</v>
@@ -2494,13 +2503,13 @@
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>169</v>
+        <v>164</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>170</v>
+        <v>165</v>
       </c>
       <c r="C11" s="9">
-        <v>6400</v>
+        <v>6446</v>
       </c>
       <c r="D11" s="9">
         <v>2</v>
@@ -2509,16 +2518,16 @@
         <v>108</v>
       </c>
       <c r="F11" s="9">
-        <v>267</v>
+        <v>272</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="H11" s="9">
         <v>6</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="J11" s="9">
         <v>0</v>
@@ -2527,10 +2536,10 @@
         <v>97</v>
       </c>
       <c r="L11" s="9">
-        <v>1430</v>
+        <v>1450</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="N11" s="9">
         <v>0</v>
@@ -2542,19 +2551,19 @@
         <v>15</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>174</v>
+        <v>153</v>
       </c>
       <c r="R11" s="9">
         <v>28</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>120</v>
+        <v>169</v>
       </c>
       <c r="T11" s="9">
         <v>381</v>
       </c>
       <c r="U11" s="10" t="s">
-        <v>175</v>
+        <v>170</v>
       </c>
       <c r="V11" s="9">
         <v>2</v>
@@ -2563,34 +2572,34 @@
         <v>108</v>
       </c>
       <c r="X11" s="9">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="Y11" s="10" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="Z11" s="9">
         <v>29</v>
       </c>
       <c r="AA11" s="10" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="AB11" s="9">
         <v>9</v>
       </c>
       <c r="AC11" s="10" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="AD11" s="9">
-        <v>2888</v>
+        <v>2905</v>
       </c>
       <c r="AE11" s="10" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="AF11" s="9">
         <v>73</v>
       </c>
       <c r="AG11" s="10" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="AH11" s="9">
         <v>0</v>
@@ -2599,16 +2608,16 @@
         <v>97</v>
       </c>
       <c r="AJ11" s="9">
-        <v>959</v>
+        <v>962</v>
       </c>
       <c r="AK11" s="10" t="s">
-        <v>181</v>
+        <v>176</v>
       </c>
       <c r="AL11" s="9">
         <v>39</v>
       </c>
       <c r="AM11" s="10" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="AN11" s="9">
         <v>0</v>
@@ -2631,13 +2640,13 @@
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>184</v>
+        <v>179</v>
       </c>
       <c r="C12" s="9">
-        <v>5899</v>
+        <v>5904</v>
       </c>
       <c r="D12" s="9">
         <v>0</v>
@@ -2649,13 +2658,13 @@
         <v>152</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>185</v>
+        <v>180</v>
       </c>
       <c r="H12" s="9">
         <v>135</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="J12" s="9">
         <v>0</v>
@@ -2664,10 +2673,10 @@
         <v>97</v>
       </c>
       <c r="L12" s="9">
-        <v>853</v>
+        <v>856</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="N12" s="9">
         <v>0</v>
@@ -2691,7 +2700,7 @@
         <v>135</v>
       </c>
       <c r="U12" s="10" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="V12" s="9">
         <v>0</v>
@@ -2700,16 +2709,16 @@
         <v>97</v>
       </c>
       <c r="X12" s="9">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="Z12" s="9">
         <v>33</v>
       </c>
       <c r="AA12" s="10" t="s">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AB12" s="9">
         <v>0</v>
@@ -2721,13 +2730,13 @@
         <v>2622</v>
       </c>
       <c r="AE12" s="10" t="s">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="AF12" s="9">
         <v>46</v>
       </c>
       <c r="AG12" s="10" t="s">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="AH12" s="9">
         <v>0</v>
@@ -2739,13 +2748,13 @@
         <v>988</v>
       </c>
       <c r="AK12" s="10" t="s">
-        <v>192</v>
+        <v>187</v>
       </c>
       <c r="AL12" s="9">
         <v>757</v>
       </c>
       <c r="AM12" s="10" t="s">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="AN12" s="9">
         <v>0</v>
@@ -2763,18 +2772,18 @@
         <v>7</v>
       </c>
       <c r="AS12" s="10" t="s">
-        <v>136</v>
+        <v>99</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="C13" s="9">
-        <v>3429</v>
+        <v>3443</v>
       </c>
       <c r="D13" s="9">
         <v>0</v>
@@ -2786,7 +2795,7 @@
         <v>144</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="H13" s="9">
         <v>2</v>
@@ -2801,10 +2810,10 @@
         <v>97</v>
       </c>
       <c r="L13" s="9">
-        <v>690</v>
+        <v>699</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="N13" s="9">
         <v>1</v>
@@ -2813,76 +2822,76 @@
         <v>108</v>
       </c>
       <c r="P13" s="9">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="R13" s="9">
         <v>20</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>198</v>
+        <v>96</v>
       </c>
       <c r="T13" s="9">
         <v>82</v>
       </c>
       <c r="U13" s="10" t="s">
-        <v>199</v>
+        <v>193</v>
       </c>
       <c r="V13" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W13" s="10" t="s">
-        <v>108</v>
+        <v>129</v>
       </c>
       <c r="X13" s="9">
         <v>99</v>
       </c>
       <c r="Y13" s="10" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
       <c r="Z13" s="9">
         <v>14</v>
       </c>
       <c r="AA13" s="10" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AB13" s="9">
         <v>62</v>
       </c>
       <c r="AC13" s="10" t="s">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="AD13" s="9">
-        <v>1390</v>
+        <v>1392</v>
       </c>
       <c r="AE13" s="10" t="s">
-        <v>202</v>
+        <v>196</v>
       </c>
       <c r="AF13" s="9">
         <v>12</v>
       </c>
       <c r="AG13" s="10" t="s">
-        <v>165</v>
+        <v>197</v>
       </c>
       <c r="AH13" s="9">
         <v>3</v>
       </c>
       <c r="AI13" s="10" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AJ13" s="9">
         <v>867</v>
       </c>
       <c r="AK13" s="10" t="s">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="AL13" s="9">
         <v>39</v>
       </c>
       <c r="AM13" s="10" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="AN13" s="9">
         <v>1</v>
@@ -2905,13 +2914,13 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="C14" s="9">
-        <v>2376</v>
+        <v>2390</v>
       </c>
       <c r="D14" s="9">
         <v>0</v>
@@ -2923,13 +2932,13 @@
         <v>104</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="H14" s="9">
         <v>17</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="J14" s="9">
         <v>0</v>
@@ -2938,10 +2947,10 @@
         <v>97</v>
       </c>
       <c r="L14" s="9">
-        <v>553</v>
+        <v>560</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="N14" s="9">
         <v>1</v>
@@ -2950,52 +2959,52 @@
         <v>111</v>
       </c>
       <c r="P14" s="9">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>133</v>
+        <v>204</v>
       </c>
       <c r="R14" s="9">
         <v>28</v>
       </c>
       <c r="S14" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="T14" s="9">
+        <v>60</v>
+      </c>
+      <c r="U14" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="V14" s="9">
+        <v>3</v>
+      </c>
+      <c r="W14" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="X14" s="9">
+        <v>55</v>
+      </c>
+      <c r="Y14" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="Z14" s="9">
+        <v>3</v>
+      </c>
+      <c r="AA14" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="AB14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD14" s="9">
+        <v>1099</v>
+      </c>
+      <c r="AE14" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="T14" s="9">
-        <v>59</v>
-      </c>
-      <c r="U14" s="10" t="s">
-        <v>210</v>
-      </c>
-      <c r="V14" s="9">
-        <v>6</v>
-      </c>
-      <c r="W14" s="10" t="s">
-        <v>211</v>
-      </c>
-      <c r="X14" s="9">
-        <v>51</v>
-      </c>
-      <c r="Y14" s="10" t="s">
-        <v>212</v>
-      </c>
-      <c r="Z14" s="9">
-        <v>2</v>
-      </c>
-      <c r="AA14" s="10" t="s">
-        <v>122</v>
-      </c>
-      <c r="AB14" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD14" s="9">
-        <v>1096</v>
-      </c>
-      <c r="AE14" s="10" t="s">
-        <v>213</v>
       </c>
       <c r="AF14" s="9">
         <v>2</v>
@@ -3010,16 +3019,16 @@
         <v>97</v>
       </c>
       <c r="AJ14" s="9">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="AK14" s="10" t="s">
-        <v>214</v>
+        <v>210</v>
       </c>
       <c r="AL14" s="9">
         <v>99</v>
       </c>
       <c r="AM14" s="10" t="s">
-        <v>171</v>
+        <v>211</v>
       </c>
       <c r="AN14" s="9">
         <v>0</v>
@@ -3042,13 +3051,13 @@
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="C15" s="9">
-        <v>7728</v>
+        <v>7730</v>
       </c>
       <c r="D15" s="9">
         <v>0</v>
@@ -3060,13 +3069,13 @@
         <v>255</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="H15" s="9">
         <v>88</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>180</v>
+        <v>215</v>
       </c>
       <c r="J15" s="9">
         <v>0</v>
@@ -3078,7 +3087,7 @@
         <v>1041</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="N15" s="9">
         <v>0</v>
@@ -3090,19 +3099,19 @@
         <v>4</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="R15" s="9">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>220</v>
+        <v>148</v>
       </c>
       <c r="T15" s="9">
         <v>109</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="V15" s="9">
         <v>1</v>
@@ -3114,13 +3123,13 @@
         <v>99</v>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="Z15" s="9">
         <v>10</v>
       </c>
       <c r="AA15" s="10" t="s">
-        <v>99</v>
+        <v>207</v>
       </c>
       <c r="AB15" s="9">
         <v>0</v>
@@ -3129,16 +3138,16 @@
         <v>97</v>
       </c>
       <c r="AD15" s="9">
-        <v>3142</v>
+        <v>3143</v>
       </c>
       <c r="AE15" s="10" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="AF15" s="9">
         <v>66</v>
       </c>
       <c r="AG15" s="10" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="AH15" s="9">
         <v>0</v>
@@ -3150,13 +3159,13 @@
         <v>1136</v>
       </c>
       <c r="AK15" s="10" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="AL15" s="9">
         <v>1696</v>
       </c>
       <c r="AM15" s="10" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="AN15" s="9">
         <v>0</v>
@@ -3179,13 +3188,13 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C16" s="9">
-        <v>2260</v>
+        <v>2277</v>
       </c>
       <c r="D16" s="9">
         <v>0</v>
@@ -3197,13 +3206,13 @@
         <v>112</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="H16" s="9">
         <v>6</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>162</v>
+        <v>227</v>
       </c>
       <c r="J16" s="9">
         <v>0</v>
@@ -3212,10 +3221,10 @@
         <v>97</v>
       </c>
       <c r="L16" s="9">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N16" s="9">
         <v>0</v>
@@ -3233,13 +3242,13 @@
         <v>30</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="T16" s="9">
         <v>112</v>
       </c>
       <c r="U16" s="10" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="V16" s="9">
         <v>0</v>
@@ -3251,22 +3260,22 @@
         <v>91</v>
       </c>
       <c r="Y16" s="10" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="Z16" s="9">
         <v>20</v>
       </c>
       <c r="AA16" s="10" t="s">
-        <v>130</v>
+        <v>231</v>
       </c>
       <c r="AB16" s="9">
         <v>4</v>
       </c>
       <c r="AC16" s="10" t="s">
-        <v>134</v>
+        <v>232</v>
       </c>
       <c r="AD16" s="9">
-        <v>982</v>
+        <v>987</v>
       </c>
       <c r="AE16" s="10" t="s">
         <v>233</v>
@@ -3284,7 +3293,7 @@
         <v>111</v>
       </c>
       <c r="AJ16" s="9">
-        <v>429</v>
+        <v>433</v>
       </c>
       <c r="AK16" s="10" t="s">
         <v>235</v>
@@ -3311,7 +3320,7 @@
         <v>2</v>
       </c>
       <c r="AS16" s="10" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
@@ -3322,7 +3331,7 @@
         <v>238</v>
       </c>
       <c r="C17" s="9">
-        <v>4334</v>
+        <v>4364</v>
       </c>
       <c r="D17" s="9">
         <v>1</v>
@@ -3331,7 +3340,7 @@
         <v>239</v>
       </c>
       <c r="F17" s="9">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="G17" s="10" t="s">
         <v>240</v>
@@ -3349,7 +3358,7 @@
         <v>97</v>
       </c>
       <c r="L17" s="9">
-        <v>995</v>
+        <v>1018</v>
       </c>
       <c r="M17" s="10" t="s">
         <v>242</v>
@@ -3364,73 +3373,73 @@
         <v>22</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>144</v>
+        <v>243</v>
       </c>
       <c r="R17" s="9">
         <v>29</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>115</v>
+        <v>244</v>
       </c>
       <c r="T17" s="9">
         <v>30</v>
       </c>
       <c r="U17" s="10" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="V17" s="9">
         <v>9</v>
       </c>
       <c r="W17" s="10" t="s">
-        <v>160</v>
+        <v>156</v>
       </c>
       <c r="X17" s="9">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="Y17" s="10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="Z17" s="9">
         <v>2</v>
       </c>
       <c r="AA17" s="10" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="AB17" s="9">
         <v>4</v>
       </c>
       <c r="AC17" s="10" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="AD17" s="9">
-        <v>2177</v>
+        <v>2179</v>
       </c>
       <c r="AE17" s="10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AF17" s="9">
         <v>42</v>
       </c>
       <c r="AG17" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AH17" s="9">
         <v>3</v>
       </c>
       <c r="AI17" s="10" t="s">
-        <v>166</v>
+        <v>249</v>
       </c>
       <c r="AJ17" s="9">
         <v>502</v>
       </c>
       <c r="AK17" s="10" t="s">
-        <v>247</v>
+        <v>250</v>
       </c>
       <c r="AL17" s="9">
         <v>220</v>
       </c>
       <c r="AM17" s="10" t="s">
-        <v>248</v>
+        <v>251</v>
       </c>
       <c r="AN17" s="9">
         <v>0</v>
@@ -3453,13 +3462,13 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>249</v>
+        <v>252</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>250</v>
+        <v>253</v>
       </c>
       <c r="C18" s="9">
-        <v>5014</v>
+        <v>5041</v>
       </c>
       <c r="D18" s="9">
         <v>0</v>
@@ -3468,16 +3477,16 @@
         <v>97</v>
       </c>
       <c r="F18" s="9">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>114</v>
+        <v>254</v>
       </c>
       <c r="H18" s="9">
         <v>6</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>136</v>
+        <v>99</v>
       </c>
       <c r="J18" s="9">
         <v>0</v>
@@ -3486,10 +3495,10 @@
         <v>97</v>
       </c>
       <c r="L18" s="9">
-        <v>1131</v>
+        <v>1146</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="N18" s="9">
         <v>0</v>
@@ -3498,40 +3507,40 @@
         <v>97</v>
       </c>
       <c r="P18" s="9">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>252</v>
+        <v>99</v>
       </c>
       <c r="R18" s="9">
         <v>21</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>253</v>
+        <v>256</v>
       </c>
       <c r="T18" s="9">
         <v>81</v>
       </c>
       <c r="U18" s="10" t="s">
-        <v>254</v>
+        <v>257</v>
       </c>
       <c r="V18" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W18" s="10" t="s">
-        <v>111</v>
+        <v>239</v>
       </c>
       <c r="X18" s="9">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y18" s="10" t="s">
-        <v>201</v>
+        <v>258</v>
       </c>
       <c r="Z18" s="9">
         <v>14</v>
       </c>
       <c r="AA18" s="10" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="AB18" s="9">
         <v>0</v>
@@ -3540,16 +3549,16 @@
         <v>97</v>
       </c>
       <c r="AD18" s="9">
-        <v>2289</v>
+        <v>2295</v>
       </c>
       <c r="AE18" s="10" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="AF18" s="9">
         <v>12</v>
       </c>
       <c r="AG18" s="10" t="s">
-        <v>157</v>
+        <v>261</v>
       </c>
       <c r="AH18" s="9">
         <v>0</v>
@@ -3558,16 +3567,16 @@
         <v>97</v>
       </c>
       <c r="AJ18" s="9">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="AK18" s="10" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="AL18" s="9">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="AM18" s="10" t="s">
-        <v>258</v>
+        <v>130</v>
       </c>
       <c r="AN18" s="9">
         <v>0</v>
@@ -3590,13 +3599,13 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="C19" s="9">
-        <v>5695</v>
+        <v>6424</v>
       </c>
       <c r="D19" s="9">
         <v>0</v>
@@ -3605,16 +3614,16 @@
         <v>97</v>
       </c>
       <c r="F19" s="9">
-        <v>248</v>
+        <v>317</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="H19" s="9">
         <v>18</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="J19" s="9">
         <v>0</v>
@@ -3623,10 +3632,10 @@
         <v>97</v>
       </c>
       <c r="L19" s="9">
-        <v>1592</v>
+        <v>1841</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="N19" s="9">
         <v>0</v>
@@ -3644,13 +3653,13 @@
         <v>18</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>105</v>
+        <v>259</v>
       </c>
       <c r="T19" s="9">
         <v>17</v>
       </c>
       <c r="U19" s="10" t="s">
-        <v>155</v>
+        <v>227</v>
       </c>
       <c r="V19" s="9">
         <v>0</v>
@@ -3659,16 +3668,16 @@
         <v>97</v>
       </c>
       <c r="X19" s="9">
-        <v>180</v>
+        <v>225</v>
       </c>
       <c r="Y19" s="10" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="Z19" s="9">
         <v>4</v>
       </c>
       <c r="AA19" s="10" t="s">
-        <v>166</v>
+        <v>129</v>
       </c>
       <c r="AB19" s="9">
         <v>0</v>
@@ -3677,16 +3686,16 @@
         <v>97</v>
       </c>
       <c r="AD19" s="9">
-        <v>2580</v>
+        <v>2882</v>
       </c>
       <c r="AE19" s="10" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="AF19" s="9">
         <v>26</v>
       </c>
       <c r="AG19" s="10" t="s">
-        <v>118</v>
+        <v>269</v>
       </c>
       <c r="AH19" s="9">
         <v>0</v>
@@ -3695,16 +3704,16 @@
         <v>97</v>
       </c>
       <c r="AJ19" s="9">
-        <v>864</v>
+        <v>928</v>
       </c>
       <c r="AK19" s="10" t="s">
-        <v>265</v>
+        <v>270</v>
       </c>
       <c r="AL19" s="9">
         <v>146</v>
       </c>
       <c r="AM19" s="10" t="s">
-        <v>266</v>
+        <v>101</v>
       </c>
       <c r="AN19" s="9">
         <v>0</v>
@@ -3722,18 +3731,18 @@
         <v>2</v>
       </c>
       <c r="AS19" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="C20" s="9">
-        <v>686</v>
+        <v>697</v>
       </c>
       <c r="D20" s="9">
         <v>0</v>
@@ -3742,16 +3751,16 @@
         <v>97</v>
       </c>
       <c r="F20" s="9">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="H20" s="9">
         <v>6</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="J20" s="9">
         <v>0</v>
@@ -3760,10 +3769,10 @@
         <v>97</v>
       </c>
       <c r="L20" s="9">
-        <v>66</v>
+        <v>70</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="N20" s="9">
         <v>0</v>
@@ -3775,55 +3784,55 @@
         <v>4</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>198</v>
+        <v>276</v>
       </c>
       <c r="R20" s="9">
         <v>4</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>198</v>
+        <v>276</v>
       </c>
       <c r="T20" s="9">
         <v>41</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="V20" s="9">
         <v>8</v>
       </c>
       <c r="W20" s="10" t="s">
-        <v>273</v>
+        <v>278</v>
       </c>
       <c r="X20" s="9">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>274</v>
+        <v>279</v>
       </c>
       <c r="Z20" s="9">
         <v>90</v>
       </c>
       <c r="AA20" s="10" t="s">
-        <v>275</v>
+        <v>280</v>
       </c>
       <c r="AB20" s="9">
         <v>4</v>
       </c>
       <c r="AC20" s="10" t="s">
-        <v>198</v>
+        <v>276</v>
       </c>
       <c r="AD20" s="9">
         <v>273</v>
       </c>
       <c r="AE20" s="10" t="s">
-        <v>276</v>
+        <v>281</v>
       </c>
       <c r="AF20" s="9">
         <v>12</v>
       </c>
       <c r="AG20" s="10" t="s">
-        <v>277</v>
+        <v>246</v>
       </c>
       <c r="AH20" s="9">
         <v>0</v>
@@ -3835,13 +3844,13 @@
         <v>64</v>
       </c>
       <c r="AK20" s="10" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="AL20" s="9">
         <v>19</v>
       </c>
       <c r="AM20" s="10" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="AN20" s="9">
         <v>0</v>
@@ -3864,10 +3873,10 @@
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="C21" s="9">
         <v>1500</v>
@@ -3882,13 +3891,13 @@
         <v>40</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="H21" s="9">
         <v>6</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>283</v>
+        <v>269</v>
       </c>
       <c r="J21" s="9">
         <v>0</v>
@@ -3900,7 +3909,7 @@
         <v>174</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>284</v>
+        <v>287</v>
       </c>
       <c r="N21" s="9">
         <v>0</v>
@@ -3924,43 +3933,43 @@
         <v>35</v>
       </c>
       <c r="U21" s="10" t="s">
-        <v>285</v>
+        <v>288</v>
       </c>
       <c r="V21" s="9">
         <v>1</v>
       </c>
       <c r="W21" s="10" t="s">
-        <v>166</v>
+        <v>249</v>
       </c>
       <c r="X21" s="9">
         <v>42</v>
       </c>
       <c r="Y21" s="10" t="s">
-        <v>286</v>
+        <v>289</v>
       </c>
       <c r="Z21" s="9">
         <v>39</v>
       </c>
       <c r="AA21" s="10" t="s">
-        <v>287</v>
+        <v>290</v>
       </c>
       <c r="AB21" s="9">
         <v>15</v>
       </c>
       <c r="AC21" s="10" t="s">
-        <v>288</v>
+        <v>291</v>
       </c>
       <c r="AD21" s="9">
         <v>632</v>
       </c>
       <c r="AE21" s="10" t="s">
-        <v>289</v>
+        <v>292</v>
       </c>
       <c r="AF21" s="9">
         <v>3</v>
       </c>
       <c r="AG21" s="10" t="s">
-        <v>290</v>
+        <v>293</v>
       </c>
       <c r="AH21" s="9">
         <v>0</v>
@@ -3972,13 +3981,13 @@
         <v>120</v>
       </c>
       <c r="AK21" s="10" t="s">
-        <v>291</v>
+        <v>294</v>
       </c>
       <c r="AL21" s="9">
         <v>384</v>
       </c>
       <c r="AM21" s="10" t="s">
-        <v>292</v>
+        <v>295</v>
       </c>
       <c r="AN21" s="9">
         <v>0</v>
@@ -4001,13 +4010,13 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>293</v>
+        <v>296</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>294</v>
+        <v>297</v>
       </c>
       <c r="C22" s="12">
-        <v>66820</v>
+        <v>67943</v>
       </c>
       <c r="D22" s="12">
         <v>6</v>
@@ -4016,7 +4025,7 @@
         <v>94</v>
       </c>
       <c r="F22" s="12">
-        <v>2811</v>
+        <v>2916</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>95</v>
@@ -4034,7 +4043,7 @@
         <v>97</v>
       </c>
       <c r="L22" s="12">
-        <v>14103</v>
+        <v>14570</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>98</v>
@@ -4046,49 +4055,49 @@
         <v>97</v>
       </c>
       <c r="P22" s="12">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="Q22" s="13" t="s">
         <v>99</v>
       </c>
       <c r="R22" s="12">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="S22" s="13" t="s">
         <v>100</v>
       </c>
       <c r="T22" s="12">
-        <v>1541</v>
+        <v>1542</v>
       </c>
       <c r="U22" s="13" t="s">
         <v>101</v>
       </c>
       <c r="V22" s="12">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="W22" s="13" t="s">
         <v>102</v>
       </c>
       <c r="X22" s="12">
-        <v>1912</v>
+        <v>1981</v>
       </c>
       <c r="Y22" s="13" t="s">
         <v>103</v>
       </c>
       <c r="Z22" s="12">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AA22" s="13" t="s">
         <v>104</v>
       </c>
       <c r="AB22" s="12">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="AC22" s="13" t="s">
         <v>105</v>
       </c>
       <c r="AD22" s="12">
-        <v>29290</v>
+        <v>29682</v>
       </c>
       <c r="AE22" s="13" t="s">
         <v>106</v>
@@ -4100,19 +4109,19 @@
         <v>107</v>
       </c>
       <c r="AH22" s="12">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI22" s="13" t="s">
         <v>108</v>
       </c>
       <c r="AJ22" s="12">
-        <v>10867</v>
+        <v>10959</v>
       </c>
       <c r="AK22" s="13" t="s">
         <v>109</v>
       </c>
       <c r="AL22" s="12">
-        <v>4074</v>
+        <v>4075</v>
       </c>
       <c r="AM22" s="13" t="s">
         <v>110</v>

--- a/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
+++ b/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="298">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="293">
   <si>
     <t>DATA RADAR ANOMALI KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 6 Sep 2026, 07.59</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 7 Sep 2026, 15.58</t>
   </si>
   <si>
     <t>Kode</t>
@@ -298,7 +298,7 @@
     <t>0,01</t>
   </si>
   <si>
-    <t>4,29</t>
+    <t>4,32</t>
   </si>
   <si>
     <t>0,58</t>
@@ -313,517 +313,502 @@
     <t>0,12</t>
   </si>
   <si>
-    <t>0,63</t>
-  </si>
-  <si>
-    <t>2,27</t>
+    <t>0,62</t>
+  </si>
+  <si>
+    <t>2,25</t>
   </si>
   <si>
     <t>0,1</t>
   </si>
   <si>
-    <t>2,92</t>
-  </si>
-  <si>
-    <t>0,52</t>
-  </si>
-  <si>
-    <t>0,32</t>
-  </si>
-  <si>
-    <t>43,69</t>
+    <t>2,91</t>
+  </si>
+  <si>
+    <t>0,51</t>
+  </si>
+  <si>
+    <t>0,33</t>
+  </si>
+  <si>
+    <t>43,82</t>
   </si>
   <si>
     <t>0,91</t>
   </si>
   <si>
+    <t>0,02</t>
+  </si>
+  <si>
+    <t>16,06</t>
+  </si>
+  <si>
+    <t>5,94</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>LAMPUNG BARAT</t>
+  </si>
+  <si>
+    <t>4,23</t>
+  </si>
+  <si>
+    <t>0,67</t>
+  </si>
+  <si>
+    <t>28,4</t>
+  </si>
+  <si>
+    <t>0,17</t>
+  </si>
+  <si>
+    <t>0,46</t>
+  </si>
+  <si>
+    <t>4,12</t>
+  </si>
+  <si>
+    <t>0,44</t>
+  </si>
+  <si>
+    <t>39,65</t>
+  </si>
+  <si>
+    <t>0,08</t>
+  </si>
+  <si>
+    <t>12,81</t>
+  </si>
+  <si>
+    <t>7,97</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>TANGGAMUS</t>
+  </si>
+  <si>
+    <t>6,63</t>
+  </si>
+  <si>
+    <t>19,72</t>
+  </si>
+  <si>
+    <t>0,06</t>
+  </si>
+  <si>
+    <t>0,87</t>
+  </si>
+  <si>
+    <t>3,43</t>
+  </si>
+  <si>
+    <t>3,32</t>
+  </si>
+  <si>
+    <t>0,29</t>
+  </si>
+  <si>
+    <t>41,88</t>
+  </si>
+  <si>
+    <t>22,92</t>
+  </si>
+  <si>
+    <t>0,41</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>LAMPUNG SELATAN</t>
+  </si>
+  <si>
+    <t>5,73</t>
+  </si>
+  <si>
+    <t>20,57</t>
+  </si>
+  <si>
+    <t>2,87</t>
+  </si>
+  <si>
+    <t>3,27</t>
+  </si>
+  <si>
+    <t>44,15</t>
+  </si>
+  <si>
+    <t>3,56</t>
+  </si>
+  <si>
+    <t>17,27</t>
+  </si>
+  <si>
+    <t>1,01</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>4,16</t>
+  </si>
+  <si>
+    <t>26,39</t>
+  </si>
+  <si>
+    <t>0,23</t>
+  </si>
+  <si>
+    <t>0,92</t>
+  </si>
+  <si>
+    <t>2,16</t>
+  </si>
+  <si>
+    <t>0,21</t>
+  </si>
+  <si>
+    <t>3,04</t>
+  </si>
+  <si>
+    <t>0,27</t>
+  </si>
+  <si>
+    <t>1,28</t>
+  </si>
+  <si>
+    <t>43,5</t>
+  </si>
+  <si>
+    <t>0,34</t>
+  </si>
+  <si>
+    <t>15,67</t>
+  </si>
+  <si>
+    <t>1,39</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
     <t>0,03</t>
   </si>
   <si>
-    <t>16,13</t>
-  </si>
-  <si>
-    <t>6</t>
-  </si>
-  <si>
-    <t>0,04</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>LAMPUNG BARAT</t>
-  </si>
-  <si>
-    <t>4,23</t>
-  </si>
-  <si>
-    <t>0,67</t>
-  </si>
-  <si>
-    <t>28,4</t>
-  </si>
-  <si>
-    <t>0,17</t>
-  </si>
-  <si>
-    <t>0,46</t>
-  </si>
-  <si>
-    <t>4,12</t>
-  </si>
-  <si>
-    <t>0,44</t>
-  </si>
-  <si>
-    <t>39,65</t>
-  </si>
-  <si>
-    <t>0,08</t>
-  </si>
-  <si>
-    <t>12,81</t>
-  </si>
-  <si>
-    <t>7,97</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>TANGGAMUS</t>
-  </si>
-  <si>
-    <t>6,64</t>
-  </si>
-  <si>
-    <t>19,74</t>
-  </si>
-  <si>
-    <t>0,06</t>
-  </si>
-  <si>
-    <t>0,87</t>
+    <t>4,26</t>
+  </si>
+  <si>
+    <t>0,09</t>
+  </si>
+  <si>
+    <t>22,46</t>
+  </si>
+  <si>
+    <t>0,43</t>
+  </si>
+  <si>
+    <t>5,86</t>
+  </si>
+  <si>
+    <t>4,17</t>
+  </si>
+  <si>
+    <t>0,45</t>
+  </si>
+  <si>
+    <t>0,14</t>
+  </si>
+  <si>
+    <t>45,11</t>
+  </si>
+  <si>
+    <t>1,12</t>
+  </si>
+  <si>
+    <t>14,97</t>
+  </si>
+  <si>
+    <t>0,6</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>2,57</t>
+  </si>
+  <si>
+    <t>2,29</t>
+  </si>
+  <si>
+    <t>14,5</t>
+  </si>
+  <si>
+    <t>2,49</t>
+  </si>
+  <si>
+    <t>0,56</t>
+  </si>
+  <si>
+    <t>44,41</t>
+  </si>
+  <si>
+    <t>0,78</t>
+  </si>
+  <si>
+    <t>16,73</t>
+  </si>
+  <si>
+    <t>12,82</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>20,21</t>
+  </si>
+  <si>
+    <t>2,37</t>
+  </si>
+  <si>
+    <t>2,86</t>
+  </si>
+  <si>
+    <t>0,4</t>
+  </si>
+  <si>
+    <t>2,17</t>
+  </si>
+  <si>
+    <t>40,25</t>
+  </si>
+  <si>
+    <t>0,35</t>
+  </si>
+  <si>
+    <t>25,07</t>
+  </si>
+  <si>
+    <t>1,13</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG</t>
+  </si>
+  <si>
+    <t>4,35</t>
+  </si>
+  <si>
+    <t>0,71</t>
+  </si>
+  <si>
+    <t>23,43</t>
+  </si>
+  <si>
+    <t>0,25</t>
+  </si>
+  <si>
+    <t>1,17</t>
+  </si>
+  <si>
+    <t>2,51</t>
+  </si>
+  <si>
+    <t>0,13</t>
+  </si>
+  <si>
+    <t>2,3</t>
+  </si>
+  <si>
+    <t>45,98</t>
+  </si>
+  <si>
+    <t>14,69</t>
+  </si>
+  <si>
+    <t>4,14</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>3,3</t>
+  </si>
+  <si>
+    <t>1,14</t>
+  </si>
+  <si>
+    <t>13,47</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>1,02</t>
+  </si>
+  <si>
+    <t>1,41</t>
+  </si>
+  <si>
+    <t>40,65</t>
+  </si>
+  <si>
+    <t>0,85</t>
+  </si>
+  <si>
+    <t>21,94</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>4,91</t>
+  </si>
+  <si>
+    <t>0,26</t>
+  </si>
+  <si>
+    <t>16,94</t>
+  </si>
+  <si>
+    <t>1,32</t>
+  </si>
+  <si>
+    <t>3,99</t>
+  </si>
+  <si>
+    <t>0,88</t>
+  </si>
+  <si>
+    <t>0,18</t>
+  </si>
+  <si>
+    <t>43,35</t>
+  </si>
+  <si>
+    <t>1,54</t>
+  </si>
+  <si>
+    <t>19,04</t>
+  </si>
+  <si>
+    <t>2,5</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
+  </si>
+  <si>
+    <t>4,65</t>
+  </si>
+  <si>
+    <t>23,32</t>
+  </si>
+  <si>
+    <t>0,5</t>
+  </si>
+  <si>
+    <t>0,66</t>
+  </si>
+  <si>
+    <t>0,69</t>
+  </si>
+  <si>
+    <t>1,72</t>
+  </si>
+  <si>
+    <t>49,93</t>
+  </si>
+  <si>
+    <t>0,96</t>
+  </si>
+  <si>
+    <t>0,07</t>
+  </si>
+  <si>
+    <t>11,5</t>
+  </si>
+  <si>
+    <t>5,04</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>4,24</t>
+  </si>
+  <si>
+    <t>22,86</t>
+  </si>
+  <si>
+    <t>1,6</t>
+  </si>
+  <si>
+    <t>1,81</t>
+  </si>
+  <si>
+    <t>0,28</t>
+  </si>
+  <si>
+    <t>45,47</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>5,16</t>
+  </si>
+  <si>
+    <t>28,16</t>
   </si>
   <si>
     <t>3,44</t>
   </si>
   <si>
-    <t>3,32</t>
-  </si>
-  <si>
-    <t>0,29</t>
-  </si>
-  <si>
-    <t>41,88</t>
-  </si>
-  <si>
-    <t>22,89</t>
-  </si>
-  <si>
-    <t>0,41</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>LAMPUNG SELATAN</t>
-  </si>
-  <si>
-    <t>5,74</t>
-  </si>
-  <si>
-    <t>0,33</t>
-  </si>
-  <si>
-    <t>20,57</t>
-  </si>
-  <si>
-    <t>0,51</t>
-  </si>
-  <si>
-    <t>2,89</t>
-  </si>
-  <si>
-    <t>3,27</t>
-  </si>
-  <si>
-    <t>44,09</t>
-  </si>
-  <si>
-    <t>3,57</t>
-  </si>
-  <si>
-    <t>17,28</t>
-  </si>
-  <si>
-    <t>1,02</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>4,16</t>
-  </si>
-  <si>
-    <t>26,42</t>
-  </si>
-  <si>
-    <t>0,23</t>
-  </si>
-  <si>
-    <t>0,92</t>
-  </si>
-  <si>
-    <t>2,17</t>
-  </si>
-  <si>
-    <t>0,21</t>
-  </si>
-  <si>
-    <t>3,04</t>
-  </si>
-  <si>
-    <t>0,27</t>
-  </si>
-  <si>
-    <t>1,29</t>
-  </si>
-  <si>
-    <t>43,43</t>
-  </si>
-  <si>
-    <t>0,34</t>
-  </si>
-  <si>
-    <t>15,68</t>
-  </si>
-  <si>
-    <t>1,39</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>4,22</t>
-  </si>
-  <si>
-    <t>0,09</t>
-  </si>
-  <si>
-    <t>22,49</t>
-  </si>
-  <si>
-    <t>0,43</t>
-  </si>
-  <si>
-    <t>5,91</t>
-  </si>
-  <si>
-    <t>4,2</t>
-  </si>
-  <si>
-    <t>0,45</t>
-  </si>
-  <si>
-    <t>0,14</t>
-  </si>
-  <si>
-    <t>45,07</t>
-  </si>
-  <si>
-    <t>1,13</t>
-  </si>
-  <si>
-    <t>14,92</t>
-  </si>
-  <si>
-    <t>0,61</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>2,57</t>
-  </si>
-  <si>
-    <t>2,29</t>
-  </si>
-  <si>
-    <t>14,5</t>
-  </si>
-  <si>
-    <t>2,49</t>
-  </si>
-  <si>
-    <t>0,56</t>
-  </si>
-  <si>
-    <t>44,41</t>
-  </si>
-  <si>
-    <t>0,78</t>
-  </si>
-  <si>
-    <t>16,73</t>
-  </si>
-  <si>
-    <t>12,82</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>4,18</t>
-  </si>
-  <si>
-    <t>20,3</t>
-  </si>
-  <si>
-    <t>2,38</t>
-  </si>
-  <si>
-    <t>2,88</t>
-  </si>
-  <si>
-    <t>1,8</t>
-  </si>
-  <si>
-    <t>40,43</t>
-  </si>
-  <si>
-    <t>0,35</t>
-  </si>
-  <si>
-    <t>25,18</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG</t>
-  </si>
-  <si>
-    <t>4,35</t>
-  </si>
-  <si>
-    <t>0,71</t>
-  </si>
-  <si>
-    <t>23,43</t>
-  </si>
-  <si>
-    <t>0,25</t>
-  </si>
-  <si>
-    <t>1,17</t>
-  </si>
-  <si>
-    <t>2,51</t>
-  </si>
-  <si>
-    <t>0,13</t>
-  </si>
-  <si>
-    <t>2,3</t>
-  </si>
-  <si>
-    <t>45,98</t>
-  </si>
-  <si>
-    <t>14,69</t>
-  </si>
-  <si>
-    <t>4,14</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>3,3</t>
-  </si>
-  <si>
-    <t>1,14</t>
-  </si>
-  <si>
-    <t>13,47</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>1,41</t>
-  </si>
-  <si>
-    <t>1,28</t>
-  </si>
-  <si>
-    <t>40,66</t>
-  </si>
-  <si>
-    <t>0,85</t>
-  </si>
-  <si>
-    <t>14,7</t>
-  </si>
-  <si>
-    <t>21,94</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>4,92</t>
-  </si>
-  <si>
-    <t>0,26</t>
-  </si>
-  <si>
-    <t>16,95</t>
-  </si>
-  <si>
-    <t>1,32</t>
-  </si>
-  <si>
-    <t>4</t>
-  </si>
-  <si>
-    <t>0,88</t>
-  </si>
-  <si>
-    <t>0,18</t>
-  </si>
-  <si>
-    <t>43,35</t>
-  </si>
-  <si>
-    <t>1,54</t>
-  </si>
-  <si>
-    <t>19,02</t>
-  </si>
-  <si>
-    <t>2,5</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>0,02</t>
-  </si>
-  <si>
-    <t>4,63</t>
-  </si>
-  <si>
-    <t>0,6</t>
-  </si>
-  <si>
-    <t>23,33</t>
-  </si>
-  <si>
-    <t>0,5</t>
-  </si>
-  <si>
-    <t>0,66</t>
-  </si>
-  <si>
-    <t>0,69</t>
-  </si>
-  <si>
-    <t>1,72</t>
-  </si>
-  <si>
-    <t>49,93</t>
-  </si>
-  <si>
-    <t>0,96</t>
-  </si>
-  <si>
-    <t>0,07</t>
-  </si>
-  <si>
-    <t>11,5</t>
-  </si>
-  <si>
-    <t>5,04</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>4,27</t>
-  </si>
-  <si>
-    <t>22,73</t>
-  </si>
-  <si>
-    <t>0,42</t>
-  </si>
-  <si>
-    <t>1,61</t>
-  </si>
-  <si>
-    <t>1,83</t>
-  </si>
-  <si>
-    <t>0,28</t>
-  </si>
-  <si>
-    <t>45,53</t>
-  </si>
-  <si>
-    <t>0,24</t>
-  </si>
-  <si>
-    <t>21,98</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>4,93</t>
-  </si>
-  <si>
-    <t>28,66</t>
-  </si>
-  <si>
-    <t>3,5</t>
-  </si>
-  <si>
-    <t>44,86</t>
-  </si>
-  <si>
-    <t>0,4</t>
-  </si>
-  <si>
-    <t>14,45</t>
+    <t>46,03</t>
+  </si>
+  <si>
+    <t>0,38</t>
+  </si>
+  <si>
+    <t>13,86</t>
+  </si>
+  <si>
+    <t>2,12</t>
   </si>
   <si>
     <t>1871</t>
@@ -832,34 +817,34 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>6,89</t>
+    <t>6,9</t>
   </si>
   <si>
     <t>0,86</t>
   </si>
   <si>
-    <t>10,04</t>
+    <t>10,06</t>
   </si>
   <si>
     <t>0,57</t>
   </si>
   <si>
-    <t>5,88</t>
+    <t>5,89</t>
   </si>
   <si>
     <t>1,15</t>
   </si>
   <si>
-    <t>7,46</t>
-  </si>
-  <si>
-    <t>12,91</t>
-  </si>
-  <si>
-    <t>39,17</t>
-  </si>
-  <si>
-    <t>9,18</t>
+    <t>7,47</t>
+  </si>
+  <si>
+    <t>12,93</t>
+  </si>
+  <si>
+    <t>39,22</t>
+  </si>
+  <si>
+    <t>9,2</t>
   </si>
   <si>
     <t>2,73</t>
@@ -1824,16 +1809,16 @@
         <v>93</v>
       </c>
       <c r="C6" s="6">
-        <v>67943</v>
+        <v>68566</v>
       </c>
       <c r="D6" s="6">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>94</v>
       </c>
       <c r="F6" s="6">
-        <v>2916</v>
+        <v>2962</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>95</v>
@@ -1851,7 +1836,7 @@
         <v>97</v>
       </c>
       <c r="L6" s="6">
-        <v>14570</v>
+        <v>14702</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>98</v>
@@ -1863,7 +1848,7 @@
         <v>97</v>
       </c>
       <c r="P6" s="6">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q6" s="7" t="s">
         <v>99</v>
@@ -1887,7 +1872,7 @@
         <v>102</v>
       </c>
       <c r="X6" s="6">
-        <v>1981</v>
+        <v>1994</v>
       </c>
       <c r="Y6" s="7" t="s">
         <v>103</v>
@@ -1899,19 +1884,19 @@
         <v>104</v>
       </c>
       <c r="AB6" s="6">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="AC6" s="7" t="s">
         <v>105</v>
       </c>
       <c r="AD6" s="6">
-        <v>29682</v>
+        <v>30045</v>
       </c>
       <c r="AE6" s="7" t="s">
         <v>106</v>
       </c>
       <c r="AF6" s="6">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG6" s="7" t="s">
         <v>107</v>
@@ -1923,7 +1908,7 @@
         <v>108</v>
       </c>
       <c r="AJ6" s="6">
-        <v>10959</v>
+        <v>11011</v>
       </c>
       <c r="AK6" s="7" t="s">
         <v>109</v>
@@ -2098,7 +2083,7 @@
         <v>126</v>
       </c>
       <c r="C8" s="9">
-        <v>1717</v>
+        <v>1719</v>
       </c>
       <c r="D8" s="9">
         <v>0</v>
@@ -2179,7 +2164,7 @@
         <v>117</v>
       </c>
       <c r="AD8" s="9">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AE8" s="10" t="s">
         <v>134</v>
@@ -2197,7 +2182,7 @@
         <v>129</v>
       </c>
       <c r="AJ8" s="9">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="AK8" s="10" t="s">
         <v>135</v>
@@ -2235,7 +2220,7 @@
         <v>138</v>
       </c>
       <c r="C9" s="9">
-        <v>6689</v>
+        <v>6722</v>
       </c>
       <c r="D9" s="9">
         <v>0</v>
@@ -2244,7 +2229,7 @@
         <v>97</v>
       </c>
       <c r="F9" s="9">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>139</v>
@@ -2253,19 +2238,19 @@
         <v>22</v>
       </c>
       <c r="I9" s="10" t="s">
+        <v>105</v>
+      </c>
+      <c r="J9" s="9">
+        <v>0</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L9" s="9">
+        <v>1383</v>
+      </c>
+      <c r="M9" s="10" t="s">
         <v>140</v>
-      </c>
-      <c r="J9" s="9">
-        <v>0</v>
-      </c>
-      <c r="K9" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="L9" s="9">
-        <v>1376</v>
-      </c>
-      <c r="M9" s="10" t="s">
-        <v>141</v>
       </c>
       <c r="N9" s="9">
         <v>0</v>
@@ -2283,13 +2268,13 @@
         <v>34</v>
       </c>
       <c r="S9" s="10" t="s">
-        <v>142</v>
+        <v>104</v>
       </c>
       <c r="T9" s="9">
         <v>193</v>
       </c>
       <c r="U9" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="V9" s="9">
         <v>0</v>
@@ -2298,10 +2283,10 @@
         <v>97</v>
       </c>
       <c r="X9" s="9">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Z9" s="9">
         <v>45</v>
@@ -2316,16 +2301,16 @@
         <v>97</v>
       </c>
       <c r="AD9" s="9">
-        <v>2949</v>
+        <v>2968</v>
       </c>
       <c r="AE9" s="10" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="AF9" s="9">
         <v>239</v>
       </c>
       <c r="AG9" s="10" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="AH9" s="9">
         <v>0</v>
@@ -2334,16 +2319,16 @@
         <v>97</v>
       </c>
       <c r="AJ9" s="9">
-        <v>1156</v>
+        <v>1161</v>
       </c>
       <c r="AK9" s="10" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="AL9" s="9">
         <v>68</v>
       </c>
       <c r="AM9" s="10" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="AN9" s="9">
         <v>0</v>
@@ -2366,13 +2351,13 @@
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C10" s="9">
-        <v>8542</v>
+        <v>8564</v>
       </c>
       <c r="D10" s="9">
         <v>3</v>
@@ -2381,10 +2366,10 @@
         <v>111</v>
       </c>
       <c r="F10" s="9">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="H10" s="9">
         <v>25</v>
@@ -2399,10 +2384,10 @@
         <v>97</v>
       </c>
       <c r="L10" s="9">
-        <v>2257</v>
+        <v>2260</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="N10" s="9">
         <v>1</v>
@@ -2414,55 +2399,55 @@
         <v>20</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="R10" s="9">
         <v>79</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="T10" s="9">
         <v>185</v>
       </c>
       <c r="U10" s="10" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="V10" s="9">
         <v>18</v>
       </c>
       <c r="W10" s="10" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="X10" s="9">
         <v>260</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="Z10" s="9">
         <v>23</v>
       </c>
       <c r="AA10" s="10" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="AB10" s="9">
         <v>110</v>
       </c>
       <c r="AC10" s="10" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="AD10" s="9">
-        <v>3710</v>
+        <v>3725</v>
       </c>
       <c r="AE10" s="10" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="AF10" s="9">
         <v>29</v>
       </c>
       <c r="AG10" s="10" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="AH10" s="9">
         <v>5</v>
@@ -2471,16 +2456,16 @@
         <v>129</v>
       </c>
       <c r="AJ10" s="9">
-        <v>1339</v>
+        <v>1342</v>
       </c>
       <c r="AK10" s="10" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="AL10" s="9">
         <v>119</v>
       </c>
       <c r="AM10" s="10" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="AN10" s="9">
         <v>1</v>
@@ -2503,43 +2488,43 @@
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="C11" s="9">
-        <v>6446</v>
+        <v>6499</v>
       </c>
       <c r="D11" s="9">
         <v>2</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>108</v>
+        <v>164</v>
       </c>
       <c r="F11" s="9">
-        <v>272</v>
+        <v>277</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="H11" s="9">
         <v>6</v>
       </c>
       <c r="I11" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="J11" s="9">
+        <v>0</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L11" s="9">
+        <v>1460</v>
+      </c>
+      <c r="M11" s="10" t="s">
         <v>167</v>
-      </c>
-      <c r="J11" s="9">
-        <v>0</v>
-      </c>
-      <c r="K11" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="L11" s="9">
-        <v>1450</v>
-      </c>
-      <c r="M11" s="10" t="s">
-        <v>168</v>
       </c>
       <c r="N11" s="9">
         <v>0</v>
@@ -2551,73 +2536,73 @@
         <v>15</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="R11" s="9">
         <v>28</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="T11" s="9">
         <v>381</v>
       </c>
       <c r="U11" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="V11" s="9">
         <v>2</v>
       </c>
       <c r="W11" s="10" t="s">
-        <v>108</v>
+        <v>164</v>
       </c>
       <c r="X11" s="9">
         <v>271</v>
       </c>
       <c r="Y11" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Z11" s="9">
         <v>29</v>
       </c>
       <c r="AA11" s="10" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="AB11" s="9">
         <v>9</v>
       </c>
       <c r="AC11" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AD11" s="9">
+        <v>2932</v>
+      </c>
+      <c r="AE11" s="10" t="s">
         <v>173</v>
-      </c>
-      <c r="AD11" s="9">
-        <v>2905</v>
-      </c>
-      <c r="AE11" s="10" t="s">
-        <v>174</v>
       </c>
       <c r="AF11" s="9">
         <v>73</v>
       </c>
       <c r="AG11" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="AH11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ11" s="9">
+        <v>973</v>
+      </c>
+      <c r="AK11" s="10" t="s">
         <v>175</v>
-      </c>
-      <c r="AH11" s="9">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ11" s="9">
-        <v>962</v>
-      </c>
-      <c r="AK11" s="10" t="s">
-        <v>176</v>
       </c>
       <c r="AL11" s="9">
         <v>39</v>
       </c>
       <c r="AM11" s="10" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="AN11" s="9">
         <v>0</v>
@@ -2635,15 +2620,15 @@
         <v>2</v>
       </c>
       <c r="AS11" s="10" t="s">
-        <v>108</v>
+        <v>164</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
+        <v>177</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>178</v>
-      </c>
-      <c r="B12" s="8" t="s">
-        <v>179</v>
       </c>
       <c r="C12" s="9">
         <v>5904</v>
@@ -2658,13 +2643,13 @@
         <v>152</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H12" s="9">
         <v>135</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J12" s="9">
         <v>0</v>
@@ -2676,7 +2661,7 @@
         <v>856</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="N12" s="9">
         <v>0</v>
@@ -2700,7 +2685,7 @@
         <v>135</v>
       </c>
       <c r="U12" s="10" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="V12" s="9">
         <v>0</v>
@@ -2712,13 +2697,13 @@
         <v>147</v>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="Z12" s="9">
         <v>33</v>
       </c>
       <c r="AA12" s="10" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="AB12" s="9">
         <v>0</v>
@@ -2730,13 +2715,13 @@
         <v>2622</v>
       </c>
       <c r="AE12" s="10" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="AF12" s="9">
         <v>46</v>
       </c>
       <c r="AG12" s="10" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="AH12" s="9">
         <v>0</v>
@@ -2748,13 +2733,13 @@
         <v>988</v>
       </c>
       <c r="AK12" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AL12" s="9">
         <v>757</v>
       </c>
       <c r="AM12" s="10" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AN12" s="9">
         <v>0</v>
@@ -2777,25 +2762,25 @@
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
+        <v>188</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>189</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>190</v>
-      </c>
       <c r="C13" s="9">
-        <v>3443</v>
+        <v>3458</v>
       </c>
       <c r="D13" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>97</v>
+        <v>164</v>
       </c>
       <c r="F13" s="9">
         <v>144</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>191</v>
+        <v>149</v>
       </c>
       <c r="H13" s="9">
         <v>2</v>
@@ -2813,19 +2798,19 @@
         <v>699</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="N13" s="9">
         <v>1</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>108</v>
+        <v>164</v>
       </c>
       <c r="P13" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>99</v>
+        <v>172</v>
       </c>
       <c r="R13" s="9">
         <v>20</v>
@@ -2837,7 +2822,7 @@
         <v>82</v>
       </c>
       <c r="U13" s="10" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="V13" s="9">
         <v>2</v>
@@ -2849,55 +2834,55 @@
         <v>99</v>
       </c>
       <c r="Y13" s="10" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="Z13" s="9">
         <v>14</v>
       </c>
       <c r="AA13" s="10" t="s">
-        <v>136</v>
+        <v>193</v>
       </c>
       <c r="AB13" s="9">
-        <v>62</v>
+        <v>75</v>
       </c>
       <c r="AC13" s="10" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="AD13" s="9">
         <v>1392</v>
       </c>
       <c r="AE13" s="10" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="AF13" s="9">
         <v>12</v>
       </c>
       <c r="AG13" s="10" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="AH13" s="9">
         <v>3</v>
       </c>
       <c r="AI13" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AJ13" s="9">
         <v>867</v>
       </c>
       <c r="AK13" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AL13" s="9">
         <v>39</v>
       </c>
       <c r="AM13" s="10" t="s">
-        <v>175</v>
+        <v>198</v>
       </c>
       <c r="AN13" s="9">
         <v>1</v>
       </c>
       <c r="AO13" s="10" t="s">
-        <v>108</v>
+        <v>164</v>
       </c>
       <c r="AP13" s="9">
         <v>0</v>
@@ -3057,13 +3042,13 @@
         <v>213</v>
       </c>
       <c r="C15" s="9">
-        <v>7730</v>
+        <v>7731</v>
       </c>
       <c r="D15" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="F15" s="9">
         <v>255</v>
@@ -3105,13 +3090,13 @@
         <v>79</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>148</v>
+        <v>218</v>
       </c>
       <c r="T15" s="9">
         <v>109</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="V15" s="9">
         <v>1</v>
@@ -3123,7 +3108,7 @@
         <v>99</v>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>219</v>
+        <v>157</v>
       </c>
       <c r="Z15" s="9">
         <v>10</v>
@@ -3159,13 +3144,13 @@
         <v>1136</v>
       </c>
       <c r="AK15" s="10" t="s">
-        <v>222</v>
+        <v>210</v>
       </c>
       <c r="AL15" s="9">
         <v>1696</v>
       </c>
       <c r="AM15" s="10" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="AN15" s="9">
         <v>0</v>
@@ -3188,13 +3173,13 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
+        <v>223</v>
+      </c>
+      <c r="B16" s="8" t="s">
         <v>224</v>
       </c>
-      <c r="B16" s="8" t="s">
-        <v>225</v>
-      </c>
       <c r="C16" s="9">
-        <v>2277</v>
+        <v>2279</v>
       </c>
       <c r="D16" s="9">
         <v>0</v>
@@ -3206,13 +3191,13 @@
         <v>112</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="H16" s="9">
         <v>6</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="J16" s="9">
         <v>0</v>
@@ -3224,7 +3209,7 @@
         <v>386</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="N16" s="9">
         <v>0</v>
@@ -3242,13 +3227,13 @@
         <v>30</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
       <c r="T16" s="9">
         <v>112</v>
       </c>
       <c r="U16" s="10" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="V16" s="9">
         <v>0</v>
@@ -3260,31 +3245,31 @@
         <v>91</v>
       </c>
       <c r="Y16" s="10" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="Z16" s="9">
         <v>20</v>
       </c>
       <c r="AA16" s="10" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AB16" s="9">
         <v>4</v>
       </c>
       <c r="AC16" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="AD16" s="9">
+        <v>988</v>
+      </c>
+      <c r="AE16" s="10" t="s">
         <v>232</v>
-      </c>
-      <c r="AD16" s="9">
-        <v>987</v>
-      </c>
-      <c r="AE16" s="10" t="s">
-        <v>233</v>
       </c>
       <c r="AF16" s="9">
         <v>35</v>
       </c>
       <c r="AG16" s="10" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="AH16" s="9">
         <v>1</v>
@@ -3293,16 +3278,16 @@
         <v>111</v>
       </c>
       <c r="AJ16" s="9">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AK16" s="10" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="AL16" s="9">
         <v>57</v>
       </c>
       <c r="AM16" s="10" t="s">
-        <v>236</v>
+        <v>235</v>
       </c>
       <c r="AN16" s="9">
         <v>0</v>
@@ -3320,36 +3305,36 @@
         <v>2</v>
       </c>
       <c r="AS16" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
+        <v>236</v>
+      </c>
+      <c r="B17" s="8" t="s">
         <v>237</v>
       </c>
-      <c r="B17" s="8" t="s">
-        <v>238</v>
-      </c>
       <c r="C17" s="9">
-        <v>4364</v>
+        <v>4366</v>
       </c>
       <c r="D17" s="9">
         <v>1</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>239</v>
+        <v>108</v>
       </c>
       <c r="F17" s="9">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="H17" s="9">
         <v>26</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>241</v>
+        <v>176</v>
       </c>
       <c r="J17" s="9">
         <v>0</v>
@@ -3361,7 +3346,7 @@
         <v>1018</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="N17" s="9">
         <v>0</v>
@@ -3373,31 +3358,31 @@
         <v>22</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="R17" s="9">
         <v>29</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="T17" s="9">
         <v>30</v>
       </c>
       <c r="U17" s="10" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="V17" s="9">
         <v>9</v>
       </c>
       <c r="W17" s="10" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="X17" s="9">
         <v>75</v>
       </c>
       <c r="Y17" s="10" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="Z17" s="9">
         <v>2</v>
@@ -3409,37 +3394,37 @@
         <v>4</v>
       </c>
       <c r="AC17" s="10" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="AD17" s="9">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="AE17" s="10" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="AF17" s="9">
         <v>42</v>
       </c>
       <c r="AG17" s="10" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="AH17" s="9">
         <v>3</v>
       </c>
       <c r="AI17" s="10" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="AJ17" s="9">
         <v>502</v>
       </c>
       <c r="AK17" s="10" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="AL17" s="9">
         <v>220</v>
       </c>
       <c r="AM17" s="10" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="AN17" s="9">
         <v>0</v>
@@ -3462,13 +3447,13 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="C18" s="9">
-        <v>5041</v>
+        <v>5074</v>
       </c>
       <c r="D18" s="9">
         <v>0</v>
@@ -3480,7 +3465,7 @@
         <v>215</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="H18" s="9">
         <v>6</v>
@@ -3495,10 +3480,10 @@
         <v>97</v>
       </c>
       <c r="L18" s="9">
-        <v>1146</v>
+        <v>1160</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="N18" s="9">
         <v>0</v>
@@ -3516,49 +3501,49 @@
         <v>21</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>256</v>
+        <v>136</v>
       </c>
       <c r="T18" s="9">
         <v>81</v>
       </c>
       <c r="U18" s="10" t="s">
-        <v>257</v>
+        <v>253</v>
       </c>
       <c r="V18" s="9">
         <v>1</v>
       </c>
       <c r="W18" s="10" t="s">
-        <v>239</v>
+        <v>108</v>
       </c>
       <c r="X18" s="9">
         <v>92</v>
       </c>
       <c r="Y18" s="10" t="s">
-        <v>258</v>
+        <v>254</v>
       </c>
       <c r="Z18" s="9">
         <v>14</v>
       </c>
       <c r="AA18" s="10" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="AB18" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC18" s="10" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="AD18" s="9">
-        <v>2295</v>
+        <v>2307</v>
       </c>
       <c r="AE18" s="10" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="AF18" s="9">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AG18" s="10" t="s">
-        <v>261</v>
+        <v>226</v>
       </c>
       <c r="AH18" s="9">
         <v>0</v>
@@ -3567,10 +3552,10 @@
         <v>97</v>
       </c>
       <c r="AJ18" s="9">
-        <v>1108</v>
+        <v>1113</v>
       </c>
       <c r="AK18" s="10" t="s">
-        <v>262</v>
+        <v>222</v>
       </c>
       <c r="AL18" s="9">
         <v>44</v>
@@ -3599,13 +3584,13 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>263</v>
+        <v>257</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>264</v>
+        <v>258</v>
       </c>
       <c r="C19" s="9">
-        <v>6424</v>
+        <v>6885</v>
       </c>
       <c r="D19" s="9">
         <v>0</v>
@@ -3614,16 +3599,16 @@
         <v>97</v>
       </c>
       <c r="F19" s="9">
-        <v>317</v>
+        <v>355</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>265</v>
+        <v>259</v>
       </c>
       <c r="H19" s="9">
         <v>18</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="J19" s="9">
         <v>0</v>
@@ -3632,10 +3617,10 @@
         <v>97</v>
       </c>
       <c r="L19" s="9">
-        <v>1841</v>
+        <v>1939</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>266</v>
+        <v>260</v>
       </c>
       <c r="N19" s="9">
         <v>0</v>
@@ -3653,13 +3638,13 @@
         <v>18</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>259</v>
+        <v>226</v>
       </c>
       <c r="T19" s="9">
         <v>17</v>
       </c>
       <c r="U19" s="10" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="V19" s="9">
         <v>0</v>
@@ -3668,10 +3653,10 @@
         <v>97</v>
       </c>
       <c r="X19" s="9">
-        <v>225</v>
+        <v>237</v>
       </c>
       <c r="Y19" s="10" t="s">
-        <v>267</v>
+        <v>261</v>
       </c>
       <c r="Z19" s="9">
         <v>4</v>
@@ -3686,16 +3671,16 @@
         <v>97</v>
       </c>
       <c r="AD19" s="9">
-        <v>2882</v>
+        <v>3169</v>
       </c>
       <c r="AE19" s="10" t="s">
-        <v>268</v>
+        <v>262</v>
       </c>
       <c r="AF19" s="9">
         <v>26</v>
       </c>
       <c r="AG19" s="10" t="s">
-        <v>269</v>
+        <v>263</v>
       </c>
       <c r="AH19" s="9">
         <v>0</v>
@@ -3704,16 +3689,16 @@
         <v>97</v>
       </c>
       <c r="AJ19" s="9">
-        <v>928</v>
+        <v>954</v>
       </c>
       <c r="AK19" s="10" t="s">
-        <v>270</v>
+        <v>264</v>
       </c>
       <c r="AL19" s="9">
         <v>146</v>
       </c>
       <c r="AM19" s="10" t="s">
-        <v>101</v>
+        <v>265</v>
       </c>
       <c r="AN19" s="9">
         <v>0</v>
@@ -3731,18 +3716,18 @@
         <v>2</v>
       </c>
       <c r="AS19" s="10" t="s">
-        <v>108</v>
+        <v>164</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>272</v>
+        <v>267</v>
       </c>
       <c r="C20" s="9">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D20" s="9">
         <v>0</v>
@@ -3754,13 +3739,13 @@
         <v>48</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>273</v>
+        <v>268</v>
       </c>
       <c r="H20" s="9">
         <v>6</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>274</v>
+        <v>269</v>
       </c>
       <c r="J20" s="9">
         <v>0</v>
@@ -3772,7 +3757,7 @@
         <v>70</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>275</v>
+        <v>270</v>
       </c>
       <c r="N20" s="9">
         <v>0</v>
@@ -3784,55 +3769,55 @@
         <v>4</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="R20" s="9">
         <v>4</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>276</v>
+        <v>271</v>
       </c>
       <c r="T20" s="9">
         <v>41</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>277</v>
+        <v>272</v>
       </c>
       <c r="V20" s="9">
         <v>8</v>
       </c>
       <c r="W20" s="10" t="s">
-        <v>278</v>
+        <v>273</v>
       </c>
       <c r="X20" s="9">
         <v>52</v>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>279</v>
+        <v>274</v>
       </c>
       <c r="Z20" s="9">
         <v>90</v>
       </c>
       <c r="AA20" s="10" t="s">
-        <v>280</v>
+        <v>275</v>
       </c>
       <c r="AB20" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC20" s="10" t="s">
-        <v>276</v>
+        <v>168</v>
       </c>
       <c r="AD20" s="9">
         <v>273</v>
       </c>
       <c r="AE20" s="10" t="s">
-        <v>281</v>
+        <v>276</v>
       </c>
       <c r="AF20" s="9">
         <v>12</v>
       </c>
       <c r="AG20" s="10" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="AH20" s="9">
         <v>0</v>
@@ -3844,13 +3829,13 @@
         <v>64</v>
       </c>
       <c r="AK20" s="10" t="s">
-        <v>282</v>
+        <v>277</v>
       </c>
       <c r="AL20" s="9">
         <v>19</v>
       </c>
       <c r="AM20" s="10" t="s">
-        <v>283</v>
+        <v>278</v>
       </c>
       <c r="AN20" s="9">
         <v>0</v>
@@ -3873,10 +3858,10 @@
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>284</v>
+        <v>279</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>285</v>
+        <v>280</v>
       </c>
       <c r="C21" s="9">
         <v>1500</v>
@@ -3891,13 +3876,13 @@
         <v>40</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="H21" s="9">
         <v>6</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>269</v>
+        <v>193</v>
       </c>
       <c r="J21" s="9">
         <v>0</v>
@@ -3909,7 +3894,7 @@
         <v>174</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>287</v>
+        <v>282</v>
       </c>
       <c r="N21" s="9">
         <v>0</v>
@@ -3927,49 +3912,49 @@
         <v>9</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>241</v>
+        <v>176</v>
       </c>
       <c r="T21" s="9">
         <v>35</v>
       </c>
       <c r="U21" s="10" t="s">
-        <v>288</v>
+        <v>283</v>
       </c>
       <c r="V21" s="9">
         <v>1</v>
       </c>
       <c r="W21" s="10" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="X21" s="9">
         <v>42</v>
       </c>
       <c r="Y21" s="10" t="s">
-        <v>289</v>
+        <v>284</v>
       </c>
       <c r="Z21" s="9">
         <v>39</v>
       </c>
       <c r="AA21" s="10" t="s">
-        <v>290</v>
+        <v>285</v>
       </c>
       <c r="AB21" s="9">
         <v>15</v>
       </c>
       <c r="AC21" s="10" t="s">
-        <v>291</v>
+        <v>286</v>
       </c>
       <c r="AD21" s="9">
         <v>632</v>
       </c>
       <c r="AE21" s="10" t="s">
-        <v>292</v>
+        <v>287</v>
       </c>
       <c r="AF21" s="9">
         <v>3</v>
       </c>
       <c r="AG21" s="10" t="s">
-        <v>293</v>
+        <v>288</v>
       </c>
       <c r="AH21" s="9">
         <v>0</v>
@@ -3981,13 +3966,13 @@
         <v>120</v>
       </c>
       <c r="AK21" s="10" t="s">
-        <v>294</v>
+        <v>289</v>
       </c>
       <c r="AL21" s="9">
         <v>384</v>
       </c>
       <c r="AM21" s="10" t="s">
-        <v>295</v>
+        <v>290</v>
       </c>
       <c r="AN21" s="9">
         <v>0</v>
@@ -4010,22 +3995,22 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>296</v>
+        <v>291</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>297</v>
+        <v>292</v>
       </c>
       <c r="C22" s="12">
-        <v>67943</v>
+        <v>68566</v>
       </c>
       <c r="D22" s="12">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>94</v>
       </c>
       <c r="F22" s="12">
-        <v>2916</v>
+        <v>2962</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>95</v>
@@ -4043,7 +4028,7 @@
         <v>97</v>
       </c>
       <c r="L22" s="12">
-        <v>14570</v>
+        <v>14702</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>98</v>
@@ -4055,7 +4040,7 @@
         <v>97</v>
       </c>
       <c r="P22" s="12">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="Q22" s="13" t="s">
         <v>99</v>
@@ -4079,7 +4064,7 @@
         <v>102</v>
       </c>
       <c r="X22" s="12">
-        <v>1981</v>
+        <v>1994</v>
       </c>
       <c r="Y22" s="13" t="s">
         <v>103</v>
@@ -4091,19 +4076,19 @@
         <v>104</v>
       </c>
       <c r="AB22" s="12">
-        <v>216</v>
+        <v>229</v>
       </c>
       <c r="AC22" s="13" t="s">
         <v>105</v>
       </c>
       <c r="AD22" s="12">
-        <v>29682</v>
+        <v>30045</v>
       </c>
       <c r="AE22" s="13" t="s">
         <v>106</v>
       </c>
       <c r="AF22" s="12">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="AG22" s="13" t="s">
         <v>107</v>
@@ -4115,7 +4100,7 @@
         <v>108</v>
       </c>
       <c r="AJ22" s="12">
-        <v>10959</v>
+        <v>11011</v>
       </c>
       <c r="AK22" s="13" t="s">
         <v>109</v>

--- a/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
+++ b/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="291">
   <si>
     <t>DATA RADAR ANOMALI KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 7 Sep 2026, 15.58</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 8 Sep 2026, 07.19</t>
   </si>
   <si>
     <t>Kode</t>
@@ -298,570 +298,567 @@
     <t>0,01</t>
   </si>
   <si>
-    <t>4,32</t>
+    <t>4,34</t>
+  </si>
+  <si>
+    <t>0,57</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>21,6</t>
+  </si>
+  <si>
+    <t>0,12</t>
+  </si>
+  <si>
+    <t>0,62</t>
+  </si>
+  <si>
+    <t>2,22</t>
+  </si>
+  <si>
+    <t>0,09</t>
+  </si>
+  <si>
+    <t>2,9</t>
+  </si>
+  <si>
+    <t>0,51</t>
+  </si>
+  <si>
+    <t>0,32</t>
+  </si>
+  <si>
+    <t>43,88</t>
+  </si>
+  <si>
+    <t>0,89</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>16,01</t>
+  </si>
+  <si>
+    <t>5,85</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>LAMPUNG BARAT</t>
+  </si>
+  <si>
+    <t>4,22</t>
+  </si>
+  <si>
+    <t>0,67</t>
+  </si>
+  <si>
+    <t>28,4</t>
+  </si>
+  <si>
+    <t>0,17</t>
+  </si>
+  <si>
+    <t>0,46</t>
+  </si>
+  <si>
+    <t>4,12</t>
+  </si>
+  <si>
+    <t>0,44</t>
+  </si>
+  <si>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>39,65</t>
+  </si>
+  <si>
+    <t>0,08</t>
+  </si>
+  <si>
+    <t>12,82</t>
+  </si>
+  <si>
+    <t>7,97</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>TANGGAMUS</t>
+  </si>
+  <si>
+    <t>6,62</t>
+  </si>
+  <si>
+    <t>19,74</t>
+  </si>
+  <si>
+    <t>0,87</t>
+  </si>
+  <si>
+    <t>3,48</t>
+  </si>
+  <si>
+    <t>3,31</t>
+  </si>
+  <si>
+    <t>0,29</t>
+  </si>
+  <si>
+    <t>41,87</t>
+  </si>
+  <si>
+    <t>22,94</t>
+  </si>
+  <si>
+    <t>0,41</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>LAMPUNG SELATAN</t>
+  </si>
+  <si>
+    <t>5,75</t>
+  </si>
+  <si>
+    <t>20,6</t>
+  </si>
+  <si>
+    <t>0,5</t>
+  </si>
+  <si>
+    <t>2,85</t>
+  </si>
+  <si>
+    <t>3,26</t>
+  </si>
+  <si>
+    <t>0,66</t>
+  </si>
+  <si>
+    <t>44,16</t>
+  </si>
+  <si>
+    <t>3,53</t>
+  </si>
+  <si>
+    <t>17,28</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>0,06</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>4,2</t>
+  </si>
+  <si>
+    <t>26,46</t>
+  </si>
+  <si>
+    <t>0,23</t>
+  </si>
+  <si>
+    <t>0,91</t>
+  </si>
+  <si>
+    <t>2,14</t>
+  </si>
+  <si>
+    <t>0,21</t>
+  </si>
+  <si>
+    <t>3,05</t>
+  </si>
+  <si>
+    <t>0,27</t>
+  </si>
+  <si>
+    <t>1,29</t>
+  </si>
+  <si>
+    <t>43,5</t>
+  </si>
+  <si>
+    <t>0,34</t>
+  </si>
+  <si>
+    <t>15,59</t>
+  </si>
+  <si>
+    <t>1,38</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
+    <t>4,38</t>
+  </si>
+  <si>
+    <t>23,1</t>
+  </si>
+  <si>
+    <t>0,22</t>
+  </si>
+  <si>
+    <t>5,53</t>
+  </si>
+  <si>
+    <t>4,08</t>
+  </si>
+  <si>
+    <t>0,42</t>
+  </si>
+  <si>
+    <t>45,16</t>
+  </si>
+  <si>
+    <t>1,06</t>
+  </si>
+  <si>
+    <t>14,82</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>2,56</t>
+  </si>
+  <si>
+    <t>2,27</t>
+  </si>
+  <si>
+    <t>14,62</t>
+  </si>
+  <si>
+    <t>2,48</t>
+  </si>
+  <si>
+    <t>0,56</t>
+  </si>
+  <si>
+    <t>44,42</t>
+  </si>
+  <si>
+    <t>0,77</t>
+  </si>
+  <si>
+    <t>16,75</t>
+  </si>
+  <si>
+    <t>12,75</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>4,19</t>
+  </si>
+  <si>
+    <t>20,24</t>
+  </si>
+  <si>
+    <t>0,14</t>
   </si>
   <si>
     <t>0,58</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>21,44</t>
-  </si>
-  <si>
-    <t>0,12</t>
-  </si>
-  <si>
-    <t>0,62</t>
-  </si>
-  <si>
-    <t>2,25</t>
-  </si>
-  <si>
-    <t>0,1</t>
-  </si>
-  <si>
-    <t>2,91</t>
-  </si>
-  <si>
-    <t>0,51</t>
-  </si>
-  <si>
-    <t>0,33</t>
-  </si>
-  <si>
-    <t>43,82</t>
-  </si>
-  <si>
-    <t>0,91</t>
+    <t>2,37</t>
+  </si>
+  <si>
+    <t>2,86</t>
+  </si>
+  <si>
+    <t>0,4</t>
+  </si>
+  <si>
+    <t>2,11</t>
+  </si>
+  <si>
+    <t>40,28</t>
+  </si>
+  <si>
+    <t>0,35</t>
+  </si>
+  <si>
+    <t>25,06</t>
+  </si>
+  <si>
+    <t>1,13</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG</t>
+  </si>
+  <si>
+    <t>4,35</t>
+  </si>
+  <si>
+    <t>0,71</t>
+  </si>
+  <si>
+    <t>23,43</t>
+  </si>
+  <si>
+    <t>0,25</t>
+  </si>
+  <si>
+    <t>1,17</t>
+  </si>
+  <si>
+    <t>2,51</t>
+  </si>
+  <si>
+    <t>0,13</t>
+  </si>
+  <si>
+    <t>2,3</t>
+  </si>
+  <si>
+    <t>45,98</t>
+  </si>
+  <si>
+    <t>14,69</t>
+  </si>
+  <si>
+    <t>4,14</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>3,3</t>
+  </si>
+  <si>
+    <t>1,14</t>
+  </si>
+  <si>
+    <t>13,47</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>1,02</t>
+  </si>
+  <si>
+    <t>1,41</t>
+  </si>
+  <si>
+    <t>40,69</t>
+  </si>
+  <si>
+    <t>0,85</t>
+  </si>
+  <si>
+    <t>14,68</t>
+  </si>
+  <si>
+    <t>21,92</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>4,93</t>
+  </si>
+  <si>
+    <t>0,26</t>
+  </si>
+  <si>
+    <t>16,9</t>
+  </si>
+  <si>
+    <t>1,31</t>
+  </si>
+  <si>
+    <t>4,89</t>
+  </si>
+  <si>
+    <t>4,02</t>
+  </si>
+  <si>
+    <t>43,45</t>
+  </si>
+  <si>
+    <t>1,53</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>2,49</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
   </si>
   <si>
     <t>0,02</t>
   </si>
   <si>
-    <t>16,06</t>
-  </si>
-  <si>
-    <t>5,94</t>
-  </si>
-  <si>
-    <t>0,04</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>LAMPUNG BARAT</t>
-  </si>
-  <si>
-    <t>4,23</t>
-  </si>
-  <si>
-    <t>0,67</t>
-  </si>
-  <si>
-    <t>28,4</t>
-  </si>
-  <si>
-    <t>0,17</t>
-  </si>
-  <si>
-    <t>0,46</t>
-  </si>
-  <si>
-    <t>4,12</t>
-  </si>
-  <si>
-    <t>0,44</t>
-  </si>
-  <si>
-    <t>39,65</t>
-  </si>
-  <si>
-    <t>0,08</t>
-  </si>
-  <si>
-    <t>12,81</t>
-  </si>
-  <si>
-    <t>7,97</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>TANGGAMUS</t>
-  </si>
-  <si>
-    <t>6,63</t>
-  </si>
-  <si>
-    <t>19,72</t>
-  </si>
-  <si>
-    <t>0,06</t>
-  </si>
-  <si>
-    <t>0,87</t>
-  </si>
-  <si>
-    <t>3,43</t>
-  </si>
-  <si>
-    <t>3,32</t>
-  </si>
-  <si>
-    <t>0,29</t>
-  </si>
-  <si>
-    <t>41,88</t>
-  </si>
-  <si>
-    <t>22,92</t>
-  </si>
-  <si>
-    <t>0,41</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>LAMPUNG SELATAN</t>
-  </si>
-  <si>
-    <t>5,73</t>
-  </si>
-  <si>
-    <t>20,57</t>
-  </si>
-  <si>
-    <t>2,87</t>
-  </si>
-  <si>
-    <t>3,27</t>
-  </si>
-  <si>
-    <t>44,15</t>
-  </si>
-  <si>
-    <t>3,56</t>
-  </si>
-  <si>
-    <t>17,27</t>
-  </si>
-  <si>
-    <t>1,01</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>4,16</t>
-  </si>
-  <si>
-    <t>26,39</t>
-  </si>
-  <si>
-    <t>0,23</t>
-  </si>
-  <si>
-    <t>0,92</t>
-  </si>
-  <si>
-    <t>2,16</t>
-  </si>
-  <si>
-    <t>0,21</t>
-  </si>
-  <si>
-    <t>3,04</t>
-  </si>
-  <si>
-    <t>0,27</t>
-  </si>
-  <si>
-    <t>1,28</t>
-  </si>
-  <si>
-    <t>43,5</t>
-  </si>
-  <si>
-    <t>0,34</t>
-  </si>
-  <si>
-    <t>15,67</t>
-  </si>
-  <si>
-    <t>1,39</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>0,03</t>
-  </si>
-  <si>
-    <t>4,26</t>
-  </si>
-  <si>
-    <t>0,09</t>
-  </si>
-  <si>
-    <t>22,46</t>
-  </si>
-  <si>
-    <t>0,43</t>
-  </si>
-  <si>
-    <t>5,86</t>
-  </si>
-  <si>
-    <t>4,17</t>
-  </si>
-  <si>
-    <t>0,45</t>
-  </si>
-  <si>
-    <t>0,14</t>
-  </si>
-  <si>
-    <t>45,11</t>
-  </si>
-  <si>
-    <t>1,12</t>
-  </si>
-  <si>
-    <t>14,97</t>
+    <t>4,65</t>
+  </si>
+  <si>
+    <t>0,59</t>
+  </si>
+  <si>
+    <t>23,4</t>
+  </si>
+  <si>
+    <t>0,68</t>
+  </si>
+  <si>
+    <t>1,71</t>
+  </si>
+  <si>
+    <t>49,93</t>
+  </si>
+  <si>
+    <t>0,96</t>
+  </si>
+  <si>
+    <t>0,07</t>
+  </si>
+  <si>
+    <t>11,46</t>
+  </si>
+  <si>
+    <t>5,01</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>1,62</t>
+  </si>
+  <si>
+    <t>1,8</t>
+  </si>
+  <si>
+    <t>45,39</t>
+  </si>
+  <si>
+    <t>22</t>
+  </si>
+  <si>
+    <t>0,86</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>5,06</t>
+  </si>
+  <si>
+    <t>28,28</t>
+  </si>
+  <si>
+    <t>3,37</t>
+  </si>
+  <si>
+    <t>46,27</t>
+  </si>
+  <si>
+    <t>13,83</t>
+  </si>
+  <si>
+    <t>2,02</t>
+  </si>
+  <si>
+    <t>1871</t>
+  </si>
+  <si>
+    <t>BANDAR LAMPUNG</t>
+  </si>
+  <si>
+    <t>7,15</t>
+  </si>
+  <si>
+    <t>0,81</t>
+  </si>
+  <si>
+    <t>10,93</t>
+  </si>
+  <si>
+    <t>0,54</t>
+  </si>
+  <si>
+    <t>1,08</t>
+  </si>
+  <si>
+    <t>7,56</t>
+  </si>
+  <si>
+    <t>12,15</t>
+  </si>
+  <si>
+    <t>39,68</t>
+  </si>
+  <si>
+    <t>9,04</t>
+  </si>
+  <si>
+    <t>1872</t>
+  </si>
+  <si>
+    <t>METRO</t>
+  </si>
+  <si>
+    <t>2,67</t>
+  </si>
+  <si>
+    <t>11,6</t>
   </si>
   <si>
     <t>0,6</t>
   </si>
   <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>2,57</t>
-  </si>
-  <si>
-    <t>2,29</t>
-  </si>
-  <si>
-    <t>14,5</t>
-  </si>
-  <si>
-    <t>2,49</t>
-  </si>
-  <si>
-    <t>0,56</t>
-  </si>
-  <si>
-    <t>44,41</t>
-  </si>
-  <si>
-    <t>0,78</t>
-  </si>
-  <si>
-    <t>16,73</t>
-  </si>
-  <si>
-    <t>12,82</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>20,21</t>
-  </si>
-  <si>
-    <t>2,37</t>
-  </si>
-  <si>
-    <t>2,86</t>
-  </si>
-  <si>
-    <t>0,4</t>
-  </si>
-  <si>
-    <t>2,17</t>
-  </si>
-  <si>
-    <t>40,25</t>
-  </si>
-  <si>
-    <t>0,35</t>
-  </si>
-  <si>
-    <t>25,07</t>
-  </si>
-  <si>
-    <t>1,13</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG</t>
-  </si>
-  <si>
-    <t>4,35</t>
-  </si>
-  <si>
-    <t>0,71</t>
-  </si>
-  <si>
-    <t>23,43</t>
-  </si>
-  <si>
-    <t>0,25</t>
-  </si>
-  <si>
-    <t>1,17</t>
-  </si>
-  <si>
-    <t>2,51</t>
-  </si>
-  <si>
-    <t>0,13</t>
-  </si>
-  <si>
-    <t>2,3</t>
-  </si>
-  <si>
-    <t>45,98</t>
-  </si>
-  <si>
-    <t>14,69</t>
-  </si>
-  <si>
-    <t>4,14</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>3,3</t>
-  </si>
-  <si>
-    <t>1,14</t>
-  </si>
-  <si>
-    <t>13,47</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>1,02</t>
-  </si>
-  <si>
-    <t>1,41</t>
-  </si>
-  <si>
-    <t>40,65</t>
-  </si>
-  <si>
-    <t>0,85</t>
-  </si>
-  <si>
-    <t>21,94</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>4,91</t>
-  </si>
-  <si>
-    <t>0,26</t>
-  </si>
-  <si>
-    <t>16,94</t>
-  </si>
-  <si>
-    <t>1,32</t>
-  </si>
-  <si>
-    <t>3,99</t>
-  </si>
-  <si>
-    <t>0,88</t>
-  </si>
-  <si>
-    <t>0,18</t>
-  </si>
-  <si>
-    <t>43,35</t>
-  </si>
-  <si>
-    <t>1,54</t>
-  </si>
-  <si>
-    <t>19,04</t>
-  </si>
-  <si>
-    <t>2,5</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>4,65</t>
-  </si>
-  <si>
-    <t>23,32</t>
-  </si>
-  <si>
-    <t>0,5</t>
-  </si>
-  <si>
-    <t>0,66</t>
-  </si>
-  <si>
-    <t>0,69</t>
-  </si>
-  <si>
-    <t>1,72</t>
-  </si>
-  <si>
-    <t>49,93</t>
-  </si>
-  <si>
-    <t>0,96</t>
-  </si>
-  <si>
-    <t>0,07</t>
-  </si>
-  <si>
-    <t>11,5</t>
-  </si>
-  <si>
-    <t>5,04</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>4,24</t>
-  </si>
-  <si>
-    <t>22,86</t>
-  </si>
-  <si>
-    <t>1,6</t>
-  </si>
-  <si>
-    <t>1,81</t>
-  </si>
-  <si>
-    <t>0,28</t>
-  </si>
-  <si>
-    <t>45,47</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>5,16</t>
-  </si>
-  <si>
-    <t>28,16</t>
-  </si>
-  <si>
-    <t>3,44</t>
-  </si>
-  <si>
-    <t>46,03</t>
-  </si>
-  <si>
-    <t>0,38</t>
-  </si>
-  <si>
-    <t>13,86</t>
-  </si>
-  <si>
-    <t>2,12</t>
-  </si>
-  <si>
-    <t>1871</t>
-  </si>
-  <si>
-    <t>BANDAR LAMPUNG</t>
-  </si>
-  <si>
-    <t>6,9</t>
-  </si>
-  <si>
-    <t>0,86</t>
-  </si>
-  <si>
-    <t>10,06</t>
-  </si>
-  <si>
-    <t>0,57</t>
-  </si>
-  <si>
-    <t>5,89</t>
-  </si>
-  <si>
-    <t>1,15</t>
-  </si>
-  <si>
-    <t>7,47</t>
-  </si>
-  <si>
-    <t>12,93</t>
-  </si>
-  <si>
-    <t>39,22</t>
-  </si>
-  <si>
-    <t>9,2</t>
-  </si>
-  <si>
-    <t>2,73</t>
-  </si>
-  <si>
-    <t>1872</t>
-  </si>
-  <si>
-    <t>METRO</t>
-  </si>
-  <si>
-    <t>2,67</t>
-  </si>
-  <si>
-    <t>11,6</t>
-  </si>
-  <si>
     <t>2,33</t>
   </si>
   <si>
@@ -869,9 +866,6 @@
   </si>
   <si>
     <t>2,6</t>
-  </si>
-  <si>
-    <t>1</t>
   </si>
   <si>
     <t>42,13</t>
@@ -1809,16 +1803,16 @@
         <v>93</v>
       </c>
       <c r="C6" s="6">
-        <v>68566</v>
+        <v>69705</v>
       </c>
       <c r="D6" s="6">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E6" s="7" t="s">
         <v>94</v>
       </c>
       <c r="F6" s="6">
-        <v>2962</v>
+        <v>3024</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>95</v>
@@ -1836,7 +1830,7 @@
         <v>97</v>
       </c>
       <c r="L6" s="6">
-        <v>14702</v>
+        <v>15059</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>98</v>
@@ -1848,49 +1842,49 @@
         <v>97</v>
       </c>
       <c r="P6" s="6">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q6" s="7" t="s">
         <v>99</v>
       </c>
       <c r="R6" s="6">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="S6" s="7" t="s">
         <v>100</v>
       </c>
       <c r="T6" s="6">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="U6" s="7" t="s">
         <v>101</v>
       </c>
       <c r="V6" s="6">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="W6" s="7" t="s">
         <v>102</v>
       </c>
       <c r="X6" s="6">
-        <v>1994</v>
+        <v>2024</v>
       </c>
       <c r="Y6" s="7" t="s">
         <v>103</v>
       </c>
       <c r="Z6" s="6">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AA6" s="7" t="s">
         <v>104</v>
       </c>
       <c r="AB6" s="6">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="AC6" s="7" t="s">
         <v>105</v>
       </c>
       <c r="AD6" s="6">
-        <v>30045</v>
+        <v>30586</v>
       </c>
       <c r="AE6" s="7" t="s">
         <v>106</v>
@@ -1902,19 +1896,19 @@
         <v>107</v>
       </c>
       <c r="AH6" s="6">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI6" s="7" t="s">
         <v>108</v>
       </c>
       <c r="AJ6" s="6">
-        <v>11011</v>
+        <v>11161</v>
       </c>
       <c r="AK6" s="7" t="s">
         <v>109</v>
       </c>
       <c r="AL6" s="6">
-        <v>4075</v>
+        <v>4077</v>
       </c>
       <c r="AM6" s="7" t="s">
         <v>110</v>
@@ -1946,7 +1940,7 @@
         <v>113</v>
       </c>
       <c r="C7" s="9">
-        <v>4779</v>
+        <v>4782</v>
       </c>
       <c r="D7" s="9">
         <v>0</v>
@@ -1973,7 +1967,7 @@
         <v>97</v>
       </c>
       <c r="L7" s="9">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>116</v>
@@ -2024,13 +2018,13 @@
         <v>5</v>
       </c>
       <c r="AC7" s="10" t="s">
-        <v>102</v>
+        <v>121</v>
       </c>
       <c r="AD7" s="9">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="AE7" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AF7" s="9">
         <v>21</v>
@@ -2042,19 +2036,19 @@
         <v>4</v>
       </c>
       <c r="AI7" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AJ7" s="9">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="AK7" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AL7" s="9">
         <v>381</v>
       </c>
       <c r="AM7" s="10" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="AN7" s="9">
         <v>0</v>
@@ -2077,13 +2071,13 @@
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="C8" s="9">
-        <v>1719</v>
+        <v>1722</v>
       </c>
       <c r="D8" s="9">
         <v>0</v>
@@ -2095,7 +2089,7 @@
         <v>114</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
@@ -2110,10 +2104,10 @@
         <v>97</v>
       </c>
       <c r="L8" s="9">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="N8" s="9">
         <v>0</v>
@@ -2122,10 +2116,10 @@
         <v>97</v>
       </c>
       <c r="P8" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>129</v>
+        <v>97</v>
       </c>
       <c r="R8" s="9">
         <v>15</v>
@@ -2134,7 +2128,7 @@
         <v>130</v>
       </c>
       <c r="T8" s="9">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="U8" s="10" t="s">
         <v>131</v>
@@ -2158,13 +2152,13 @@
         <v>133</v>
       </c>
       <c r="AB8" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AC8" s="10" t="s">
-        <v>117</v>
+        <v>99</v>
       </c>
       <c r="AD8" s="9">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AE8" s="10" t="s">
         <v>134</v>
@@ -2176,13 +2170,13 @@
         <v>99</v>
       </c>
       <c r="AH8" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI8" s="10" t="s">
-        <v>129</v>
+        <v>99</v>
       </c>
       <c r="AJ8" s="9">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="AK8" s="10" t="s">
         <v>135</v>
@@ -2220,7 +2214,7 @@
         <v>138</v>
       </c>
       <c r="C9" s="9">
-        <v>6722</v>
+        <v>6777</v>
       </c>
       <c r="D9" s="9">
         <v>0</v>
@@ -2229,7 +2223,7 @@
         <v>97</v>
       </c>
       <c r="F9" s="9">
-        <v>385</v>
+        <v>390</v>
       </c>
       <c r="G9" s="10" t="s">
         <v>139</v>
@@ -2247,7 +2241,7 @@
         <v>97</v>
       </c>
       <c r="L9" s="9">
-        <v>1383</v>
+        <v>1396</v>
       </c>
       <c r="M9" s="10" t="s">
         <v>140</v>
@@ -2268,13 +2262,13 @@
         <v>34</v>
       </c>
       <c r="S9" s="10" t="s">
-        <v>104</v>
+        <v>141</v>
       </c>
       <c r="T9" s="9">
         <v>193</v>
       </c>
       <c r="U9" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="V9" s="9">
         <v>0</v>
@@ -2283,34 +2277,34 @@
         <v>97</v>
       </c>
       <c r="X9" s="9">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="Z9" s="9">
         <v>45</v>
       </c>
       <c r="AA9" s="10" t="s">
-        <v>115</v>
+        <v>144</v>
       </c>
       <c r="AB9" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC9" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="AD9" s="9">
-        <v>2968</v>
+        <v>2993</v>
       </c>
       <c r="AE9" s="10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AF9" s="9">
         <v>239</v>
       </c>
       <c r="AG9" s="10" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="AH9" s="9">
         <v>0</v>
@@ -2319,16 +2313,16 @@
         <v>97</v>
       </c>
       <c r="AJ9" s="9">
-        <v>1161</v>
+        <v>1171</v>
       </c>
       <c r="AK9" s="10" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="AL9" s="9">
         <v>68</v>
       </c>
       <c r="AM9" s="10" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AN9" s="9">
         <v>0</v>
@@ -2346,30 +2340,30 @@
         <v>4</v>
       </c>
       <c r="AS9" s="10" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="C10" s="9">
-        <v>8564</v>
+        <v>8635</v>
       </c>
       <c r="D10" s="9">
         <v>3</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F10" s="9">
-        <v>356</v>
+        <v>363</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="H10" s="9">
         <v>25</v>
@@ -2384,10 +2378,10 @@
         <v>97</v>
       </c>
       <c r="L10" s="9">
-        <v>2260</v>
+        <v>2285</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>150</v>
+        <v>153</v>
       </c>
       <c r="N10" s="9">
         <v>1</v>
@@ -2399,73 +2393,73 @@
         <v>20</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="R10" s="9">
         <v>79</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="T10" s="9">
         <v>185</v>
       </c>
       <c r="U10" s="10" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="V10" s="9">
         <v>18</v>
       </c>
       <c r="W10" s="10" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="X10" s="9">
-        <v>260</v>
+        <v>263</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="Z10" s="9">
         <v>23</v>
       </c>
       <c r="AA10" s="10" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="AB10" s="9">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="AC10" s="10" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AD10" s="9">
-        <v>3725</v>
+        <v>3756</v>
       </c>
       <c r="AE10" s="10" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AF10" s="9">
         <v>29</v>
       </c>
       <c r="AG10" s="10" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AH10" s="9">
         <v>5</v>
       </c>
       <c r="AI10" s="10" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="AJ10" s="9">
-        <v>1342</v>
+        <v>1346</v>
       </c>
       <c r="AK10" s="10" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AL10" s="9">
         <v>119</v>
       </c>
       <c r="AM10" s="10" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AN10" s="9">
         <v>1</v>
@@ -2483,36 +2477,36 @@
         <v>3</v>
       </c>
       <c r="AS10" s="10" t="s">
-        <v>111</v>
+        <v>108</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="C11" s="9">
-        <v>6499</v>
+        <v>6895</v>
       </c>
       <c r="D11" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>164</v>
+        <v>94</v>
       </c>
       <c r="F11" s="9">
-        <v>277</v>
+        <v>302</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="H11" s="9">
         <v>6</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>166</v>
+        <v>102</v>
       </c>
       <c r="J11" s="9">
         <v>0</v>
@@ -2521,10 +2515,10 @@
         <v>97</v>
       </c>
       <c r="L11" s="9">
-        <v>1460</v>
+        <v>1593</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="N11" s="9">
         <v>0</v>
@@ -2536,46 +2530,46 @@
         <v>15</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>151</v>
+        <v>169</v>
       </c>
       <c r="R11" s="9">
         <v>28</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>168</v>
+        <v>136</v>
       </c>
       <c r="T11" s="9">
         <v>381</v>
       </c>
       <c r="U11" s="10" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="V11" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W11" s="10" t="s">
-        <v>164</v>
+        <v>94</v>
       </c>
       <c r="X11" s="9">
-        <v>271</v>
+        <v>281</v>
       </c>
       <c r="Y11" s="10" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="Z11" s="9">
         <v>29</v>
       </c>
       <c r="AA11" s="10" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="AB11" s="9">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AC11" s="10" t="s">
-        <v>172</v>
+        <v>99</v>
       </c>
       <c r="AD11" s="9">
-        <v>2932</v>
+        <v>3114</v>
       </c>
       <c r="AE11" s="10" t="s">
         <v>173</v>
@@ -2593,7 +2587,7 @@
         <v>97</v>
       </c>
       <c r="AJ11" s="9">
-        <v>973</v>
+        <v>1022</v>
       </c>
       <c r="AK11" s="10" t="s">
         <v>175</v>
@@ -2602,7 +2596,7 @@
         <v>39</v>
       </c>
       <c r="AM11" s="10" t="s">
-        <v>176</v>
+        <v>96</v>
       </c>
       <c r="AN11" s="9">
         <v>0</v>
@@ -2620,18 +2614,18 @@
         <v>2</v>
       </c>
       <c r="AS11" s="10" t="s">
-        <v>164</v>
+        <v>108</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
+        <v>176</v>
+      </c>
+      <c r="B12" s="8" t="s">
         <v>177</v>
       </c>
-      <c r="B12" s="8" t="s">
-        <v>178</v>
-      </c>
       <c r="C12" s="9">
-        <v>5904</v>
+        <v>5939</v>
       </c>
       <c r="D12" s="9">
         <v>0</v>
@@ -2643,25 +2637,25 @@
         <v>152</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="H12" s="9">
         <v>135</v>
       </c>
       <c r="I12" s="10" t="s">
+        <v>179</v>
+      </c>
+      <c r="J12" s="9">
+        <v>0</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L12" s="9">
+        <v>868</v>
+      </c>
+      <c r="M12" s="10" t="s">
         <v>180</v>
-      </c>
-      <c r="J12" s="9">
-        <v>0</v>
-      </c>
-      <c r="K12" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="L12" s="9">
-        <v>856</v>
-      </c>
-      <c r="M12" s="10" t="s">
-        <v>181</v>
       </c>
       <c r="N12" s="9">
         <v>0</v>
@@ -2685,7 +2679,7 @@
         <v>135</v>
       </c>
       <c r="U12" s="10" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="V12" s="9">
         <v>0</v>
@@ -2697,49 +2691,49 @@
         <v>147</v>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="Z12" s="9">
         <v>33</v>
       </c>
       <c r="AA12" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="AB12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD12" s="9">
+        <v>2638</v>
+      </c>
+      <c r="AE12" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="AB12" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD12" s="9">
-        <v>2622</v>
-      </c>
-      <c r="AE12" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="AF12" s="9">
         <v>46</v>
       </c>
       <c r="AG12" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="AH12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ12" s="9">
+        <v>995</v>
+      </c>
+      <c r="AK12" s="10" t="s">
         <v>185</v>
-      </c>
-      <c r="AH12" s="9">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ12" s="9">
-        <v>988</v>
-      </c>
-      <c r="AK12" s="10" t="s">
-        <v>186</v>
       </c>
       <c r="AL12" s="9">
         <v>757</v>
       </c>
       <c r="AM12" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AN12" s="9">
         <v>0</v>
@@ -2762,31 +2756,31 @@
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
+        <v>187</v>
+      </c>
+      <c r="B13" s="8" t="s">
         <v>188</v>
       </c>
-      <c r="B13" s="8" t="s">
-        <v>189</v>
-      </c>
       <c r="C13" s="9">
-        <v>3458</v>
+        <v>3463</v>
       </c>
       <c r="D13" s="9">
         <v>1</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>164</v>
+        <v>108</v>
       </c>
       <c r="F13" s="9">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>149</v>
+        <v>189</v>
       </c>
       <c r="H13" s="9">
         <v>2</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="J13" s="9">
         <v>0</v>
@@ -2795,7 +2789,7 @@
         <v>97</v>
       </c>
       <c r="L13" s="9">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="M13" s="10" t="s">
         <v>190</v>
@@ -2804,85 +2798,85 @@
         <v>1</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>164</v>
+        <v>108</v>
       </c>
       <c r="P13" s="9">
         <v>5</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>172</v>
+        <v>191</v>
       </c>
       <c r="R13" s="9">
         <v>20</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>96</v>
+        <v>192</v>
       </c>
       <c r="T13" s="9">
         <v>82</v>
       </c>
       <c r="U13" s="10" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="V13" s="9">
         <v>2</v>
       </c>
       <c r="W13" s="10" t="s">
-        <v>129</v>
+        <v>149</v>
       </c>
       <c r="X13" s="9">
         <v>99</v>
       </c>
       <c r="Y13" s="10" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="Z13" s="9">
         <v>14</v>
       </c>
       <c r="AA13" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AB13" s="9">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="AC13" s="10" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="AD13" s="9">
-        <v>1392</v>
+        <v>1395</v>
       </c>
       <c r="AE13" s="10" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="AF13" s="9">
         <v>12</v>
       </c>
       <c r="AG13" s="10" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="AH13" s="9">
         <v>3</v>
       </c>
       <c r="AI13" s="10" t="s">
-        <v>166</v>
+        <v>102</v>
       </c>
       <c r="AJ13" s="9">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="AK13" s="10" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="AL13" s="9">
         <v>39</v>
       </c>
       <c r="AM13" s="10" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="AN13" s="9">
         <v>1</v>
       </c>
       <c r="AO13" s="10" t="s">
-        <v>164</v>
+        <v>108</v>
       </c>
       <c r="AP13" s="9">
         <v>0</v>
@@ -2899,10 +2893,10 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="C14" s="9">
         <v>2390</v>
@@ -2917,13 +2911,13 @@
         <v>104</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="H14" s="9">
         <v>17</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="J14" s="9">
         <v>0</v>
@@ -2935,7 +2929,7 @@
         <v>560</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="N14" s="9">
         <v>1</v>
@@ -2947,37 +2941,37 @@
         <v>6</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="R14" s="9">
         <v>28</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="T14" s="9">
         <v>60</v>
       </c>
       <c r="U14" s="10" t="s">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="V14" s="9">
         <v>3</v>
       </c>
       <c r="W14" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="X14" s="9">
         <v>55</v>
       </c>
       <c r="Y14" s="10" t="s">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Z14" s="9">
         <v>3</v>
       </c>
       <c r="AA14" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AB14" s="9">
         <v>0</v>
@@ -2989,13 +2983,13 @@
         <v>1099</v>
       </c>
       <c r="AE14" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="AF14" s="9">
         <v>2</v>
       </c>
       <c r="AG14" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AH14" s="9">
         <v>0</v>
@@ -3007,13 +3001,13 @@
         <v>351</v>
       </c>
       <c r="AK14" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AL14" s="9">
         <v>99</v>
       </c>
       <c r="AM14" s="10" t="s">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AN14" s="9">
         <v>0</v>
@@ -3031,36 +3025,36 @@
         <v>2</v>
       </c>
       <c r="AS14" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="C15" s="9">
-        <v>7731</v>
+        <v>7737</v>
       </c>
       <c r="D15" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="F15" s="9">
         <v>255</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="H15" s="9">
         <v>88</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="J15" s="9">
         <v>0</v>
@@ -3069,10 +3063,10 @@
         <v>97</v>
       </c>
       <c r="L15" s="9">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="N15" s="9">
         <v>0</v>
@@ -3084,19 +3078,19 @@
         <v>4</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="R15" s="9">
         <v>79</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="T15" s="9">
         <v>109</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="V15" s="9">
         <v>1</v>
@@ -3105,16 +3099,16 @@
         <v>94</v>
       </c>
       <c r="X15" s="9">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="Z15" s="9">
         <v>10</v>
       </c>
       <c r="AA15" s="10" t="s">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="AB15" s="9">
         <v>0</v>
@@ -3123,16 +3117,16 @@
         <v>97</v>
       </c>
       <c r="AD15" s="9">
-        <v>3143</v>
+        <v>3148</v>
       </c>
       <c r="AE15" s="10" t="s">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AF15" s="9">
         <v>66</v>
       </c>
       <c r="AG15" s="10" t="s">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="AH15" s="9">
         <v>0</v>
@@ -3144,13 +3138,13 @@
         <v>1136</v>
       </c>
       <c r="AK15" s="10" t="s">
-        <v>210</v>
+        <v>224</v>
       </c>
       <c r="AL15" s="9">
         <v>1696</v>
       </c>
       <c r="AM15" s="10" t="s">
-        <v>222</v>
+        <v>225</v>
       </c>
       <c r="AN15" s="9">
         <v>0</v>
@@ -3173,13 +3167,13 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>223</v>
+        <v>226</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>224</v>
+        <v>227</v>
       </c>
       <c r="C16" s="9">
-        <v>2279</v>
+        <v>2290</v>
       </c>
       <c r="D16" s="9">
         <v>0</v>
@@ -3188,16 +3182,16 @@
         <v>97</v>
       </c>
       <c r="F16" s="9">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>225</v>
+        <v>228</v>
       </c>
       <c r="H16" s="9">
         <v>6</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="J16" s="9">
         <v>0</v>
@@ -3206,10 +3200,10 @@
         <v>97</v>
       </c>
       <c r="L16" s="9">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="N16" s="9">
         <v>0</v>
@@ -3227,49 +3221,49 @@
         <v>30</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>228</v>
+        <v>231</v>
       </c>
       <c r="T16" s="9">
         <v>112</v>
       </c>
       <c r="U16" s="10" t="s">
-        <v>225</v>
+        <v>232</v>
       </c>
       <c r="V16" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W16" s="10" t="s">
-        <v>97</v>
+        <v>111</v>
       </c>
       <c r="X16" s="9">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="Y16" s="10" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="Z16" s="9">
         <v>20</v>
       </c>
       <c r="AA16" s="10" t="s">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="AB16" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AC16" s="10" t="s">
-        <v>231</v>
+        <v>209</v>
       </c>
       <c r="AD16" s="9">
-        <v>988</v>
+        <v>995</v>
       </c>
       <c r="AE16" s="10" t="s">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AF16" s="9">
         <v>35</v>
       </c>
       <c r="AG16" s="10" t="s">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AH16" s="9">
         <v>1</v>
@@ -3278,16 +3272,16 @@
         <v>111</v>
       </c>
       <c r="AJ16" s="9">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AK16" s="10" t="s">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="AL16" s="9">
         <v>57</v>
       </c>
       <c r="AM16" s="10" t="s">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="AN16" s="9">
         <v>0</v>
@@ -3305,36 +3299,36 @@
         <v>2</v>
       </c>
       <c r="AS16" s="10" t="s">
-        <v>166</v>
+        <v>102</v>
       </c>
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="C17" s="9">
-        <v>4366</v>
+        <v>4388</v>
       </c>
       <c r="D17" s="9">
         <v>1</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>108</v>
+        <v>240</v>
       </c>
       <c r="F17" s="9">
-        <v>203</v>
+        <v>204</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="H17" s="9">
         <v>26</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>176</v>
+        <v>242</v>
       </c>
       <c r="J17" s="9">
         <v>0</v>
@@ -3343,10 +3337,10 @@
         <v>97</v>
       </c>
       <c r="L17" s="9">
-        <v>1018</v>
+        <v>1027</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="N17" s="9">
         <v>0</v>
@@ -3358,73 +3352,73 @@
         <v>22</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>240</v>
+        <v>141</v>
       </c>
       <c r="R17" s="9">
         <v>29</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>241</v>
+        <v>144</v>
       </c>
       <c r="T17" s="9">
         <v>30</v>
       </c>
       <c r="U17" s="10" t="s">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="V17" s="9">
         <v>9</v>
       </c>
       <c r="W17" s="10" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="X17" s="9">
         <v>75</v>
       </c>
       <c r="Y17" s="10" t="s">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="Z17" s="9">
         <v>2</v>
       </c>
       <c r="AA17" s="10" t="s">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="AB17" s="9">
         <v>4</v>
       </c>
       <c r="AC17" s="10" t="s">
-        <v>166</v>
+        <v>102</v>
       </c>
       <c r="AD17" s="9">
-        <v>2180</v>
+        <v>2191</v>
       </c>
       <c r="AE17" s="10" t="s">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="AF17" s="9">
         <v>42</v>
       </c>
       <c r="AG17" s="10" t="s">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="AH17" s="9">
         <v>3</v>
       </c>
       <c r="AI17" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AJ17" s="9">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="AK17" s="10" t="s">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AL17" s="9">
         <v>220</v>
       </c>
       <c r="AM17" s="10" t="s">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AN17" s="9">
         <v>0</v>
@@ -3447,13 +3441,13 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="C18" s="9">
-        <v>5074</v>
+        <v>5113</v>
       </c>
       <c r="D18" s="9">
         <v>0</v>
@@ -3462,10 +3456,10 @@
         <v>97</v>
       </c>
       <c r="F18" s="9">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>251</v>
+        <v>114</v>
       </c>
       <c r="H18" s="9">
         <v>6</v>
@@ -3480,10 +3474,10 @@
         <v>97</v>
       </c>
       <c r="L18" s="9">
-        <v>1160</v>
+        <v>1173</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>252</v>
+        <v>135</v>
       </c>
       <c r="N18" s="9">
         <v>0</v>
@@ -3492,10 +3486,10 @@
         <v>97</v>
       </c>
       <c r="P18" s="9">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>99</v>
+        <v>123</v>
       </c>
       <c r="R18" s="9">
         <v>21</v>
@@ -3504,16 +3498,16 @@
         <v>136</v>
       </c>
       <c r="T18" s="9">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="U18" s="10" t="s">
         <v>253</v>
       </c>
       <c r="V18" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W18" s="10" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="X18" s="9">
         <v>92</v>
@@ -3522,28 +3516,28 @@
         <v>254</v>
       </c>
       <c r="Z18" s="9">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AA18" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB18" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC18" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD18" s="9">
+        <v>2321</v>
+      </c>
+      <c r="AE18" s="10" t="s">
         <v>255</v>
-      </c>
-      <c r="AB18" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC18" s="10" t="s">
-        <v>108</v>
-      </c>
-      <c r="AD18" s="9">
-        <v>2307</v>
-      </c>
-      <c r="AE18" s="10" t="s">
-        <v>256</v>
       </c>
       <c r="AF18" s="9">
         <v>13</v>
       </c>
       <c r="AG18" s="10" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="AH18" s="9">
         <v>0</v>
@@ -3552,16 +3546,16 @@
         <v>97</v>
       </c>
       <c r="AJ18" s="9">
-        <v>1113</v>
+        <v>1125</v>
       </c>
       <c r="AK18" s="10" t="s">
-        <v>222</v>
+        <v>256</v>
       </c>
       <c r="AL18" s="9">
         <v>44</v>
       </c>
       <c r="AM18" s="10" t="s">
-        <v>130</v>
+        <v>257</v>
       </c>
       <c r="AN18" s="9">
         <v>0</v>
@@ -3584,13 +3578,13 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C19" s="9">
-        <v>6885</v>
+        <v>7333</v>
       </c>
       <c r="D19" s="9">
         <v>0</v>
@@ -3599,16 +3593,16 @@
         <v>97</v>
       </c>
       <c r="F19" s="9">
-        <v>355</v>
+        <v>371</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="H19" s="9">
         <v>18</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>226</v>
+        <v>206</v>
       </c>
       <c r="J19" s="9">
         <v>0</v>
@@ -3617,10 +3611,10 @@
         <v>97</v>
       </c>
       <c r="L19" s="9">
-        <v>1939</v>
+        <v>2074</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="N19" s="9">
         <v>0</v>
@@ -3635,16 +3629,16 @@
         <v>97</v>
       </c>
       <c r="R19" s="9">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="T19" s="9">
         <v>17</v>
       </c>
       <c r="U19" s="10" t="s">
-        <v>204</v>
+        <v>154</v>
       </c>
       <c r="V19" s="9">
         <v>0</v>
@@ -3653,16 +3647,16 @@
         <v>97</v>
       </c>
       <c r="X19" s="9">
-        <v>237</v>
+        <v>247</v>
       </c>
       <c r="Y19" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="Z19" s="9">
         <v>4</v>
       </c>
       <c r="AA19" s="10" t="s">
-        <v>129</v>
+        <v>219</v>
       </c>
       <c r="AB19" s="9">
         <v>0</v>
@@ -3671,16 +3665,16 @@
         <v>97</v>
       </c>
       <c r="AD19" s="9">
-        <v>3169</v>
+        <v>3393</v>
       </c>
       <c r="AE19" s="10" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="AF19" s="9">
         <v>26</v>
       </c>
       <c r="AG19" s="10" t="s">
-        <v>263</v>
+        <v>198</v>
       </c>
       <c r="AH19" s="9">
         <v>0</v>
@@ -3689,13 +3683,13 @@
         <v>97</v>
       </c>
       <c r="AJ19" s="9">
-        <v>954</v>
+        <v>1014</v>
       </c>
       <c r="AK19" s="10" t="s">
         <v>264</v>
       </c>
       <c r="AL19" s="9">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="AM19" s="10" t="s">
         <v>265</v>
@@ -3716,7 +3710,7 @@
         <v>2</v>
       </c>
       <c r="AS19" s="10" t="s">
-        <v>164</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
@@ -3727,7 +3721,7 @@
         <v>267</v>
       </c>
       <c r="C20" s="9">
-        <v>696</v>
+        <v>741</v>
       </c>
       <c r="D20" s="9">
         <v>0</v>
@@ -3736,7 +3730,7 @@
         <v>97</v>
       </c>
       <c r="F20" s="9">
-        <v>48</v>
+        <v>53</v>
       </c>
       <c r="G20" s="10" t="s">
         <v>268</v>
@@ -3754,7 +3748,7 @@
         <v>97</v>
       </c>
       <c r="L20" s="9">
-        <v>70</v>
+        <v>81</v>
       </c>
       <c r="M20" s="10" t="s">
         <v>270</v>
@@ -3781,43 +3775,43 @@
         <v>41</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>272</v>
+        <v>170</v>
       </c>
       <c r="V20" s="9">
         <v>8</v>
       </c>
       <c r="W20" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="X20" s="9">
+        <v>56</v>
+      </c>
+      <c r="Y20" s="10" t="s">
         <v>273</v>
-      </c>
-      <c r="X20" s="9">
-        <v>52</v>
-      </c>
-      <c r="Y20" s="10" t="s">
-        <v>274</v>
       </c>
       <c r="Z20" s="9">
         <v>90</v>
       </c>
       <c r="AA20" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="AB20" s="9">
+        <v>4</v>
+      </c>
+      <c r="AC20" s="10" t="s">
+        <v>271</v>
+      </c>
+      <c r="AD20" s="9">
+        <v>294</v>
+      </c>
+      <c r="AE20" s="10" t="s">
         <v>275</v>
-      </c>
-      <c r="AB20" s="9">
-        <v>3</v>
-      </c>
-      <c r="AC20" s="10" t="s">
-        <v>168</v>
-      </c>
-      <c r="AD20" s="9">
-        <v>273</v>
-      </c>
-      <c r="AE20" s="10" t="s">
-        <v>276</v>
       </c>
       <c r="AF20" s="9">
         <v>12</v>
       </c>
       <c r="AG20" s="10" t="s">
-        <v>243</v>
+        <v>253</v>
       </c>
       <c r="AH20" s="9">
         <v>0</v>
@@ -3826,16 +3820,16 @@
         <v>97</v>
       </c>
       <c r="AJ20" s="9">
-        <v>64</v>
+        <v>67</v>
       </c>
       <c r="AK20" s="10" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="AL20" s="9">
         <v>19</v>
       </c>
       <c r="AM20" s="10" t="s">
-        <v>278</v>
+        <v>178</v>
       </c>
       <c r="AN20" s="9">
         <v>0</v>
@@ -3853,15 +3847,15 @@
         <v>2</v>
       </c>
       <c r="AS20" s="10" t="s">
-        <v>133</v>
+        <v>159</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="C21" s="9">
         <v>1500</v>
@@ -3876,13 +3870,13 @@
         <v>40</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H21" s="9">
         <v>6</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="J21" s="9">
         <v>0</v>
@@ -3894,7 +3888,7 @@
         <v>174</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="N21" s="9">
         <v>0</v>
@@ -3912,49 +3906,49 @@
         <v>9</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>176</v>
+        <v>281</v>
       </c>
       <c r="T21" s="9">
         <v>35</v>
       </c>
       <c r="U21" s="10" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="V21" s="9">
         <v>1</v>
       </c>
       <c r="W21" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="X21" s="9">
         <v>42</v>
       </c>
       <c r="Y21" s="10" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="Z21" s="9">
         <v>39</v>
       </c>
       <c r="AA21" s="10" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="AB21" s="9">
         <v>15</v>
       </c>
       <c r="AC21" s="10" t="s">
-        <v>286</v>
+        <v>148</v>
       </c>
       <c r="AD21" s="9">
         <v>632</v>
       </c>
       <c r="AE21" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AF21" s="9">
         <v>3</v>
       </c>
       <c r="AG21" s="10" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="AH21" s="9">
         <v>0</v>
@@ -3966,13 +3960,13 @@
         <v>120</v>
       </c>
       <c r="AK21" s="10" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="AL21" s="9">
         <v>384</v>
       </c>
       <c r="AM21" s="10" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="AN21" s="9">
         <v>0</v>
@@ -3995,22 +3989,22 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="C22" s="12">
-        <v>68566</v>
+        <v>69705</v>
       </c>
       <c r="D22" s="12">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="E22" s="13" t="s">
         <v>94</v>
       </c>
       <c r="F22" s="12">
-        <v>2962</v>
+        <v>3024</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>95</v>
@@ -4028,7 +4022,7 @@
         <v>97</v>
       </c>
       <c r="L22" s="12">
-        <v>14702</v>
+        <v>15059</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>98</v>
@@ -4040,49 +4034,49 @@
         <v>97</v>
       </c>
       <c r="P22" s="12">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="Q22" s="13" t="s">
         <v>99</v>
       </c>
       <c r="R22" s="12">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="S22" s="13" t="s">
         <v>100</v>
       </c>
       <c r="T22" s="12">
-        <v>1542</v>
+        <v>1545</v>
       </c>
       <c r="U22" s="13" t="s">
         <v>101</v>
       </c>
       <c r="V22" s="12">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="W22" s="13" t="s">
         <v>102</v>
       </c>
       <c r="X22" s="12">
-        <v>1994</v>
+        <v>2024</v>
       </c>
       <c r="Y22" s="13" t="s">
         <v>103</v>
       </c>
       <c r="Z22" s="12">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="AA22" s="13" t="s">
         <v>104</v>
       </c>
       <c r="AB22" s="12">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="AC22" s="13" t="s">
         <v>105</v>
       </c>
       <c r="AD22" s="12">
-        <v>30045</v>
+        <v>30586</v>
       </c>
       <c r="AE22" s="13" t="s">
         <v>106</v>
@@ -4094,19 +4088,19 @@
         <v>107</v>
       </c>
       <c r="AH22" s="12">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AI22" s="13" t="s">
         <v>108</v>
       </c>
       <c r="AJ22" s="12">
-        <v>11011</v>
+        <v>11161</v>
       </c>
       <c r="AK22" s="13" t="s">
         <v>109</v>
       </c>
       <c r="AL22" s="12">
-        <v>4075</v>
+        <v>4077</v>
       </c>
       <c r="AM22" s="13" t="s">
         <v>110</v>

--- a/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
+++ b/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="291">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="296">
   <si>
     <t>DATA RADAR ANOMALI KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 8 Sep 2026, 07.19</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 9 Sep 2026, 08.17</t>
   </si>
   <si>
     <t>Kode</t>
@@ -298,574 +298,589 @@
     <t>0,01</t>
   </si>
   <si>
-    <t>4,34</t>
+    <t>4,35</t>
+  </si>
+  <si>
+    <t>0,56</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>21,72</t>
+  </si>
+  <si>
+    <t>0,11</t>
+  </si>
+  <si>
+    <t>0,61</t>
+  </si>
+  <si>
+    <t>2,19</t>
+  </si>
+  <si>
+    <t>0,09</t>
+  </si>
+  <si>
+    <t>2,9</t>
+  </si>
+  <si>
+    <t>0,5</t>
+  </si>
+  <si>
+    <t>0,32</t>
+  </si>
+  <si>
+    <t>43,92</t>
+  </si>
+  <si>
+    <t>0,88</t>
+  </si>
+  <si>
+    <t>0,02</t>
+  </si>
+  <si>
+    <t>16,03</t>
+  </si>
+  <si>
+    <t>5,76</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>LAMPUNG BARAT</t>
+  </si>
+  <si>
+    <t>4,22</t>
+  </si>
+  <si>
+    <t>0,67</t>
+  </si>
+  <si>
+    <t>28,41</t>
+  </si>
+  <si>
+    <t>0,17</t>
+  </si>
+  <si>
+    <t>0,46</t>
+  </si>
+  <si>
+    <t>4,12</t>
+  </si>
+  <si>
+    <t>0,44</t>
+  </si>
+  <si>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>39,65</t>
+  </si>
+  <si>
+    <t>0,08</t>
+  </si>
+  <si>
+    <t>12,81</t>
+  </si>
+  <si>
+    <t>7,96</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>TANGGAMUS</t>
+  </si>
+  <si>
+    <t>6,64</t>
+  </si>
+  <si>
+    <t>19,85</t>
+  </si>
+  <si>
+    <t>0,87</t>
+  </si>
+  <si>
+    <t>3,46</t>
+  </si>
+  <si>
+    <t>3,35</t>
+  </si>
+  <si>
+    <t>0,29</t>
+  </si>
+  <si>
+    <t>0,12</t>
+  </si>
+  <si>
+    <t>41,83</t>
+  </si>
+  <si>
+    <t>0,06</t>
+  </si>
+  <si>
+    <t>22,91</t>
+  </si>
+  <si>
+    <t>0,4</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>LAMPUNG SELATAN</t>
+  </si>
+  <si>
+    <t>5,74</t>
+  </si>
+  <si>
+    <t>20,74</t>
+  </si>
+  <si>
+    <t>2,82</t>
+  </si>
+  <si>
+    <t>3,24</t>
+  </si>
+  <si>
+    <t>0,66</t>
+  </si>
+  <si>
+    <t>44,09</t>
+  </si>
+  <si>
+    <t>3,49</t>
+  </si>
+  <si>
+    <t>17,34</t>
+  </si>
+  <si>
+    <t>0,99</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>4,21</t>
+  </si>
+  <si>
+    <t>26,48</t>
+  </si>
+  <si>
+    <t>0,23</t>
+  </si>
+  <si>
+    <t>0,91</t>
+  </si>
+  <si>
+    <t>2,14</t>
+  </si>
+  <si>
+    <t>0,21</t>
+  </si>
+  <si>
+    <t>3,04</t>
+  </si>
+  <si>
+    <t>0,27</t>
+  </si>
+  <si>
+    <t>1,28</t>
+  </si>
+  <si>
+    <t>43,5</t>
+  </si>
+  <si>
+    <t>0,34</t>
+  </si>
+  <si>
+    <t>15,58</t>
+  </si>
+  <si>
+    <t>1,38</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
+    <t>4,38</t>
+  </si>
+  <si>
+    <t>23,12</t>
+  </si>
+  <si>
+    <t>5,44</t>
+  </si>
+  <si>
+    <t>4,06</t>
+  </si>
+  <si>
+    <t>0,41</t>
+  </si>
+  <si>
+    <t>45,32</t>
+  </si>
+  <si>
+    <t>1,04</t>
+  </si>
+  <si>
+    <t>14,8</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>2,7</t>
+  </si>
+  <si>
+    <t>2,18</t>
+  </si>
+  <si>
+    <t>15,28</t>
+  </si>
+  <si>
+    <t>0,42</t>
+  </si>
+  <si>
+    <t>2,47</t>
+  </si>
+  <si>
+    <t>0,53</t>
+  </si>
+  <si>
+    <t>44,12</t>
+  </si>
+  <si>
+    <t>0,74</t>
+  </si>
+  <si>
+    <t>17,04</t>
+  </si>
+  <si>
+    <t>12,23</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>4,15</t>
+  </si>
+  <si>
+    <t>20,17</t>
+  </si>
+  <si>
+    <t>0,14</t>
   </si>
   <si>
     <t>0,57</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>21,6</t>
-  </si>
-  <si>
-    <t>0,12</t>
-  </si>
-  <si>
-    <t>0,62</t>
-  </si>
-  <si>
-    <t>2,22</t>
-  </si>
-  <si>
-    <t>0,09</t>
-  </si>
-  <si>
-    <t>2,9</t>
-  </si>
-  <si>
-    <t>0,51</t>
-  </si>
-  <si>
-    <t>0,32</t>
-  </si>
-  <si>
-    <t>43,88</t>
-  </si>
-  <si>
-    <t>0,89</t>
-  </si>
-  <si>
-    <t>0,03</t>
-  </si>
-  <si>
-    <t>16,01</t>
-  </si>
-  <si>
-    <t>5,85</t>
-  </si>
-  <si>
-    <t>0,04</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>LAMPUNG BARAT</t>
-  </si>
-  <si>
-    <t>4,22</t>
-  </si>
-  <si>
-    <t>0,67</t>
-  </si>
-  <si>
-    <t>28,4</t>
-  </si>
-  <si>
-    <t>0,17</t>
-  </si>
-  <si>
-    <t>0,46</t>
-  </si>
-  <si>
-    <t>4,12</t>
-  </si>
-  <si>
-    <t>0,44</t>
-  </si>
-  <si>
-    <t>0,1</t>
-  </si>
-  <si>
-    <t>39,65</t>
-  </si>
-  <si>
-    <t>0,08</t>
-  </si>
-  <si>
-    <t>12,82</t>
-  </si>
-  <si>
-    <t>7,97</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>TANGGAMUS</t>
-  </si>
-  <si>
-    <t>6,62</t>
-  </si>
-  <si>
-    <t>19,74</t>
-  </si>
-  <si>
-    <t>0,87</t>
-  </si>
-  <si>
-    <t>3,48</t>
-  </si>
-  <si>
-    <t>3,31</t>
-  </si>
-  <si>
-    <t>0,29</t>
-  </si>
-  <si>
-    <t>41,87</t>
-  </si>
-  <si>
-    <t>22,94</t>
-  </si>
-  <si>
-    <t>0,41</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>LAMPUNG SELATAN</t>
-  </si>
-  <si>
-    <t>5,75</t>
-  </si>
-  <si>
-    <t>20,6</t>
-  </si>
-  <si>
-    <t>0,5</t>
-  </si>
-  <si>
-    <t>2,85</t>
-  </si>
-  <si>
-    <t>3,26</t>
-  </si>
-  <si>
-    <t>0,66</t>
-  </si>
-  <si>
-    <t>44,16</t>
-  </si>
-  <si>
-    <t>3,53</t>
-  </si>
-  <si>
-    <t>17,28</t>
+    <t>2,35</t>
+  </si>
+  <si>
+    <t>2,89</t>
+  </si>
+  <si>
+    <t>2,09</t>
+  </si>
+  <si>
+    <t>40,32</t>
+  </si>
+  <si>
+    <t>25,13</t>
+  </si>
+  <si>
+    <t>1,12</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG</t>
+  </si>
+  <si>
+    <t>0,71</t>
+  </si>
+  <si>
+    <t>23,4</t>
+  </si>
+  <si>
+    <t>0,25</t>
+  </si>
+  <si>
+    <t>1,17</t>
+  </si>
+  <si>
+    <t>2,51</t>
+  </si>
+  <si>
+    <t>0,13</t>
+  </si>
+  <si>
+    <t>2,3</t>
+  </si>
+  <si>
+    <t>46,01</t>
+  </si>
+  <si>
+    <t>14,71</t>
+  </si>
+  <si>
+    <t>4,14</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>3,29</t>
+  </si>
+  <si>
+    <t>1,14</t>
+  </si>
+  <si>
+    <t>13,47</t>
+  </si>
+  <si>
+    <t>1,02</t>
+  </si>
+  <si>
+    <t>1,45</t>
+  </si>
+  <si>
+    <t>1,29</t>
+  </si>
+  <si>
+    <t>40,68</t>
+  </si>
+  <si>
+    <t>0,85</t>
+  </si>
+  <si>
+    <t>14,7</t>
+  </si>
+  <si>
+    <t>21,91</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>4,8</t>
+  </si>
+  <si>
+    <t>0,26</t>
+  </si>
+  <si>
+    <t>17,07</t>
+  </si>
+  <si>
+    <t>4,03</t>
+  </si>
+  <si>
+    <t>0,86</t>
+  </si>
+  <si>
+    <t>43,76</t>
+  </si>
+  <si>
+    <t>1,5</t>
+  </si>
+  <si>
+    <t>18,83</t>
+  </si>
+  <si>
+    <t>2,45</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
+  </si>
+  <si>
+    <t>4,65</t>
+  </si>
+  <si>
+    <t>0,59</t>
+  </si>
+  <si>
+    <t>0,68</t>
+  </si>
+  <si>
+    <t>1,71</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>49,94</t>
+  </si>
+  <si>
+    <t>0,96</t>
+  </si>
+  <si>
+    <t>0,07</t>
+  </si>
+  <si>
+    <t>11,46</t>
+  </si>
+  <si>
+    <t>5,01</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>4,23</t>
+  </si>
+  <si>
+    <t>23,38</t>
+  </si>
+  <si>
+    <t>0,39</t>
+  </si>
+  <si>
+    <t>1,56</t>
+  </si>
+  <si>
+    <t>1,82</t>
+  </si>
+  <si>
+    <t>0,28</t>
+  </si>
+  <si>
+    <t>45,48</t>
+  </si>
+  <si>
+    <t>0,24</t>
+  </si>
+  <si>
+    <t>21,63</t>
+  </si>
+  <si>
+    <t>0,82</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>5,15</t>
+  </si>
+  <si>
+    <t>28,24</t>
+  </si>
+  <si>
+    <t>0,22</t>
+  </si>
+  <si>
+    <t>3,34</t>
+  </si>
+  <si>
+    <t>46,4</t>
+  </si>
+  <si>
+    <t>13,8</t>
+  </si>
+  <si>
+    <t>1,94</t>
+  </si>
+  <si>
+    <t>1871</t>
+  </si>
+  <si>
+    <t>BANDAR LAMPUNG</t>
+  </si>
+  <si>
+    <t>7,25</t>
+  </si>
+  <si>
+    <t>0,81</t>
+  </si>
+  <si>
+    <t>10,87</t>
+  </si>
+  <si>
+    <t>0,54</t>
+  </si>
+  <si>
+    <t>5,64</t>
+  </si>
+  <si>
+    <t>7,52</t>
+  </si>
+  <si>
+    <t>12,21</t>
+  </si>
+  <si>
+    <t>40</t>
+  </si>
+  <si>
+    <t>1,61</t>
+  </si>
+  <si>
+    <t>8,99</t>
+  </si>
+  <si>
+    <t>2,55</t>
+  </si>
+  <si>
+    <t>1872</t>
+  </si>
+  <si>
+    <t>METRO</t>
+  </si>
+  <si>
+    <t>2,67</t>
+  </si>
+  <si>
+    <t>11,6</t>
+  </si>
+  <si>
+    <t>0,6</t>
+  </si>
+  <si>
+    <t>2,33</t>
+  </si>
+  <si>
+    <t>2,8</t>
+  </si>
+  <si>
+    <t>2,6</t>
   </si>
   <si>
     <t>1</t>
-  </si>
-  <si>
-    <t>0,06</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>4,2</t>
-  </si>
-  <si>
-    <t>26,46</t>
-  </si>
-  <si>
-    <t>0,23</t>
-  </si>
-  <si>
-    <t>0,91</t>
-  </si>
-  <si>
-    <t>2,14</t>
-  </si>
-  <si>
-    <t>0,21</t>
-  </si>
-  <si>
-    <t>3,05</t>
-  </si>
-  <si>
-    <t>0,27</t>
-  </si>
-  <si>
-    <t>1,29</t>
-  </si>
-  <si>
-    <t>43,5</t>
-  </si>
-  <si>
-    <t>0,34</t>
-  </si>
-  <si>
-    <t>15,59</t>
-  </si>
-  <si>
-    <t>1,38</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>4,38</t>
-  </si>
-  <si>
-    <t>23,1</t>
-  </si>
-  <si>
-    <t>0,22</t>
-  </si>
-  <si>
-    <t>5,53</t>
-  </si>
-  <si>
-    <t>4,08</t>
-  </si>
-  <si>
-    <t>0,42</t>
-  </si>
-  <si>
-    <t>45,16</t>
-  </si>
-  <si>
-    <t>1,06</t>
-  </si>
-  <si>
-    <t>14,82</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>2,56</t>
-  </si>
-  <si>
-    <t>2,27</t>
-  </si>
-  <si>
-    <t>14,62</t>
-  </si>
-  <si>
-    <t>2,48</t>
-  </si>
-  <si>
-    <t>0,56</t>
-  </si>
-  <si>
-    <t>44,42</t>
-  </si>
-  <si>
-    <t>0,77</t>
-  </si>
-  <si>
-    <t>16,75</t>
-  </si>
-  <si>
-    <t>12,75</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>4,19</t>
-  </si>
-  <si>
-    <t>20,24</t>
-  </si>
-  <si>
-    <t>0,14</t>
-  </si>
-  <si>
-    <t>0,58</t>
-  </si>
-  <si>
-    <t>2,37</t>
-  </si>
-  <si>
-    <t>2,86</t>
-  </si>
-  <si>
-    <t>0,4</t>
-  </si>
-  <si>
-    <t>2,11</t>
-  </si>
-  <si>
-    <t>40,28</t>
-  </si>
-  <si>
-    <t>0,35</t>
-  </si>
-  <si>
-    <t>25,06</t>
-  </si>
-  <si>
-    <t>1,13</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG</t>
-  </si>
-  <si>
-    <t>4,35</t>
-  </si>
-  <si>
-    <t>0,71</t>
-  </si>
-  <si>
-    <t>23,43</t>
-  </si>
-  <si>
-    <t>0,25</t>
-  </si>
-  <si>
-    <t>1,17</t>
-  </si>
-  <si>
-    <t>2,51</t>
-  </si>
-  <si>
-    <t>0,13</t>
-  </si>
-  <si>
-    <t>2,3</t>
-  </si>
-  <si>
-    <t>45,98</t>
-  </si>
-  <si>
-    <t>14,69</t>
-  </si>
-  <si>
-    <t>4,14</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>3,3</t>
-  </si>
-  <si>
-    <t>1,14</t>
-  </si>
-  <si>
-    <t>13,47</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>1,02</t>
-  </si>
-  <si>
-    <t>1,41</t>
-  </si>
-  <si>
-    <t>40,69</t>
-  </si>
-  <si>
-    <t>0,85</t>
-  </si>
-  <si>
-    <t>14,68</t>
-  </si>
-  <si>
-    <t>21,92</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>4,93</t>
-  </si>
-  <si>
-    <t>0,26</t>
-  </si>
-  <si>
-    <t>16,9</t>
-  </si>
-  <si>
-    <t>1,31</t>
-  </si>
-  <si>
-    <t>4,89</t>
-  </si>
-  <si>
-    <t>4,02</t>
-  </si>
-  <si>
-    <t>43,45</t>
-  </si>
-  <si>
-    <t>1,53</t>
-  </si>
-  <si>
-    <t>19</t>
-  </si>
-  <si>
-    <t>2,49</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>0,02</t>
-  </si>
-  <si>
-    <t>4,65</t>
-  </si>
-  <si>
-    <t>0,59</t>
-  </si>
-  <si>
-    <t>23,4</t>
-  </si>
-  <si>
-    <t>0,68</t>
-  </si>
-  <si>
-    <t>1,71</t>
-  </si>
-  <si>
-    <t>49,93</t>
-  </si>
-  <si>
-    <t>0,96</t>
-  </si>
-  <si>
-    <t>0,07</t>
-  </si>
-  <si>
-    <t>11,46</t>
-  </si>
-  <si>
-    <t>5,01</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>1,62</t>
-  </si>
-  <si>
-    <t>1,8</t>
-  </si>
-  <si>
-    <t>45,39</t>
-  </si>
-  <si>
-    <t>22</t>
-  </si>
-  <si>
-    <t>0,86</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>5,06</t>
-  </si>
-  <si>
-    <t>28,28</t>
-  </si>
-  <si>
-    <t>3,37</t>
-  </si>
-  <si>
-    <t>46,27</t>
-  </si>
-  <si>
-    <t>13,83</t>
-  </si>
-  <si>
-    <t>2,02</t>
-  </si>
-  <si>
-    <t>1871</t>
-  </si>
-  <si>
-    <t>BANDAR LAMPUNG</t>
-  </si>
-  <si>
-    <t>7,15</t>
-  </si>
-  <si>
-    <t>0,81</t>
-  </si>
-  <si>
-    <t>10,93</t>
-  </si>
-  <si>
-    <t>0,54</t>
-  </si>
-  <si>
-    <t>1,08</t>
-  </si>
-  <si>
-    <t>7,56</t>
-  </si>
-  <si>
-    <t>12,15</t>
-  </si>
-  <si>
-    <t>39,68</t>
-  </si>
-  <si>
-    <t>9,04</t>
-  </si>
-  <si>
-    <t>1872</t>
-  </si>
-  <si>
-    <t>METRO</t>
-  </si>
-  <si>
-    <t>2,67</t>
-  </si>
-  <si>
-    <t>11,6</t>
-  </si>
-  <si>
-    <t>0,6</t>
-  </si>
-  <si>
-    <t>2,33</t>
-  </si>
-  <si>
-    <t>2,8</t>
-  </si>
-  <si>
-    <t>2,6</t>
   </si>
   <si>
     <t>42,13</t>
@@ -1803,7 +1818,7 @@
         <v>93</v>
       </c>
       <c r="C6" s="6">
-        <v>69705</v>
+        <v>70811</v>
       </c>
       <c r="D6" s="6">
         <v>6</v>
@@ -1812,7 +1827,7 @@
         <v>94</v>
       </c>
       <c r="F6" s="6">
-        <v>3024</v>
+        <v>3083</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>95</v>
@@ -1830,7 +1845,7 @@
         <v>97</v>
       </c>
       <c r="L6" s="6">
-        <v>15059</v>
+        <v>15380</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>98</v>
@@ -1842,7 +1857,7 @@
         <v>97</v>
       </c>
       <c r="P6" s="6">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="Q6" s="7" t="s">
         <v>99</v>
@@ -1854,37 +1869,37 @@
         <v>100</v>
       </c>
       <c r="T6" s="6">
-        <v>1545</v>
+        <v>1550</v>
       </c>
       <c r="U6" s="7" t="s">
         <v>101</v>
       </c>
       <c r="V6" s="6">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="W6" s="7" t="s">
         <v>102</v>
       </c>
       <c r="X6" s="6">
-        <v>2024</v>
+        <v>2053</v>
       </c>
       <c r="Y6" s="7" t="s">
         <v>103</v>
       </c>
       <c r="Z6" s="6">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AA6" s="7" t="s">
         <v>104</v>
       </c>
       <c r="AB6" s="6">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AC6" s="7" t="s">
         <v>105</v>
       </c>
       <c r="AD6" s="6">
-        <v>30586</v>
+        <v>31097</v>
       </c>
       <c r="AE6" s="7" t="s">
         <v>106</v>
@@ -1896,13 +1911,13 @@
         <v>107</v>
       </c>
       <c r="AH6" s="6">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI6" s="7" t="s">
         <v>108</v>
       </c>
       <c r="AJ6" s="6">
-        <v>11161</v>
+        <v>11348</v>
       </c>
       <c r="AK6" s="7" t="s">
         <v>109</v>
@@ -1940,7 +1955,7 @@
         <v>113</v>
       </c>
       <c r="C7" s="9">
-        <v>4782</v>
+        <v>4784</v>
       </c>
       <c r="D7" s="9">
         <v>0</v>
@@ -1967,7 +1982,7 @@
         <v>97</v>
       </c>
       <c r="L7" s="9">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>116</v>
@@ -2021,7 +2036,7 @@
         <v>121</v>
       </c>
       <c r="AD7" s="9">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="AE7" s="10" t="s">
         <v>122</v>
@@ -2077,7 +2092,7 @@
         <v>127</v>
       </c>
       <c r="C8" s="9">
-        <v>1722</v>
+        <v>1733</v>
       </c>
       <c r="D8" s="9">
         <v>0</v>
@@ -2086,7 +2101,7 @@
         <v>97</v>
       </c>
       <c r="F8" s="9">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G8" s="10" t="s">
         <v>128</v>
@@ -2104,7 +2119,7 @@
         <v>97</v>
       </c>
       <c r="L8" s="9">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="M8" s="10" t="s">
         <v>129</v>
@@ -2140,7 +2155,7 @@
         <v>97</v>
       </c>
       <c r="X8" s="9">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="Y8" s="10" t="s">
         <v>132</v>
@@ -2155,37 +2170,37 @@
         <v>2</v>
       </c>
       <c r="AC8" s="10" t="s">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="AD8" s="9">
-        <v>721</v>
+        <v>725</v>
       </c>
       <c r="AE8" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AF8" s="9">
         <v>2</v>
       </c>
       <c r="AG8" s="10" t="s">
-        <v>99</v>
+        <v>134</v>
       </c>
       <c r="AH8" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI8" s="10" t="s">
-        <v>99</v>
+        <v>136</v>
       </c>
       <c r="AJ8" s="9">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="AK8" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AL8" s="9">
         <v>7</v>
       </c>
       <c r="AM8" s="10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AN8" s="9">
         <v>0</v>
@@ -2203,18 +2218,18 @@
         <v>2</v>
       </c>
       <c r="AS8" s="10" t="s">
-        <v>99</v>
+        <v>134</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C9" s="9">
-        <v>6777</v>
+        <v>6847</v>
       </c>
       <c r="D9" s="9">
         <v>0</v>
@@ -2223,10 +2238,10 @@
         <v>97</v>
       </c>
       <c r="F9" s="9">
-        <v>390</v>
+        <v>393</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H9" s="9">
         <v>22</v>
@@ -2241,10 +2256,10 @@
         <v>97</v>
       </c>
       <c r="L9" s="9">
-        <v>1396</v>
+        <v>1420</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N9" s="9">
         <v>0</v>
@@ -2262,13 +2277,13 @@
         <v>34</v>
       </c>
       <c r="S9" s="10" t="s">
-        <v>141</v>
+        <v>104</v>
       </c>
       <c r="T9" s="9">
         <v>193</v>
       </c>
       <c r="U9" s="10" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="V9" s="9">
         <v>0</v>
@@ -2277,16 +2292,16 @@
         <v>97</v>
       </c>
       <c r="X9" s="9">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="Z9" s="9">
         <v>45</v>
       </c>
       <c r="AA9" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="AB9" s="9">
         <v>1</v>
@@ -2295,16 +2310,16 @@
         <v>94</v>
       </c>
       <c r="AD9" s="9">
-        <v>2993</v>
+        <v>3019</v>
       </c>
       <c r="AE9" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AF9" s="9">
         <v>239</v>
       </c>
       <c r="AG9" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AH9" s="9">
         <v>0</v>
@@ -2313,16 +2328,16 @@
         <v>97</v>
       </c>
       <c r="AJ9" s="9">
-        <v>1171</v>
+        <v>1187</v>
       </c>
       <c r="AK9" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL9" s="9">
         <v>68</v>
       </c>
       <c r="AM9" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AN9" s="9">
         <v>0</v>
@@ -2340,7 +2355,7 @@
         <v>4</v>
       </c>
       <c r="AS9" s="10" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
@@ -2351,19 +2366,19 @@
         <v>151</v>
       </c>
       <c r="C10" s="9">
-        <v>8635</v>
+        <v>8648</v>
       </c>
       <c r="D10" s="9">
         <v>3</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="F10" s="9">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="H10" s="9">
         <v>25</v>
@@ -2378,10 +2393,10 @@
         <v>97</v>
       </c>
       <c r="L10" s="9">
-        <v>2285</v>
+        <v>2290</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="N10" s="9">
         <v>1</v>
@@ -2393,73 +2408,73 @@
         <v>20</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="R10" s="9">
         <v>79</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="T10" s="9">
         <v>185</v>
       </c>
       <c r="U10" s="10" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="V10" s="9">
         <v>18</v>
       </c>
       <c r="W10" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="X10" s="9">
         <v>263</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="Z10" s="9">
         <v>23</v>
       </c>
       <c r="AA10" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="AB10" s="9">
         <v>111</v>
       </c>
       <c r="AC10" s="10" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="AD10" s="9">
-        <v>3756</v>
+        <v>3762</v>
       </c>
       <c r="AE10" s="10" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="AF10" s="9">
         <v>29</v>
       </c>
       <c r="AG10" s="10" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="AH10" s="9">
         <v>5</v>
       </c>
       <c r="AI10" s="10" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="AJ10" s="9">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="AK10" s="10" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="AL10" s="9">
         <v>119</v>
       </c>
       <c r="AM10" s="10" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="AN10" s="9">
         <v>1</v>
@@ -2477,18 +2492,18 @@
         <v>3</v>
       </c>
       <c r="AS10" s="10" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C11" s="9">
-        <v>6895</v>
+        <v>7002</v>
       </c>
       <c r="D11" s="9">
         <v>1</v>
@@ -2497,10 +2512,10 @@
         <v>94</v>
       </c>
       <c r="F11" s="9">
-        <v>302</v>
+        <v>307</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="H11" s="9">
         <v>6</v>
@@ -2515,10 +2530,10 @@
         <v>97</v>
       </c>
       <c r="L11" s="9">
-        <v>1593</v>
+        <v>1619</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="N11" s="9">
         <v>0</v>
@@ -2530,13 +2545,13 @@
         <v>15</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="R11" s="9">
         <v>28</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="T11" s="9">
         <v>381</v>
@@ -2551,7 +2566,7 @@
         <v>94</v>
       </c>
       <c r="X11" s="9">
-        <v>281</v>
+        <v>284</v>
       </c>
       <c r="Y11" s="10" t="s">
         <v>171</v>
@@ -2569,7 +2584,7 @@
         <v>99</v>
       </c>
       <c r="AD11" s="9">
-        <v>3114</v>
+        <v>3173</v>
       </c>
       <c r="AE11" s="10" t="s">
         <v>173</v>
@@ -2587,7 +2602,7 @@
         <v>97</v>
       </c>
       <c r="AJ11" s="9">
-        <v>1022</v>
+        <v>1036</v>
       </c>
       <c r="AK11" s="10" t="s">
         <v>175</v>
@@ -2614,7 +2629,7 @@
         <v>2</v>
       </c>
       <c r="AS11" s="10" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
@@ -2625,7 +2640,7 @@
         <v>177</v>
       </c>
       <c r="C12" s="9">
-        <v>5939</v>
+        <v>6192</v>
       </c>
       <c r="D12" s="9">
         <v>0</v>
@@ -2634,7 +2649,7 @@
         <v>97</v>
       </c>
       <c r="F12" s="9">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="G12" s="10" t="s">
         <v>178</v>
@@ -2652,7 +2667,7 @@
         <v>97</v>
       </c>
       <c r="L12" s="9">
-        <v>868</v>
+        <v>946</v>
       </c>
       <c r="M12" s="10" t="s">
         <v>180</v>
@@ -2673,7 +2688,7 @@
         <v>26</v>
       </c>
       <c r="S12" s="10" t="s">
-        <v>120</v>
+        <v>181</v>
       </c>
       <c r="T12" s="9">
         <v>135</v>
@@ -2688,16 +2703,16 @@
         <v>97</v>
       </c>
       <c r="X12" s="9">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="Z12" s="9">
         <v>33</v>
       </c>
       <c r="AA12" s="10" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="AB12" s="9">
         <v>0</v>
@@ -2706,16 +2721,16 @@
         <v>97</v>
       </c>
       <c r="AD12" s="9">
-        <v>2638</v>
+        <v>2732</v>
       </c>
       <c r="AE12" s="10" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="AF12" s="9">
         <v>46</v>
       </c>
       <c r="AG12" s="10" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="AH12" s="9">
         <v>0</v>
@@ -2724,16 +2739,16 @@
         <v>97</v>
       </c>
       <c r="AJ12" s="9">
-        <v>995</v>
+        <v>1055</v>
       </c>
       <c r="AK12" s="10" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="AL12" s="9">
         <v>757</v>
       </c>
       <c r="AM12" s="10" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AN12" s="9">
         <v>0</v>
@@ -2756,31 +2771,31 @@
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C13" s="9">
-        <v>3463</v>
+        <v>3490</v>
       </c>
       <c r="D13" s="9">
         <v>1</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="F13" s="9">
         <v>145</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="H13" s="9">
         <v>2</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>149</v>
+        <v>136</v>
       </c>
       <c r="J13" s="9">
         <v>0</v>
@@ -2789,52 +2804,52 @@
         <v>97</v>
       </c>
       <c r="L13" s="9">
-        <v>701</v>
+        <v>704</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="N13" s="9">
         <v>1</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="P13" s="9">
         <v>5</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="R13" s="9">
         <v>20</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="T13" s="9">
         <v>82</v>
       </c>
       <c r="U13" s="10" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="V13" s="9">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="W13" s="10" t="s">
-        <v>149</v>
+        <v>102</v>
       </c>
       <c r="X13" s="9">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="Y13" s="10" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="Z13" s="9">
         <v>14</v>
       </c>
       <c r="AA13" s="10" t="s">
-        <v>195</v>
+        <v>138</v>
       </c>
       <c r="AB13" s="9">
         <v>73</v>
@@ -2843,7 +2858,7 @@
         <v>196</v>
       </c>
       <c r="AD13" s="9">
-        <v>1395</v>
+        <v>1407</v>
       </c>
       <c r="AE13" s="10" t="s">
         <v>197</v>
@@ -2852,7 +2867,7 @@
         <v>12</v>
       </c>
       <c r="AG13" s="10" t="s">
-        <v>198</v>
+        <v>163</v>
       </c>
       <c r="AH13" s="9">
         <v>3</v>
@@ -2861,22 +2876,22 @@
         <v>102</v>
       </c>
       <c r="AJ13" s="9">
-        <v>868</v>
+        <v>877</v>
       </c>
       <c r="AK13" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AL13" s="9">
         <v>39</v>
       </c>
       <c r="AM13" s="10" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
       <c r="AN13" s="9">
         <v>1</v>
       </c>
       <c r="AO13" s="10" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
       <c r="AP13" s="9">
         <v>0</v>
@@ -2893,13 +2908,13 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>202</v>
-      </c>
       <c r="C14" s="9">
-        <v>2390</v>
+        <v>2393</v>
       </c>
       <c r="D14" s="9">
         <v>0</v>
@@ -2911,13 +2926,13 @@
         <v>104</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>203</v>
+        <v>95</v>
       </c>
       <c r="H14" s="9">
         <v>17</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="J14" s="9">
         <v>0</v>
@@ -2929,7 +2944,7 @@
         <v>560</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="N14" s="9">
         <v>1</v>
@@ -2941,49 +2956,49 @@
         <v>6</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="R14" s="9">
         <v>28</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="T14" s="9">
         <v>60</v>
       </c>
       <c r="U14" s="10" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="V14" s="9">
         <v>3</v>
       </c>
       <c r="W14" s="10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="X14" s="9">
         <v>55</v>
       </c>
       <c r="Y14" s="10" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="Z14" s="9">
         <v>3</v>
       </c>
       <c r="AA14" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="AB14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD14" s="9">
+        <v>1101</v>
+      </c>
+      <c r="AE14" s="10" t="s">
         <v>209</v>
-      </c>
-      <c r="AB14" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD14" s="9">
-        <v>1099</v>
-      </c>
-      <c r="AE14" s="10" t="s">
-        <v>211</v>
       </c>
       <c r="AF14" s="9">
         <v>2</v>
@@ -2998,16 +3013,16 @@
         <v>97</v>
       </c>
       <c r="AJ14" s="9">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="AK14" s="10" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="AL14" s="9">
         <v>99</v>
       </c>
       <c r="AM14" s="10" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="AN14" s="9">
         <v>0</v>
@@ -3030,13 +3045,13 @@
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="C15" s="9">
-        <v>7737</v>
+        <v>7741</v>
       </c>
       <c r="D15" s="9">
         <v>0</v>
@@ -3048,13 +3063,13 @@
         <v>255</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="H15" s="9">
         <v>88</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="J15" s="9">
         <v>0</v>
@@ -3063,10 +3078,10 @@
         <v>97</v>
       </c>
       <c r="L15" s="9">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="N15" s="9">
         <v>0</v>
@@ -3075,22 +3090,22 @@
         <v>97</v>
       </c>
       <c r="P15" s="9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>219</v>
+        <v>94</v>
       </c>
       <c r="R15" s="9">
         <v>79</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="T15" s="9">
-        <v>109</v>
+        <v>112</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="V15" s="9">
         <v>1</v>
@@ -3102,13 +3117,13 @@
         <v>100</v>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>160</v>
+        <v>219</v>
       </c>
       <c r="Z15" s="9">
         <v>10</v>
       </c>
       <c r="AA15" s="10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AB15" s="9">
         <v>0</v>
@@ -3117,16 +3132,16 @@
         <v>97</v>
       </c>
       <c r="AD15" s="9">
-        <v>3148</v>
+        <v>3149</v>
       </c>
       <c r="AE15" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AF15" s="9">
         <v>66</v>
       </c>
       <c r="AG15" s="10" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AH15" s="9">
         <v>0</v>
@@ -3135,16 +3150,16 @@
         <v>97</v>
       </c>
       <c r="AJ15" s="9">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="AK15" s="10" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="AL15" s="9">
         <v>1696</v>
       </c>
       <c r="AM15" s="10" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AN15" s="9">
         <v>0</v>
@@ -3167,31 +3182,31 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="B16" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="C16" s="9">
+        <v>2331</v>
+      </c>
+      <c r="D16" s="9">
+        <v>0</v>
+      </c>
+      <c r="E16" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F16" s="9">
+        <v>112</v>
+      </c>
+      <c r="G16" s="10" t="s">
         <v>226</v>
-      </c>
-      <c r="B16" s="8" t="s">
-        <v>227</v>
-      </c>
-      <c r="C16" s="9">
-        <v>2290</v>
-      </c>
-      <c r="D16" s="9">
-        <v>0</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="F16" s="9">
-        <v>113</v>
-      </c>
-      <c r="G16" s="10" t="s">
-        <v>228</v>
       </c>
       <c r="H16" s="9">
         <v>6</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="J16" s="9">
         <v>0</v>
@@ -3200,10 +3215,10 @@
         <v>97</v>
       </c>
       <c r="L16" s="9">
-        <v>387</v>
+        <v>398</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="N16" s="9">
         <v>0</v>
@@ -3221,13 +3236,13 @@
         <v>30</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>231</v>
+        <v>219</v>
       </c>
       <c r="T16" s="9">
         <v>112</v>
       </c>
       <c r="U16" s="10" t="s">
-        <v>232</v>
+        <v>226</v>
       </c>
       <c r="V16" s="9">
         <v>1</v>
@@ -3236,34 +3251,34 @@
         <v>111</v>
       </c>
       <c r="X16" s="9">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="Y16" s="10" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
       <c r="Z16" s="9">
         <v>20</v>
       </c>
       <c r="AA16" s="10" t="s">
-        <v>130</v>
+        <v>230</v>
       </c>
       <c r="AB16" s="9">
         <v>3</v>
       </c>
       <c r="AC16" s="10" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="AD16" s="9">
-        <v>995</v>
+        <v>1020</v>
       </c>
       <c r="AE16" s="10" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="AF16" s="9">
         <v>35</v>
       </c>
       <c r="AG16" s="10" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="AH16" s="9">
         <v>1</v>
@@ -3272,16 +3287,16 @@
         <v>111</v>
       </c>
       <c r="AJ16" s="9">
-        <v>435</v>
+        <v>439</v>
       </c>
       <c r="AK16" s="10" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="AL16" s="9">
         <v>57</v>
       </c>
       <c r="AM16" s="10" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="AN16" s="9">
         <v>0</v>
@@ -3304,31 +3319,31 @@
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="C17" s="9">
-        <v>4388</v>
+        <v>4389</v>
       </c>
       <c r="D17" s="9">
         <v>1</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>240</v>
+        <v>108</v>
       </c>
       <c r="F17" s="9">
         <v>204</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>241</v>
+        <v>237</v>
       </c>
       <c r="H17" s="9">
         <v>26</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>242</v>
+        <v>238</v>
       </c>
       <c r="J17" s="9">
         <v>0</v>
@@ -3340,7 +3355,7 @@
         <v>1027</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>243</v>
+        <v>203</v>
       </c>
       <c r="N17" s="9">
         <v>0</v>
@@ -3352,37 +3367,37 @@
         <v>22</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>141</v>
+        <v>104</v>
       </c>
       <c r="R17" s="9">
         <v>29</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="T17" s="9">
         <v>30</v>
       </c>
       <c r="U17" s="10" t="s">
-        <v>244</v>
+        <v>239</v>
       </c>
       <c r="V17" s="9">
         <v>9</v>
       </c>
       <c r="W17" s="10" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="X17" s="9">
         <v>75</v>
       </c>
       <c r="Y17" s="10" t="s">
-        <v>245</v>
+        <v>240</v>
       </c>
       <c r="Z17" s="9">
         <v>2</v>
       </c>
       <c r="AA17" s="10" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="AB17" s="9">
         <v>4</v>
@@ -3391,34 +3406,34 @@
         <v>102</v>
       </c>
       <c r="AD17" s="9">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="AE17" s="10" t="s">
-        <v>246</v>
+        <v>242</v>
       </c>
       <c r="AF17" s="9">
         <v>42</v>
       </c>
       <c r="AG17" s="10" t="s">
-        <v>247</v>
+        <v>243</v>
       </c>
       <c r="AH17" s="9">
         <v>3</v>
       </c>
       <c r="AI17" s="10" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="AJ17" s="9">
         <v>503</v>
       </c>
       <c r="AK17" s="10" t="s">
-        <v>249</v>
+        <v>245</v>
       </c>
       <c r="AL17" s="9">
         <v>220</v>
       </c>
       <c r="AM17" s="10" t="s">
-        <v>250</v>
+        <v>246</v>
       </c>
       <c r="AN17" s="9">
         <v>0</v>
@@ -3441,13 +3456,13 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>251</v>
+        <v>247</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>252</v>
+        <v>248</v>
       </c>
       <c r="C18" s="9">
-        <v>5113</v>
+        <v>5372</v>
       </c>
       <c r="D18" s="9">
         <v>0</v>
@@ -3456,10 +3471,10 @@
         <v>97</v>
       </c>
       <c r="F18" s="9">
-        <v>216</v>
+        <v>227</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>114</v>
+        <v>249</v>
       </c>
       <c r="H18" s="9">
         <v>6</v>
@@ -3474,10 +3489,10 @@
         <v>97</v>
       </c>
       <c r="L18" s="9">
-        <v>1173</v>
+        <v>1256</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>135</v>
+        <v>250</v>
       </c>
       <c r="N18" s="9">
         <v>0</v>
@@ -3486,40 +3501,40 @@
         <v>97</v>
       </c>
       <c r="P18" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>123</v>
+        <v>136</v>
       </c>
       <c r="R18" s="9">
         <v>21</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>136</v>
+        <v>251</v>
       </c>
       <c r="T18" s="9">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="U18" s="10" t="s">
+        <v>252</v>
+      </c>
+      <c r="V18" s="9">
+        <v>0</v>
+      </c>
+      <c r="W18" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="X18" s="9">
+        <v>98</v>
+      </c>
+      <c r="Y18" s="10" t="s">
         <v>253</v>
-      </c>
-      <c r="V18" s="9">
-        <v>0</v>
-      </c>
-      <c r="W18" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="X18" s="9">
-        <v>92</v>
-      </c>
-      <c r="Y18" s="10" t="s">
-        <v>254</v>
       </c>
       <c r="Z18" s="9">
         <v>15</v>
       </c>
       <c r="AA18" s="10" t="s">
-        <v>133</v>
+        <v>254</v>
       </c>
       <c r="AB18" s="9">
         <v>0</v>
@@ -3528,7 +3543,7 @@
         <v>97</v>
       </c>
       <c r="AD18" s="9">
-        <v>2321</v>
+        <v>2443</v>
       </c>
       <c r="AE18" s="10" t="s">
         <v>255</v>
@@ -3537,7 +3552,7 @@
         <v>13</v>
       </c>
       <c r="AG18" s="10" t="s">
-        <v>206</v>
+        <v>256</v>
       </c>
       <c r="AH18" s="9">
         <v>0</v>
@@ -3546,16 +3561,16 @@
         <v>97</v>
       </c>
       <c r="AJ18" s="9">
-        <v>1125</v>
+        <v>1162</v>
       </c>
       <c r="AK18" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="AL18" s="9">
         <v>44</v>
       </c>
       <c r="AM18" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="AN18" s="9">
         <v>0</v>
@@ -3578,13 +3593,13 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="C19" s="9">
-        <v>7333</v>
+        <v>7644</v>
       </c>
       <c r="D19" s="9">
         <v>0</v>
@@ -3593,16 +3608,16 @@
         <v>97</v>
       </c>
       <c r="F19" s="9">
-        <v>371</v>
+        <v>394</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="H19" s="9">
         <v>18</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>206</v>
+        <v>256</v>
       </c>
       <c r="J19" s="9">
         <v>0</v>
@@ -3611,10 +3626,10 @@
         <v>97</v>
       </c>
       <c r="L19" s="9">
-        <v>2074</v>
+        <v>2159</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="N19" s="9">
         <v>0</v>
@@ -3632,13 +3647,13 @@
         <v>19</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>229</v>
+        <v>204</v>
       </c>
       <c r="T19" s="9">
         <v>17</v>
       </c>
       <c r="U19" s="10" t="s">
-        <v>154</v>
+        <v>263</v>
       </c>
       <c r="V19" s="9">
         <v>0</v>
@@ -3647,16 +3662,16 @@
         <v>97</v>
       </c>
       <c r="X19" s="9">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="Y19" s="10" t="s">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="Z19" s="9">
         <v>4</v>
       </c>
       <c r="AA19" s="10" t="s">
-        <v>219</v>
+        <v>241</v>
       </c>
       <c r="AB19" s="9">
         <v>0</v>
@@ -3665,16 +3680,16 @@
         <v>97</v>
       </c>
       <c r="AD19" s="9">
-        <v>3393</v>
+        <v>3547</v>
       </c>
       <c r="AE19" s="10" t="s">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AF19" s="9">
         <v>26</v>
       </c>
       <c r="AG19" s="10" t="s">
-        <v>198</v>
+        <v>163</v>
       </c>
       <c r="AH19" s="9">
         <v>0</v>
@@ -3683,16 +3698,16 @@
         <v>97</v>
       </c>
       <c r="AJ19" s="9">
-        <v>1014</v>
+        <v>1055</v>
       </c>
       <c r="AK19" s="10" t="s">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AL19" s="9">
         <v>148</v>
       </c>
       <c r="AM19" s="10" t="s">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AN19" s="9">
         <v>0</v>
@@ -3710,18 +3725,18 @@
         <v>2</v>
       </c>
       <c r="AS19" s="10" t="s">
-        <v>108</v>
+        <v>152</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="C20" s="9">
-        <v>741</v>
+        <v>745</v>
       </c>
       <c r="D20" s="9">
         <v>0</v>
@@ -3730,16 +3745,16 @@
         <v>97</v>
       </c>
       <c r="F20" s="9">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="H20" s="9">
         <v>6</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="J20" s="9">
         <v>0</v>
@@ -3751,7 +3766,7 @@
         <v>81</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="N20" s="9">
         <v>0</v>
@@ -3760,58 +3775,58 @@
         <v>97</v>
       </c>
       <c r="P20" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>271</v>
+        <v>138</v>
       </c>
       <c r="R20" s="9">
         <v>4</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="T20" s="9">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>170</v>
+        <v>274</v>
       </c>
       <c r="V20" s="9">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="W20" s="10" t="s">
-        <v>272</v>
+        <v>115</v>
       </c>
       <c r="X20" s="9">
         <v>56</v>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="Z20" s="9">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="AA20" s="10" t="s">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="AB20" s="9">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AC20" s="10" t="s">
-        <v>271</v>
+        <v>115</v>
       </c>
       <c r="AD20" s="9">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="AE20" s="10" t="s">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="AF20" s="9">
         <v>12</v>
       </c>
       <c r="AG20" s="10" t="s">
-        <v>253</v>
+        <v>278</v>
       </c>
       <c r="AH20" s="9">
         <v>0</v>
@@ -3823,13 +3838,13 @@
         <v>67</v>
       </c>
       <c r="AK20" s="10" t="s">
-        <v>276</v>
+        <v>279</v>
       </c>
       <c r="AL20" s="9">
         <v>19</v>
       </c>
       <c r="AM20" s="10" t="s">
-        <v>178</v>
+        <v>280</v>
       </c>
       <c r="AN20" s="9">
         <v>0</v>
@@ -3847,15 +3862,15 @@
         <v>2</v>
       </c>
       <c r="AS20" s="10" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="C21" s="9">
         <v>1500</v>
@@ -3870,13 +3885,13 @@
         <v>40</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="H21" s="9">
         <v>6</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>195</v>
+        <v>138</v>
       </c>
       <c r="J21" s="9">
         <v>0</v>
@@ -3888,7 +3903,7 @@
         <v>174</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="N21" s="9">
         <v>0</v>
@@ -3906,49 +3921,49 @@
         <v>9</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="T21" s="9">
         <v>35</v>
       </c>
       <c r="U21" s="10" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="V21" s="9">
         <v>1</v>
       </c>
       <c r="W21" s="10" t="s">
-        <v>248</v>
+        <v>244</v>
       </c>
       <c r="X21" s="9">
         <v>42</v>
       </c>
       <c r="Y21" s="10" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="Z21" s="9">
         <v>39</v>
       </c>
       <c r="AA21" s="10" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="AB21" s="9">
         <v>15</v>
       </c>
       <c r="AC21" s="10" t="s">
-        <v>148</v>
+        <v>289</v>
       </c>
       <c r="AD21" s="9">
         <v>632</v>
       </c>
       <c r="AE21" s="10" t="s">
-        <v>285</v>
+        <v>290</v>
       </c>
       <c r="AF21" s="9">
         <v>3</v>
       </c>
       <c r="AG21" s="10" t="s">
-        <v>286</v>
+        <v>291</v>
       </c>
       <c r="AH21" s="9">
         <v>0</v>
@@ -3960,13 +3975,13 @@
         <v>120</v>
       </c>
       <c r="AK21" s="10" t="s">
-        <v>287</v>
+        <v>292</v>
       </c>
       <c r="AL21" s="9">
         <v>384</v>
       </c>
       <c r="AM21" s="10" t="s">
-        <v>288</v>
+        <v>293</v>
       </c>
       <c r="AN21" s="9">
         <v>0</v>
@@ -3989,13 +4004,13 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>289</v>
+        <v>294</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>290</v>
+        <v>295</v>
       </c>
       <c r="C22" s="12">
-        <v>69705</v>
+        <v>70811</v>
       </c>
       <c r="D22" s="12">
         <v>6</v>
@@ -4004,7 +4019,7 @@
         <v>94</v>
       </c>
       <c r="F22" s="12">
-        <v>3024</v>
+        <v>3083</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>95</v>
@@ -4022,7 +4037,7 @@
         <v>97</v>
       </c>
       <c r="L22" s="12">
-        <v>15059</v>
+        <v>15380</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>98</v>
@@ -4034,7 +4049,7 @@
         <v>97</v>
       </c>
       <c r="P22" s="12">
-        <v>81</v>
+        <v>76</v>
       </c>
       <c r="Q22" s="13" t="s">
         <v>99</v>
@@ -4046,37 +4061,37 @@
         <v>100</v>
       </c>
       <c r="T22" s="12">
-        <v>1545</v>
+        <v>1550</v>
       </c>
       <c r="U22" s="13" t="s">
         <v>101</v>
       </c>
       <c r="V22" s="12">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="W22" s="13" t="s">
         <v>102</v>
       </c>
       <c r="X22" s="12">
-        <v>2024</v>
+        <v>2053</v>
       </c>
       <c r="Y22" s="13" t="s">
         <v>103</v>
       </c>
       <c r="Z22" s="12">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AA22" s="13" t="s">
         <v>104</v>
       </c>
       <c r="AB22" s="12">
-        <v>226</v>
+        <v>227</v>
       </c>
       <c r="AC22" s="13" t="s">
         <v>105</v>
       </c>
       <c r="AD22" s="12">
-        <v>30586</v>
+        <v>31097</v>
       </c>
       <c r="AE22" s="13" t="s">
         <v>106</v>
@@ -4088,13 +4103,13 @@
         <v>107</v>
       </c>
       <c r="AH22" s="12">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI22" s="13" t="s">
         <v>108</v>
       </c>
       <c r="AJ22" s="12">
-        <v>11161</v>
+        <v>11348</v>
       </c>
       <c r="AK22" s="13" t="s">
         <v>109</v>

--- a/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
+++ b/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="292">
   <si>
     <t>DATA RADAR ANOMALI KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 9 Sep 2026, 08.17</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 10 Sep 2026, 08.08</t>
   </si>
   <si>
     <t>Kode</t>
@@ -298,448 +298,451 @@
     <t>0,01</t>
   </si>
   <si>
-    <t>4,35</t>
-  </si>
-  <si>
-    <t>0,56</t>
+    <t>4,37</t>
+  </si>
+  <si>
+    <t>0,54</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>21,72</t>
+    <t>22,07</t>
+  </si>
+  <si>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>0,59</t>
+  </si>
+  <si>
+    <t>2,13</t>
+  </si>
+  <si>
+    <t>0,08</t>
+  </si>
+  <si>
+    <t>2,86</t>
+  </si>
+  <si>
+    <t>0,49</t>
+  </si>
+  <si>
+    <t>0,31</t>
+  </si>
+  <si>
+    <t>43,88</t>
+  </si>
+  <si>
+    <t>0,85</t>
+  </si>
+  <si>
+    <t>0,02</t>
+  </si>
+  <si>
+    <t>16,03</t>
+  </si>
+  <si>
+    <t>5,61</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>LAMPUNG BARAT</t>
+  </si>
+  <si>
+    <t>4,21</t>
+  </si>
+  <si>
+    <t>0,67</t>
+  </si>
+  <si>
+    <t>28,43</t>
+  </si>
+  <si>
+    <t>0,17</t>
+  </si>
+  <si>
+    <t>0,46</t>
+  </si>
+  <si>
+    <t>4,13</t>
+  </si>
+  <si>
+    <t>0,44</t>
+  </si>
+  <si>
+    <t>39,67</t>
+  </si>
+  <si>
+    <t>12,81</t>
+  </si>
+  <si>
+    <t>7,95</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>TANGGAMUS</t>
+  </si>
+  <si>
+    <t>6,67</t>
+  </si>
+  <si>
+    <t>19,78</t>
+  </si>
+  <si>
+    <t>0,86</t>
+  </si>
+  <si>
+    <t>3,45</t>
+  </si>
+  <si>
+    <t>3,34</t>
+  </si>
+  <si>
+    <t>0,29</t>
+  </si>
+  <si>
+    <t>0,12</t>
+  </si>
+  <si>
+    <t>41,81</t>
+  </si>
+  <si>
+    <t>0,06</t>
+  </si>
+  <si>
+    <t>23</t>
+  </si>
+  <si>
+    <t>0,4</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>LAMPUNG SELATAN</t>
+  </si>
+  <si>
+    <t>5,75</t>
+  </si>
+  <si>
+    <t>20,99</t>
+  </si>
+  <si>
+    <t>2,76</t>
+  </si>
+  <si>
+    <t>3,23</t>
+  </si>
+  <si>
+    <t>0,64</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>44,11</t>
+  </si>
+  <si>
+    <t>3,42</t>
+  </si>
+  <si>
+    <t>17,24</t>
+  </si>
+  <si>
+    <t>0,97</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>26,49</t>
+  </si>
+  <si>
+    <t>0,23</t>
+  </si>
+  <si>
+    <t>0,91</t>
+  </si>
+  <si>
+    <t>2,14</t>
+  </si>
+  <si>
+    <t>0,21</t>
+  </si>
+  <si>
+    <t>3,04</t>
+  </si>
+  <si>
+    <t>0,27</t>
+  </si>
+  <si>
+    <t>1,26</t>
+  </si>
+  <si>
+    <t>43,51</t>
+  </si>
+  <si>
+    <t>0,34</t>
+  </si>
+  <si>
+    <t>15,58</t>
+  </si>
+  <si>
+    <t>1,38</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
+    <t>4,39</t>
+  </si>
+  <si>
+    <t>23,6</t>
+  </si>
+  <si>
+    <t>0,2</t>
+  </si>
+  <si>
+    <t>0,39</t>
+  </si>
+  <si>
+    <t>5,13</t>
+  </si>
+  <si>
+    <t>3,89</t>
+  </si>
+  <si>
+    <t>0,15</t>
+  </si>
+  <si>
+    <t>45,47</t>
+  </si>
+  <si>
+    <t>0,98</t>
+  </si>
+  <si>
+    <t>14,75</t>
+  </si>
+  <si>
+    <t>0,52</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>2,79</t>
+  </si>
+  <si>
+    <t>2,11</t>
+  </si>
+  <si>
+    <t>16,54</t>
+  </si>
+  <si>
+    <t>0,41</t>
+  </si>
+  <si>
+    <t>2,42</t>
+  </si>
+  <si>
+    <t>43,59</t>
+  </si>
+  <si>
+    <t>0,72</t>
+  </si>
+  <si>
+    <t>16,87</t>
+  </si>
+  <si>
+    <t>11,82</t>
   </si>
   <si>
     <t>0,11</t>
   </si>
   <si>
-    <t>0,61</t>
-  </si>
-  <si>
-    <t>2,19</t>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>20,2</t>
+  </si>
+  <si>
+    <t>0,14</t>
+  </si>
+  <si>
+    <t>0,57</t>
+  </si>
+  <si>
+    <t>2,35</t>
+  </si>
+  <si>
+    <t>2,92</t>
+  </si>
+  <si>
+    <t>1,97</t>
+  </si>
+  <si>
+    <t>40,37</t>
+  </si>
+  <si>
+    <t>25,18</t>
+  </si>
+  <si>
+    <t>1,12</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG</t>
+  </si>
+  <si>
+    <t>4,34</t>
+  </si>
+  <si>
+    <t>0,71</t>
+  </si>
+  <si>
+    <t>23,46</t>
+  </si>
+  <si>
+    <t>0,25</t>
+  </si>
+  <si>
+    <t>1,17</t>
+  </si>
+  <si>
+    <t>2,5</t>
+  </si>
+  <si>
+    <t>0,13</t>
+  </si>
+  <si>
+    <t>2,3</t>
+  </si>
+  <si>
+    <t>45,99</t>
+  </si>
+  <si>
+    <t>14,69</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>3,29</t>
+  </si>
+  <si>
+    <t>1,14</t>
+  </si>
+  <si>
+    <t>13,47</t>
+  </si>
+  <si>
+    <t>1,02</t>
+  </si>
+  <si>
+    <t>1,45</t>
+  </si>
+  <si>
+    <t>1,29</t>
+  </si>
+  <si>
+    <t>40,69</t>
+  </si>
+  <si>
+    <t>14,7</t>
+  </si>
+  <si>
+    <t>21,9</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>4,73</t>
+  </si>
+  <si>
+    <t>17,32</t>
+  </si>
+  <si>
+    <t>1,27</t>
+  </si>
+  <si>
+    <t>4,01</t>
+  </si>
+  <si>
+    <t>0,84</t>
+  </si>
+  <si>
+    <t>43,77</t>
+  </si>
+  <si>
+    <t>1,48</t>
+  </si>
+  <si>
+    <t>18,88</t>
+  </si>
+  <si>
+    <t>2,41</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
+  </si>
+  <si>
+    <t>4,64</t>
+  </si>
+  <si>
+    <t>23,41</t>
+  </si>
+  <si>
+    <t>0,5</t>
+  </si>
+  <si>
+    <t>0,66</t>
+  </si>
+  <si>
+    <t>0,68</t>
+  </si>
+  <si>
+    <t>1,71</t>
+  </si>
+  <si>
+    <t>0,05</t>
   </si>
   <si>
     <t>0,09</t>
   </si>
   <si>
-    <t>2,9</t>
-  </si>
-  <si>
-    <t>0,5</t>
-  </si>
-  <si>
-    <t>0,32</t>
-  </si>
-  <si>
-    <t>43,92</t>
-  </si>
-  <si>
-    <t>0,88</t>
-  </si>
-  <si>
-    <t>0,02</t>
-  </si>
-  <si>
-    <t>16,03</t>
-  </si>
-  <si>
-    <t>5,76</t>
-  </si>
-  <si>
-    <t>0,04</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>LAMPUNG BARAT</t>
-  </si>
-  <si>
-    <t>4,22</t>
-  </si>
-  <si>
-    <t>0,67</t>
-  </si>
-  <si>
-    <t>28,41</t>
-  </si>
-  <si>
-    <t>0,17</t>
-  </si>
-  <si>
-    <t>0,46</t>
-  </si>
-  <si>
-    <t>4,12</t>
-  </si>
-  <si>
-    <t>0,44</t>
-  </si>
-  <si>
-    <t>0,1</t>
-  </si>
-  <si>
-    <t>39,65</t>
-  </si>
-  <si>
-    <t>0,08</t>
-  </si>
-  <si>
-    <t>12,81</t>
-  </si>
-  <si>
-    <t>7,96</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>TANGGAMUS</t>
-  </si>
-  <si>
-    <t>6,64</t>
-  </si>
-  <si>
-    <t>19,85</t>
-  </si>
-  <si>
-    <t>0,87</t>
-  </si>
-  <si>
-    <t>3,46</t>
-  </si>
-  <si>
-    <t>3,35</t>
-  </si>
-  <si>
-    <t>0,29</t>
-  </si>
-  <si>
-    <t>0,12</t>
-  </si>
-  <si>
-    <t>41,83</t>
-  </si>
-  <si>
-    <t>0,06</t>
-  </si>
-  <si>
-    <t>22,91</t>
-  </si>
-  <si>
-    <t>0,4</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>LAMPUNG SELATAN</t>
-  </si>
-  <si>
-    <t>5,74</t>
-  </si>
-  <si>
-    <t>20,74</t>
-  </si>
-  <si>
-    <t>2,82</t>
-  </si>
-  <si>
-    <t>3,24</t>
-  </si>
-  <si>
-    <t>0,66</t>
-  </si>
-  <si>
-    <t>44,09</t>
-  </si>
-  <si>
-    <t>3,49</t>
-  </si>
-  <si>
-    <t>17,34</t>
-  </si>
-  <si>
-    <t>0,99</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>0,03</t>
-  </si>
-  <si>
-    <t>4,21</t>
-  </si>
-  <si>
-    <t>26,48</t>
-  </si>
-  <si>
-    <t>0,23</t>
-  </si>
-  <si>
-    <t>0,91</t>
-  </si>
-  <si>
-    <t>2,14</t>
-  </si>
-  <si>
-    <t>0,21</t>
-  </si>
-  <si>
-    <t>3,04</t>
-  </si>
-  <si>
-    <t>0,27</t>
-  </si>
-  <si>
-    <t>1,28</t>
-  </si>
-  <si>
-    <t>43,5</t>
-  </si>
-  <si>
-    <t>0,34</t>
-  </si>
-  <si>
-    <t>15,58</t>
-  </si>
-  <si>
-    <t>1,38</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>4,38</t>
-  </si>
-  <si>
-    <t>23,12</t>
-  </si>
-  <si>
-    <t>5,44</t>
-  </si>
-  <si>
-    <t>4,06</t>
-  </si>
-  <si>
-    <t>0,41</t>
-  </si>
-  <si>
-    <t>45,32</t>
-  </si>
-  <si>
-    <t>1,04</t>
-  </si>
-  <si>
-    <t>14,8</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>2,7</t>
-  </si>
-  <si>
-    <t>2,18</t>
-  </si>
-  <si>
-    <t>15,28</t>
-  </si>
-  <si>
-    <t>0,42</t>
-  </si>
-  <si>
-    <t>2,47</t>
-  </si>
-  <si>
-    <t>0,53</t>
-  </si>
-  <si>
-    <t>44,12</t>
-  </si>
-  <si>
-    <t>0,74</t>
-  </si>
-  <si>
-    <t>17,04</t>
-  </si>
-  <si>
-    <t>12,23</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>4,15</t>
-  </si>
-  <si>
-    <t>20,17</t>
-  </si>
-  <si>
-    <t>0,14</t>
-  </si>
-  <si>
-    <t>0,57</t>
-  </si>
-  <si>
-    <t>2,35</t>
-  </si>
-  <si>
-    <t>2,89</t>
-  </si>
-  <si>
-    <t>2,09</t>
-  </si>
-  <si>
-    <t>40,32</t>
-  </si>
-  <si>
-    <t>25,13</t>
-  </si>
-  <si>
-    <t>1,12</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG</t>
-  </si>
-  <si>
-    <t>0,71</t>
-  </si>
-  <si>
-    <t>23,4</t>
-  </si>
-  <si>
-    <t>0,25</t>
-  </si>
-  <si>
-    <t>1,17</t>
-  </si>
-  <si>
-    <t>2,51</t>
-  </si>
-  <si>
-    <t>0,13</t>
-  </si>
-  <si>
-    <t>2,3</t>
-  </si>
-  <si>
-    <t>46,01</t>
-  </si>
-  <si>
-    <t>14,71</t>
-  </si>
-  <si>
-    <t>4,14</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>3,29</t>
-  </si>
-  <si>
-    <t>1,14</t>
-  </si>
-  <si>
-    <t>13,47</t>
-  </si>
-  <si>
-    <t>1,02</t>
-  </si>
-  <si>
-    <t>1,45</t>
-  </si>
-  <si>
-    <t>1,29</t>
-  </si>
-  <si>
-    <t>40,68</t>
-  </si>
-  <si>
-    <t>0,85</t>
-  </si>
-  <si>
-    <t>14,7</t>
-  </si>
-  <si>
-    <t>21,91</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>4,8</t>
-  </si>
-  <si>
-    <t>0,26</t>
-  </si>
-  <si>
-    <t>17,07</t>
-  </si>
-  <si>
-    <t>4,03</t>
-  </si>
-  <si>
-    <t>0,86</t>
-  </si>
-  <si>
-    <t>43,76</t>
-  </si>
-  <si>
-    <t>1,5</t>
-  </si>
-  <si>
-    <t>18,83</t>
-  </si>
-  <si>
-    <t>2,45</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>4,65</t>
-  </si>
-  <si>
-    <t>0,59</t>
-  </si>
-  <si>
-    <t>0,68</t>
-  </si>
-  <si>
-    <t>1,71</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>49,94</t>
+    <t>49,95</t>
   </si>
   <si>
     <t>0,96</t>
@@ -748,7 +751,7 @@
     <t>0,07</t>
   </si>
   <si>
-    <t>11,46</t>
+    <t>11,45</t>
   </si>
   <si>
     <t>5,01</t>
@@ -760,13 +763,10 @@
     <t>TULANG BAWANG BARAT</t>
   </si>
   <si>
-    <t>4,23</t>
-  </si>
-  <si>
-    <t>23,38</t>
-  </si>
-  <si>
-    <t>0,39</t>
+    <t>4,25</t>
+  </si>
+  <si>
+    <t>23,66</t>
   </si>
   <si>
     <t>1,56</t>
@@ -784,10 +784,10 @@
     <t>0,24</t>
   </si>
   <si>
-    <t>21,63</t>
-  </si>
-  <si>
-    <t>0,82</t>
+    <t>21,38</t>
+  </si>
+  <si>
+    <t>0,81</t>
   </si>
   <si>
     <t>1813</t>
@@ -796,25 +796,25 @@
     <t>PESISIR BARAT</t>
   </si>
   <si>
-    <t>5,15</t>
-  </si>
-  <si>
-    <t>28,24</t>
-  </si>
-  <si>
-    <t>0,22</t>
-  </si>
-  <si>
-    <t>3,34</t>
-  </si>
-  <si>
-    <t>46,4</t>
-  </si>
-  <si>
-    <t>13,8</t>
-  </si>
-  <si>
-    <t>1,94</t>
+    <t>5,09</t>
+  </si>
+  <si>
+    <t>28,72</t>
+  </si>
+  <si>
+    <t>3,12</t>
+  </si>
+  <si>
+    <t>45,94</t>
+  </si>
+  <si>
+    <t>0,3</t>
+  </si>
+  <si>
+    <t>14,4</t>
+  </si>
+  <si>
+    <t>1,72</t>
   </si>
   <si>
     <t>1871</t>
@@ -823,37 +823,31 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>7,25</t>
-  </si>
-  <si>
-    <t>0,81</t>
-  </si>
-  <si>
-    <t>10,87</t>
-  </si>
-  <si>
-    <t>0,54</t>
-  </si>
-  <si>
-    <t>5,64</t>
-  </si>
-  <si>
-    <t>7,52</t>
-  </si>
-  <si>
-    <t>12,21</t>
-  </si>
-  <si>
-    <t>40</t>
-  </si>
-  <si>
-    <t>1,61</t>
-  </si>
-  <si>
-    <t>8,99</t>
-  </si>
-  <si>
-    <t>2,55</t>
+    <t>7,27</t>
+  </si>
+  <si>
+    <t>10,9</t>
+  </si>
+  <si>
+    <t>5,65</t>
+  </si>
+  <si>
+    <t>7,54</t>
+  </si>
+  <si>
+    <t>12,25</t>
+  </si>
+  <si>
+    <t>40,11</t>
+  </si>
+  <si>
+    <t>1,62</t>
+  </si>
+  <si>
+    <t>9,02</t>
+  </si>
+  <si>
+    <t>2,56</t>
   </si>
   <si>
     <t>1872</t>
@@ -862,10 +856,10 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>2,67</t>
-  </si>
-  <si>
-    <t>11,6</t>
+    <t>2,66</t>
+  </si>
+  <si>
+    <t>11,7</t>
   </si>
   <si>
     <t>0,6</t>
@@ -874,25 +868,19 @@
     <t>2,33</t>
   </si>
   <si>
-    <t>2,8</t>
-  </si>
-  <si>
-    <t>2,6</t>
+    <t>2,59</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>42,13</t>
-  </si>
-  <si>
-    <t>0,2</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>25,6</t>
+    <t>42,15</t>
+  </si>
+  <si>
+    <t>7,98</t>
+  </si>
+  <si>
+    <t>25,53</t>
   </si>
   <si>
     <t/>
@@ -1818,7 +1806,7 @@
         <v>93</v>
       </c>
       <c r="C6" s="6">
-        <v>70811</v>
+        <v>72712</v>
       </c>
       <c r="D6" s="6">
         <v>6</v>
@@ -1827,7 +1815,7 @@
         <v>94</v>
       </c>
       <c r="F6" s="6">
-        <v>3083</v>
+        <v>3175</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>95</v>
@@ -1845,7 +1833,7 @@
         <v>97</v>
       </c>
       <c r="L6" s="6">
-        <v>15380</v>
+        <v>16048</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>98</v>
@@ -1857,31 +1845,31 @@
         <v>97</v>
       </c>
       <c r="P6" s="6">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q6" s="7" t="s">
         <v>99</v>
       </c>
       <c r="R6" s="6">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="S6" s="7" t="s">
         <v>100</v>
       </c>
       <c r="T6" s="6">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="U6" s="7" t="s">
         <v>101</v>
       </c>
       <c r="V6" s="6">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="W6" s="7" t="s">
         <v>102</v>
       </c>
       <c r="X6" s="6">
-        <v>2053</v>
+        <v>2082</v>
       </c>
       <c r="Y6" s="7" t="s">
         <v>103</v>
@@ -1893,13 +1881,13 @@
         <v>104</v>
       </c>
       <c r="AB6" s="6">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AC6" s="7" t="s">
         <v>105</v>
       </c>
       <c r="AD6" s="6">
-        <v>31097</v>
+        <v>31908</v>
       </c>
       <c r="AE6" s="7" t="s">
         <v>106</v>
@@ -1911,13 +1899,13 @@
         <v>107</v>
       </c>
       <c r="AH6" s="6">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI6" s="7" t="s">
         <v>108</v>
       </c>
       <c r="AJ6" s="6">
-        <v>11348</v>
+        <v>11655</v>
       </c>
       <c r="AK6" s="7" t="s">
         <v>109</v>
@@ -1955,7 +1943,7 @@
         <v>113</v>
       </c>
       <c r="C7" s="9">
-        <v>4784</v>
+        <v>4795</v>
       </c>
       <c r="D7" s="9">
         <v>0</v>
@@ -1982,7 +1970,7 @@
         <v>97</v>
       </c>
       <c r="L7" s="9">
-        <v>1359</v>
+        <v>1363</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>116</v>
@@ -2018,7 +2006,7 @@
         <v>118</v>
       </c>
       <c r="X7" s="9">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="Y7" s="10" t="s">
         <v>119</v>
@@ -2033,13 +2021,13 @@
         <v>5</v>
       </c>
       <c r="AC7" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="AD7" s="9">
+        <v>1902</v>
+      </c>
+      <c r="AE7" s="10" t="s">
         <v>121</v>
-      </c>
-      <c r="AD7" s="9">
-        <v>1897</v>
-      </c>
-      <c r="AE7" s="10" t="s">
-        <v>122</v>
       </c>
       <c r="AF7" s="9">
         <v>21</v>
@@ -2051,19 +2039,19 @@
         <v>4</v>
       </c>
       <c r="AI7" s="10" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="AJ7" s="9">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="AK7" s="10" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="AL7" s="9">
         <v>381</v>
       </c>
       <c r="AM7" s="10" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="AN7" s="9">
         <v>0</v>
@@ -2086,25 +2074,25 @@
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
+        <v>124</v>
+      </c>
+      <c r="B8" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="C8" s="9">
+        <v>1739</v>
+      </c>
+      <c r="D8" s="9">
+        <v>0</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F8" s="9">
+        <v>116</v>
+      </c>
+      <c r="G8" s="10" t="s">
         <v>126</v>
-      </c>
-      <c r="B8" s="8" t="s">
-        <v>127</v>
-      </c>
-      <c r="C8" s="9">
-        <v>1733</v>
-      </c>
-      <c r="D8" s="9">
-        <v>0</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="F8" s="9">
-        <v>115</v>
-      </c>
-      <c r="G8" s="10" t="s">
-        <v>128</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
@@ -2122,7 +2110,7 @@
         <v>344</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="N8" s="9">
         <v>0</v>
@@ -2140,13 +2128,13 @@
         <v>15</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="T8" s="9">
         <v>60</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="V8" s="9">
         <v>0</v>
@@ -2158,49 +2146,49 @@
         <v>58</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="Z8" s="9">
         <v>5</v>
       </c>
       <c r="AA8" s="10" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="AB8" s="9">
         <v>2</v>
       </c>
       <c r="AC8" s="10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AD8" s="9">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="AE8" s="10" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="AF8" s="9">
         <v>2</v>
       </c>
       <c r="AG8" s="10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="AH8" s="9">
         <v>1</v>
       </c>
       <c r="AI8" s="10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AJ8" s="9">
-        <v>397</v>
+        <v>400</v>
       </c>
       <c r="AK8" s="10" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="AL8" s="9">
         <v>7</v>
       </c>
       <c r="AM8" s="10" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AN8" s="9">
         <v>0</v>
@@ -2218,30 +2206,30 @@
         <v>2</v>
       </c>
       <c r="AS8" s="10" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="B9" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="C9" s="9">
+        <v>6994</v>
+      </c>
+      <c r="D9" s="9">
+        <v>0</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F9" s="9">
+        <v>402</v>
+      </c>
+      <c r="G9" s="10" t="s">
         <v>139</v>
-      </c>
-      <c r="B9" s="8" t="s">
-        <v>140</v>
-      </c>
-      <c r="C9" s="9">
-        <v>6847</v>
-      </c>
-      <c r="D9" s="9">
-        <v>0</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="F9" s="9">
-        <v>393</v>
-      </c>
-      <c r="G9" s="10" t="s">
-        <v>141</v>
       </c>
       <c r="H9" s="9">
         <v>22</v>
@@ -2256,10 +2244,10 @@
         <v>97</v>
       </c>
       <c r="L9" s="9">
-        <v>1420</v>
+        <v>1468</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="N9" s="9">
         <v>0</v>
@@ -2283,7 +2271,7 @@
         <v>193</v>
       </c>
       <c r="U9" s="10" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="V9" s="9">
         <v>0</v>
@@ -2292,52 +2280,52 @@
         <v>97</v>
       </c>
       <c r="X9" s="9">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="Z9" s="9">
         <v>45</v>
       </c>
       <c r="AA9" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="AB9" s="9">
+        <v>2</v>
+      </c>
+      <c r="AC9" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="AD9" s="9">
+        <v>3085</v>
+      </c>
+      <c r="AE9" s="10" t="s">
         <v>145</v>
-      </c>
-      <c r="AB9" s="9">
-        <v>1</v>
-      </c>
-      <c r="AC9" s="10" t="s">
-        <v>94</v>
-      </c>
-      <c r="AD9" s="9">
-        <v>3019</v>
-      </c>
-      <c r="AE9" s="10" t="s">
-        <v>146</v>
       </c>
       <c r="AF9" s="9">
         <v>239</v>
       </c>
       <c r="AG9" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="AH9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ9" s="9">
+        <v>1206</v>
+      </c>
+      <c r="AK9" s="10" t="s">
         <v>147</v>
-      </c>
-      <c r="AH9" s="9">
-        <v>0</v>
-      </c>
-      <c r="AI9" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ9" s="9">
-        <v>1187</v>
-      </c>
-      <c r="AK9" s="10" t="s">
-        <v>148</v>
       </c>
       <c r="AL9" s="9">
         <v>68</v>
       </c>
       <c r="AM9" s="10" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="AN9" s="9">
         <v>0</v>
@@ -2355,36 +2343,36 @@
         <v>4</v>
       </c>
       <c r="AS9" s="10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="B10" s="8" t="s">
         <v>150</v>
       </c>
-      <c r="B10" s="8" t="s">
-        <v>151</v>
-      </c>
       <c r="C10" s="9">
-        <v>8648</v>
+        <v>8646</v>
       </c>
       <c r="D10" s="9">
         <v>3</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="F10" s="9">
         <v>364</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>153</v>
+        <v>114</v>
       </c>
       <c r="H10" s="9">
         <v>25</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="J10" s="9">
         <v>0</v>
@@ -2396,7 +2384,7 @@
         <v>2290</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="N10" s="9">
         <v>1</v>
@@ -2408,73 +2396,73 @@
         <v>20</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="R10" s="9">
         <v>79</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="T10" s="9">
         <v>185</v>
       </c>
       <c r="U10" s="10" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
       <c r="V10" s="9">
         <v>18</v>
       </c>
       <c r="W10" s="10" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="X10" s="9">
         <v>263</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="Z10" s="9">
         <v>23</v>
       </c>
       <c r="AA10" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
       <c r="AB10" s="9">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="AC10" s="10" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="AD10" s="9">
         <v>3762</v>
       </c>
       <c r="AE10" s="10" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="AF10" s="9">
         <v>29</v>
       </c>
       <c r="AG10" s="10" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="AH10" s="9">
         <v>5</v>
       </c>
       <c r="AI10" s="10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="AJ10" s="9">
         <v>1347</v>
       </c>
       <c r="AK10" s="10" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="AL10" s="9">
         <v>119</v>
       </c>
       <c r="AM10" s="10" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="AN10" s="9">
         <v>1</v>
@@ -2492,18 +2480,18 @@
         <v>3</v>
       </c>
       <c r="AS10" s="10" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="C11" s="9">
-        <v>7002</v>
+        <v>7431</v>
       </c>
       <c r="D11" s="9">
         <v>1</v>
@@ -2512,10 +2500,10 @@
         <v>94</v>
       </c>
       <c r="F11" s="9">
-        <v>307</v>
+        <v>326</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="H11" s="9">
         <v>6</v>
@@ -2530,10 +2518,10 @@
         <v>97</v>
       </c>
       <c r="L11" s="9">
-        <v>1619</v>
+        <v>1754</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="N11" s="9">
         <v>0</v>
@@ -2545,19 +2533,19 @@
         <v>15</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="R11" s="9">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>138</v>
+        <v>168</v>
       </c>
       <c r="T11" s="9">
         <v>381</v>
       </c>
       <c r="U11" s="10" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="V11" s="9">
         <v>1</v>
@@ -2566,52 +2554,52 @@
         <v>94</v>
       </c>
       <c r="X11" s="9">
-        <v>284</v>
+        <v>289</v>
       </c>
       <c r="Y11" s="10" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="Z11" s="9">
         <v>29</v>
       </c>
       <c r="AA11" s="10" t="s">
+        <v>168</v>
+      </c>
+      <c r="AB11" s="9">
+        <v>11</v>
+      </c>
+      <c r="AC11" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="AD11" s="9">
+        <v>3379</v>
+      </c>
+      <c r="AE11" s="10" t="s">
         <v>172</v>
-      </c>
-      <c r="AB11" s="9">
-        <v>8</v>
-      </c>
-      <c r="AC11" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="AD11" s="9">
-        <v>3173</v>
-      </c>
-      <c r="AE11" s="10" t="s">
-        <v>173</v>
       </c>
       <c r="AF11" s="9">
         <v>73</v>
       </c>
       <c r="AG11" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="AH11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ11" s="9">
+        <v>1096</v>
+      </c>
+      <c r="AK11" s="10" t="s">
         <v>174</v>
-      </c>
-      <c r="AH11" s="9">
-        <v>0</v>
-      </c>
-      <c r="AI11" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ11" s="9">
-        <v>1036</v>
-      </c>
-      <c r="AK11" s="10" t="s">
-        <v>175</v>
       </c>
       <c r="AL11" s="9">
         <v>39</v>
       </c>
       <c r="AM11" s="10" t="s">
-        <v>96</v>
+        <v>175</v>
       </c>
       <c r="AN11" s="9">
         <v>0</v>
@@ -2629,7 +2617,7 @@
         <v>2</v>
       </c>
       <c r="AS11" s="10" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
@@ -2640,7 +2628,7 @@
         <v>177</v>
       </c>
       <c r="C12" s="9">
-        <v>6192</v>
+        <v>6407</v>
       </c>
       <c r="D12" s="9">
         <v>0</v>
@@ -2649,7 +2637,7 @@
         <v>97</v>
       </c>
       <c r="F12" s="9">
-        <v>167</v>
+        <v>179</v>
       </c>
       <c r="G12" s="10" t="s">
         <v>178</v>
@@ -2667,7 +2655,7 @@
         <v>97</v>
       </c>
       <c r="L12" s="9">
-        <v>946</v>
+        <v>1060</v>
       </c>
       <c r="M12" s="10" t="s">
         <v>180</v>
@@ -2703,7 +2691,7 @@
         <v>97</v>
       </c>
       <c r="X12" s="9">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="Y12" s="10" t="s">
         <v>182</v>
@@ -2712,43 +2700,43 @@
         <v>33</v>
       </c>
       <c r="AA12" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="AB12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC12" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD12" s="9">
+        <v>2793</v>
+      </c>
+      <c r="AE12" s="10" t="s">
         <v>183</v>
-      </c>
-      <c r="AB12" s="9">
-        <v>0</v>
-      </c>
-      <c r="AC12" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AD12" s="9">
-        <v>2732</v>
-      </c>
-      <c r="AE12" s="10" t="s">
-        <v>184</v>
       </c>
       <c r="AF12" s="9">
         <v>46</v>
       </c>
       <c r="AG12" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="AH12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ12" s="9">
+        <v>1081</v>
+      </c>
+      <c r="AK12" s="10" t="s">
         <v>185</v>
-      </c>
-      <c r="AH12" s="9">
-        <v>0</v>
-      </c>
-      <c r="AI12" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AJ12" s="9">
-        <v>1055</v>
-      </c>
-      <c r="AK12" s="10" t="s">
-        <v>186</v>
       </c>
       <c r="AL12" s="9">
         <v>757</v>
       </c>
       <c r="AM12" s="10" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="AN12" s="9">
         <v>0</v>
@@ -2766,7 +2754,7 @@
         <v>7</v>
       </c>
       <c r="AS12" s="10" t="s">
-        <v>99</v>
+        <v>187</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
@@ -2777,25 +2765,25 @@
         <v>189</v>
       </c>
       <c r="C13" s="9">
-        <v>3490</v>
+        <v>3495</v>
       </c>
       <c r="D13" s="9">
         <v>1</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="F13" s="9">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>190</v>
+        <v>114</v>
       </c>
       <c r="H13" s="9">
         <v>2</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="J13" s="9">
         <v>0</v>
@@ -2804,94 +2792,94 @@
         <v>97</v>
       </c>
       <c r="L13" s="9">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="N13" s="9">
         <v>1</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="P13" s="9">
         <v>5</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="R13" s="9">
         <v>20</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="T13" s="9">
         <v>82</v>
       </c>
       <c r="U13" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="V13" s="9">
+        <v>1</v>
+      </c>
+      <c r="W13" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="X13" s="9">
+        <v>102</v>
+      </c>
+      <c r="Y13" s="10" t="s">
         <v>194</v>
-      </c>
-      <c r="V13" s="9">
-        <v>3</v>
-      </c>
-      <c r="W13" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="X13" s="9">
-        <v>101</v>
-      </c>
-      <c r="Y13" s="10" t="s">
-        <v>195</v>
       </c>
       <c r="Z13" s="9">
         <v>14</v>
       </c>
       <c r="AA13" s="10" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="AB13" s="9">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="AC13" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="AD13" s="9">
+        <v>1411</v>
+      </c>
+      <c r="AE13" s="10" t="s">
         <v>196</v>
-      </c>
-      <c r="AD13" s="9">
-        <v>1407</v>
-      </c>
-      <c r="AE13" s="10" t="s">
-        <v>197</v>
       </c>
       <c r="AF13" s="9">
         <v>12</v>
       </c>
       <c r="AG13" s="10" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="AH13" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AI13" s="10" t="s">
-        <v>102</v>
+        <v>134</v>
       </c>
       <c r="AJ13" s="9">
-        <v>877</v>
+        <v>880</v>
       </c>
       <c r="AK13" s="10" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="AL13" s="9">
         <v>39</v>
       </c>
       <c r="AM13" s="10" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="AN13" s="9">
         <v>1</v>
       </c>
       <c r="AO13" s="10" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="AP13" s="9">
         <v>0</v>
@@ -2908,13 +2896,13 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="B14" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="B14" s="8" t="s">
-        <v>201</v>
-      </c>
       <c r="C14" s="9">
-        <v>2393</v>
+        <v>2396</v>
       </c>
       <c r="D14" s="9">
         <v>0</v>
@@ -2926,7 +2914,7 @@
         <v>104</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>95</v>
+        <v>201</v>
       </c>
       <c r="H14" s="9">
         <v>17</v>
@@ -2941,7 +2929,7 @@
         <v>97</v>
       </c>
       <c r="L14" s="9">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="M14" s="10" t="s">
         <v>203</v>
@@ -2995,7 +2983,7 @@
         <v>97</v>
       </c>
       <c r="AD14" s="9">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="AE14" s="10" t="s">
         <v>209</v>
@@ -3004,7 +2992,7 @@
         <v>2</v>
       </c>
       <c r="AG14" s="10" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
       <c r="AH14" s="9">
         <v>0</v>
@@ -3022,7 +3010,7 @@
         <v>99</v>
       </c>
       <c r="AM14" s="10" t="s">
-        <v>211</v>
+        <v>119</v>
       </c>
       <c r="AN14" s="9">
         <v>0</v>
@@ -3040,18 +3028,18 @@
         <v>2</v>
       </c>
       <c r="AS14" s="10" t="s">
-        <v>123</v>
+        <v>102</v>
       </c>
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
+        <v>211</v>
+      </c>
+      <c r="B15" s="8" t="s">
         <v>212</v>
       </c>
-      <c r="B15" s="8" t="s">
-        <v>213</v>
-      </c>
       <c r="C15" s="9">
-        <v>7741</v>
+        <v>7743</v>
       </c>
       <c r="D15" s="9">
         <v>0</v>
@@ -3063,13 +3051,13 @@
         <v>255</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="H15" s="9">
         <v>88</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="J15" s="9">
         <v>0</v>
@@ -3081,7 +3069,7 @@
         <v>1043</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="N15" s="9">
         <v>0</v>
@@ -3099,13 +3087,13 @@
         <v>79</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="T15" s="9">
         <v>112</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="V15" s="9">
         <v>1</v>
@@ -3117,7 +3105,7 @@
         <v>100</v>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="Z15" s="9">
         <v>10</v>
@@ -3132,16 +3120,16 @@
         <v>97</v>
       </c>
       <c r="AD15" s="9">
-        <v>3149</v>
+        <v>3151</v>
       </c>
       <c r="AE15" s="10" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="AF15" s="9">
         <v>66</v>
       </c>
       <c r="AG15" s="10" t="s">
-        <v>221</v>
+        <v>107</v>
       </c>
       <c r="AH15" s="9">
         <v>0</v>
@@ -3153,13 +3141,13 @@
         <v>1138</v>
       </c>
       <c r="AK15" s="10" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="AL15" s="9">
         <v>1696</v>
       </c>
       <c r="AM15" s="10" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="AN15" s="9">
         <v>0</v>
@@ -3182,13 +3170,13 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="C16" s="9">
-        <v>2331</v>
+        <v>2367</v>
       </c>
       <c r="D16" s="9">
         <v>0</v>
@@ -3200,13 +3188,13 @@
         <v>112</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="H16" s="9">
         <v>6</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>227</v>
+        <v>204</v>
       </c>
       <c r="J16" s="9">
         <v>0</v>
@@ -3215,10 +3203,10 @@
         <v>97</v>
       </c>
       <c r="L16" s="9">
-        <v>398</v>
+        <v>410</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="N16" s="9">
         <v>0</v>
@@ -3236,31 +3224,31 @@
         <v>30</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>219</v>
+        <v>226</v>
       </c>
       <c r="T16" s="9">
         <v>112</v>
       </c>
       <c r="U16" s="10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="V16" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W16" s="10" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="X16" s="9">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="Y16" s="10" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="Z16" s="9">
         <v>20</v>
       </c>
       <c r="AA16" s="10" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="AB16" s="9">
         <v>3</v>
@@ -3269,16 +3257,16 @@
         <v>207</v>
       </c>
       <c r="AD16" s="9">
-        <v>1020</v>
+        <v>1036</v>
       </c>
       <c r="AE16" s="10" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="AF16" s="9">
         <v>35</v>
       </c>
       <c r="AG16" s="10" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="AH16" s="9">
         <v>1</v>
@@ -3287,16 +3275,16 @@
         <v>111</v>
       </c>
       <c r="AJ16" s="9">
-        <v>439</v>
+        <v>447</v>
       </c>
       <c r="AK16" s="10" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="AL16" s="9">
         <v>57</v>
       </c>
       <c r="AM16" s="10" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="AN16" s="9">
         <v>0</v>
@@ -3319,13 +3307,13 @@
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="C17" s="9">
-        <v>4389</v>
+        <v>4392</v>
       </c>
       <c r="D17" s="9">
         <v>1</v>
@@ -3337,13 +3325,13 @@
         <v>204</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="H17" s="9">
         <v>26</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>238</v>
+        <v>100</v>
       </c>
       <c r="J17" s="9">
         <v>0</v>
@@ -3352,10 +3340,10 @@
         <v>97</v>
       </c>
       <c r="L17" s="9">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>203</v>
+        <v>236</v>
       </c>
       <c r="N17" s="9">
         <v>0</v>
@@ -3367,13 +3355,13 @@
         <v>22</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>104</v>
+        <v>237</v>
       </c>
       <c r="R17" s="9">
         <v>29</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>145</v>
+        <v>238</v>
       </c>
       <c r="T17" s="9">
         <v>30</v>
@@ -3385,7 +3373,7 @@
         <v>9</v>
       </c>
       <c r="W17" s="10" t="s">
-        <v>158</v>
+        <v>167</v>
       </c>
       <c r="X17" s="9">
         <v>75</v>
@@ -3403,37 +3391,37 @@
         <v>4</v>
       </c>
       <c r="AC17" s="10" t="s">
-        <v>102</v>
+        <v>242</v>
       </c>
       <c r="AD17" s="9">
-        <v>2192</v>
+        <v>2194</v>
       </c>
       <c r="AE17" s="10" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="AF17" s="9">
         <v>42</v>
       </c>
       <c r="AG17" s="10" t="s">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="AH17" s="9">
         <v>3</v>
       </c>
       <c r="AI17" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AJ17" s="9">
         <v>503</v>
       </c>
       <c r="AK17" s="10" t="s">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AL17" s="9">
         <v>220</v>
       </c>
       <c r="AM17" s="10" t="s">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="AN17" s="9">
         <v>0</v>
@@ -3456,13 +3444,13 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="C18" s="9">
-        <v>5372</v>
+        <v>5440</v>
       </c>
       <c r="D18" s="9">
         <v>0</v>
@@ -3471,16 +3459,16 @@
         <v>97</v>
       </c>
       <c r="F18" s="9">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="H18" s="9">
         <v>6</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>99</v>
+        <v>187</v>
       </c>
       <c r="J18" s="9">
         <v>0</v>
@@ -3489,10 +3477,10 @@
         <v>97</v>
       </c>
       <c r="L18" s="9">
-        <v>1256</v>
+        <v>1287</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="N18" s="9">
         <v>0</v>
@@ -3501,19 +3489,19 @@
         <v>97</v>
       </c>
       <c r="P18" s="9">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>136</v>
+        <v>111</v>
       </c>
       <c r="R18" s="9">
         <v>21</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>251</v>
+        <v>168</v>
       </c>
       <c r="T18" s="9">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="U18" s="10" t="s">
         <v>252</v>
@@ -3525,7 +3513,7 @@
         <v>97</v>
       </c>
       <c r="X18" s="9">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="Y18" s="10" t="s">
         <v>253</v>
@@ -3543,7 +3531,7 @@
         <v>97</v>
       </c>
       <c r="AD18" s="9">
-        <v>2443</v>
+        <v>2474</v>
       </c>
       <c r="AE18" s="10" t="s">
         <v>255</v>
@@ -3561,7 +3549,7 @@
         <v>97</v>
       </c>
       <c r="AJ18" s="9">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="AK18" s="10" t="s">
         <v>257</v>
@@ -3599,7 +3587,7 @@
         <v>260</v>
       </c>
       <c r="C19" s="9">
-        <v>7644</v>
+        <v>8620</v>
       </c>
       <c r="D19" s="9">
         <v>0</v>
@@ -3608,7 +3596,7 @@
         <v>97</v>
       </c>
       <c r="F19" s="9">
-        <v>394</v>
+        <v>439</v>
       </c>
       <c r="G19" s="10" t="s">
         <v>261</v>
@@ -3617,7 +3605,7 @@
         <v>18</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>256</v>
+        <v>155</v>
       </c>
       <c r="J19" s="9">
         <v>0</v>
@@ -3626,7 +3614,7 @@
         <v>97</v>
       </c>
       <c r="L19" s="9">
-        <v>2159</v>
+        <v>2476</v>
       </c>
       <c r="M19" s="10" t="s">
         <v>262</v>
@@ -3644,28 +3632,28 @@
         <v>97</v>
       </c>
       <c r="R19" s="9">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>204</v>
+        <v>152</v>
       </c>
       <c r="T19" s="9">
         <v>17</v>
       </c>
       <c r="U19" s="10" t="s">
+        <v>167</v>
+      </c>
+      <c r="V19" s="9">
+        <v>0</v>
+      </c>
+      <c r="W19" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="X19" s="9">
+        <v>269</v>
+      </c>
+      <c r="Y19" s="10" t="s">
         <v>263</v>
-      </c>
-      <c r="V19" s="9">
-        <v>0</v>
-      </c>
-      <c r="W19" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="X19" s="9">
-        <v>255</v>
-      </c>
-      <c r="Y19" s="10" t="s">
-        <v>264</v>
       </c>
       <c r="Z19" s="9">
         <v>4</v>
@@ -3680,16 +3668,16 @@
         <v>97</v>
       </c>
       <c r="AD19" s="9">
-        <v>3547</v>
+        <v>3960</v>
       </c>
       <c r="AE19" s="10" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="AF19" s="9">
         <v>26</v>
       </c>
       <c r="AG19" s="10" t="s">
-        <v>163</v>
+        <v>265</v>
       </c>
       <c r="AH19" s="9">
         <v>0</v>
@@ -3698,7 +3686,7 @@
         <v>97</v>
       </c>
       <c r="AJ19" s="9">
-        <v>1055</v>
+        <v>1241</v>
       </c>
       <c r="AK19" s="10" t="s">
         <v>266</v>
@@ -3725,7 +3713,7 @@
         <v>2</v>
       </c>
       <c r="AS19" s="10" t="s">
-        <v>152</v>
+        <v>108</v>
       </c>
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
@@ -3736,7 +3724,7 @@
         <v>269</v>
       </c>
       <c r="C20" s="9">
-        <v>745</v>
+        <v>743</v>
       </c>
       <c r="D20" s="9">
         <v>0</v>
@@ -3754,7 +3742,7 @@
         <v>6</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>271</v>
+        <v>258</v>
       </c>
       <c r="J20" s="9">
         <v>0</v>
@@ -3766,7 +3754,7 @@
         <v>81</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="N20" s="9">
         <v>0</v>
@@ -3775,22 +3763,22 @@
         <v>97</v>
       </c>
       <c r="P20" s="9">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>138</v>
+        <v>207</v>
       </c>
       <c r="R20" s="9">
         <v>4</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>273</v>
+        <v>96</v>
       </c>
       <c r="T20" s="9">
         <v>42</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="V20" s="9">
         <v>5</v>
@@ -3802,13 +3790,13 @@
         <v>56</v>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="Z20" s="9">
         <v>91</v>
       </c>
       <c r="AA20" s="10" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="AB20" s="9">
         <v>5</v>
@@ -3820,13 +3808,13 @@
         <v>298</v>
       </c>
       <c r="AE20" s="10" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="AF20" s="9">
         <v>12</v>
       </c>
       <c r="AG20" s="10" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="AH20" s="9">
         <v>0</v>
@@ -3838,13 +3826,13 @@
         <v>67</v>
       </c>
       <c r="AK20" s="10" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="AL20" s="9">
         <v>19</v>
       </c>
       <c r="AM20" s="10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="AN20" s="9">
         <v>0</v>
@@ -3862,18 +3850,18 @@
         <v>2</v>
       </c>
       <c r="AS20" s="10" t="s">
-        <v>160</v>
+        <v>157</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="C21" s="9">
-        <v>1500</v>
+        <v>1504</v>
       </c>
       <c r="D21" s="9">
         <v>0</v>
@@ -3885,13 +3873,13 @@
         <v>40</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="H21" s="9">
         <v>6</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="J21" s="9">
         <v>0</v>
@@ -3900,10 +3888,10 @@
         <v>97</v>
       </c>
       <c r="L21" s="9">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="N21" s="9">
         <v>0</v>
@@ -3921,49 +3909,49 @@
         <v>9</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="T21" s="9">
         <v>35</v>
       </c>
       <c r="U21" s="10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="V21" s="9">
         <v>1</v>
       </c>
       <c r="W21" s="10" t="s">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="X21" s="9">
         <v>42</v>
       </c>
       <c r="Y21" s="10" t="s">
-        <v>287</v>
+        <v>178</v>
       </c>
       <c r="Z21" s="9">
         <v>39</v>
       </c>
       <c r="AA21" s="10" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="AB21" s="9">
         <v>15</v>
       </c>
       <c r="AC21" s="10" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="AD21" s="9">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AE21" s="10" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="AF21" s="9">
         <v>3</v>
       </c>
       <c r="AG21" s="10" t="s">
-        <v>291</v>
+        <v>167</v>
       </c>
       <c r="AH21" s="9">
         <v>0</v>
@@ -3975,13 +3963,13 @@
         <v>120</v>
       </c>
       <c r="AK21" s="10" t="s">
-        <v>292</v>
+        <v>288</v>
       </c>
       <c r="AL21" s="9">
         <v>384</v>
       </c>
       <c r="AM21" s="10" t="s">
-        <v>293</v>
+        <v>289</v>
       </c>
       <c r="AN21" s="9">
         <v>0</v>
@@ -4004,13 +3992,13 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>294</v>
+        <v>290</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>295</v>
+        <v>291</v>
       </c>
       <c r="C22" s="12">
-        <v>70811</v>
+        <v>72712</v>
       </c>
       <c r="D22" s="12">
         <v>6</v>
@@ -4019,7 +4007,7 @@
         <v>94</v>
       </c>
       <c r="F22" s="12">
-        <v>3083</v>
+        <v>3175</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>95</v>
@@ -4037,7 +4025,7 @@
         <v>97</v>
       </c>
       <c r="L22" s="12">
-        <v>15380</v>
+        <v>16048</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>98</v>
@@ -4049,31 +4037,31 @@
         <v>97</v>
       </c>
       <c r="P22" s="12">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="Q22" s="13" t="s">
         <v>99</v>
       </c>
       <c r="R22" s="12">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="S22" s="13" t="s">
         <v>100</v>
       </c>
       <c r="T22" s="12">
-        <v>1550</v>
+        <v>1551</v>
       </c>
       <c r="U22" s="13" t="s">
         <v>101</v>
       </c>
       <c r="V22" s="12">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="W22" s="13" t="s">
         <v>102</v>
       </c>
       <c r="X22" s="12">
-        <v>2053</v>
+        <v>2082</v>
       </c>
       <c r="Y22" s="13" t="s">
         <v>103</v>
@@ -4085,13 +4073,13 @@
         <v>104</v>
       </c>
       <c r="AB22" s="12">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="AC22" s="13" t="s">
         <v>105</v>
       </c>
       <c r="AD22" s="12">
-        <v>31097</v>
+        <v>31908</v>
       </c>
       <c r="AE22" s="13" t="s">
         <v>106</v>
@@ -4103,13 +4091,13 @@
         <v>107</v>
       </c>
       <c r="AH22" s="12">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI22" s="13" t="s">
         <v>108</v>
       </c>
       <c r="AJ22" s="12">
-        <v>11348</v>
+        <v>11655</v>
       </c>
       <c r="AK22" s="13" t="s">
         <v>109</v>

--- a/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
+++ b/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="302">
   <si>
     <t>DATA RADAR ANOMALI KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 10 Sep 2026, 08.08</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 11 Sep 2026, 07.32</t>
   </si>
   <si>
     <t>Kode</t>
@@ -298,589 +298,619 @@
     <t>0,01</t>
   </si>
   <si>
-    <t>4,37</t>
+    <t>4,41</t>
+  </si>
+  <si>
+    <t>0,53</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>22,39</t>
+  </si>
+  <si>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>0,58</t>
+  </si>
+  <si>
+    <t>2,07</t>
+  </si>
+  <si>
+    <t>0,08</t>
+  </si>
+  <si>
+    <t>2,83</t>
+  </si>
+  <si>
+    <t>0,47</t>
+  </si>
+  <si>
+    <t>0,3</t>
+  </si>
+  <si>
+    <t>43,93</t>
+  </si>
+  <si>
+    <t>0,83</t>
+  </si>
+  <si>
+    <t>0,02</t>
+  </si>
+  <si>
+    <t>15,98</t>
+  </si>
+  <si>
+    <t>5,42</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>LAMPUNG BARAT</t>
+  </si>
+  <si>
+    <t>4,22</t>
+  </si>
+  <si>
+    <t>0,66</t>
+  </si>
+  <si>
+    <t>28,41</t>
+  </si>
+  <si>
+    <t>0,17</t>
+  </si>
+  <si>
+    <t>0,46</t>
+  </si>
+  <si>
+    <t>0,42</t>
+  </si>
+  <si>
+    <t>4,15</t>
+  </si>
+  <si>
+    <t>0,48</t>
+  </si>
+  <si>
+    <t>39,74</t>
+  </si>
+  <si>
+    <t>0,44</t>
+  </si>
+  <si>
+    <t>12,77</t>
+  </si>
+  <si>
+    <t>7,91</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>TANGGAMUS</t>
+  </si>
+  <si>
+    <t>6,64</t>
+  </si>
+  <si>
+    <t>19,87</t>
+  </si>
+  <si>
+    <t>0,06</t>
+  </si>
+  <si>
+    <t>0,86</t>
+  </si>
+  <si>
+    <t>3,44</t>
+  </si>
+  <si>
+    <t>3,32</t>
+  </si>
+  <si>
+    <t>0,29</t>
+  </si>
+  <si>
+    <t>0,11</t>
+  </si>
+  <si>
+    <t>41,75</t>
+  </si>
+  <si>
+    <t>22,97</t>
+  </si>
+  <si>
+    <t>0,4</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>LAMPUNG SELATAN</t>
+  </si>
+  <si>
+    <t>5,74</t>
+  </si>
+  <si>
+    <t>21,44</t>
+  </si>
+  <si>
+    <t>2,68</t>
+  </si>
+  <si>
+    <t>3,17</t>
+  </si>
+  <si>
+    <t>0,62</t>
+  </si>
+  <si>
+    <t>43,98</t>
+  </si>
+  <si>
+    <t>3,31</t>
+  </si>
+  <si>
+    <t>17,27</t>
+  </si>
+  <si>
+    <t>0,94</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>4,21</t>
+  </si>
+  <si>
+    <t>26,52</t>
+  </si>
+  <si>
+    <t>0,23</t>
+  </si>
+  <si>
+    <t>0,91</t>
+  </si>
+  <si>
+    <t>2,14</t>
+  </si>
+  <si>
+    <t>0,21</t>
+  </si>
+  <si>
+    <t>3,04</t>
+  </si>
+  <si>
+    <t>0,27</t>
+  </si>
+  <si>
+    <t>1,26</t>
+  </si>
+  <si>
+    <t>43,5</t>
+  </si>
+  <si>
+    <t>0,33</t>
+  </si>
+  <si>
+    <t>15,57</t>
+  </si>
+  <si>
+    <t>1,37</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
+    <t>4,45</t>
+  </si>
+  <si>
+    <t>24,07</t>
+  </si>
+  <si>
+    <t>0,19</t>
+  </si>
+  <si>
+    <t>0,37</t>
+  </si>
+  <si>
+    <t>4,86</t>
+  </si>
+  <si>
+    <t>3,8</t>
+  </si>
+  <si>
+    <t>0,15</t>
+  </si>
+  <si>
+    <t>45,69</t>
+  </si>
+  <si>
+    <t>0,93</t>
+  </si>
+  <si>
+    <t>14,49</t>
+  </si>
+  <si>
+    <t>0,5</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>2,84</t>
+  </si>
+  <si>
+    <t>2,03</t>
+  </si>
+  <si>
+    <t>17,93</t>
+  </si>
+  <si>
+    <t>0,39</t>
+  </si>
+  <si>
+    <t>2,42</t>
+  </si>
+  <si>
+    <t>43,04</t>
+  </si>
+  <si>
+    <t>0,69</t>
+  </si>
+  <si>
+    <t>16,62</t>
+  </si>
+  <si>
+    <t>11,39</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>4,25</t>
+  </si>
+  <si>
+    <t>20,33</t>
+  </si>
+  <si>
+    <t>0,14</t>
+  </si>
+  <si>
+    <t>0,56</t>
+  </si>
+  <si>
+    <t>2,31</t>
+  </si>
+  <si>
+    <t>2,87</t>
+  </si>
+  <si>
+    <t>1,94</t>
+  </si>
+  <si>
+    <t>40,21</t>
+  </si>
+  <si>
+    <t>0,34</t>
+  </si>
+  <si>
+    <t>25,34</t>
+  </si>
+  <si>
+    <t>1,1</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG</t>
+  </si>
+  <si>
+    <t>4,38</t>
+  </si>
+  <si>
+    <t>0,7</t>
+  </si>
+  <si>
+    <t>23,51</t>
+  </si>
+  <si>
+    <t>0,25</t>
+  </si>
+  <si>
+    <t>1,16</t>
+  </si>
+  <si>
+    <t>2,48</t>
+  </si>
+  <si>
+    <t>0,12</t>
+  </si>
+  <si>
+    <t>2,27</t>
+  </si>
+  <si>
+    <t>46,03</t>
+  </si>
+  <si>
+    <t>14,67</t>
+  </si>
+  <si>
+    <t>4,09</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>1,14</t>
+  </si>
+  <si>
+    <t>13,46</t>
+  </si>
+  <si>
+    <t>1,02</t>
+  </si>
+  <si>
+    <t>1,46</t>
+  </si>
+  <si>
+    <t>1,29</t>
+  </si>
+  <si>
+    <t>40,69</t>
+  </si>
+  <si>
+    <t>0,85</t>
+  </si>
+  <si>
+    <t>14,71</t>
+  </si>
+  <si>
+    <t>21,89</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>5,06</t>
+  </si>
+  <si>
+    <t>17,29</t>
+  </si>
+  <si>
+    <t>1,24</t>
+  </si>
+  <si>
+    <t>4,61</t>
+  </si>
+  <si>
+    <t>3,99</t>
+  </si>
+  <si>
+    <t>0,82</t>
+  </si>
+  <si>
+    <t>43,8</t>
+  </si>
+  <si>
+    <t>1,44</t>
+  </si>
+  <si>
+    <t>18,86</t>
+  </si>
+  <si>
+    <t>2,35</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
+  </si>
+  <si>
+    <t>4,66</t>
+  </si>
+  <si>
+    <t>0,59</t>
+  </si>
+  <si>
+    <t>23,43</t>
+  </si>
+  <si>
+    <t>0,68</t>
+  </si>
+  <si>
+    <t>0,2</t>
+  </si>
+  <si>
+    <t>1,7</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>0,09</t>
+  </si>
+  <si>
+    <t>49,92</t>
+  </si>
+  <si>
+    <t>0,95</t>
+  </si>
+  <si>
+    <t>0,07</t>
+  </si>
+  <si>
+    <t>11,47</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>23,84</t>
+  </si>
+  <si>
+    <t>0,38</t>
+  </si>
+  <si>
+    <t>1,59</t>
+  </si>
+  <si>
+    <t>1,81</t>
+  </si>
+  <si>
+    <t>45,47</t>
+  </si>
+  <si>
+    <t>0,24</t>
+  </si>
+  <si>
+    <t>21,23</t>
+  </si>
+  <si>
+    <t>0,8</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>5,14</t>
+  </si>
+  <si>
+    <t>0,18</t>
+  </si>
+  <si>
+    <t>28,54</t>
+  </si>
+  <si>
+    <t>2,95</t>
+  </si>
+  <si>
+    <t>46,36</t>
+  </si>
+  <si>
+    <t>0,26</t>
+  </si>
+  <si>
+    <t>14,6</t>
+  </si>
+  <si>
+    <t>1,49</t>
+  </si>
+  <si>
+    <t>1871</t>
+  </si>
+  <si>
+    <t>BANDAR LAMPUNG</t>
+  </si>
+  <si>
+    <t>7,24</t>
+  </si>
+  <si>
+    <t>11,13</t>
+  </si>
+  <si>
+    <t>0,13</t>
   </si>
   <si>
     <t>0,54</t>
   </si>
   <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>22,07</t>
-  </si>
-  <si>
-    <t>0,1</t>
-  </si>
-  <si>
-    <t>0,59</t>
-  </si>
-  <si>
-    <t>2,13</t>
-  </si>
-  <si>
-    <t>0,08</t>
-  </si>
-  <si>
-    <t>2,86</t>
-  </si>
-  <si>
-    <t>0,49</t>
-  </si>
-  <si>
-    <t>0,31</t>
-  </si>
-  <si>
-    <t>43,88</t>
-  </si>
-  <si>
-    <t>0,85</t>
-  </si>
-  <si>
-    <t>0,02</t>
-  </si>
-  <si>
-    <t>16,03</t>
-  </si>
-  <si>
-    <t>5,61</t>
-  </si>
-  <si>
-    <t>0,04</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>LAMPUNG BARAT</t>
-  </si>
-  <si>
-    <t>4,21</t>
+    <t>5,63</t>
   </si>
   <si>
     <t>0,67</t>
   </si>
   <si>
-    <t>28,43</t>
-  </si>
-  <si>
-    <t>0,17</t>
-  </si>
-  <si>
-    <t>0,46</t>
-  </si>
-  <si>
-    <t>4,13</t>
-  </si>
-  <si>
-    <t>0,44</t>
-  </si>
-  <si>
-    <t>39,67</t>
-  </si>
-  <si>
-    <t>12,81</t>
-  </si>
-  <si>
-    <t>7,95</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>TANGGAMUS</t>
-  </si>
-  <si>
-    <t>6,67</t>
-  </si>
-  <si>
-    <t>19,78</t>
-  </si>
-  <si>
-    <t>0,86</t>
-  </si>
-  <si>
-    <t>3,45</t>
-  </si>
-  <si>
-    <t>3,34</t>
-  </si>
-  <si>
-    <t>0,29</t>
-  </si>
-  <si>
-    <t>0,12</t>
-  </si>
-  <si>
-    <t>41,81</t>
-  </si>
-  <si>
-    <t>0,06</t>
-  </si>
-  <si>
-    <t>23</t>
-  </si>
-  <si>
-    <t>0,4</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>LAMPUNG SELATAN</t>
-  </si>
-  <si>
-    <t>5,75</t>
-  </si>
-  <si>
-    <t>20,99</t>
-  </si>
-  <si>
-    <t>2,76</t>
-  </si>
-  <si>
-    <t>3,23</t>
-  </si>
-  <si>
-    <t>0,64</t>
-  </si>
-  <si>
-    <t>0,03</t>
-  </si>
-  <si>
-    <t>44,11</t>
-  </si>
-  <si>
-    <t>3,42</t>
-  </si>
-  <si>
-    <t>17,24</t>
-  </si>
-  <si>
-    <t>0,97</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>26,49</t>
-  </si>
-  <si>
-    <t>0,23</t>
-  </si>
-  <si>
-    <t>0,91</t>
-  </si>
-  <si>
-    <t>2,14</t>
-  </si>
-  <si>
-    <t>0,21</t>
-  </si>
-  <si>
-    <t>3,04</t>
-  </si>
-  <si>
-    <t>0,27</t>
-  </si>
-  <si>
-    <t>1,26</t>
-  </si>
-  <si>
-    <t>43,51</t>
-  </si>
-  <si>
-    <t>0,34</t>
-  </si>
-  <si>
-    <t>15,58</t>
-  </si>
-  <si>
-    <t>1,38</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>4,39</t>
-  </si>
-  <si>
-    <t>23,6</t>
-  </si>
-  <si>
-    <t>0,2</t>
-  </si>
-  <si>
-    <t>0,39</t>
-  </si>
-  <si>
-    <t>5,13</t>
-  </si>
-  <si>
-    <t>3,89</t>
-  </si>
-  <si>
-    <t>0,15</t>
-  </si>
-  <si>
-    <t>45,47</t>
-  </si>
-  <si>
-    <t>0,98</t>
-  </si>
-  <si>
-    <t>14,75</t>
-  </si>
-  <si>
-    <t>0,52</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
+    <t>7,51</t>
+  </si>
+  <si>
+    <t>12,2</t>
+  </si>
+  <si>
+    <t>39,95</t>
+  </si>
+  <si>
+    <t>1,61</t>
+  </si>
+  <si>
+    <t>9,12</t>
+  </si>
+  <si>
+    <t>2,55</t>
+  </si>
+  <si>
+    <t>1872</t>
+  </si>
+  <si>
+    <t>METRO</t>
+  </si>
+  <si>
+    <t>2,72</t>
+  </si>
+  <si>
+    <t>11,68</t>
+  </si>
+  <si>
+    <t>0,6</t>
+  </si>
+  <si>
+    <t>2,32</t>
   </si>
   <si>
     <t>2,79</t>
   </si>
   <si>
-    <t>2,11</t>
-  </si>
-  <si>
-    <t>16,54</t>
-  </si>
-  <si>
-    <t>0,41</t>
-  </si>
-  <si>
-    <t>2,42</t>
-  </si>
-  <si>
-    <t>43,59</t>
-  </si>
-  <si>
-    <t>0,72</t>
-  </si>
-  <si>
-    <t>16,87</t>
-  </si>
-  <si>
-    <t>11,82</t>
-  </si>
-  <si>
-    <t>0,11</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>20,2</t>
-  </si>
-  <si>
-    <t>0,14</t>
-  </si>
-  <si>
-    <t>0,57</t>
-  </si>
-  <si>
-    <t>2,35</t>
-  </si>
-  <si>
-    <t>2,92</t>
-  </si>
-  <si>
-    <t>1,97</t>
-  </si>
-  <si>
-    <t>40,37</t>
-  </si>
-  <si>
-    <t>25,18</t>
-  </si>
-  <si>
-    <t>1,12</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG</t>
-  </si>
-  <si>
-    <t>4,34</t>
-  </si>
-  <si>
-    <t>0,71</t>
-  </si>
-  <si>
-    <t>23,46</t>
-  </si>
-  <si>
-    <t>0,25</t>
-  </si>
-  <si>
-    <t>1,17</t>
-  </si>
-  <si>
-    <t>2,5</t>
-  </si>
-  <si>
-    <t>0,13</t>
-  </si>
-  <si>
-    <t>2,3</t>
-  </si>
-  <si>
-    <t>45,99</t>
-  </si>
-  <si>
-    <t>14,69</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>3,29</t>
-  </si>
-  <si>
-    <t>1,14</t>
-  </si>
-  <si>
-    <t>13,47</t>
-  </si>
-  <si>
-    <t>1,02</t>
-  </si>
-  <si>
-    <t>1,45</t>
-  </si>
-  <si>
-    <t>1,29</t>
-  </si>
-  <si>
-    <t>40,69</t>
-  </si>
-  <si>
-    <t>14,7</t>
-  </si>
-  <si>
-    <t>21,9</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>4,73</t>
-  </si>
-  <si>
-    <t>17,32</t>
-  </si>
-  <si>
-    <t>1,27</t>
-  </si>
-  <si>
-    <t>4,01</t>
-  </si>
-  <si>
-    <t>0,84</t>
-  </si>
-  <si>
-    <t>43,77</t>
-  </si>
-  <si>
-    <t>1,48</t>
-  </si>
-  <si>
-    <t>18,88</t>
-  </si>
-  <si>
-    <t>2,41</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>4,64</t>
-  </si>
-  <si>
-    <t>23,41</t>
-  </si>
-  <si>
-    <t>0,5</t>
-  </si>
-  <si>
-    <t>0,66</t>
-  </si>
-  <si>
-    <t>0,68</t>
-  </si>
-  <si>
-    <t>1,71</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>0,09</t>
-  </si>
-  <si>
-    <t>49,95</t>
-  </si>
-  <si>
-    <t>0,96</t>
-  </si>
-  <si>
-    <t>0,07</t>
-  </si>
-  <si>
-    <t>11,45</t>
-  </si>
-  <si>
-    <t>5,01</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>4,25</t>
-  </si>
-  <si>
-    <t>23,66</t>
-  </si>
-  <si>
-    <t>1,56</t>
-  </si>
-  <si>
-    <t>1,82</t>
-  </si>
-  <si>
-    <t>0,28</t>
-  </si>
-  <si>
-    <t>45,48</t>
-  </si>
-  <si>
-    <t>0,24</t>
-  </si>
-  <si>
-    <t>21,38</t>
-  </si>
-  <si>
-    <t>0,81</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>5,09</t>
-  </si>
-  <si>
-    <t>28,72</t>
-  </si>
-  <si>
-    <t>3,12</t>
-  </si>
-  <si>
-    <t>45,94</t>
-  </si>
-  <si>
-    <t>0,3</t>
-  </si>
-  <si>
-    <t>14,4</t>
-  </si>
-  <si>
-    <t>1,72</t>
-  </si>
-  <si>
-    <t>1871</t>
-  </si>
-  <si>
-    <t>BANDAR LAMPUNG</t>
-  </si>
-  <si>
-    <t>7,27</t>
-  </si>
-  <si>
-    <t>10,9</t>
-  </si>
-  <si>
-    <t>5,65</t>
-  </si>
-  <si>
-    <t>7,54</t>
-  </si>
-  <si>
-    <t>12,25</t>
-  </si>
-  <si>
-    <t>40,11</t>
-  </si>
-  <si>
-    <t>1,62</t>
-  </si>
-  <si>
-    <t>9,02</t>
-  </si>
-  <si>
-    <t>2,56</t>
-  </si>
-  <si>
-    <t>1872</t>
-  </si>
-  <si>
-    <t>METRO</t>
-  </si>
-  <si>
-    <t>2,66</t>
-  </si>
-  <si>
-    <t>11,7</t>
-  </si>
-  <si>
-    <t>0,6</t>
-  </si>
-  <si>
-    <t>2,33</t>
-  </si>
-  <si>
     <t>2,59</t>
   </si>
   <si>
     <t>1</t>
   </si>
   <si>
-    <t>42,15</t>
-  </si>
-  <si>
-    <t>7,98</t>
-  </si>
-  <si>
-    <t>25,53</t>
+    <t>42,07</t>
+  </si>
+  <si>
+    <t>7,96</t>
+  </si>
+  <si>
+    <t>25,48</t>
   </si>
   <si>
     <t/>
@@ -1806,7 +1836,7 @@
         <v>93</v>
       </c>
       <c r="C6" s="6">
-        <v>72712</v>
+        <v>75166</v>
       </c>
       <c r="D6" s="6">
         <v>6</v>
@@ -1815,7 +1845,7 @@
         <v>94</v>
       </c>
       <c r="F6" s="6">
-        <v>3175</v>
+        <v>3318</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>95</v>
@@ -1833,7 +1863,7 @@
         <v>97</v>
       </c>
       <c r="L6" s="6">
-        <v>16048</v>
+        <v>16831</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>98</v>
@@ -1845,49 +1875,49 @@
         <v>97</v>
       </c>
       <c r="P6" s="6">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q6" s="7" t="s">
         <v>99</v>
       </c>
       <c r="R6" s="6">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="S6" s="7" t="s">
         <v>100</v>
       </c>
       <c r="T6" s="6">
-        <v>1551</v>
+        <v>1554</v>
       </c>
       <c r="U6" s="7" t="s">
         <v>101</v>
       </c>
       <c r="V6" s="6">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="W6" s="7" t="s">
         <v>102</v>
       </c>
       <c r="X6" s="6">
-        <v>2082</v>
+        <v>2129</v>
       </c>
       <c r="Y6" s="7" t="s">
         <v>103</v>
       </c>
       <c r="Z6" s="6">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AA6" s="7" t="s">
         <v>104</v>
       </c>
       <c r="AB6" s="6">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AC6" s="7" t="s">
         <v>105</v>
       </c>
       <c r="AD6" s="6">
-        <v>31908</v>
+        <v>33023</v>
       </c>
       <c r="AE6" s="7" t="s">
         <v>106</v>
@@ -1905,7 +1935,7 @@
         <v>108</v>
       </c>
       <c r="AJ6" s="6">
-        <v>11655</v>
+        <v>12015</v>
       </c>
       <c r="AK6" s="7" t="s">
         <v>109</v>
@@ -1943,7 +1973,7 @@
         <v>113</v>
       </c>
       <c r="C7" s="9">
-        <v>4795</v>
+        <v>4816</v>
       </c>
       <c r="D7" s="9">
         <v>0</v>
@@ -1952,7 +1982,7 @@
         <v>97</v>
       </c>
       <c r="F7" s="9">
-        <v>202</v>
+        <v>203</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>114</v>
@@ -1970,7 +2000,7 @@
         <v>97</v>
       </c>
       <c r="L7" s="9">
-        <v>1363</v>
+        <v>1368</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>116</v>
@@ -2000,22 +2030,22 @@
         <v>118</v>
       </c>
       <c r="V7" s="9">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="W7" s="10" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="X7" s="9">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Y7" s="10" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="Z7" s="9">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AA7" s="10" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AB7" s="9">
         <v>5</v>
@@ -2024,16 +2054,16 @@
         <v>99</v>
       </c>
       <c r="AD7" s="9">
-        <v>1902</v>
+        <v>1914</v>
       </c>
       <c r="AE7" s="10" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="AF7" s="9">
         <v>21</v>
       </c>
       <c r="AG7" s="10" t="s">
-        <v>120</v>
+        <v>123</v>
       </c>
       <c r="AH7" s="9">
         <v>4</v>
@@ -2042,16 +2072,16 @@
         <v>102</v>
       </c>
       <c r="AJ7" s="9">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="AK7" s="10" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="AL7" s="9">
         <v>381</v>
       </c>
       <c r="AM7" s="10" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="AN7" s="9">
         <v>0</v>
@@ -2074,13 +2104,13 @@
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C8" s="9">
-        <v>1739</v>
+        <v>1746</v>
       </c>
       <c r="D8" s="9">
         <v>0</v>
@@ -2092,7 +2122,7 @@
         <v>116</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
@@ -2107,10 +2137,10 @@
         <v>97</v>
       </c>
       <c r="L8" s="9">
-        <v>344</v>
+        <v>347</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="N8" s="9">
         <v>0</v>
@@ -2119,22 +2149,22 @@
         <v>97</v>
       </c>
       <c r="P8" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>97</v>
+        <v>130</v>
       </c>
       <c r="R8" s="9">
         <v>15</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>128</v>
+        <v>131</v>
       </c>
       <c r="T8" s="9">
         <v>60</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>129</v>
+        <v>132</v>
       </c>
       <c r="V8" s="9">
         <v>0</v>
@@ -2146,49 +2176,49 @@
         <v>58</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>130</v>
+        <v>133</v>
       </c>
       <c r="Z8" s="9">
         <v>5</v>
       </c>
       <c r="AA8" s="10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="AB8" s="9">
         <v>2</v>
       </c>
       <c r="AC8" s="10" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="AD8" s="9">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="AE8" s="10" t="s">
-        <v>133</v>
+        <v>136</v>
       </c>
       <c r="AF8" s="9">
         <v>2</v>
       </c>
       <c r="AG8" s="10" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
       <c r="AH8" s="9">
         <v>1</v>
       </c>
       <c r="AI8" s="10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="AJ8" s="9">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="AK8" s="10" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="AL8" s="9">
         <v>7</v>
       </c>
       <c r="AM8" s="10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="AN8" s="9">
         <v>0</v>
@@ -2206,18 +2236,18 @@
         <v>2</v>
       </c>
       <c r="AS8" s="10" t="s">
-        <v>132</v>
+        <v>135</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="C9" s="9">
-        <v>6994</v>
+        <v>7214</v>
       </c>
       <c r="D9" s="9">
         <v>0</v>
@@ -2226,10 +2256,10 @@
         <v>97</v>
       </c>
       <c r="F9" s="9">
-        <v>402</v>
+        <v>414</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="H9" s="9">
         <v>22</v>
@@ -2244,10 +2274,10 @@
         <v>97</v>
       </c>
       <c r="L9" s="9">
-        <v>1468</v>
+        <v>1547</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="N9" s="9">
         <v>0</v>
@@ -2271,7 +2301,7 @@
         <v>193</v>
       </c>
       <c r="U9" s="10" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="V9" s="9">
         <v>0</v>
@@ -2280,34 +2310,34 @@
         <v>97</v>
       </c>
       <c r="X9" s="9">
-        <v>226</v>
+        <v>229</v>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="Z9" s="9">
         <v>45</v>
       </c>
       <c r="AA9" s="10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="AB9" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AC9" s="10" t="s">
-        <v>144</v>
+        <v>97</v>
       </c>
       <c r="AD9" s="9">
-        <v>3085</v>
+        <v>3173</v>
       </c>
       <c r="AE9" s="10" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="AF9" s="9">
         <v>239</v>
       </c>
       <c r="AG9" s="10" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="AH9" s="9">
         <v>0</v>
@@ -2316,16 +2346,16 @@
         <v>97</v>
       </c>
       <c r="AJ9" s="9">
-        <v>1206</v>
+        <v>1246</v>
       </c>
       <c r="AK9" s="10" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="AL9" s="9">
         <v>68</v>
       </c>
       <c r="AM9" s="10" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="AN9" s="9">
         <v>0</v>
@@ -2343,36 +2373,36 @@
         <v>4</v>
       </c>
       <c r="AS9" s="10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="C10" s="9">
-        <v>8646</v>
+        <v>8660</v>
       </c>
       <c r="D10" s="9">
         <v>3</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="F10" s="9">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>114</v>
+        <v>153</v>
       </c>
       <c r="H10" s="9">
         <v>25</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>131</v>
+        <v>134</v>
       </c>
       <c r="J10" s="9">
         <v>0</v>
@@ -2381,10 +2411,10 @@
         <v>97</v>
       </c>
       <c r="L10" s="9">
-        <v>2290</v>
+        <v>2297</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>151</v>
+        <v>154</v>
       </c>
       <c r="N10" s="9">
         <v>1</v>
@@ -2396,73 +2426,73 @@
         <v>20</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="R10" s="9">
         <v>79</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="T10" s="9">
         <v>185</v>
       </c>
       <c r="U10" s="10" t="s">
-        <v>154</v>
+        <v>157</v>
       </c>
       <c r="V10" s="9">
         <v>18</v>
       </c>
       <c r="W10" s="10" t="s">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="X10" s="9">
         <v>263</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>156</v>
+        <v>159</v>
       </c>
       <c r="Z10" s="9">
         <v>23</v>
       </c>
       <c r="AA10" s="10" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
       <c r="AB10" s="9">
         <v>109</v>
       </c>
       <c r="AC10" s="10" t="s">
-        <v>158</v>
+        <v>161</v>
       </c>
       <c r="AD10" s="9">
-        <v>3762</v>
+        <v>3767</v>
       </c>
       <c r="AE10" s="10" t="s">
-        <v>159</v>
+        <v>162</v>
       </c>
       <c r="AF10" s="9">
         <v>29</v>
       </c>
       <c r="AG10" s="10" t="s">
-        <v>160</v>
+        <v>163</v>
       </c>
       <c r="AH10" s="9">
         <v>5</v>
       </c>
       <c r="AI10" s="10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="AJ10" s="9">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="AK10" s="10" t="s">
-        <v>161</v>
+        <v>164</v>
       </c>
       <c r="AL10" s="9">
         <v>119</v>
       </c>
       <c r="AM10" s="10" t="s">
-        <v>162</v>
+        <v>165</v>
       </c>
       <c r="AN10" s="9">
         <v>1</v>
@@ -2480,18 +2510,18 @@
         <v>3</v>
       </c>
       <c r="AS10" s="10" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>163</v>
+        <v>166</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>164</v>
+        <v>167</v>
       </c>
       <c r="C11" s="9">
-        <v>7431</v>
+        <v>7840</v>
       </c>
       <c r="D11" s="9">
         <v>1</v>
@@ -2500,10 +2530,10 @@
         <v>94</v>
       </c>
       <c r="F11" s="9">
-        <v>326</v>
+        <v>349</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>165</v>
+        <v>168</v>
       </c>
       <c r="H11" s="9">
         <v>6</v>
@@ -2518,10 +2548,10 @@
         <v>97</v>
       </c>
       <c r="L11" s="9">
-        <v>1754</v>
+        <v>1887</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="N11" s="9">
         <v>0</v>
@@ -2533,19 +2563,19 @@
         <v>15</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>167</v>
+        <v>170</v>
       </c>
       <c r="R11" s="9">
         <v>29</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="T11" s="9">
         <v>381</v>
       </c>
       <c r="U11" s="10" t="s">
-        <v>169</v>
+        <v>172</v>
       </c>
       <c r="V11" s="9">
         <v>1</v>
@@ -2554,34 +2584,34 @@
         <v>94</v>
       </c>
       <c r="X11" s="9">
-        <v>289</v>
+        <v>298</v>
       </c>
       <c r="Y11" s="10" t="s">
-        <v>170</v>
+        <v>173</v>
       </c>
       <c r="Z11" s="9">
         <v>29</v>
       </c>
       <c r="AA11" s="10" t="s">
-        <v>168</v>
+        <v>171</v>
       </c>
       <c r="AB11" s="9">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AC11" s="10" t="s">
-        <v>171</v>
+        <v>174</v>
       </c>
       <c r="AD11" s="9">
-        <v>3379</v>
+        <v>3582</v>
       </c>
       <c r="AE11" s="10" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="AF11" s="9">
         <v>73</v>
       </c>
       <c r="AG11" s="10" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="AH11" s="9">
         <v>0</v>
@@ -2590,16 +2620,16 @@
         <v>97</v>
       </c>
       <c r="AJ11" s="9">
-        <v>1096</v>
+        <v>1136</v>
       </c>
       <c r="AK11" s="10" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="AL11" s="9">
         <v>39</v>
       </c>
       <c r="AM11" s="10" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="AN11" s="9">
         <v>0</v>
@@ -2617,18 +2647,18 @@
         <v>2</v>
       </c>
       <c r="AS11" s="10" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="C12" s="9">
-        <v>6407</v>
+        <v>6647</v>
       </c>
       <c r="D12" s="9">
         <v>0</v>
@@ -2637,16 +2667,16 @@
         <v>97</v>
       </c>
       <c r="F12" s="9">
-        <v>179</v>
+        <v>189</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="H12" s="9">
         <v>135</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="J12" s="9">
         <v>0</v>
@@ -2655,10 +2685,10 @@
         <v>97</v>
       </c>
       <c r="L12" s="9">
-        <v>1060</v>
+        <v>1192</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="N12" s="9">
         <v>0</v>
@@ -2676,13 +2706,13 @@
         <v>26</v>
       </c>
       <c r="S12" s="10" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="T12" s="9">
         <v>135</v>
       </c>
       <c r="U12" s="10" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="V12" s="9">
         <v>0</v>
@@ -2691,16 +2721,16 @@
         <v>97</v>
       </c>
       <c r="X12" s="9">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="Z12" s="9">
         <v>33</v>
       </c>
       <c r="AA12" s="10" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="AB12" s="9">
         <v>0</v>
@@ -2709,16 +2739,16 @@
         <v>97</v>
       </c>
       <c r="AD12" s="9">
-        <v>2793</v>
+        <v>2861</v>
       </c>
       <c r="AE12" s="10" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="AF12" s="9">
         <v>46</v>
       </c>
       <c r="AG12" s="10" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="AH12" s="9">
         <v>0</v>
@@ -2727,16 +2757,16 @@
         <v>97</v>
       </c>
       <c r="AJ12" s="9">
-        <v>1081</v>
+        <v>1105</v>
       </c>
       <c r="AK12" s="10" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="AL12" s="9">
         <v>757</v>
       </c>
       <c r="AM12" s="10" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="AN12" s="9">
         <v>0</v>
@@ -2754,36 +2784,36 @@
         <v>7</v>
       </c>
       <c r="AS12" s="10" t="s">
-        <v>187</v>
+        <v>135</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C13" s="9">
-        <v>3495</v>
+        <v>3556</v>
       </c>
       <c r="D13" s="9">
         <v>1</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="F13" s="9">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>114</v>
+        <v>192</v>
       </c>
       <c r="H13" s="9">
         <v>2</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="J13" s="9">
         <v>0</v>
@@ -2792,94 +2822,94 @@
         <v>97</v>
       </c>
       <c r="L13" s="9">
-        <v>706</v>
+        <v>723</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="N13" s="9">
         <v>1</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="P13" s="9">
         <v>5</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="R13" s="9">
         <v>20</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="T13" s="9">
         <v>82</v>
       </c>
       <c r="U13" s="10" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="V13" s="9">
         <v>1</v>
       </c>
       <c r="W13" s="10" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="X13" s="9">
         <v>102</v>
       </c>
       <c r="Y13" s="10" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="Z13" s="9">
         <v>14</v>
       </c>
       <c r="AA13" s="10" t="s">
-        <v>136</v>
+        <v>184</v>
       </c>
       <c r="AB13" s="9">
         <v>69</v>
       </c>
       <c r="AC13" s="10" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="AD13" s="9">
-        <v>1411</v>
+        <v>1430</v>
       </c>
       <c r="AE13" s="10" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="AF13" s="9">
         <v>12</v>
       </c>
       <c r="AG13" s="10" t="s">
-        <v>160</v>
+        <v>200</v>
       </c>
       <c r="AH13" s="9">
         <v>2</v>
       </c>
       <c r="AI13" s="10" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="AJ13" s="9">
-        <v>880</v>
+        <v>901</v>
       </c>
       <c r="AK13" s="10" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="AL13" s="9">
         <v>39</v>
       </c>
       <c r="AM13" s="10" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="AN13" s="9">
         <v>1</v>
       </c>
       <c r="AO13" s="10" t="s">
-        <v>144</v>
+        <v>152</v>
       </c>
       <c r="AP13" s="9">
         <v>0</v>
@@ -2896,13 +2926,13 @@
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="C14" s="9">
-        <v>2396</v>
+        <v>2420</v>
       </c>
       <c r="D14" s="9">
         <v>0</v>
@@ -2911,16 +2941,16 @@
         <v>97</v>
       </c>
       <c r="F14" s="9">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="H14" s="9">
         <v>17</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="J14" s="9">
         <v>0</v>
@@ -2929,10 +2959,10 @@
         <v>97</v>
       </c>
       <c r="L14" s="9">
-        <v>562</v>
+        <v>569</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="N14" s="9">
         <v>1</v>
@@ -2944,37 +2974,37 @@
         <v>6</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="R14" s="9">
         <v>28</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="T14" s="9">
         <v>60</v>
       </c>
       <c r="U14" s="10" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="V14" s="9">
         <v>3</v>
       </c>
       <c r="W14" s="10" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="X14" s="9">
         <v>55</v>
       </c>
       <c r="Y14" s="10" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="Z14" s="9">
         <v>3</v>
       </c>
       <c r="AA14" s="10" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AB14" s="9">
         <v>0</v>
@@ -2983,10 +3013,10 @@
         <v>97</v>
       </c>
       <c r="AD14" s="9">
-        <v>1102</v>
+        <v>1114</v>
       </c>
       <c r="AE14" s="10" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="AF14" s="9">
         <v>2</v>
@@ -3001,16 +3031,16 @@
         <v>97</v>
       </c>
       <c r="AJ14" s="9">
-        <v>352</v>
+        <v>355</v>
       </c>
       <c r="AK14" s="10" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="AL14" s="9">
         <v>99</v>
       </c>
       <c r="AM14" s="10" t="s">
-        <v>119</v>
+        <v>215</v>
       </c>
       <c r="AN14" s="9">
         <v>0</v>
@@ -3033,13 +3063,13 @@
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>211</v>
+        <v>216</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>212</v>
+        <v>217</v>
       </c>
       <c r="C15" s="9">
-        <v>7743</v>
+        <v>7749</v>
       </c>
       <c r="D15" s="9">
         <v>0</v>
@@ -3048,16 +3078,16 @@
         <v>97</v>
       </c>
       <c r="F15" s="9">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>213</v>
+        <v>133</v>
       </c>
       <c r="H15" s="9">
         <v>88</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
       <c r="J15" s="9">
         <v>0</v>
@@ -3069,7 +3099,7 @@
         <v>1043</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="N15" s="9">
         <v>0</v>
@@ -3078,40 +3108,40 @@
         <v>97</v>
       </c>
       <c r="P15" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="R15" s="9">
         <v>79</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="T15" s="9">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="V15" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W15" s="10" t="s">
-        <v>94</v>
+        <v>97</v>
       </c>
       <c r="X15" s="9">
         <v>100</v>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="Z15" s="9">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AA15" s="10" t="s">
-        <v>207</v>
+        <v>194</v>
       </c>
       <c r="AB15" s="9">
         <v>0</v>
@@ -3120,16 +3150,16 @@
         <v>97</v>
       </c>
       <c r="AD15" s="9">
-        <v>3151</v>
+        <v>3153</v>
       </c>
       <c r="AE15" s="10" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="AF15" s="9">
         <v>66</v>
       </c>
       <c r="AG15" s="10" t="s">
-        <v>107</v>
+        <v>224</v>
       </c>
       <c r="AH15" s="9">
         <v>0</v>
@@ -3138,16 +3168,16 @@
         <v>97</v>
       </c>
       <c r="AJ15" s="9">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="AK15" s="10" t="s">
-        <v>220</v>
+        <v>225</v>
       </c>
       <c r="AL15" s="9">
         <v>1696</v>
       </c>
       <c r="AM15" s="10" t="s">
-        <v>221</v>
+        <v>226</v>
       </c>
       <c r="AN15" s="9">
         <v>0</v>
@@ -3170,13 +3200,13 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>222</v>
+        <v>227</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>223</v>
+        <v>228</v>
       </c>
       <c r="C16" s="9">
-        <v>2367</v>
+        <v>2429</v>
       </c>
       <c r="D16" s="9">
         <v>0</v>
@@ -3185,16 +3215,16 @@
         <v>97</v>
       </c>
       <c r="F16" s="9">
-        <v>112</v>
+        <v>123</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>224</v>
+        <v>229</v>
       </c>
       <c r="H16" s="9">
         <v>6</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="J16" s="9">
         <v>0</v>
@@ -3203,10 +3233,10 @@
         <v>97</v>
       </c>
       <c r="L16" s="9">
-        <v>410</v>
+        <v>420</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>225</v>
+        <v>230</v>
       </c>
       <c r="N16" s="9">
         <v>0</v>
@@ -3224,13 +3254,13 @@
         <v>30</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>226</v>
+        <v>231</v>
       </c>
       <c r="T16" s="9">
         <v>112</v>
       </c>
       <c r="U16" s="10" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="V16" s="9">
         <v>0</v>
@@ -3239,34 +3269,34 @@
         <v>97</v>
       </c>
       <c r="X16" s="9">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="Y16" s="10" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="Z16" s="9">
         <v>20</v>
       </c>
       <c r="AA16" s="10" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="AB16" s="9">
         <v>3</v>
       </c>
       <c r="AC16" s="10" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="AD16" s="9">
-        <v>1036</v>
+        <v>1064</v>
       </c>
       <c r="AE16" s="10" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="AF16" s="9">
         <v>35</v>
       </c>
       <c r="AG16" s="10" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="AH16" s="9">
         <v>1</v>
@@ -3275,16 +3305,16 @@
         <v>111</v>
       </c>
       <c r="AJ16" s="9">
-        <v>447</v>
+        <v>458</v>
       </c>
       <c r="AK16" s="10" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="AL16" s="9">
         <v>57</v>
       </c>
       <c r="AM16" s="10" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="AN16" s="9">
         <v>0</v>
@@ -3307,13 +3337,13 @@
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="C17" s="9">
-        <v>4392</v>
+        <v>4401</v>
       </c>
       <c r="D17" s="9">
         <v>1</v>
@@ -3322,16 +3352,16 @@
         <v>108</v>
       </c>
       <c r="F17" s="9">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="H17" s="9">
         <v>26</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>100</v>
+        <v>242</v>
       </c>
       <c r="J17" s="9">
         <v>0</v>
@@ -3340,10 +3370,10 @@
         <v>97</v>
       </c>
       <c r="L17" s="9">
-        <v>1028</v>
+        <v>1031</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="N17" s="9">
         <v>0</v>
@@ -3355,73 +3385,73 @@
         <v>22</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>237</v>
+        <v>178</v>
       </c>
       <c r="R17" s="9">
         <v>29</v>
       </c>
       <c r="S17" s="10" t="s">
-        <v>238</v>
+        <v>115</v>
       </c>
       <c r="T17" s="9">
         <v>30</v>
       </c>
       <c r="U17" s="10" t="s">
-        <v>239</v>
+        <v>244</v>
       </c>
       <c r="V17" s="9">
         <v>9</v>
       </c>
       <c r="W17" s="10" t="s">
-        <v>167</v>
+        <v>245</v>
       </c>
       <c r="X17" s="9">
         <v>75</v>
       </c>
       <c r="Y17" s="10" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="Z17" s="9">
         <v>2</v>
       </c>
       <c r="AA17" s="10" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="AB17" s="9">
         <v>4</v>
       </c>
       <c r="AC17" s="10" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="AD17" s="9">
-        <v>2194</v>
+        <v>2197</v>
       </c>
       <c r="AE17" s="10" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="AF17" s="9">
         <v>42</v>
       </c>
       <c r="AG17" s="10" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="AH17" s="9">
         <v>3</v>
       </c>
       <c r="AI17" s="10" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="AJ17" s="9">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="AK17" s="10" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="AL17" s="9">
         <v>220</v>
       </c>
       <c r="AM17" s="10" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="AN17" s="9">
         <v>0</v>
@@ -3444,13 +3474,13 @@
     </row>
     <row r="18" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="C18" s="9">
-        <v>5440</v>
+        <v>5478</v>
       </c>
       <c r="D18" s="9">
         <v>0</v>
@@ -3459,16 +3489,16 @@
         <v>97</v>
       </c>
       <c r="F18" s="9">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>250</v>
+        <v>192</v>
       </c>
       <c r="H18" s="9">
         <v>6</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>187</v>
+        <v>135</v>
       </c>
       <c r="J18" s="9">
         <v>0</v>
@@ -3477,10 +3507,10 @@
         <v>97</v>
       </c>
       <c r="L18" s="9">
-        <v>1287</v>
+        <v>1306</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>251</v>
+        <v>256</v>
       </c>
       <c r="N18" s="9">
         <v>0</v>
@@ -3489,22 +3519,22 @@
         <v>97</v>
       </c>
       <c r="P18" s="9">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="Q18" s="10" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="R18" s="9">
         <v>21</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>168</v>
+        <v>257</v>
       </c>
       <c r="T18" s="9">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="U18" s="10" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="V18" s="9">
         <v>0</v>
@@ -3516,13 +3546,13 @@
         <v>99</v>
       </c>
       <c r="Y18" s="10" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="Z18" s="9">
         <v>15</v>
       </c>
       <c r="AA18" s="10" t="s">
-        <v>254</v>
+        <v>160</v>
       </c>
       <c r="AB18" s="9">
         <v>0</v>
@@ -3531,16 +3561,16 @@
         <v>97</v>
       </c>
       <c r="AD18" s="9">
-        <v>2474</v>
+        <v>2491</v>
       </c>
       <c r="AE18" s="10" t="s">
-        <v>255</v>
+        <v>260</v>
       </c>
       <c r="AF18" s="9">
         <v>13</v>
       </c>
       <c r="AG18" s="10" t="s">
-        <v>256</v>
+        <v>261</v>
       </c>
       <c r="AH18" s="9">
         <v>0</v>
@@ -3552,13 +3582,13 @@
         <v>1163</v>
       </c>
       <c r="AK18" s="10" t="s">
-        <v>257</v>
+        <v>262</v>
       </c>
       <c r="AL18" s="9">
         <v>44</v>
       </c>
       <c r="AM18" s="10" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="AN18" s="9">
         <v>0</v>
@@ -3581,13 +3611,13 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>260</v>
+        <v>265</v>
       </c>
       <c r="C19" s="9">
-        <v>8620</v>
+        <v>9957</v>
       </c>
       <c r="D19" s="9">
         <v>0</v>
@@ -3596,16 +3626,16 @@
         <v>97</v>
       </c>
       <c r="F19" s="9">
-        <v>439</v>
+        <v>512</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>261</v>
+        <v>266</v>
       </c>
       <c r="H19" s="9">
         <v>18</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>155</v>
+        <v>267</v>
       </c>
       <c r="J19" s="9">
         <v>0</v>
@@ -3614,10 +3644,10 @@
         <v>97</v>
       </c>
       <c r="L19" s="9">
-        <v>2476</v>
+        <v>2842</v>
       </c>
       <c r="M19" s="10" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="N19" s="9">
         <v>0</v>
@@ -3632,16 +3662,16 @@
         <v>97</v>
       </c>
       <c r="R19" s="9">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="S19" s="10" t="s">
-        <v>152</v>
+        <v>261</v>
       </c>
       <c r="T19" s="9">
         <v>17</v>
       </c>
       <c r="U19" s="10" t="s">
-        <v>167</v>
+        <v>117</v>
       </c>
       <c r="V19" s="9">
         <v>0</v>
@@ -3650,16 +3680,16 @@
         <v>97</v>
       </c>
       <c r="X19" s="9">
+        <v>294</v>
+      </c>
+      <c r="Y19" s="10" t="s">
         <v>269</v>
-      </c>
-      <c r="Y19" s="10" t="s">
-        <v>263</v>
       </c>
       <c r="Z19" s="9">
         <v>4</v>
       </c>
       <c r="AA19" s="10" t="s">
-        <v>241</v>
+        <v>111</v>
       </c>
       <c r="AB19" s="9">
         <v>0</v>
@@ -3668,16 +3698,16 @@
         <v>97</v>
       </c>
       <c r="AD19" s="9">
-        <v>3960</v>
+        <v>4616</v>
       </c>
       <c r="AE19" s="10" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="AF19" s="9">
         <v>26</v>
       </c>
       <c r="AG19" s="10" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="AH19" s="9">
         <v>0</v>
@@ -3686,16 +3716,16 @@
         <v>97</v>
       </c>
       <c r="AJ19" s="9">
-        <v>1241</v>
+        <v>1454</v>
       </c>
       <c r="AK19" s="10" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="AL19" s="9">
         <v>148</v>
       </c>
       <c r="AM19" s="10" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="AN19" s="9">
         <v>0</v>
@@ -3718,13 +3748,13 @@
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C20" s="9">
-        <v>743</v>
+        <v>746</v>
       </c>
       <c r="D20" s="9">
         <v>0</v>
@@ -3736,13 +3766,13 @@
         <v>54</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="H20" s="9">
         <v>6</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>258</v>
+        <v>263</v>
       </c>
       <c r="J20" s="9">
         <v>0</v>
@@ -3751,10 +3781,10 @@
         <v>97</v>
       </c>
       <c r="L20" s="9">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="N20" s="9">
         <v>0</v>
@@ -3766,55 +3796,55 @@
         <v>1</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>207</v>
+        <v>278</v>
       </c>
       <c r="R20" s="9">
         <v>4</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>96</v>
+        <v>279</v>
       </c>
       <c r="T20" s="9">
         <v>42</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="V20" s="9">
         <v>5</v>
       </c>
       <c r="W20" s="10" t="s">
-        <v>115</v>
+        <v>281</v>
       </c>
       <c r="X20" s="9">
         <v>56</v>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>273</v>
+        <v>282</v>
       </c>
       <c r="Z20" s="9">
         <v>91</v>
       </c>
       <c r="AA20" s="10" t="s">
-        <v>274</v>
+        <v>283</v>
       </c>
       <c r="AB20" s="9">
         <v>5</v>
       </c>
       <c r="AC20" s="10" t="s">
-        <v>115</v>
+        <v>281</v>
       </c>
       <c r="AD20" s="9">
         <v>298</v>
       </c>
       <c r="AE20" s="10" t="s">
-        <v>275</v>
+        <v>284</v>
       </c>
       <c r="AF20" s="9">
         <v>12</v>
       </c>
       <c r="AG20" s="10" t="s">
-        <v>276</v>
+        <v>285</v>
       </c>
       <c r="AH20" s="9">
         <v>0</v>
@@ -3823,16 +3853,16 @@
         <v>97</v>
       </c>
       <c r="AJ20" s="9">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="AK20" s="10" t="s">
-        <v>277</v>
+        <v>286</v>
       </c>
       <c r="AL20" s="9">
         <v>19</v>
       </c>
       <c r="AM20" s="10" t="s">
-        <v>278</v>
+        <v>287</v>
       </c>
       <c r="AN20" s="9">
         <v>0</v>
@@ -3850,18 +3880,18 @@
         <v>2</v>
       </c>
       <c r="AS20" s="10" t="s">
-        <v>157</v>
+        <v>160</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>279</v>
+        <v>288</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>280</v>
+        <v>289</v>
       </c>
       <c r="C21" s="9">
-        <v>1504</v>
+        <v>1507</v>
       </c>
       <c r="D21" s="9">
         <v>0</v>
@@ -3870,16 +3900,16 @@
         <v>97</v>
       </c>
       <c r="F21" s="9">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>281</v>
+        <v>290</v>
       </c>
       <c r="H21" s="9">
         <v>6</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J21" s="9">
         <v>0</v>
@@ -3891,7 +3921,7 @@
         <v>176</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>282</v>
+        <v>291</v>
       </c>
       <c r="N21" s="9">
         <v>0</v>
@@ -3900,58 +3930,58 @@
         <v>97</v>
       </c>
       <c r="P21" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q21" s="10" t="s">
-        <v>97</v>
+        <v>251</v>
       </c>
       <c r="R21" s="9">
         <v>9</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>283</v>
+        <v>292</v>
       </c>
       <c r="T21" s="9">
         <v>35</v>
       </c>
       <c r="U21" s="10" t="s">
-        <v>284</v>
+        <v>293</v>
       </c>
       <c r="V21" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="W21" s="10" t="s">
-        <v>245</v>
+        <v>278</v>
       </c>
       <c r="X21" s="9">
         <v>42</v>
       </c>
       <c r="Y21" s="10" t="s">
-        <v>178</v>
+        <v>294</v>
       </c>
       <c r="Z21" s="9">
         <v>39</v>
       </c>
       <c r="AA21" s="10" t="s">
-        <v>285</v>
+        <v>295</v>
       </c>
       <c r="AB21" s="9">
         <v>15</v>
       </c>
       <c r="AC21" s="10" t="s">
-        <v>286</v>
+        <v>296</v>
       </c>
       <c r="AD21" s="9">
         <v>634</v>
       </c>
       <c r="AE21" s="10" t="s">
-        <v>287</v>
+        <v>297</v>
       </c>
       <c r="AF21" s="9">
         <v>3</v>
       </c>
       <c r="AG21" s="10" t="s">
-        <v>167</v>
+        <v>245</v>
       </c>
       <c r="AH21" s="9">
         <v>0</v>
@@ -3963,13 +3993,13 @@
         <v>120</v>
       </c>
       <c r="AK21" s="10" t="s">
-        <v>288</v>
+        <v>298</v>
       </c>
       <c r="AL21" s="9">
         <v>384</v>
       </c>
       <c r="AM21" s="10" t="s">
-        <v>289</v>
+        <v>299</v>
       </c>
       <c r="AN21" s="9">
         <v>0</v>
@@ -3992,13 +4022,13 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>290</v>
+        <v>300</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>291</v>
+        <v>301</v>
       </c>
       <c r="C22" s="12">
-        <v>72712</v>
+        <v>75166</v>
       </c>
       <c r="D22" s="12">
         <v>6</v>
@@ -4007,7 +4037,7 @@
         <v>94</v>
       </c>
       <c r="F22" s="12">
-        <v>3175</v>
+        <v>3318</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>95</v>
@@ -4025,7 +4055,7 @@
         <v>97</v>
       </c>
       <c r="L22" s="12">
-        <v>16048</v>
+        <v>16831</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>98</v>
@@ -4037,49 +4067,49 @@
         <v>97</v>
       </c>
       <c r="P22" s="12">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="Q22" s="13" t="s">
         <v>99</v>
       </c>
       <c r="R22" s="12">
-        <v>431</v>
+        <v>435</v>
       </c>
       <c r="S22" s="13" t="s">
         <v>100</v>
       </c>
       <c r="T22" s="12">
-        <v>1551</v>
+        <v>1554</v>
       </c>
       <c r="U22" s="13" t="s">
         <v>101</v>
       </c>
       <c r="V22" s="12">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="W22" s="13" t="s">
         <v>102</v>
       </c>
       <c r="X22" s="12">
-        <v>2082</v>
+        <v>2129</v>
       </c>
       <c r="Y22" s="13" t="s">
         <v>103</v>
       </c>
       <c r="Z22" s="12">
-        <v>354</v>
+        <v>357</v>
       </c>
       <c r="AA22" s="13" t="s">
         <v>104</v>
       </c>
       <c r="AB22" s="12">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="AC22" s="13" t="s">
         <v>105</v>
       </c>
       <c r="AD22" s="12">
-        <v>31908</v>
+        <v>33023</v>
       </c>
       <c r="AE22" s="13" t="s">
         <v>106</v>
@@ -4097,7 +4127,7 @@
         <v>108</v>
       </c>
       <c r="AJ22" s="12">
-        <v>11655</v>
+        <v>12015</v>
       </c>
       <c r="AK22" s="13" t="s">
         <v>109</v>

--- a/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
+++ b/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="302">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="299">
   <si>
     <t>DATA RADAR ANOMALI KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 11 Sep 2026, 07.32</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 13 Sep 2026, 14.36</t>
   </si>
   <si>
     <t>Kode</t>
@@ -298,619 +298,610 @@
     <t>0,01</t>
   </si>
   <si>
-    <t>4,41</t>
-  </si>
-  <si>
-    <t>0,53</t>
+    <t>4,44</t>
+  </si>
+  <si>
+    <t>0,51</t>
   </si>
   <si>
     <t>0</t>
   </si>
   <si>
-    <t>22,39</t>
-  </si>
-  <si>
-    <t>0,1</t>
+    <t>22,82</t>
+  </si>
+  <si>
+    <t>0,09</t>
+  </si>
+  <si>
+    <t>0,56</t>
+  </si>
+  <si>
+    <t>1,99</t>
+  </si>
+  <si>
+    <t>0,08</t>
+  </si>
+  <si>
+    <t>2,82</t>
+  </si>
+  <si>
+    <t>0,46</t>
+  </si>
+  <si>
+    <t>0,27</t>
+  </si>
+  <si>
+    <t>43,95</t>
+  </si>
+  <si>
+    <t>0,8</t>
+  </si>
+  <si>
+    <t>0,02</t>
+  </si>
+  <si>
+    <t>15,94</t>
+  </si>
+  <si>
+    <t>5,22</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>LAMPUNG BARAT</t>
+  </si>
+  <si>
+    <t>4,29</t>
+  </si>
+  <si>
+    <t>0,66</t>
+  </si>
+  <si>
+    <t>28,47</t>
+  </si>
+  <si>
+    <t>0,16</t>
+  </si>
+  <si>
+    <t>0,45</t>
+  </si>
+  <si>
+    <t>0,41</t>
+  </si>
+  <si>
+    <t>4,16</t>
+  </si>
+  <si>
+    <t>0,47</t>
+  </si>
+  <si>
+    <t>0,12</t>
+  </si>
+  <si>
+    <t>39,63</t>
+  </si>
+  <si>
+    <t>0,43</t>
+  </si>
+  <si>
+    <t>0,06</t>
+  </si>
+  <si>
+    <t>12,8</t>
+  </si>
+  <si>
+    <t>7,86</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>TANGGAMUS</t>
+  </si>
+  <si>
+    <t>6,64</t>
+  </si>
+  <si>
+    <t>19,86</t>
+  </si>
+  <si>
+    <t>0,86</t>
+  </si>
+  <si>
+    <t>3,43</t>
+  </si>
+  <si>
+    <t>3,32</t>
+  </si>
+  <si>
+    <t>0,29</t>
+  </si>
+  <si>
+    <t>0,11</t>
+  </si>
+  <si>
+    <t>41,73</t>
+  </si>
+  <si>
+    <t>22,95</t>
+  </si>
+  <si>
+    <t>0,4</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>LAMPUNG SELATAN</t>
+  </si>
+  <si>
+    <t>5,7</t>
+  </si>
+  <si>
+    <t>0,3</t>
+  </si>
+  <si>
+    <t>21,84</t>
+  </si>
+  <si>
+    <t>2,61</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>3,21</t>
+  </si>
+  <si>
+    <t>0,61</t>
+  </si>
+  <si>
+    <t>43,85</t>
+  </si>
+  <si>
+    <t>3,23</t>
+  </si>
+  <si>
+    <t>17,19</t>
+  </si>
+  <si>
+    <t>0,92</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>4,19</t>
+  </si>
+  <si>
+    <t>0,28</t>
+  </si>
+  <si>
+    <t>26,57</t>
+  </si>
+  <si>
+    <t>0,23</t>
+  </si>
+  <si>
+    <t>0,89</t>
+  </si>
+  <si>
+    <t>2,08</t>
+  </si>
+  <si>
+    <t>0,2</t>
+  </si>
+  <si>
+    <t>2,99</t>
+  </si>
+  <si>
+    <t>0,26</t>
+  </si>
+  <si>
+    <t>1,23</t>
+  </si>
+  <si>
+    <t>43,74</t>
+  </si>
+  <si>
+    <t>0,33</t>
+  </si>
+  <si>
+    <t>15,53</t>
+  </si>
+  <si>
+    <t>1,34</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
+    <t>4,48</t>
+  </si>
+  <si>
+    <t>24,16</t>
+  </si>
+  <si>
+    <t>0,19</t>
+  </si>
+  <si>
+    <t>0,36</t>
+  </si>
+  <si>
+    <t>4,79</t>
+  </si>
+  <si>
+    <t>3,81</t>
+  </si>
+  <si>
+    <t>0,15</t>
+  </si>
+  <si>
+    <t>45,75</t>
+  </si>
+  <si>
+    <t>14,41</t>
+  </si>
+  <si>
+    <t>0,49</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>2,84</t>
+  </si>
+  <si>
+    <t>2,03</t>
+  </si>
+  <si>
+    <t>17,94</t>
+  </si>
+  <si>
+    <t>0,39</t>
+  </si>
+  <si>
+    <t>2,42</t>
+  </si>
+  <si>
+    <t>0,5</t>
+  </si>
+  <si>
+    <t>43,04</t>
+  </si>
+  <si>
+    <t>0,69</t>
+  </si>
+  <si>
+    <t>16,62</t>
+  </si>
+  <si>
+    <t>11,38</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>4,22</t>
+  </si>
+  <si>
+    <t>20,73</t>
   </si>
   <si>
     <t>0,58</t>
   </si>
   <si>
-    <t>2,07</t>
-  </si>
-  <si>
-    <t>0,08</t>
-  </si>
-  <si>
-    <t>2,83</t>
-  </si>
-  <si>
-    <t>0,47</t>
-  </si>
-  <si>
-    <t>0,3</t>
-  </si>
-  <si>
-    <t>43,93</t>
-  </si>
-  <si>
-    <t>0,83</t>
-  </si>
-  <si>
-    <t>0,02</t>
-  </si>
-  <si>
-    <t>15,98</t>
-  </si>
-  <si>
-    <t>5,42</t>
-  </si>
-  <si>
-    <t>0,04</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>LAMPUNG BARAT</t>
-  </si>
-  <si>
-    <t>4,22</t>
-  </si>
-  <si>
-    <t>0,66</t>
-  </si>
-  <si>
-    <t>28,41</t>
-  </si>
-  <si>
-    <t>0,17</t>
-  </si>
-  <si>
-    <t>0,46</t>
-  </si>
-  <si>
-    <t>0,42</t>
-  </si>
-  <si>
-    <t>4,15</t>
-  </si>
-  <si>
-    <t>0,48</t>
-  </si>
-  <si>
-    <t>39,74</t>
+    <t>2,26</t>
+  </si>
+  <si>
+    <t>2,9</t>
+  </si>
+  <si>
+    <t>1,55</t>
+  </si>
+  <si>
+    <t>40,33</t>
   </si>
   <si>
     <t>0,44</t>
   </si>
   <si>
-    <t>12,77</t>
-  </si>
-  <si>
-    <t>7,91</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>TANGGAMUS</t>
-  </si>
-  <si>
-    <t>6,64</t>
-  </si>
-  <si>
-    <t>19,87</t>
-  </si>
-  <si>
-    <t>0,06</t>
-  </si>
-  <si>
-    <t>0,86</t>
-  </si>
-  <si>
-    <t>3,44</t>
-  </si>
-  <si>
-    <t>3,32</t>
-  </si>
-  <si>
-    <t>0,29</t>
-  </si>
-  <si>
-    <t>0,11</t>
-  </si>
-  <si>
-    <t>41,75</t>
-  </si>
-  <si>
-    <t>22,97</t>
-  </si>
-  <si>
-    <t>0,4</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>LAMPUNG SELATAN</t>
-  </si>
-  <si>
-    <t>5,74</t>
-  </si>
-  <si>
-    <t>21,44</t>
-  </si>
-  <si>
-    <t>2,68</t>
-  </si>
-  <si>
-    <t>3,17</t>
-  </si>
-  <si>
-    <t>0,62</t>
-  </si>
-  <si>
-    <t>43,98</t>
-  </si>
-  <si>
-    <t>3,31</t>
-  </si>
-  <si>
-    <t>17,27</t>
-  </si>
-  <si>
-    <t>0,94</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>0,03</t>
-  </si>
-  <si>
-    <t>4,21</t>
-  </si>
-  <si>
-    <t>26,52</t>
-  </si>
-  <si>
-    <t>0,23</t>
-  </si>
-  <si>
-    <t>0,91</t>
-  </si>
-  <si>
-    <t>2,14</t>
+    <t>25,2</t>
+  </si>
+  <si>
+    <t>1,08</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG</t>
+  </si>
+  <si>
+    <t>4,32</t>
+  </si>
+  <si>
+    <t>0,67</t>
+  </si>
+  <si>
+    <t>24</t>
+  </si>
+  <si>
+    <t>1,1</t>
+  </si>
+  <si>
+    <t>2,4</t>
+  </si>
+  <si>
+    <t>2,2</t>
+  </si>
+  <si>
+    <t>46,7</t>
+  </si>
+  <si>
+    <t>14,1</t>
+  </si>
+  <si>
+    <t>3,89</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>1,14</t>
+  </si>
+  <si>
+    <t>13,46</t>
+  </si>
+  <si>
+    <t>1,01</t>
+  </si>
+  <si>
+    <t>1,46</t>
+  </si>
+  <si>
+    <t>1,29</t>
+  </si>
+  <si>
+    <t>0,14</t>
+  </si>
+  <si>
+    <t>40,7</t>
+  </si>
+  <si>
+    <t>0,85</t>
+  </si>
+  <si>
+    <t>14,71</t>
+  </si>
+  <si>
+    <t>21,88</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>5,06</t>
+  </si>
+  <si>
+    <t>0,24</t>
+  </si>
+  <si>
+    <t>17,56</t>
+  </si>
+  <si>
+    <t>1,22</t>
+  </si>
+  <si>
+    <t>4,57</t>
+  </si>
+  <si>
+    <t>3,96</t>
+  </si>
+  <si>
+    <t>0,82</t>
+  </si>
+  <si>
+    <t>43,9</t>
+  </si>
+  <si>
+    <t>1,43</t>
+  </si>
+  <si>
+    <t>18,82</t>
+  </si>
+  <si>
+    <t>2,33</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
+  </si>
+  <si>
+    <t>4,66</t>
+  </si>
+  <si>
+    <t>0,59</t>
+  </si>
+  <si>
+    <t>23,43</t>
+  </si>
+  <si>
+    <t>0,68</t>
+  </si>
+  <si>
+    <t>1,7</t>
+  </si>
+  <si>
+    <t>49,92</t>
+  </si>
+  <si>
+    <t>0,95</t>
+  </si>
+  <si>
+    <t>0,07</t>
+  </si>
+  <si>
+    <t>11,47</t>
+  </si>
+  <si>
+    <t>5</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>4,25</t>
+  </si>
+  <si>
+    <t>23,84</t>
+  </si>
+  <si>
+    <t>0,38</t>
+  </si>
+  <si>
+    <t>1,59</t>
+  </si>
+  <si>
+    <t>1,81</t>
+  </si>
+  <si>
+    <t>45,46</t>
+  </si>
+  <si>
+    <t>21,24</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>5,17</t>
+  </si>
+  <si>
+    <t>29,5</t>
   </si>
   <si>
     <t>0,21</t>
   </si>
   <si>
-    <t>3,04</t>
-  </si>
-  <si>
-    <t>0,27</t>
-  </si>
-  <si>
-    <t>1,26</t>
-  </si>
-  <si>
-    <t>43,5</t>
-  </si>
-  <si>
-    <t>0,33</t>
-  </si>
-  <si>
-    <t>15,57</t>
-  </si>
-  <si>
-    <t>1,37</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>4,45</t>
-  </si>
-  <si>
-    <t>24,07</t>
-  </si>
-  <si>
-    <t>0,19</t>
-  </si>
-  <si>
-    <t>0,37</t>
-  </si>
-  <si>
-    <t>4,86</t>
-  </si>
-  <si>
-    <t>3,8</t>
-  </si>
-  <si>
-    <t>0,15</t>
-  </si>
-  <si>
-    <t>45,69</t>
-  </si>
-  <si>
-    <t>0,93</t>
-  </si>
-  <si>
-    <t>14,49</t>
-  </si>
-  <si>
-    <t>0,5</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>2,84</t>
-  </si>
-  <si>
-    <t>2,03</t>
-  </si>
-  <si>
-    <t>17,93</t>
-  </si>
-  <si>
-    <t>0,39</t>
-  </si>
-  <si>
-    <t>2,42</t>
-  </si>
-  <si>
-    <t>43,04</t>
-  </si>
-  <si>
-    <t>0,69</t>
-  </si>
-  <si>
-    <t>16,62</t>
-  </si>
-  <si>
-    <t>11,39</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>4,25</t>
-  </si>
-  <si>
-    <t>20,33</t>
-  </si>
-  <si>
-    <t>0,14</t>
-  </si>
-  <si>
-    <t>0,56</t>
+    <t>2,79</t>
+  </si>
+  <si>
+    <t>45,74</t>
+  </si>
+  <si>
+    <t>14,82</t>
+  </si>
+  <si>
+    <t>1871</t>
+  </si>
+  <si>
+    <t>BANDAR LAMPUNG</t>
+  </si>
+  <si>
+    <t>7,33</t>
+  </si>
+  <si>
+    <t>0,79</t>
+  </si>
+  <si>
+    <t>10,86</t>
+  </si>
+  <si>
+    <t>0,13</t>
+  </si>
+  <si>
+    <t>0,52</t>
+  </si>
+  <si>
+    <t>5,5</t>
+  </si>
+  <si>
+    <t>0,65</t>
+  </si>
+  <si>
+    <t>7,72</t>
+  </si>
+  <si>
+    <t>11,91</t>
+  </si>
+  <si>
+    <t>40,31</t>
+  </si>
+  <si>
+    <t>1,57</t>
+  </si>
+  <si>
+    <t>9,42</t>
+  </si>
+  <si>
+    <t>2,49</t>
+  </si>
+  <si>
+    <t>1872</t>
+  </si>
+  <si>
+    <t>METRO</t>
+  </si>
+  <si>
+    <t>2,77</t>
+  </si>
+  <si>
+    <t>11,79</t>
   </si>
   <si>
     <t>2,31</t>
   </si>
   <si>
-    <t>2,87</t>
-  </si>
-  <si>
-    <t>1,94</t>
-  </si>
-  <si>
-    <t>40,21</t>
-  </si>
-  <si>
-    <t>0,34</t>
-  </si>
-  <si>
-    <t>25,34</t>
-  </si>
-  <si>
-    <t>1,1</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG</t>
-  </si>
-  <si>
-    <t>4,38</t>
-  </si>
-  <si>
-    <t>0,7</t>
-  </si>
-  <si>
-    <t>23,51</t>
-  </si>
-  <si>
-    <t>0,25</t>
-  </si>
-  <si>
-    <t>1,16</t>
-  </si>
-  <si>
-    <t>2,48</t>
-  </si>
-  <si>
-    <t>0,12</t>
-  </si>
-  <si>
-    <t>2,27</t>
-  </si>
-  <si>
-    <t>46,03</t>
-  </si>
-  <si>
-    <t>14,67</t>
-  </si>
-  <si>
-    <t>4,09</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>1,14</t>
-  </si>
-  <si>
-    <t>13,46</t>
-  </si>
-  <si>
-    <t>1,02</t>
-  </si>
-  <si>
-    <t>1,46</t>
-  </si>
-  <si>
-    <t>1,29</t>
-  </si>
-  <si>
-    <t>40,69</t>
-  </si>
-  <si>
-    <t>0,85</t>
-  </si>
-  <si>
-    <t>14,71</t>
-  </si>
-  <si>
-    <t>21,89</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>5,06</t>
-  </si>
-  <si>
-    <t>17,29</t>
-  </si>
-  <si>
-    <t>1,24</t>
-  </si>
-  <si>
-    <t>4,61</t>
-  </si>
-  <si>
-    <t>3,99</t>
-  </si>
-  <si>
-    <t>0,82</t>
-  </si>
-  <si>
-    <t>43,8</t>
-  </si>
-  <si>
-    <t>1,44</t>
-  </si>
-  <si>
-    <t>18,86</t>
-  </si>
-  <si>
-    <t>2,35</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>4,66</t>
-  </si>
-  <si>
-    <t>0,59</t>
-  </si>
-  <si>
-    <t>23,43</t>
-  </si>
-  <si>
-    <t>0,68</t>
-  </si>
-  <si>
-    <t>0,2</t>
-  </si>
-  <si>
-    <t>1,7</t>
-  </si>
-  <si>
-    <t>0,05</t>
-  </si>
-  <si>
-    <t>0,09</t>
-  </si>
-  <si>
-    <t>49,92</t>
-  </si>
-  <si>
-    <t>0,95</t>
-  </si>
-  <si>
-    <t>0,07</t>
-  </si>
-  <si>
-    <t>11,47</t>
-  </si>
-  <si>
-    <t>5</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>23,84</t>
-  </si>
-  <si>
-    <t>0,38</t>
-  </si>
-  <si>
-    <t>1,59</t>
-  </si>
-  <si>
-    <t>1,81</t>
-  </si>
-  <si>
-    <t>45,47</t>
-  </si>
-  <si>
-    <t>0,24</t>
-  </si>
-  <si>
-    <t>21,23</t>
-  </si>
-  <si>
-    <t>0,8</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>5,14</t>
-  </si>
-  <si>
-    <t>0,18</t>
-  </si>
-  <si>
-    <t>28,54</t>
-  </si>
-  <si>
-    <t>2,95</t>
-  </si>
-  <si>
-    <t>46,36</t>
-  </si>
-  <si>
-    <t>0,26</t>
-  </si>
-  <si>
-    <t>14,6</t>
-  </si>
-  <si>
-    <t>1,49</t>
-  </si>
-  <si>
-    <t>1871</t>
-  </si>
-  <si>
-    <t>BANDAR LAMPUNG</t>
-  </si>
-  <si>
-    <t>7,24</t>
-  </si>
-  <si>
-    <t>11,13</t>
-  </si>
-  <si>
-    <t>0,13</t>
-  </si>
-  <si>
-    <t>0,54</t>
-  </si>
-  <si>
-    <t>5,63</t>
-  </si>
-  <si>
-    <t>0,67</t>
-  </si>
-  <si>
-    <t>7,51</t>
-  </si>
-  <si>
-    <t>12,2</t>
-  </si>
-  <si>
-    <t>39,95</t>
-  </si>
-  <si>
-    <t>1,61</t>
-  </si>
-  <si>
-    <t>9,12</t>
-  </si>
-  <si>
-    <t>2,55</t>
-  </si>
-  <si>
-    <t>1872</t>
-  </si>
-  <si>
-    <t>METRO</t>
-  </si>
-  <si>
-    <t>2,72</t>
-  </si>
-  <si>
-    <t>11,68</t>
-  </si>
-  <si>
-    <t>0,6</t>
-  </si>
-  <si>
-    <t>2,32</t>
-  </si>
-  <si>
-    <t>2,79</t>
-  </si>
-  <si>
-    <t>2,59</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
-    <t>42,07</t>
-  </si>
-  <si>
-    <t>7,96</t>
-  </si>
-  <si>
-    <t>25,48</t>
+    <t>2,96</t>
+  </si>
+  <si>
+    <t>2,57</t>
+  </si>
+  <si>
+    <t>0,99</t>
+  </si>
+  <si>
+    <t>42,09</t>
+  </si>
+  <si>
+    <t>7,97</t>
+  </si>
+  <si>
+    <t>25,3</t>
   </si>
   <si>
     <t/>
@@ -1836,7 +1827,7 @@
         <v>93</v>
       </c>
       <c r="C6" s="6">
-        <v>75166</v>
+        <v>78157</v>
       </c>
       <c r="D6" s="6">
         <v>6</v>
@@ -1845,7 +1836,7 @@
         <v>94</v>
       </c>
       <c r="F6" s="6">
-        <v>3318</v>
+        <v>3471</v>
       </c>
       <c r="G6" s="7" t="s">
         <v>95</v>
@@ -1863,7 +1854,7 @@
         <v>97</v>
       </c>
       <c r="L6" s="6">
-        <v>16831</v>
+        <v>17835</v>
       </c>
       <c r="M6" s="7" t="s">
         <v>98</v>
@@ -1875,31 +1866,31 @@
         <v>97</v>
       </c>
       <c r="P6" s="6">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Q6" s="7" t="s">
         <v>99</v>
       </c>
       <c r="R6" s="6">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="S6" s="7" t="s">
         <v>100</v>
       </c>
       <c r="T6" s="6">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="U6" s="7" t="s">
         <v>101</v>
       </c>
       <c r="V6" s="6">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="W6" s="7" t="s">
         <v>102</v>
       </c>
       <c r="X6" s="6">
-        <v>2129</v>
+        <v>2202</v>
       </c>
       <c r="Y6" s="7" t="s">
         <v>103</v>
@@ -1911,31 +1902,31 @@
         <v>104</v>
       </c>
       <c r="AB6" s="6">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="AC6" s="7" t="s">
         <v>105</v>
       </c>
       <c r="AD6" s="6">
-        <v>33023</v>
+        <v>34351</v>
       </c>
       <c r="AE6" s="7" t="s">
         <v>106</v>
       </c>
       <c r="AF6" s="6">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="AG6" s="7" t="s">
         <v>107</v>
       </c>
       <c r="AH6" s="6">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI6" s="7" t="s">
         <v>108</v>
       </c>
       <c r="AJ6" s="6">
-        <v>12015</v>
+        <v>12460</v>
       </c>
       <c r="AK6" s="7" t="s">
         <v>109</v>
@@ -1947,7 +1938,7 @@
         <v>110</v>
       </c>
       <c r="AN6" s="6">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO6" s="7" t="s">
         <v>97</v>
@@ -1959,7 +1950,7 @@
         <v>97</v>
       </c>
       <c r="AR6" s="6">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS6" s="7" t="s">
         <v>111</v>
@@ -1973,7 +1964,7 @@
         <v>113</v>
       </c>
       <c r="C7" s="9">
-        <v>4816</v>
+        <v>4850</v>
       </c>
       <c r="D7" s="9">
         <v>0</v>
@@ -1982,7 +1973,7 @@
         <v>97</v>
       </c>
       <c r="F7" s="9">
-        <v>203</v>
+        <v>208</v>
       </c>
       <c r="G7" s="10" t="s">
         <v>114</v>
@@ -2000,7 +1991,7 @@
         <v>97</v>
       </c>
       <c r="L7" s="9">
-        <v>1368</v>
+        <v>1381</v>
       </c>
       <c r="M7" s="10" t="s">
         <v>116</v>
@@ -2036,7 +2027,7 @@
         <v>119</v>
       </c>
       <c r="X7" s="9">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="Y7" s="10" t="s">
         <v>120</v>
@@ -2048,40 +2039,40 @@
         <v>121</v>
       </c>
       <c r="AB7" s="9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AC7" s="10" t="s">
-        <v>99</v>
+        <v>122</v>
       </c>
       <c r="AD7" s="9">
-        <v>1914</v>
+        <v>1922</v>
       </c>
       <c r="AE7" s="10" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="AF7" s="9">
         <v>21</v>
       </c>
       <c r="AG7" s="10" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="AH7" s="9">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AI7" s="10" t="s">
-        <v>102</v>
+        <v>125</v>
       </c>
       <c r="AJ7" s="9">
-        <v>615</v>
+        <v>621</v>
       </c>
       <c r="AK7" s="10" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="AL7" s="9">
         <v>381</v>
       </c>
       <c r="AM7" s="10" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="AN7" s="9">
         <v>0</v>
@@ -2104,13 +2095,13 @@
     </row>
     <row r="8" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C8" s="9">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="D8" s="9">
         <v>0</v>
@@ -2122,7 +2113,7 @@
         <v>116</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
@@ -2140,7 +2131,7 @@
         <v>347</v>
       </c>
       <c r="M8" s="10" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="N8" s="9">
         <v>0</v>
@@ -2152,19 +2143,19 @@
         <v>1</v>
       </c>
       <c r="Q8" s="10" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="R8" s="9">
         <v>15</v>
       </c>
       <c r="S8" s="10" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="T8" s="9">
         <v>60</v>
       </c>
       <c r="U8" s="10" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="V8" s="9">
         <v>0</v>
@@ -2176,49 +2167,49 @@
         <v>58</v>
       </c>
       <c r="Y8" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="Z8" s="9">
         <v>5</v>
       </c>
       <c r="AA8" s="10" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="AB8" s="9">
         <v>2</v>
       </c>
       <c r="AC8" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AD8" s="9">
         <v>729</v>
       </c>
       <c r="AE8" s="10" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="AF8" s="9">
         <v>2</v>
       </c>
       <c r="AG8" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="AH8" s="9">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AI8" s="10" t="s">
-        <v>130</v>
+        <v>136</v>
       </c>
       <c r="AJ8" s="9">
         <v>401</v>
       </c>
       <c r="AK8" s="10" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="AL8" s="9">
         <v>7</v>
       </c>
       <c r="AM8" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="AN8" s="9">
         <v>0</v>
@@ -2236,18 +2227,18 @@
         <v>2</v>
       </c>
       <c r="AS8" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="9" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C9" s="9">
-        <v>7214</v>
+        <v>7404</v>
       </c>
       <c r="D9" s="9">
         <v>0</v>
@@ -2256,16 +2247,16 @@
         <v>97</v>
       </c>
       <c r="F9" s="9">
-        <v>414</v>
+        <v>422</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="H9" s="9">
         <v>22</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>105</v>
+        <v>143</v>
       </c>
       <c r="J9" s="9">
         <v>0</v>
@@ -2274,10 +2265,10 @@
         <v>97</v>
       </c>
       <c r="L9" s="9">
-        <v>1547</v>
+        <v>1617</v>
       </c>
       <c r="M9" s="10" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="N9" s="9">
         <v>0</v>
@@ -2301,25 +2292,25 @@
         <v>193</v>
       </c>
       <c r="U9" s="10" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="V9" s="9">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="W9" s="10" t="s">
-        <v>97</v>
+        <v>146</v>
       </c>
       <c r="X9" s="9">
-        <v>229</v>
+        <v>238</v>
       </c>
       <c r="Y9" s="10" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="Z9" s="9">
         <v>45</v>
       </c>
       <c r="AA9" s="10" t="s">
-        <v>145</v>
+        <v>148</v>
       </c>
       <c r="AB9" s="9">
         <v>0</v>
@@ -2328,16 +2319,16 @@
         <v>97</v>
       </c>
       <c r="AD9" s="9">
-        <v>3173</v>
+        <v>3247</v>
       </c>
       <c r="AE9" s="10" t="s">
-        <v>146</v>
+        <v>149</v>
       </c>
       <c r="AF9" s="9">
         <v>239</v>
       </c>
       <c r="AG9" s="10" t="s">
-        <v>147</v>
+        <v>150</v>
       </c>
       <c r="AH9" s="9">
         <v>0</v>
@@ -2346,16 +2337,16 @@
         <v>97</v>
       </c>
       <c r="AJ9" s="9">
-        <v>1246</v>
+        <v>1273</v>
       </c>
       <c r="AK9" s="10" t="s">
-        <v>148</v>
+        <v>151</v>
       </c>
       <c r="AL9" s="9">
         <v>68</v>
       </c>
       <c r="AM9" s="10" t="s">
-        <v>149</v>
+        <v>152</v>
       </c>
       <c r="AN9" s="9">
         <v>0</v>
@@ -2373,36 +2364,36 @@
         <v>4</v>
       </c>
       <c r="AS9" s="10" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C10" s="9">
-        <v>8660</v>
+        <v>8877</v>
       </c>
       <c r="D10" s="9">
         <v>3</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F10" s="9">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="H10" s="9">
         <v>25</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>134</v>
+        <v>157</v>
       </c>
       <c r="J10" s="9">
         <v>0</v>
@@ -2411,10 +2402,10 @@
         <v>97</v>
       </c>
       <c r="L10" s="9">
-        <v>2297</v>
+        <v>2359</v>
       </c>
       <c r="M10" s="10" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="N10" s="9">
         <v>1</v>
@@ -2426,73 +2417,73 @@
         <v>20</v>
       </c>
       <c r="Q10" s="10" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="R10" s="9">
         <v>79</v>
       </c>
       <c r="S10" s="10" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="T10" s="9">
         <v>185</v>
       </c>
       <c r="U10" s="10" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="V10" s="9">
         <v>18</v>
       </c>
       <c r="W10" s="10" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="X10" s="9">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="Y10" s="10" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="Z10" s="9">
         <v>23</v>
       </c>
       <c r="AA10" s="10" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="AB10" s="9">
         <v>109</v>
       </c>
       <c r="AC10" s="10" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="AD10" s="9">
-        <v>3767</v>
+        <v>3883</v>
       </c>
       <c r="AE10" s="10" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="AF10" s="9">
         <v>29</v>
       </c>
       <c r="AG10" s="10" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="AH10" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AI10" s="10" t="s">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="AJ10" s="9">
-        <v>1348</v>
+        <v>1379</v>
       </c>
       <c r="AK10" s="10" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="AL10" s="9">
         <v>119</v>
       </c>
       <c r="AM10" s="10" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="AN10" s="9">
         <v>1</v>
@@ -2510,18 +2501,18 @@
         <v>3</v>
       </c>
       <c r="AS10" s="10" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="11" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C11" s="9">
-        <v>7840</v>
+        <v>7962</v>
       </c>
       <c r="D11" s="9">
         <v>1</v>
@@ -2530,10 +2521,10 @@
         <v>94</v>
       </c>
       <c r="F11" s="9">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="H11" s="9">
         <v>6</v>
@@ -2548,10 +2539,10 @@
         <v>97</v>
       </c>
       <c r="L11" s="9">
-        <v>1887</v>
+        <v>1924</v>
       </c>
       <c r="M11" s="10" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="N11" s="9">
         <v>0</v>
@@ -2563,19 +2554,19 @@
         <v>15</v>
       </c>
       <c r="Q11" s="10" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="R11" s="9">
         <v>29</v>
       </c>
       <c r="S11" s="10" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="T11" s="9">
         <v>381</v>
       </c>
       <c r="U11" s="10" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="V11" s="9">
         <v>1</v>
@@ -2584,34 +2575,34 @@
         <v>94</v>
       </c>
       <c r="X11" s="9">
-        <v>298</v>
+        <v>303</v>
       </c>
       <c r="Y11" s="10" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="Z11" s="9">
         <v>29</v>
       </c>
       <c r="AA11" s="10" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="AB11" s="9">
         <v>12</v>
       </c>
       <c r="AC11" s="10" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="AD11" s="9">
-        <v>3582</v>
+        <v>3643</v>
       </c>
       <c r="AE11" s="10" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="AF11" s="9">
         <v>73</v>
       </c>
       <c r="AG11" s="10" t="s">
-        <v>176</v>
+        <v>152</v>
       </c>
       <c r="AH11" s="9">
         <v>0</v>
@@ -2620,16 +2611,16 @@
         <v>97</v>
       </c>
       <c r="AJ11" s="9">
-        <v>1136</v>
+        <v>1147</v>
       </c>
       <c r="AK11" s="10" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="AL11" s="9">
         <v>39</v>
       </c>
       <c r="AM11" s="10" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="AN11" s="9">
         <v>0</v>
@@ -2647,18 +2638,18 @@
         <v>2</v>
       </c>
       <c r="AS11" s="10" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
     </row>
     <row r="12" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="C12" s="9">
-        <v>6647</v>
+        <v>6650</v>
       </c>
       <c r="D12" s="9">
         <v>0</v>
@@ -2670,13 +2661,13 @@
         <v>189</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="H12" s="9">
         <v>135</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="J12" s="9">
         <v>0</v>
@@ -2685,10 +2676,10 @@
         <v>97</v>
       </c>
       <c r="L12" s="9">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="M12" s="10" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="N12" s="9">
         <v>0</v>
@@ -2706,31 +2697,31 @@
         <v>26</v>
       </c>
       <c r="S12" s="10" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="T12" s="9">
         <v>135</v>
       </c>
       <c r="U12" s="10" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="V12" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12" s="10" t="s">
-        <v>97</v>
+        <v>108</v>
       </c>
       <c r="X12" s="9">
         <v>161</v>
       </c>
       <c r="Y12" s="10" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="Z12" s="9">
         <v>33</v>
       </c>
       <c r="AA12" s="10" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="AB12" s="9">
         <v>0</v>
@@ -2739,16 +2730,16 @@
         <v>97</v>
       </c>
       <c r="AD12" s="9">
-        <v>2861</v>
+        <v>2862</v>
       </c>
       <c r="AE12" s="10" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="AF12" s="9">
         <v>46</v>
       </c>
       <c r="AG12" s="10" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="AH12" s="9">
         <v>0</v>
@@ -2760,13 +2751,13 @@
         <v>1105</v>
       </c>
       <c r="AK12" s="10" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="AL12" s="9">
         <v>757</v>
       </c>
       <c r="AM12" s="10" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="AN12" s="9">
         <v>0</v>
@@ -2784,36 +2775,36 @@
         <v>7</v>
       </c>
       <c r="AS12" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
     </row>
     <row r="13" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="C13" s="9">
-        <v>3556</v>
+        <v>3623</v>
       </c>
       <c r="D13" s="9">
         <v>1</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="F13" s="9">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="H13" s="9">
         <v>2</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="J13" s="9">
         <v>0</v>
@@ -2822,117 +2813,117 @@
         <v>97</v>
       </c>
       <c r="L13" s="9">
-        <v>723</v>
+        <v>751</v>
       </c>
       <c r="M13" s="10" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="N13" s="9">
         <v>1</v>
       </c>
       <c r="O13" s="10" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="P13" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="Q13" s="10" t="s">
-        <v>194</v>
+        <v>136</v>
       </c>
       <c r="R13" s="9">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="S13" s="10" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="T13" s="9">
         <v>82</v>
       </c>
       <c r="U13" s="10" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="V13" s="9">
         <v>1</v>
       </c>
       <c r="W13" s="10" t="s">
-        <v>152</v>
+        <v>146</v>
       </c>
       <c r="X13" s="9">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="Y13" s="10" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="Z13" s="9">
         <v>14</v>
       </c>
       <c r="AA13" s="10" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="AB13" s="9">
-        <v>69</v>
+        <v>56</v>
       </c>
       <c r="AC13" s="10" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="AD13" s="9">
-        <v>1430</v>
+        <v>1461</v>
       </c>
       <c r="AE13" s="10" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="AF13" s="9">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="AG13" s="10" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="AH13" s="9">
         <v>2</v>
       </c>
       <c r="AI13" s="10" t="s">
-        <v>130</v>
+        <v>125</v>
       </c>
       <c r="AJ13" s="9">
-        <v>901</v>
+        <v>913</v>
       </c>
       <c r="AK13" s="10" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="AL13" s="9">
         <v>39</v>
       </c>
       <c r="AM13" s="10" t="s">
-        <v>202</v>
+        <v>205</v>
       </c>
       <c r="AN13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR13" s="9">
         <v>1</v>
       </c>
-      <c r="AO13" s="10" t="s">
-        <v>152</v>
-      </c>
-      <c r="AP13" s="9">
-        <v>0</v>
-      </c>
-      <c r="AQ13" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="AR13" s="9">
-        <v>0</v>
-      </c>
       <c r="AS13" s="10" t="s">
-        <v>97</v>
+        <v>146</v>
       </c>
     </row>
     <row r="14" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="C14" s="9">
-        <v>2420</v>
+        <v>2546</v>
       </c>
       <c r="D14" s="9">
         <v>0</v>
@@ -2941,16 +2932,16 @@
         <v>97</v>
       </c>
       <c r="F14" s="9">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="H14" s="9">
         <v>17</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="J14" s="9">
         <v>0</v>
@@ -2959,10 +2950,10 @@
         <v>97</v>
       </c>
       <c r="L14" s="9">
-        <v>569</v>
+        <v>611</v>
       </c>
       <c r="M14" s="10" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="N14" s="9">
         <v>1</v>
@@ -2971,40 +2962,40 @@
         <v>111</v>
       </c>
       <c r="P14" s="9">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Q14" s="10" t="s">
-        <v>208</v>
+        <v>162</v>
       </c>
       <c r="R14" s="9">
         <v>28</v>
       </c>
       <c r="S14" s="10" t="s">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="T14" s="9">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="U14" s="10" t="s">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="V14" s="9">
         <v>3</v>
       </c>
       <c r="W14" s="10" t="s">
-        <v>211</v>
+        <v>122</v>
       </c>
       <c r="X14" s="9">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="Y14" s="10" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
       <c r="Z14" s="9">
         <v>3</v>
       </c>
       <c r="AA14" s="10" t="s">
-        <v>211</v>
+        <v>122</v>
       </c>
       <c r="AB14" s="9">
         <v>0</v>
@@ -3013,10 +3004,10 @@
         <v>97</v>
       </c>
       <c r="AD14" s="9">
-        <v>1114</v>
+        <v>1189</v>
       </c>
       <c r="AE14" s="10" t="s">
-        <v>213</v>
+        <v>214</v>
       </c>
       <c r="AF14" s="9">
         <v>2</v>
@@ -3031,16 +3022,16 @@
         <v>97</v>
       </c>
       <c r="AJ14" s="9">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="AK14" s="10" t="s">
-        <v>214</v>
+        <v>215</v>
       </c>
       <c r="AL14" s="9">
         <v>99</v>
       </c>
       <c r="AM14" s="10" t="s">
-        <v>215</v>
+        <v>216</v>
       </c>
       <c r="AN14" s="9">
         <v>0</v>
@@ -3063,13 +3054,13 @@
     </row>
     <row r="15" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>216</v>
+        <v>217</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>217</v>
+        <v>218</v>
       </c>
       <c r="C15" s="9">
-        <v>7749</v>
+        <v>7750</v>
       </c>
       <c r="D15" s="9">
         <v>0</v>
@@ -3081,13 +3072,13 @@
         <v>257</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="H15" s="9">
         <v>88</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>218</v>
+        <v>219</v>
       </c>
       <c r="J15" s="9">
         <v>0</v>
@@ -3099,7 +3090,7 @@
         <v>1043</v>
       </c>
       <c r="M15" s="10" t="s">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="N15" s="9">
         <v>0</v>
@@ -3108,22 +3099,22 @@
         <v>97</v>
       </c>
       <c r="P15" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q15" s="10" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="R15" s="9">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="S15" s="10" t="s">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="T15" s="9">
         <v>113</v>
       </c>
       <c r="U15" s="10" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="V15" s="9">
         <v>0</v>
@@ -3135,13 +3126,13 @@
         <v>100</v>
       </c>
       <c r="Y15" s="10" t="s">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="Z15" s="9">
         <v>11</v>
       </c>
       <c r="AA15" s="10" t="s">
-        <v>194</v>
+        <v>224</v>
       </c>
       <c r="AB15" s="9">
         <v>0</v>
@@ -3150,16 +3141,16 @@
         <v>97</v>
       </c>
       <c r="AD15" s="9">
-        <v>3153</v>
+        <v>3154</v>
       </c>
       <c r="AE15" s="10" t="s">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AF15" s="9">
         <v>66</v>
       </c>
       <c r="AG15" s="10" t="s">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="AH15" s="9">
         <v>0</v>
@@ -3171,13 +3162,13 @@
         <v>1140</v>
       </c>
       <c r="AK15" s="10" t="s">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AL15" s="9">
         <v>1696</v>
       </c>
       <c r="AM15" s="10" t="s">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AN15" s="9">
         <v>0</v>
@@ -3200,13 +3191,13 @@
     </row>
     <row r="16" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="C16" s="9">
-        <v>2429</v>
+        <v>2449</v>
       </c>
       <c r="D16" s="9">
         <v>0</v>
@@ -3215,16 +3206,16 @@
         <v>97</v>
       </c>
       <c r="F16" s="9">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="H16" s="9">
         <v>6</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>208</v>
+        <v>232</v>
       </c>
       <c r="J16" s="9">
         <v>0</v>
@@ -3233,10 +3224,10 @@
         <v>97</v>
       </c>
       <c r="L16" s="9">
-        <v>420</v>
+        <v>430</v>
       </c>
       <c r="M16" s="10" t="s">
-        <v>230</v>
+        <v>233</v>
       </c>
       <c r="N16" s="9">
         <v>0</v>
@@ -3245,22 +3236,22 @@
         <v>97</v>
       </c>
       <c r="P16" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16" s="10" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="R16" s="9">
         <v>30</v>
       </c>
       <c r="S16" s="10" t="s">
-        <v>231</v>
+        <v>234</v>
       </c>
       <c r="T16" s="9">
         <v>112</v>
       </c>
       <c r="U16" s="10" t="s">
-        <v>232</v>
+        <v>235</v>
       </c>
       <c r="V16" s="9">
         <v>0</v>
@@ -3272,49 +3263,49 @@
         <v>97</v>
       </c>
       <c r="Y16" s="10" t="s">
-        <v>233</v>
+        <v>236</v>
       </c>
       <c r="Z16" s="9">
         <v>20</v>
       </c>
       <c r="AA16" s="10" t="s">
-        <v>234</v>
+        <v>237</v>
       </c>
       <c r="AB16" s="9">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AC16" s="10" t="s">
-        <v>211</v>
+        <v>97</v>
       </c>
       <c r="AD16" s="9">
-        <v>1064</v>
+        <v>1075</v>
       </c>
       <c r="AE16" s="10" t="s">
-        <v>235</v>
+        <v>238</v>
       </c>
       <c r="AF16" s="9">
         <v>35</v>
       </c>
       <c r="AG16" s="10" t="s">
-        <v>236</v>
+        <v>239</v>
       </c>
       <c r="AH16" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI16" s="10" t="s">
-        <v>111</v>
+        <v>97</v>
       </c>
       <c r="AJ16" s="9">
-        <v>458</v>
+        <v>461</v>
       </c>
       <c r="AK16" s="10" t="s">
-        <v>237</v>
+        <v>240</v>
       </c>
       <c r="AL16" s="9">
         <v>57</v>
       </c>
       <c r="AM16" s="10" t="s">
-        <v>238</v>
+        <v>241</v>
       </c>
       <c r="AN16" s="9">
         <v>0</v>
@@ -3337,10 +3328,10 @@
     </row>
     <row r="17" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>239</v>
+        <v>242</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>240</v>
+        <v>243</v>
       </c>
       <c r="C17" s="9">
         <v>4401</v>
@@ -3355,13 +3346,13 @@
         <v>205</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>241</v>
+        <v>244</v>
       </c>
       <c r="H17" s="9">
         <v>26</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>242</v>
+        <v>245</v>
       </c>
       <c r="J17" s="9">
         <v>0</v>
@@ -3373,7 +3364,7 @@
         <v>1031</v>
       </c>
       <c r="M17" s="10" t="s">
-        <v>243</v>
+        <v>246</v>
       </c>
       <c r="N17" s="9">
         <v>0</v>
@@ -3385,7 +3376,7 @@
         <v>22</v>
       </c>
       <c r="Q17" s="10" t="s">
-        <v>178</v>
+        <v>189</v>
       </c>
       <c r="R17" s="9">
         <v>29</v>
@@ -3397,31 +3388,31 @@
         <v>30</v>
       </c>
       <c r="U17" s="10" t="s">
-        <v>244</v>
+        <v>247</v>
       </c>
       <c r="V17" s="9">
         <v>9</v>
       </c>
       <c r="W17" s="10" t="s">
-        <v>245</v>
+        <v>162</v>
       </c>
       <c r="X17" s="9">
         <v>75</v>
       </c>
       <c r="Y17" s="10" t="s">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="Z17" s="9">
         <v>2</v>
       </c>
       <c r="AA17" s="10" t="s">
-        <v>247</v>
+        <v>153</v>
       </c>
       <c r="AB17" s="9">
         <v>4</v>
       </c>
       <c r="AC17" s="10" t="s">
-        <v>248</v>
+        <v>99</v>
       </c>
       <c r="AD17" s="9">
         <v>2197</v>
@@ -3480,7 +3471,7 @@
         <v>255</v>
       </c>
       <c r="C18" s="9">
-        <v>5478</v>
+        <v>5479</v>
       </c>
       <c r="D18" s="9">
         <v>0</v>
@@ -3492,13 +3483,13 @@
         <v>233</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>192</v>
+        <v>256</v>
       </c>
       <c r="H18" s="9">
         <v>6</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J18" s="9">
         <v>0</v>
@@ -3510,7 +3501,7 @@
         <v>1306</v>
       </c>
       <c r="M18" s="10" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="N18" s="9">
         <v>0</v>
@@ -3528,13 +3519,13 @@
         <v>21</v>
       </c>
       <c r="S18" s="10" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="T18" s="9">
         <v>87</v>
       </c>
       <c r="U18" s="10" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="V18" s="9">
         <v>0</v>
@@ -3546,13 +3537,13 @@
         <v>99</v>
       </c>
       <c r="Y18" s="10" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="Z18" s="9">
         <v>15</v>
       </c>
       <c r="AA18" s="10" t="s">
-        <v>160</v>
+        <v>105</v>
       </c>
       <c r="AB18" s="9">
         <v>0</v>
@@ -3564,13 +3555,13 @@
         <v>2491</v>
       </c>
       <c r="AE18" s="10" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AF18" s="9">
         <v>13</v>
       </c>
       <c r="AG18" s="10" t="s">
-        <v>261</v>
+        <v>232</v>
       </c>
       <c r="AH18" s="9">
         <v>0</v>
@@ -3579,7 +3570,7 @@
         <v>97</v>
       </c>
       <c r="AJ18" s="9">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="AK18" s="10" t="s">
         <v>262</v>
@@ -3588,7 +3579,7 @@
         <v>44</v>
       </c>
       <c r="AM18" s="10" t="s">
-        <v>263</v>
+        <v>107</v>
       </c>
       <c r="AN18" s="9">
         <v>0</v>
@@ -3611,67 +3602,67 @@
     </row>
     <row r="19" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="B19" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="B19" s="8" t="s">
+      <c r="C19" s="9">
+        <v>12137</v>
+      </c>
+      <c r="D19" s="9">
+        <v>0</v>
+      </c>
+      <c r="E19" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F19" s="9">
+        <v>627</v>
+      </c>
+      <c r="G19" s="10" t="s">
         <v>265</v>
-      </c>
-      <c r="C19" s="9">
-        <v>9957</v>
-      </c>
-      <c r="D19" s="9">
-        <v>0</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="F19" s="9">
-        <v>512</v>
-      </c>
-      <c r="G19" s="10" t="s">
-        <v>266</v>
       </c>
       <c r="H19" s="9">
         <v>18</v>
       </c>
       <c r="I19" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="J19" s="9">
+        <v>0</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L19" s="9">
+        <v>3580</v>
+      </c>
+      <c r="M19" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="N19" s="9">
+        <v>0</v>
+      </c>
+      <c r="O19" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="P19" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="R19" s="9">
+        <v>26</v>
+      </c>
+      <c r="S19" s="10" t="s">
         <v>267</v>
-      </c>
-      <c r="J19" s="9">
-        <v>0</v>
-      </c>
-      <c r="K19" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="L19" s="9">
-        <v>2842</v>
-      </c>
-      <c r="M19" s="10" t="s">
-        <v>268</v>
-      </c>
-      <c r="N19" s="9">
-        <v>0</v>
-      </c>
-      <c r="O19" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="P19" s="9">
-        <v>0</v>
-      </c>
-      <c r="Q19" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="R19" s="9">
-        <v>24</v>
-      </c>
-      <c r="S19" s="10" t="s">
-        <v>261</v>
       </c>
       <c r="T19" s="9">
         <v>17</v>
       </c>
       <c r="U19" s="10" t="s">
-        <v>117</v>
+        <v>224</v>
       </c>
       <c r="V19" s="9">
         <v>0</v>
@@ -3680,16 +3671,16 @@
         <v>97</v>
       </c>
       <c r="X19" s="9">
-        <v>294</v>
+        <v>339</v>
       </c>
       <c r="Y19" s="10" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="Z19" s="9">
         <v>4</v>
       </c>
       <c r="AA19" s="10" t="s">
-        <v>111</v>
+        <v>146</v>
       </c>
       <c r="AB19" s="9">
         <v>0</v>
@@ -3698,16 +3689,16 @@
         <v>97</v>
       </c>
       <c r="AD19" s="9">
-        <v>4616</v>
+        <v>5551</v>
       </c>
       <c r="AE19" s="10" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="AF19" s="9">
         <v>26</v>
       </c>
       <c r="AG19" s="10" t="s">
-        <v>271</v>
+        <v>267</v>
       </c>
       <c r="AH19" s="9">
         <v>0</v>
@@ -3716,16 +3707,16 @@
         <v>97</v>
       </c>
       <c r="AJ19" s="9">
-        <v>1454</v>
+        <v>1799</v>
       </c>
       <c r="AK19" s="10" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="AL19" s="9">
         <v>148</v>
       </c>
       <c r="AM19" s="10" t="s">
-        <v>273</v>
+        <v>234</v>
       </c>
       <c r="AN19" s="9">
         <v>0</v>
@@ -3748,13 +3739,13 @@
     </row>
     <row r="20" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="C20" s="9">
-        <v>746</v>
+        <v>764</v>
       </c>
       <c r="D20" s="9">
         <v>0</v>
@@ -3763,16 +3754,16 @@
         <v>97</v>
       </c>
       <c r="F20" s="9">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H20" s="9">
         <v>6</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>263</v>
+        <v>274</v>
       </c>
       <c r="J20" s="9">
         <v>0</v>
@@ -3784,7 +3775,7 @@
         <v>83</v>
       </c>
       <c r="M20" s="10" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="N20" s="9">
         <v>0</v>
@@ -3796,55 +3787,55 @@
         <v>1</v>
       </c>
       <c r="Q20" s="10" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="R20" s="9">
         <v>4</v>
       </c>
       <c r="S20" s="10" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="T20" s="9">
         <v>42</v>
       </c>
       <c r="U20" s="10" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="V20" s="9">
         <v>5</v>
       </c>
       <c r="W20" s="10" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="X20" s="9">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="Y20" s="10" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="Z20" s="9">
         <v>91</v>
       </c>
       <c r="AA20" s="10" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="AB20" s="9">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AC20" s="10" t="s">
-        <v>281</v>
+        <v>277</v>
       </c>
       <c r="AD20" s="9">
-        <v>298</v>
+        <v>308</v>
       </c>
       <c r="AE20" s="10" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="AF20" s="9">
         <v>12</v>
       </c>
       <c r="AG20" s="10" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="AH20" s="9">
         <v>0</v>
@@ -3853,16 +3844,16 @@
         <v>97</v>
       </c>
       <c r="AJ20" s="9">
-        <v>68</v>
+        <v>72</v>
       </c>
       <c r="AK20" s="10" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="AL20" s="9">
         <v>19</v>
       </c>
       <c r="AM20" s="10" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="AN20" s="9">
         <v>0</v>
@@ -3880,36 +3871,36 @@
         <v>2</v>
       </c>
       <c r="AS20" s="10" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
     </row>
     <row r="21" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
+        <v>286</v>
+      </c>
+      <c r="B21" s="8" t="s">
+        <v>287</v>
+      </c>
+      <c r="C21" s="9">
+        <v>1518</v>
+      </c>
+      <c r="D21" s="9">
+        <v>0</v>
+      </c>
+      <c r="E21" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="F21" s="9">
+        <v>42</v>
+      </c>
+      <c r="G21" s="10" t="s">
         <v>288</v>
-      </c>
-      <c r="B21" s="8" t="s">
-        <v>289</v>
-      </c>
-      <c r="C21" s="9">
-        <v>1507</v>
-      </c>
-      <c r="D21" s="9">
-        <v>0</v>
-      </c>
-      <c r="E21" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="F21" s="9">
-        <v>41</v>
-      </c>
-      <c r="G21" s="10" t="s">
-        <v>290</v>
       </c>
       <c r="H21" s="9">
         <v>6</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="J21" s="9">
         <v>0</v>
@@ -3918,10 +3909,10 @@
         <v>97</v>
       </c>
       <c r="L21" s="9">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="M21" s="10" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="N21" s="9">
         <v>0</v>
@@ -3930,58 +3921,58 @@
         <v>97</v>
       </c>
       <c r="P21" s="9">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21" s="10" t="s">
-        <v>251</v>
+        <v>97</v>
       </c>
       <c r="R21" s="9">
         <v>9</v>
       </c>
       <c r="S21" s="10" t="s">
-        <v>292</v>
+        <v>245</v>
       </c>
       <c r="T21" s="9">
         <v>35</v>
       </c>
       <c r="U21" s="10" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="V21" s="9">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="W21" s="10" t="s">
-        <v>278</v>
+        <v>251</v>
       </c>
       <c r="X21" s="9">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="Y21" s="10" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="Z21" s="9">
         <v>39</v>
       </c>
       <c r="AA21" s="10" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="AB21" s="9">
         <v>15</v>
       </c>
       <c r="AC21" s="10" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="AD21" s="9">
-        <v>634</v>
+        <v>639</v>
       </c>
       <c r="AE21" s="10" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="AF21" s="9">
         <v>3</v>
       </c>
       <c r="AG21" s="10" t="s">
-        <v>245</v>
+        <v>162</v>
       </c>
       <c r="AH21" s="9">
         <v>0</v>
@@ -3990,16 +3981,16 @@
         <v>97</v>
       </c>
       <c r="AJ21" s="9">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="AK21" s="10" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="AL21" s="9">
         <v>384</v>
       </c>
       <c r="AM21" s="10" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="AN21" s="9">
         <v>0</v>
@@ -4022,13 +4013,13 @@
     </row>
     <row r="22" ht="22" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="C22" s="12">
-        <v>75166</v>
+        <v>78157</v>
       </c>
       <c r="D22" s="12">
         <v>6</v>
@@ -4037,7 +4028,7 @@
         <v>94</v>
       </c>
       <c r="F22" s="12">
-        <v>3318</v>
+        <v>3471</v>
       </c>
       <c r="G22" s="13" t="s">
         <v>95</v>
@@ -4055,7 +4046,7 @@
         <v>97</v>
       </c>
       <c r="L22" s="12">
-        <v>16831</v>
+        <v>17835</v>
       </c>
       <c r="M22" s="13" t="s">
         <v>98</v>
@@ -4067,31 +4058,31 @@
         <v>97</v>
       </c>
       <c r="P22" s="12">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="Q22" s="13" t="s">
         <v>99</v>
       </c>
       <c r="R22" s="12">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="S22" s="13" t="s">
         <v>100</v>
       </c>
       <c r="T22" s="12">
-        <v>1554</v>
+        <v>1555</v>
       </c>
       <c r="U22" s="13" t="s">
         <v>101</v>
       </c>
       <c r="V22" s="12">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="W22" s="13" t="s">
         <v>102</v>
       </c>
       <c r="X22" s="12">
-        <v>2129</v>
+        <v>2202</v>
       </c>
       <c r="Y22" s="13" t="s">
         <v>103</v>
@@ -4103,31 +4094,31 @@
         <v>104</v>
       </c>
       <c r="AB22" s="12">
-        <v>224</v>
+        <v>208</v>
       </c>
       <c r="AC22" s="13" t="s">
         <v>105</v>
       </c>
       <c r="AD22" s="12">
-        <v>33023</v>
+        <v>34351</v>
       </c>
       <c r="AE22" s="13" t="s">
         <v>106</v>
       </c>
       <c r="AF22" s="12">
-        <v>621</v>
+        <v>625</v>
       </c>
       <c r="AG22" s="13" t="s">
         <v>107</v>
       </c>
       <c r="AH22" s="12">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AI22" s="13" t="s">
         <v>108</v>
       </c>
       <c r="AJ22" s="12">
-        <v>12015</v>
+        <v>12460</v>
       </c>
       <c r="AK22" s="13" t="s">
         <v>109</v>
@@ -4139,7 +4130,7 @@
         <v>110</v>
       </c>
       <c r="AN22" s="12">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AO22" s="13" t="s">
         <v>97</v>
@@ -4151,7 +4142,7 @@
         <v>97</v>
       </c>
       <c r="AR22" s="12">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AS22" s="13" t="s">
         <v>111</v>

--- a/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
+++ b/data/20260823_125317_Radar_Anomali_Keluarga_Anomali_1_Anomali_2_Anomali_3_Anomali_4_Anomali_5_Anomali_6_Anomali_7_Kabupaten_Kota.xlsx
@@ -11,12 +11,12 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="105" uniqueCount="90">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="483" uniqueCount="297">
   <si>
     <t>DATA RADAR ANOMALI KELUARGA</t>
   </si>
   <si>
-    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 15 Sep 2026, 06.37</t>
+    <t>Seluruh data sampai Kabupaten / Kota | Dicetak: 16 Sep 2026, 08.57</t>
   </si>
   <si>
     <t>Kode</t>
@@ -46,6 +46,114 @@
     <t>Persentase Anomali 1 - Sesuai</t>
   </si>
   <si>
+    <t>Anomali 2 - Belum Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Persentase Anomali 2 - Belum Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Anomali 2 - Sudah Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Persentase Anomali 2 - Sudah Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Anomali 2 - Sesuai</t>
+  </si>
+  <si>
+    <t>Persentase Anomali 2 - Sesuai</t>
+  </si>
+  <si>
+    <t>Anomali 3 - Belum Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Persentase Anomali 3 - Belum Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Anomali 3 - Sudah Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Persentase Anomali 3 - Sudah Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Anomali 3 - Sesuai</t>
+  </si>
+  <si>
+    <t>Persentase Anomali 3 - Sesuai</t>
+  </si>
+  <si>
+    <t>Anomali 4 - Belum Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Persentase Anomali 4 - Belum Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Anomali 4 - Sudah Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Persentase Anomali 4 - Sudah Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Anomali 4 - Sesuai</t>
+  </si>
+  <si>
+    <t>Persentase Anomali 4 - Sesuai</t>
+  </si>
+  <si>
+    <t>Anomali 5 - Belum Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Persentase Anomali 5 - Belum Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Anomali 5 - Sudah Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Persentase Anomali 5 - Sudah Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Anomali 5 - Sesuai</t>
+  </si>
+  <si>
+    <t>Persentase Anomali 5 - Sesuai</t>
+  </si>
+  <si>
+    <t>Anomali 6 - Belum Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Persentase Anomali 6 - Belum Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Anomali 6 - Sudah Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Persentase Anomali 6 - Sudah Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Anomali 6 - Sesuai</t>
+  </si>
+  <si>
+    <t>Persentase Anomali 6 - Sesuai</t>
+  </si>
+  <si>
+    <t>Anomali 7 - Belum Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Persentase Anomali 7 - Belum Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Anomali 7 - Sudah Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Persentase Anomali 7 - Sudah Tindak Lanjut</t>
+  </si>
+  <si>
+    <t>Anomali 7 - Sesuai</t>
+  </si>
+  <si>
+    <t>Persentase Anomali 7 - Sesuai</t>
+  </si>
+  <si>
     <t>(1)</t>
   </si>
   <si>
@@ -73,184 +181,649 @@
     <t>(9)</t>
   </si>
   <si>
+    <t>(10)</t>
+  </si>
+  <si>
+    <t>(11)</t>
+  </si>
+  <si>
+    <t>(12)</t>
+  </si>
+  <si>
+    <t>(13)</t>
+  </si>
+  <si>
+    <t>(14)</t>
+  </si>
+  <si>
+    <t>(15)</t>
+  </si>
+  <si>
+    <t>(16)</t>
+  </si>
+  <si>
+    <t>(17)</t>
+  </si>
+  <si>
+    <t>(18)</t>
+  </si>
+  <si>
+    <t>(19)</t>
+  </si>
+  <si>
+    <t>(20)</t>
+  </si>
+  <si>
+    <t>(21)</t>
+  </si>
+  <si>
+    <t>(22)</t>
+  </si>
+  <si>
+    <t>(23)</t>
+  </si>
+  <si>
+    <t>(24)</t>
+  </si>
+  <si>
+    <t>(25)</t>
+  </si>
+  <si>
+    <t>(26)</t>
+  </si>
+  <si>
+    <t>(27)</t>
+  </si>
+  <si>
+    <t>(28)</t>
+  </si>
+  <si>
+    <t>(29)</t>
+  </si>
+  <si>
+    <t>(30)</t>
+  </si>
+  <si>
+    <t>(31)</t>
+  </si>
+  <si>
+    <t>(32)</t>
+  </si>
+  <si>
+    <t>(33)</t>
+  </si>
+  <si>
+    <t>(34)</t>
+  </si>
+  <si>
+    <t>(35)</t>
+  </si>
+  <si>
+    <t>(36)</t>
+  </si>
+  <si>
+    <t>(37)</t>
+  </si>
+  <si>
+    <t>(38)</t>
+  </si>
+  <si>
+    <t>(39)</t>
+  </si>
+  <si>
+    <t>(40)</t>
+  </si>
+  <si>
+    <t>(41)</t>
+  </si>
+  <si>
+    <t>(42)</t>
+  </si>
+  <si>
+    <t>(43)</t>
+  </si>
+  <si>
+    <t>(44)</t>
+  </si>
+  <si>
+    <t>(45)</t>
+  </si>
+  <si>
     <t>18</t>
   </si>
   <si>
     <t>LAMPUNG</t>
   </si>
   <si>
+    <t>0,01</t>
+  </si>
+  <si>
+    <t>4,49</t>
+  </si>
+  <si>
+    <t>0,48</t>
+  </si>
+  <si>
+    <t>0</t>
+  </si>
+  <si>
+    <t>23,49</t>
+  </si>
+  <si>
+    <t>0,05</t>
+  </si>
+  <si>
+    <t>0,54</t>
+  </si>
+  <si>
+    <t>1,92</t>
+  </si>
+  <si>
+    <t>0,04</t>
+  </si>
+  <si>
+    <t>2,77</t>
+  </si>
+  <si>
+    <t>0,46</t>
+  </si>
+  <si>
+    <t>0,18</t>
+  </si>
+  <si>
+    <t>43,91</t>
+  </si>
+  <si>
+    <t>0,8</t>
+  </si>
+  <si>
+    <t>0,02</t>
+  </si>
+  <si>
+    <t>15,84</t>
+  </si>
+  <si>
+    <t>4,97</t>
+  </si>
+  <si>
+    <t>1801</t>
+  </si>
+  <si>
+    <t>LAMPUNG BARAT</t>
+  </si>
+  <si>
+    <t>4,23</t>
+  </si>
+  <si>
+    <t>0,62</t>
+  </si>
+  <si>
+    <t>28,62</t>
+  </si>
+  <si>
+    <t>0,16</t>
+  </si>
+  <si>
+    <t>0,43</t>
+  </si>
+  <si>
+    <t>4,17</t>
+  </si>
+  <si>
+    <t>0,78</t>
+  </si>
+  <si>
+    <t>0,08</t>
+  </si>
+  <si>
+    <t>40,01</t>
+  </si>
+  <si>
+    <t>0,49</t>
+  </si>
+  <si>
+    <t>0,06</t>
+  </si>
+  <si>
+    <t>12,88</t>
+  </si>
+  <si>
+    <t>7,45</t>
+  </si>
+  <si>
+    <t>1802</t>
+  </si>
+  <si>
+    <t>TANGGAMUS</t>
+  </si>
+  <si>
+    <t>6,43</t>
+  </si>
+  <si>
+    <t>21,48</t>
+  </si>
+  <si>
+    <t>0,76</t>
+  </si>
+  <si>
+    <t>3,09</t>
+  </si>
+  <si>
+    <t>3,34</t>
+  </si>
+  <si>
+    <t>0,25</t>
+  </si>
+  <si>
+    <t>41,69</t>
+  </si>
+  <si>
+    <t>0,1</t>
+  </si>
+  <si>
+    <t>22,34</t>
+  </si>
+  <si>
+    <t>0,41</t>
+  </si>
+  <si>
+    <t>1803</t>
+  </si>
+  <si>
+    <t>LAMPUNG SELATAN</t>
+  </si>
+  <si>
+    <t>5,61</t>
+  </si>
+  <si>
+    <t>0,27</t>
+  </si>
+  <si>
+    <t>23,15</t>
+  </si>
+  <si>
+    <t>0,42</t>
+  </si>
+  <si>
+    <t>2,38</t>
+  </si>
+  <si>
+    <t>3,05</t>
+  </si>
+  <si>
+    <t>0,58</t>
+  </si>
+  <si>
+    <t>43,78</t>
+  </si>
+  <si>
+    <t>2,94</t>
+  </si>
+  <si>
+    <t>16,92</t>
+  </si>
+  <si>
+    <t>0,85</t>
+  </si>
+  <si>
+    <t>1804</t>
+  </si>
+  <si>
+    <t>LAMPUNG TIMUR</t>
+  </si>
+  <si>
+    <t>0,03</t>
+  </si>
+  <si>
+    <t>0,28</t>
+  </si>
+  <si>
+    <t>26,62</t>
+  </si>
+  <si>
+    <t>0,22</t>
+  </si>
+  <si>
+    <t>0,88</t>
+  </si>
+  <si>
+    <t>2,07</t>
+  </si>
+  <si>
+    <t>0,21</t>
+  </si>
+  <si>
+    <t>3</t>
+  </si>
+  <si>
+    <t>0,26</t>
+  </si>
+  <si>
+    <t>1,2</t>
+  </si>
+  <si>
+    <t>43,75</t>
+  </si>
+  <si>
+    <t>0,32</t>
+  </si>
+  <si>
+    <t>15,56</t>
+  </si>
+  <si>
+    <t>1,33</t>
+  </si>
+  <si>
+    <t>1805</t>
+  </si>
+  <si>
+    <t>LAMPUNG TENGAH</t>
+  </si>
+  <si>
+    <t>4,48</t>
+  </si>
+  <si>
+    <t>0,07</t>
+  </si>
+  <si>
+    <t>24,71</t>
+  </si>
+  <si>
+    <t>0,36</t>
+  </si>
+  <si>
+    <t>4,8</t>
+  </si>
+  <si>
+    <t>3,73</t>
+  </si>
+  <si>
+    <t>45,88</t>
+  </si>
+  <si>
+    <t>0,91</t>
+  </si>
+  <si>
+    <t>14,18</t>
+  </si>
+  <si>
+    <t>0,47</t>
+  </si>
+  <si>
+    <t>1806</t>
+  </si>
+  <si>
+    <t>LAMPUNG UTARA</t>
+  </si>
+  <si>
+    <t>2,87</t>
+  </si>
+  <si>
+    <t>1,98</t>
+  </si>
+  <si>
+    <t>18,39</t>
+  </si>
+  <si>
+    <t>0,38</t>
+  </si>
+  <si>
+    <t>2,37</t>
+  </si>
+  <si>
+    <t>43,03</t>
+  </si>
+  <si>
+    <t>0,67</t>
+  </si>
+  <si>
+    <t>16,61</t>
+  </si>
+  <si>
+    <t>11,1</t>
+  </si>
+  <si>
+    <t>1807</t>
+  </si>
+  <si>
+    <t>WAY KANAN</t>
+  </si>
+  <si>
+    <t>4,33</t>
+  </si>
+  <si>
+    <t>21,05</t>
+  </si>
+  <si>
+    <t>0,57</t>
+  </si>
+  <si>
+    <t>2,33</t>
+  </si>
+  <si>
+    <t>2,9</t>
+  </si>
+  <si>
+    <t>40,93</t>
+  </si>
+  <si>
+    <t>1,07</t>
+  </si>
+  <si>
+    <t>25,18</t>
+  </si>
+  <si>
+    <t>1,09</t>
+  </si>
+  <si>
+    <t>1808</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG</t>
+  </si>
+  <si>
+    <t>4,99</t>
+  </si>
+  <si>
+    <t>28,49</t>
+  </si>
+  <si>
+    <t>0,92</t>
+  </si>
+  <si>
+    <t>2,08</t>
+  </si>
+  <si>
+    <t>0,19</t>
+  </si>
+  <si>
+    <t>45,55</t>
+  </si>
+  <si>
+    <t>11,88</t>
+  </si>
+  <si>
+    <t>3,13</t>
+  </si>
+  <si>
+    <t>1809</t>
+  </si>
+  <si>
+    <t>PESAWARAN</t>
+  </si>
+  <si>
+    <t>3,3</t>
+  </si>
+  <si>
+    <t>1,13</t>
+  </si>
+  <si>
+    <t>13,55</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>1,46</t>
+  </si>
+  <si>
+    <t>1,28</t>
+  </si>
+  <si>
+    <t>0,14</t>
+  </si>
+  <si>
+    <t>40,75</t>
+  </si>
+  <si>
+    <t>0,84</t>
+  </si>
+  <si>
+    <t>14,8</t>
+  </si>
+  <si>
+    <t>21,7</t>
+  </si>
+  <si>
+    <t>1810</t>
+  </si>
+  <si>
+    <t>PRINGSEWU</t>
+  </si>
+  <si>
+    <t>5,13</t>
+  </si>
+  <si>
+    <t>0,23</t>
+  </si>
+  <si>
+    <t>18,01</t>
+  </si>
+  <si>
+    <t>1,17</t>
+  </si>
+  <si>
+    <t>4,39</t>
+  </si>
+  <si>
+    <t>3,92</t>
+  </si>
+  <si>
+    <t>43,7</t>
+  </si>
+  <si>
+    <t>1,37</t>
+  </si>
+  <si>
+    <t>18,99</t>
+  </si>
+  <si>
+    <t>2,23</t>
+  </si>
+  <si>
+    <t>1811</t>
+  </si>
+  <si>
+    <t>MESUJI</t>
+  </si>
+  <si>
+    <t>4,63</t>
+  </si>
+  <si>
+    <t>0,59</t>
+  </si>
+  <si>
+    <t>23,53</t>
+  </si>
+  <si>
+    <t>0,5</t>
+  </si>
+  <si>
+    <t>0,65</t>
+  </si>
+  <si>
+    <t>0,68</t>
+  </si>
+  <si>
+    <t>0,2</t>
+  </si>
+  <si>
+    <t>1,74</t>
+  </si>
+  <si>
+    <t>0,09</t>
+  </si>
+  <si>
+    <t>49,91</t>
+  </si>
+  <si>
+    <t>0,95</t>
+  </si>
+  <si>
+    <t>11,44</t>
+  </si>
+  <si>
+    <t>4,96</t>
+  </si>
+  <si>
+    <t>1812</t>
+  </si>
+  <si>
+    <t>TULANG BAWANG BARAT</t>
+  </si>
+  <si>
+    <t>4,24</t>
+  </si>
+  <si>
+    <t>0,11</t>
+  </si>
+  <si>
+    <t>23,81</t>
+  </si>
+  <si>
+    <t>1,58</t>
+  </si>
+  <si>
+    <t>1,8</t>
+  </si>
+  <si>
+    <t>0,15</t>
+  </si>
+  <si>
+    <t>45,36</t>
+  </si>
+  <si>
+    <t>0,24</t>
+  </si>
+  <si>
+    <t>21,19</t>
+  </si>
+  <si>
+    <t>1813</t>
+  </si>
+  <si>
+    <t>PESISIR BARAT</t>
+  </si>
+  <si>
+    <t>5,22</t>
+  </si>
+  <si>
     <t>0,13</t>
   </si>
   <si>
-    <t>89,98</t>
-  </si>
-  <si>
-    <t>9,89</t>
-  </si>
-  <si>
-    <t>1801</t>
-  </si>
-  <si>
-    <t>LAMPUNG BARAT</t>
-  </si>
-  <si>
-    <t>0</t>
-  </si>
-  <si>
-    <t>86,99</t>
-  </si>
-  <si>
-    <t>13,01</t>
-  </si>
-  <si>
-    <t>1802</t>
-  </si>
-  <si>
-    <t>TANGGAMUS</t>
-  </si>
-  <si>
-    <t>100</t>
-  </si>
-  <si>
-    <t>1803</t>
-  </si>
-  <si>
-    <t>LAMPUNG SELATAN</t>
-  </si>
-  <si>
-    <t>95,21</t>
-  </si>
-  <si>
-    <t>4,79</t>
-  </si>
-  <si>
-    <t>1804</t>
-  </si>
-  <si>
-    <t>LAMPUNG TIMUR</t>
-  </si>
-  <si>
-    <t>0,75</t>
-  </si>
-  <si>
-    <t>93</t>
-  </si>
-  <si>
-    <t>6,25</t>
-  </si>
-  <si>
-    <t>1805</t>
-  </si>
-  <si>
-    <t>LAMPUNG TENGAH</t>
-  </si>
-  <si>
-    <t>0,27</t>
-  </si>
-  <si>
-    <t>98,1</t>
-  </si>
-  <si>
-    <t>1,63</t>
-  </si>
-  <si>
-    <t>1806</t>
-  </si>
-  <si>
-    <t>LAMPUNG UTARA</t>
-  </si>
-  <si>
-    <t>58,33</t>
-  </si>
-  <si>
-    <t>41,67</t>
-  </si>
-  <si>
-    <t>1807</t>
-  </si>
-  <si>
-    <t>WAY KANAN</t>
-  </si>
-  <si>
-    <t>98,73</t>
-  </si>
-  <si>
-    <t>1,27</t>
-  </si>
-  <si>
-    <t>1808</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG</t>
-  </si>
-  <si>
-    <t>88,44</t>
-  </si>
-  <si>
-    <t>11,56</t>
-  </si>
-  <si>
-    <t>1809</t>
-  </si>
-  <si>
-    <t>PESAWARAN</t>
-  </si>
-  <si>
-    <t>74,49</t>
-  </si>
-  <si>
-    <t>25,51</t>
-  </si>
-  <si>
-    <t>1810</t>
-  </si>
-  <si>
-    <t>PRINGSEWU</t>
-  </si>
-  <si>
-    <t>95,62</t>
-  </si>
-  <si>
-    <t>4,38</t>
-  </si>
-  <si>
-    <t>1811</t>
-  </si>
-  <si>
-    <t>MESUJI</t>
-  </si>
-  <si>
-    <t>0,43</t>
-  </si>
-  <si>
-    <t>88,36</t>
-  </si>
-  <si>
-    <t>11,21</t>
-  </si>
-  <si>
-    <t>1812</t>
-  </si>
-  <si>
-    <t>TULANG BAWANG BARAT</t>
-  </si>
-  <si>
-    <t>97,49</t>
-  </si>
-  <si>
-    <t>2,51</t>
-  </si>
-  <si>
-    <t>1813</t>
-  </si>
-  <si>
-    <t>PESISIR BARAT</t>
-  </si>
-  <si>
-    <t>97,47</t>
-  </si>
-  <si>
-    <t>2,53</t>
+    <t>29,96</t>
+  </si>
+  <si>
+    <t>2,63</t>
+  </si>
+  <si>
+    <t>45,29</t>
+  </si>
+  <si>
+    <t>15,1</t>
+  </si>
+  <si>
+    <t>1,1</t>
   </si>
   <si>
     <t>1871</t>
@@ -259,10 +832,37 @@
     <t>BANDAR LAMPUNG</t>
   </si>
   <si>
-    <t>90,32</t>
-  </si>
-  <si>
-    <t>9,68</t>
+    <t>7,15</t>
+  </si>
+  <si>
+    <t>0,77</t>
+  </si>
+  <si>
+    <t>11,11</t>
+  </si>
+  <si>
+    <t>0,51</t>
+  </si>
+  <si>
+    <t>5,36</t>
+  </si>
+  <si>
+    <t>8,17</t>
+  </si>
+  <si>
+    <t>11,62</t>
+  </si>
+  <si>
+    <t>39,97</t>
+  </si>
+  <si>
+    <t>1,53</t>
+  </si>
+  <si>
+    <t>9,58</t>
+  </si>
+  <si>
+    <t>2,43</t>
   </si>
   <si>
     <t>1872</t>
@@ -271,10 +871,31 @@
     <t>METRO</t>
   </si>
   <si>
-    <t>87,76</t>
-  </si>
-  <si>
-    <t>12,24</t>
+    <t>2,88</t>
+  </si>
+  <si>
+    <t>0,39</t>
+  </si>
+  <si>
+    <t>11,9</t>
+  </si>
+  <si>
+    <t>2,29</t>
+  </si>
+  <si>
+    <t>2,55</t>
+  </si>
+  <si>
+    <t>0,98</t>
+  </si>
+  <si>
+    <t>42,18</t>
+  </si>
+  <si>
+    <t>7,91</t>
+  </si>
+  <si>
+    <t>25,11</t>
   </si>
   <si>
     <t/>
@@ -771,7 +1392,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:I22"/>
+  <dimension ref="A1:AS22"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="14" customWidth="1"/>
@@ -782,9 +1403,45 @@
     <col min="7" max="7" width="13" customWidth="1"/>
     <col min="8" max="8" width="18" customWidth="1"/>
     <col min="9" max="9" width="13" customWidth="1"/>
+    <col min="10" max="10" width="18" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
+    <col min="12" max="12" width="18" customWidth="1"/>
+    <col min="13" max="13" width="13" customWidth="1"/>
+    <col min="14" max="14" width="18" customWidth="1"/>
+    <col min="15" max="15" width="13" customWidth="1"/>
+    <col min="16" max="16" width="18" customWidth="1"/>
+    <col min="17" max="17" width="13" customWidth="1"/>
+    <col min="18" max="18" width="18" customWidth="1"/>
+    <col min="19" max="19" width="13" customWidth="1"/>
+    <col min="20" max="20" width="18" customWidth="1"/>
+    <col min="21" max="21" width="13" customWidth="1"/>
+    <col min="22" max="22" width="18" customWidth="1"/>
+    <col min="23" max="23" width="13" customWidth="1"/>
+    <col min="24" max="24" width="18" customWidth="1"/>
+    <col min="25" max="25" width="13" customWidth="1"/>
+    <col min="26" max="26" width="18" customWidth="1"/>
+    <col min="27" max="27" width="13" customWidth="1"/>
+    <col min="28" max="28" width="18" customWidth="1"/>
+    <col min="29" max="29" width="13" customWidth="1"/>
+    <col min="30" max="30" width="18" customWidth="1"/>
+    <col min="31" max="31" width="13" customWidth="1"/>
+    <col min="32" max="32" width="18" customWidth="1"/>
+    <col min="33" max="33" width="13" customWidth="1"/>
+    <col min="34" max="34" width="18" customWidth="1"/>
+    <col min="35" max="35" width="13" customWidth="1"/>
+    <col min="36" max="36" width="18" customWidth="1"/>
+    <col min="37" max="37" width="13" customWidth="1"/>
+    <col min="38" max="38" width="18" customWidth="1"/>
+    <col min="39" max="39" width="13" customWidth="1"/>
+    <col min="40" max="40" width="18" customWidth="1"/>
+    <col min="41" max="41" width="13" customWidth="1"/>
+    <col min="42" max="42" width="18" customWidth="1"/>
+    <col min="43" max="43" width="13" customWidth="1"/>
+    <col min="44" max="44" width="18" customWidth="1"/>
+    <col min="45" max="45" width="13" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="26" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="1" ht="26" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -796,8 +1453,44 @@
       <c r="G1" s="1"/>
       <c r="H1" s="1"/>
       <c r="I1" s="1"/>
+      <c r="J1" s="1"/>
+      <c r="K1" s="1"/>
+      <c r="L1" s="1"/>
+      <c r="M1" s="1"/>
+      <c r="N1" s="1"/>
+      <c r="O1" s="1"/>
+      <c r="P1" s="1"/>
+      <c r="Q1" s="1"/>
+      <c r="R1" s="1"/>
+      <c r="S1" s="1"/>
+      <c r="T1" s="1"/>
+      <c r="U1" s="1"/>
+      <c r="V1" s="1"/>
+      <c r="W1" s="1"/>
+      <c r="X1" s="1"/>
+      <c r="Y1" s="1"/>
+      <c r="Z1" s="1"/>
+      <c r="AA1" s="1"/>
+      <c r="AB1" s="1"/>
+      <c r="AC1" s="1"/>
+      <c r="AD1" s="1"/>
+      <c r="AE1" s="1"/>
+      <c r="AF1" s="1"/>
+      <c r="AG1" s="1"/>
+      <c r="AH1" s="1"/>
+      <c r="AI1" s="1"/>
+      <c r="AJ1" s="1"/>
+      <c r="AK1" s="1"/>
+      <c r="AL1" s="1"/>
+      <c r="AM1" s="1"/>
+      <c r="AN1" s="1"/>
+      <c r="AO1" s="1"/>
+      <c r="AP1" s="1"/>
+      <c r="AQ1" s="1"/>
+      <c r="AR1" s="1"/>
+      <c r="AS1" s="1"/>
     </row>
-    <row r="2" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="2" ht="22" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>1</v>
       </c>
@@ -809,8 +1502,44 @@
       <c r="G2" s="2"/>
       <c r="H2" s="2"/>
       <c r="I2" s="2"/>
+      <c r="J2" s="2"/>
+      <c r="K2" s="2"/>
+      <c r="L2" s="2"/>
+      <c r="M2" s="2"/>
+      <c r="N2" s="2"/>
+      <c r="O2" s="2"/>
+      <c r="P2" s="2"/>
+      <c r="Q2" s="2"/>
+      <c r="R2" s="2"/>
+      <c r="S2" s="2"/>
+      <c r="T2" s="2"/>
+      <c r="U2" s="2"/>
+      <c r="V2" s="2"/>
+      <c r="W2" s="2"/>
+      <c r="X2" s="2"/>
+      <c r="Y2" s="2"/>
+      <c r="Z2" s="2"/>
+      <c r="AA2" s="2"/>
+      <c r="AB2" s="2"/>
+      <c r="AC2" s="2"/>
+      <c r="AD2" s="2"/>
+      <c r="AE2" s="2"/>
+      <c r="AF2" s="2"/>
+      <c r="AG2" s="2"/>
+      <c r="AH2" s="2"/>
+      <c r="AI2" s="2"/>
+      <c r="AJ2" s="2"/>
+      <c r="AK2" s="2"/>
+      <c r="AL2" s="2"/>
+      <c r="AM2" s="2"/>
+      <c r="AN2" s="2"/>
+      <c r="AO2" s="2"/>
+      <c r="AP2" s="2"/>
+      <c r="AQ2" s="2"/>
+      <c r="AR2" s="2"/>
+      <c r="AS2" s="2"/>
     </row>
-    <row r="4" ht="36" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="4" ht="36" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A4" s="3" t="s">
         <v>2</v>
       </c>
@@ -838,534 +1567,2586 @@
       <c r="I4" s="3" t="s">
         <v>10</v>
       </c>
+      <c r="J4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="M4" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="N4" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="O4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="P4" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="Q4" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="R4" s="3" t="s">
+        <v>19</v>
+      </c>
+      <c r="S4" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="T4" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="U4" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="V4" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="W4" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="X4" s="3" t="s">
+        <v>25</v>
+      </c>
+      <c r="Y4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="Z4" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="AA4" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="AB4" s="3" t="s">
+        <v>29</v>
+      </c>
+      <c r="AC4" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="AD4" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="AE4" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="AF4" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="AG4" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AH4" s="3" t="s">
+        <v>35</v>
+      </c>
+      <c r="AI4" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="AJ4" s="3" t="s">
+        <v>37</v>
+      </c>
+      <c r="AK4" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="AL4" s="3" t="s">
+        <v>39</v>
+      </c>
+      <c r="AM4" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="AN4" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="AO4" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="AP4" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="AQ4" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="AR4" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="AS4" s="3" t="s">
+        <v>46</v>
+      </c>
     </row>
-    <row r="5" ht="18" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="5" ht="18" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
-        <v>11</v>
+        <v>47</v>
       </c>
       <c r="B5" s="4" t="s">
-        <v>12</v>
+        <v>48</v>
       </c>
       <c r="C5" s="4" t="s">
-        <v>13</v>
+        <v>49</v>
       </c>
       <c r="D5" s="4" t="s">
-        <v>14</v>
+        <v>50</v>
       </c>
       <c r="E5" s="4" t="s">
-        <v>15</v>
+        <v>51</v>
       </c>
       <c r="F5" s="4" t="s">
-        <v>16</v>
+        <v>52</v>
       </c>
       <c r="G5" s="4" t="s">
-        <v>17</v>
+        <v>53</v>
       </c>
       <c r="H5" s="4" t="s">
-        <v>18</v>
+        <v>54</v>
       </c>
       <c r="I5" s="4" t="s">
-        <v>19</v>
+        <v>55</v>
+      </c>
+      <c r="J5" s="4" t="s">
+        <v>56</v>
+      </c>
+      <c r="K5" s="4" t="s">
+        <v>57</v>
+      </c>
+      <c r="L5" s="4" t="s">
+        <v>58</v>
+      </c>
+      <c r="M5" s="4" t="s">
+        <v>59</v>
+      </c>
+      <c r="N5" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="O5" s="4" t="s">
+        <v>61</v>
+      </c>
+      <c r="P5" s="4" t="s">
+        <v>62</v>
+      </c>
+      <c r="Q5" s="4" t="s">
+        <v>63</v>
+      </c>
+      <c r="R5" s="4" t="s">
+        <v>64</v>
+      </c>
+      <c r="S5" s="4" t="s">
+        <v>65</v>
+      </c>
+      <c r="T5" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="U5" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="V5" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="W5" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="X5" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="Y5" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="Z5" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="AA5" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="AB5" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="AC5" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="AD5" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="AE5" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="AF5" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="AG5" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="AH5" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="AI5" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="AJ5" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="AK5" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="AL5" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="AM5" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="AN5" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="AO5" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="AP5" s="4" t="s">
+        <v>88</v>
+      </c>
+      <c r="AQ5" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="AR5" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="AS5" s="4" t="s">
+        <v>91</v>
       </c>
     </row>
-    <row r="6" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="6" ht="22" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A6" s="5" t="s">
-        <v>20</v>
+        <v>92</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>21</v>
+        <v>93</v>
       </c>
       <c r="C6" s="6">
-        <v>3994</v>
+        <v>82148</v>
       </c>
       <c r="D6" s="6">
         <v>5</v>
       </c>
       <c r="E6" s="7" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="F6" s="6">
-        <v>3594</v>
+        <v>3685</v>
       </c>
       <c r="G6" s="7" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="H6" s="6">
         <v>395</v>
       </c>
       <c r="I6" s="7" t="s">
-        <v>24</v>
+        <v>96</v>
+      </c>
+      <c r="J6" s="6">
+        <v>0</v>
+      </c>
+      <c r="K6" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="L6" s="6">
+        <v>19294</v>
+      </c>
+      <c r="M6" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="N6" s="6">
+        <v>3</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="P6" s="6">
+        <v>44</v>
+      </c>
+      <c r="Q6" s="7" t="s">
+        <v>99</v>
+      </c>
+      <c r="R6" s="6">
+        <v>440</v>
+      </c>
+      <c r="S6" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="T6" s="6">
+        <v>1581</v>
+      </c>
+      <c r="U6" s="7" t="s">
+        <v>101</v>
+      </c>
+      <c r="V6" s="6">
+        <v>34</v>
+      </c>
+      <c r="W6" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="X6" s="6">
+        <v>2277</v>
+      </c>
+      <c r="Y6" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z6" s="6">
+        <v>380</v>
+      </c>
+      <c r="AA6" s="7" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB6" s="6">
+        <v>147</v>
+      </c>
+      <c r="AC6" s="7" t="s">
+        <v>105</v>
+      </c>
+      <c r="AD6" s="6">
+        <v>36071</v>
+      </c>
+      <c r="AE6" s="7" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF6" s="6">
+        <v>654</v>
+      </c>
+      <c r="AG6" s="7" t="s">
+        <v>107</v>
+      </c>
+      <c r="AH6" s="6">
+        <v>15</v>
+      </c>
+      <c r="AI6" s="7" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ6" s="6">
+        <v>13010</v>
+      </c>
+      <c r="AK6" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="AL6" s="6">
+        <v>4082</v>
+      </c>
+      <c r="AM6" s="7" t="s">
+        <v>110</v>
+      </c>
+      <c r="AN6" s="6">
+        <v>1</v>
+      </c>
+      <c r="AO6" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP6" s="6">
+        <v>0</v>
+      </c>
+      <c r="AQ6" s="7" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR6" s="6">
+        <v>30</v>
+      </c>
+      <c r="AS6" s="7" t="s">
+        <v>102</v>
       </c>
     </row>
-    <row r="7" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="7" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A7" s="8" t="s">
-        <v>25</v>
+        <v>111</v>
       </c>
       <c r="B7" s="8" t="s">
-        <v>26</v>
+        <v>112</v>
       </c>
       <c r="C7" s="9">
-        <v>246</v>
+        <v>5126</v>
       </c>
       <c r="D7" s="9">
         <v>0</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="F7" s="9">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="G7" s="10" t="s">
-        <v>28</v>
+        <v>113</v>
       </c>
       <c r="H7" s="9">
         <v>32</v>
       </c>
       <c r="I7" s="10" t="s">
-        <v>29</v>
+        <v>114</v>
+      </c>
+      <c r="J7" s="9">
+        <v>0</v>
+      </c>
+      <c r="K7" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L7" s="9">
+        <v>1467</v>
+      </c>
+      <c r="M7" s="10" t="s">
+        <v>115</v>
+      </c>
+      <c r="N7" s="9">
+        <v>0</v>
+      </c>
+      <c r="O7" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="P7" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q7" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="R7" s="9">
+        <v>8</v>
+      </c>
+      <c r="S7" s="10" t="s">
+        <v>116</v>
+      </c>
+      <c r="T7" s="9">
+        <v>22</v>
+      </c>
+      <c r="U7" s="10" t="s">
+        <v>117</v>
+      </c>
+      <c r="V7" s="9">
+        <v>1</v>
+      </c>
+      <c r="W7" s="10" t="s">
+        <v>108</v>
+      </c>
+      <c r="X7" s="9">
+        <v>214</v>
+      </c>
+      <c r="Y7" s="10" t="s">
+        <v>118</v>
+      </c>
+      <c r="Z7" s="9">
+        <v>40</v>
+      </c>
+      <c r="AA7" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB7" s="9">
+        <v>4</v>
+      </c>
+      <c r="AC7" s="10" t="s">
+        <v>120</v>
+      </c>
+      <c r="AD7" s="9">
+        <v>2051</v>
+      </c>
+      <c r="AE7" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF7" s="9">
+        <v>25</v>
+      </c>
+      <c r="AG7" s="10" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH7" s="9">
+        <v>3</v>
+      </c>
+      <c r="AI7" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="AJ7" s="9">
+        <v>660</v>
+      </c>
+      <c r="AK7" s="10" t="s">
+        <v>124</v>
+      </c>
+      <c r="AL7" s="9">
+        <v>382</v>
+      </c>
+      <c r="AM7" s="10" t="s">
+        <v>125</v>
+      </c>
+      <c r="AN7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO7" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ7" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AS7" s="10" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="8" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="8" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A8" s="8" t="s">
-        <v>30</v>
+        <v>126</v>
       </c>
       <c r="B8" s="8" t="s">
-        <v>31</v>
+        <v>127</v>
       </c>
       <c r="C8" s="9">
-        <v>116</v>
+        <v>1974</v>
       </c>
       <c r="D8" s="9">
         <v>0</v>
       </c>
       <c r="E8" s="10" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="F8" s="9">
-        <v>116</v>
+        <v>127</v>
       </c>
       <c r="G8" s="10" t="s">
-        <v>32</v>
+        <v>128</v>
       </c>
       <c r="H8" s="9">
         <v>0</v>
       </c>
       <c r="I8" s="10" t="s">
-        <v>27</v>
+        <v>97</v>
+      </c>
+      <c r="J8" s="9">
+        <v>0</v>
+      </c>
+      <c r="K8" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L8" s="9">
+        <v>424</v>
+      </c>
+      <c r="M8" s="10" t="s">
+        <v>129</v>
+      </c>
+      <c r="N8" s="9">
+        <v>0</v>
+      </c>
+      <c r="O8" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="P8" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q8" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="R8" s="9">
+        <v>15</v>
+      </c>
+      <c r="S8" s="10" t="s">
+        <v>130</v>
+      </c>
+      <c r="T8" s="9">
+        <v>61</v>
+      </c>
+      <c r="U8" s="10" t="s">
+        <v>131</v>
+      </c>
+      <c r="V8" s="9">
+        <v>0</v>
+      </c>
+      <c r="W8" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="X8" s="9">
+        <v>66</v>
+      </c>
+      <c r="Y8" s="10" t="s">
+        <v>132</v>
+      </c>
+      <c r="Z8" s="9">
+        <v>5</v>
+      </c>
+      <c r="AA8" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="AB8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC8" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD8" s="9">
+        <v>823</v>
+      </c>
+      <c r="AE8" s="10" t="s">
+        <v>134</v>
+      </c>
+      <c r="AF8" s="9">
+        <v>2</v>
+      </c>
+      <c r="AG8" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="AH8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI8" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ8" s="9">
+        <v>441</v>
+      </c>
+      <c r="AK8" s="10" t="s">
+        <v>136</v>
+      </c>
+      <c r="AL8" s="9">
+        <v>8</v>
+      </c>
+      <c r="AM8" s="10" t="s">
+        <v>137</v>
+      </c>
+      <c r="AN8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO8" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ8" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR8" s="9">
+        <v>2</v>
+      </c>
+      <c r="AS8" s="10" t="s">
+        <v>135</v>
       </c>
     </row>
-    <row r="9" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="9" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A9" s="8" t="s">
-        <v>33</v>
+        <v>138</v>
       </c>
       <c r="B9" s="8" t="s">
-        <v>34</v>
+        <v>139</v>
       </c>
       <c r="C9" s="9">
-        <v>459</v>
+        <v>8122</v>
       </c>
       <c r="D9" s="9">
         <v>0</v>
       </c>
       <c r="E9" s="10" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="F9" s="9">
-        <v>437</v>
+        <v>456</v>
       </c>
       <c r="G9" s="10" t="s">
-        <v>35</v>
+        <v>140</v>
       </c>
       <c r="H9" s="9">
         <v>22</v>
       </c>
       <c r="I9" s="10" t="s">
-        <v>36</v>
+        <v>141</v>
+      </c>
+      <c r="J9" s="9">
+        <v>0</v>
+      </c>
+      <c r="K9" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L9" s="9">
+        <v>1880</v>
+      </c>
+      <c r="M9" s="10" t="s">
+        <v>142</v>
+      </c>
+      <c r="N9" s="9">
+        <v>0</v>
+      </c>
+      <c r="O9" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="P9" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q9" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="R9" s="9">
+        <v>34</v>
+      </c>
+      <c r="S9" s="10" t="s">
+        <v>143</v>
+      </c>
+      <c r="T9" s="9">
+        <v>193</v>
+      </c>
+      <c r="U9" s="10" t="s">
+        <v>144</v>
+      </c>
+      <c r="V9" s="9">
+        <v>0</v>
+      </c>
+      <c r="W9" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="X9" s="9">
+        <v>248</v>
+      </c>
+      <c r="Y9" s="10" t="s">
+        <v>145</v>
+      </c>
+      <c r="Z9" s="9">
+        <v>47</v>
+      </c>
+      <c r="AA9" s="10" t="s">
+        <v>146</v>
+      </c>
+      <c r="AB9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC9" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD9" s="9">
+        <v>3556</v>
+      </c>
+      <c r="AE9" s="10" t="s">
+        <v>147</v>
+      </c>
+      <c r="AF9" s="9">
+        <v>239</v>
+      </c>
+      <c r="AG9" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="AH9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI9" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ9" s="9">
+        <v>1374</v>
+      </c>
+      <c r="AK9" s="10" t="s">
+        <v>149</v>
+      </c>
+      <c r="AL9" s="9">
+        <v>69</v>
+      </c>
+      <c r="AM9" s="10" t="s">
+        <v>150</v>
+      </c>
+      <c r="AN9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO9" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ9" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR9" s="9">
+        <v>4</v>
+      </c>
+      <c r="AS9" s="10" t="s">
+        <v>99</v>
       </c>
     </row>
-    <row r="10" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="10" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A10" s="8" t="s">
-        <v>37</v>
+        <v>151</v>
       </c>
       <c r="B10" s="8" t="s">
-        <v>38</v>
+        <v>152</v>
       </c>
       <c r="C10" s="9">
-        <v>400</v>
+        <v>8948</v>
       </c>
       <c r="D10" s="9">
         <v>3</v>
       </c>
       <c r="E10" s="10" t="s">
-        <v>39</v>
+        <v>153</v>
       </c>
       <c r="F10" s="9">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="G10" s="10" t="s">
-        <v>40</v>
+        <v>118</v>
       </c>
       <c r="H10" s="9">
         <v>25</v>
       </c>
       <c r="I10" s="10" t="s">
-        <v>41</v>
+        <v>154</v>
+      </c>
+      <c r="J10" s="9">
+        <v>0</v>
+      </c>
+      <c r="K10" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L10" s="9">
+        <v>2382</v>
+      </c>
+      <c r="M10" s="10" t="s">
+        <v>155</v>
+      </c>
+      <c r="N10" s="9">
+        <v>1</v>
+      </c>
+      <c r="O10" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="P10" s="9">
+        <v>20</v>
+      </c>
+      <c r="Q10" s="10" t="s">
+        <v>156</v>
+      </c>
+      <c r="R10" s="9">
+        <v>79</v>
+      </c>
+      <c r="S10" s="10" t="s">
+        <v>157</v>
+      </c>
+      <c r="T10" s="9">
+        <v>185</v>
+      </c>
+      <c r="U10" s="10" t="s">
+        <v>158</v>
+      </c>
+      <c r="V10" s="9">
+        <v>19</v>
+      </c>
+      <c r="W10" s="10" t="s">
+        <v>159</v>
+      </c>
+      <c r="X10" s="9">
+        <v>268</v>
+      </c>
+      <c r="Y10" s="10" t="s">
+        <v>160</v>
+      </c>
+      <c r="Z10" s="9">
+        <v>23</v>
+      </c>
+      <c r="AA10" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="AB10" s="9">
+        <v>107</v>
+      </c>
+      <c r="AC10" s="10" t="s">
+        <v>162</v>
+      </c>
+      <c r="AD10" s="9">
+        <v>3915</v>
+      </c>
+      <c r="AE10" s="10" t="s">
+        <v>163</v>
+      </c>
+      <c r="AF10" s="9">
+        <v>29</v>
+      </c>
+      <c r="AG10" s="10" t="s">
+        <v>164</v>
+      </c>
+      <c r="AH10" s="9">
+        <v>4</v>
+      </c>
+      <c r="AI10" s="10" t="s">
+        <v>102</v>
+      </c>
+      <c r="AJ10" s="9">
+        <v>1392</v>
+      </c>
+      <c r="AK10" s="10" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL10" s="9">
+        <v>119</v>
+      </c>
+      <c r="AM10" s="10" t="s">
+        <v>166</v>
+      </c>
+      <c r="AN10" s="9">
+        <v>1</v>
+      </c>
+      <c r="AO10" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="AP10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ10" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR10" s="9">
+        <v>3</v>
+      </c>
+      <c r="AS10" s="10" t="s">
+        <v>153</v>
       </c>
     </row>
-    <row r="11" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="11" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A11" s="8" t="s">
-        <v>42</v>
+        <v>167</v>
       </c>
       <c r="B11" s="8" t="s">
-        <v>43</v>
+        <v>168</v>
       </c>
       <c r="C11" s="9">
-        <v>369</v>
+        <v>8263</v>
       </c>
       <c r="D11" s="9">
         <v>1</v>
       </c>
       <c r="E11" s="10" t="s">
-        <v>44</v>
+        <v>94</v>
       </c>
       <c r="F11" s="9">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="G11" s="10" t="s">
-        <v>45</v>
+        <v>169</v>
       </c>
       <c r="H11" s="9">
         <v>6</v>
       </c>
       <c r="I11" s="10" t="s">
-        <v>46</v>
+        <v>170</v>
+      </c>
+      <c r="J11" s="9">
+        <v>0</v>
+      </c>
+      <c r="K11" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L11" s="9">
+        <v>2042</v>
+      </c>
+      <c r="M11" s="10" t="s">
+        <v>171</v>
+      </c>
+      <c r="N11" s="9">
+        <v>0</v>
+      </c>
+      <c r="O11" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="P11" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q11" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="R11" s="9">
+        <v>30</v>
+      </c>
+      <c r="S11" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="T11" s="9">
+        <v>397</v>
+      </c>
+      <c r="U11" s="10" t="s">
+        <v>173</v>
+      </c>
+      <c r="V11" s="9">
+        <v>0</v>
+      </c>
+      <c r="W11" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="X11" s="9">
+        <v>308</v>
+      </c>
+      <c r="Y11" s="10" t="s">
+        <v>174</v>
+      </c>
+      <c r="Z11" s="9">
+        <v>30</v>
+      </c>
+      <c r="AA11" s="10" t="s">
+        <v>172</v>
+      </c>
+      <c r="AB11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC11" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD11" s="9">
+        <v>3791</v>
+      </c>
+      <c r="AE11" s="10" t="s">
+        <v>175</v>
+      </c>
+      <c r="AF11" s="9">
+        <v>75</v>
+      </c>
+      <c r="AG11" s="10" t="s">
+        <v>176</v>
+      </c>
+      <c r="AH11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI11" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ11" s="9">
+        <v>1172</v>
+      </c>
+      <c r="AK11" s="10" t="s">
+        <v>177</v>
+      </c>
+      <c r="AL11" s="9">
+        <v>39</v>
+      </c>
+      <c r="AM11" s="10" t="s">
+        <v>178</v>
+      </c>
+      <c r="AN11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO11" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP11" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ11" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR11" s="9">
+        <v>2</v>
+      </c>
+      <c r="AS11" s="10" t="s">
+        <v>108</v>
       </c>
     </row>
-    <row r="12" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="12" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A12" s="8" t="s">
-        <v>47</v>
+        <v>179</v>
       </c>
       <c r="B12" s="8" t="s">
-        <v>48</v>
+        <v>180</v>
       </c>
       <c r="C12" s="9">
-        <v>324</v>
+        <v>6828</v>
       </c>
       <c r="D12" s="9">
         <v>0</v>
       </c>
       <c r="E12" s="10" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="F12" s="9">
-        <v>189</v>
+        <v>196</v>
       </c>
       <c r="G12" s="10" t="s">
-        <v>49</v>
+        <v>181</v>
       </c>
       <c r="H12" s="9">
         <v>135</v>
       </c>
       <c r="I12" s="10" t="s">
-        <v>50</v>
+        <v>182</v>
+      </c>
+      <c r="J12" s="9">
+        <v>0</v>
+      </c>
+      <c r="K12" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L12" s="9">
+        <v>1256</v>
+      </c>
+      <c r="M12" s="10" t="s">
+        <v>183</v>
+      </c>
+      <c r="N12" s="9">
+        <v>0</v>
+      </c>
+      <c r="O12" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="P12" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q12" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="R12" s="9">
+        <v>26</v>
+      </c>
+      <c r="S12" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="T12" s="9">
+        <v>135</v>
+      </c>
+      <c r="U12" s="10" t="s">
+        <v>182</v>
+      </c>
+      <c r="V12" s="9">
+        <v>0</v>
+      </c>
+      <c r="W12" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="X12" s="9">
+        <v>162</v>
+      </c>
+      <c r="Y12" s="10" t="s">
+        <v>185</v>
+      </c>
+      <c r="Z12" s="9">
+        <v>33</v>
+      </c>
+      <c r="AA12" s="10" t="s">
+        <v>96</v>
+      </c>
+      <c r="AB12" s="9">
+        <v>2</v>
+      </c>
+      <c r="AC12" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD12" s="9">
+        <v>2938</v>
+      </c>
+      <c r="AE12" s="10" t="s">
+        <v>186</v>
+      </c>
+      <c r="AF12" s="9">
+        <v>46</v>
+      </c>
+      <c r="AG12" s="10" t="s">
+        <v>187</v>
+      </c>
+      <c r="AH12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI12" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ12" s="9">
+        <v>1134</v>
+      </c>
+      <c r="AK12" s="10" t="s">
+        <v>188</v>
+      </c>
+      <c r="AL12" s="9">
+        <v>758</v>
+      </c>
+      <c r="AM12" s="10" t="s">
+        <v>189</v>
+      </c>
+      <c r="AN12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO12" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP12" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ12" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR12" s="9">
+        <v>7</v>
+      </c>
+      <c r="AS12" s="10" t="s">
+        <v>135</v>
       </c>
     </row>
-    <row r="13" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="13" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A13" s="8" t="s">
-        <v>51</v>
+        <v>190</v>
       </c>
       <c r="B13" s="8" t="s">
-        <v>52</v>
+        <v>191</v>
       </c>
       <c r="C13" s="9">
-        <v>157</v>
+        <v>3653</v>
       </c>
       <c r="D13" s="9">
         <v>0</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="F13" s="9">
-        <v>155</v>
+        <v>158</v>
       </c>
       <c r="G13" s="10" t="s">
-        <v>53</v>
+        <v>192</v>
       </c>
       <c r="H13" s="9">
         <v>2</v>
       </c>
       <c r="I13" s="10" t="s">
-        <v>54</v>
+        <v>99</v>
+      </c>
+      <c r="J13" s="9">
+        <v>0</v>
+      </c>
+      <c r="K13" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L13" s="9">
+        <v>769</v>
+      </c>
+      <c r="M13" s="10" t="s">
+        <v>193</v>
+      </c>
+      <c r="N13" s="9">
+        <v>1</v>
+      </c>
+      <c r="O13" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="P13" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q13" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="R13" s="9">
+        <v>21</v>
+      </c>
+      <c r="S13" s="10" t="s">
+        <v>194</v>
+      </c>
+      <c r="T13" s="9">
+        <v>85</v>
+      </c>
+      <c r="U13" s="10" t="s">
+        <v>195</v>
+      </c>
+      <c r="V13" s="9">
+        <v>0</v>
+      </c>
+      <c r="W13" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="X13" s="9">
+        <v>106</v>
+      </c>
+      <c r="Y13" s="10" t="s">
+        <v>196</v>
+      </c>
+      <c r="Z13" s="9">
+        <v>14</v>
+      </c>
+      <c r="AA13" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="AB13" s="9">
+        <v>1</v>
+      </c>
+      <c r="AC13" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="AD13" s="9">
+        <v>1495</v>
+      </c>
+      <c r="AE13" s="10" t="s">
+        <v>197</v>
+      </c>
+      <c r="AF13" s="9">
+        <v>39</v>
+      </c>
+      <c r="AG13" s="10" t="s">
+        <v>198</v>
+      </c>
+      <c r="AH13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI13" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ13" s="9">
+        <v>920</v>
+      </c>
+      <c r="AK13" s="10" t="s">
+        <v>199</v>
+      </c>
+      <c r="AL13" s="9">
+        <v>40</v>
+      </c>
+      <c r="AM13" s="10" t="s">
+        <v>200</v>
+      </c>
+      <c r="AN13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO13" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP13" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ13" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR13" s="9">
+        <v>1</v>
+      </c>
+      <c r="AS13" s="10" t="s">
+        <v>153</v>
       </c>
     </row>
-    <row r="14" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="14" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A14" s="8" t="s">
-        <v>55</v>
+        <v>201</v>
       </c>
       <c r="B14" s="8" t="s">
-        <v>56</v>
+        <v>202</v>
       </c>
       <c r="C14" s="9">
-        <v>147</v>
+        <v>3166</v>
       </c>
       <c r="D14" s="9">
         <v>0</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="F14" s="9">
-        <v>130</v>
+        <v>158</v>
       </c>
       <c r="G14" s="10" t="s">
-        <v>57</v>
+        <v>203</v>
       </c>
       <c r="H14" s="9">
         <v>17</v>
       </c>
       <c r="I14" s="10" t="s">
-        <v>58</v>
+        <v>100</v>
+      </c>
+      <c r="J14" s="9">
+        <v>0</v>
+      </c>
+      <c r="K14" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L14" s="9">
+        <v>902</v>
+      </c>
+      <c r="M14" s="10" t="s">
+        <v>204</v>
+      </c>
+      <c r="N14" s="9">
+        <v>1</v>
+      </c>
+      <c r="O14" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="P14" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q14" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="R14" s="9">
+        <v>29</v>
+      </c>
+      <c r="S14" s="10" t="s">
+        <v>205</v>
+      </c>
+      <c r="T14" s="9">
+        <v>66</v>
+      </c>
+      <c r="U14" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="V14" s="9">
+        <v>0</v>
+      </c>
+      <c r="W14" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="X14" s="9">
+        <v>66</v>
+      </c>
+      <c r="Y14" s="10" t="s">
+        <v>206</v>
+      </c>
+      <c r="Z14" s="9">
+        <v>6</v>
+      </c>
+      <c r="AA14" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="AB14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC14" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD14" s="9">
+        <v>1442</v>
+      </c>
+      <c r="AE14" s="10" t="s">
+        <v>208</v>
+      </c>
+      <c r="AF14" s="9">
+        <v>2</v>
+      </c>
+      <c r="AG14" s="10" t="s">
+        <v>123</v>
+      </c>
+      <c r="AH14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI14" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ14" s="9">
+        <v>376</v>
+      </c>
+      <c r="AK14" s="10" t="s">
+        <v>209</v>
+      </c>
+      <c r="AL14" s="9">
+        <v>99</v>
+      </c>
+      <c r="AM14" s="10" t="s">
+        <v>210</v>
+      </c>
+      <c r="AN14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO14" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP14" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ14" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR14" s="9">
+        <v>2</v>
+      </c>
+      <c r="AS14" s="10" t="s">
+        <v>123</v>
       </c>
     </row>
-    <row r="15" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="15" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A15" s="8" t="s">
-        <v>59</v>
+        <v>211</v>
       </c>
       <c r="B15" s="8" t="s">
-        <v>60</v>
+        <v>212</v>
       </c>
       <c r="C15" s="9">
-        <v>345</v>
+        <v>7815</v>
       </c>
       <c r="D15" s="9">
         <v>0</v>
       </c>
       <c r="E15" s="10" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="F15" s="9">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="G15" s="10" t="s">
-        <v>61</v>
+        <v>213</v>
       </c>
       <c r="H15" s="9">
         <v>88</v>
       </c>
       <c r="I15" s="10" t="s">
-        <v>62</v>
+        <v>214</v>
+      </c>
+      <c r="J15" s="9">
+        <v>0</v>
+      </c>
+      <c r="K15" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L15" s="9">
+        <v>1059</v>
+      </c>
+      <c r="M15" s="10" t="s">
+        <v>215</v>
+      </c>
+      <c r="N15" s="9">
+        <v>0</v>
+      </c>
+      <c r="O15" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="P15" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q15" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="R15" s="9">
+        <v>78</v>
+      </c>
+      <c r="S15" s="10" t="s">
+        <v>216</v>
+      </c>
+      <c r="T15" s="9">
+        <v>114</v>
+      </c>
+      <c r="U15" s="10" t="s">
+        <v>217</v>
+      </c>
+      <c r="V15" s="9">
+        <v>0</v>
+      </c>
+      <c r="W15" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="X15" s="9">
+        <v>100</v>
+      </c>
+      <c r="Y15" s="10" t="s">
+        <v>218</v>
+      </c>
+      <c r="Z15" s="9">
+        <v>11</v>
+      </c>
+      <c r="AA15" s="10" t="s">
+        <v>219</v>
+      </c>
+      <c r="AB15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC15" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD15" s="9">
+        <v>3185</v>
+      </c>
+      <c r="AE15" s="10" t="s">
+        <v>220</v>
+      </c>
+      <c r="AF15" s="9">
+        <v>66</v>
+      </c>
+      <c r="AG15" s="10" t="s">
+        <v>221</v>
+      </c>
+      <c r="AH15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI15" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ15" s="9">
+        <v>1157</v>
+      </c>
+      <c r="AK15" s="10" t="s">
+        <v>222</v>
+      </c>
+      <c r="AL15" s="9">
+        <v>1696</v>
+      </c>
+      <c r="AM15" s="10" t="s">
+        <v>223</v>
+      </c>
+      <c r="AN15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO15" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP15" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ15" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR15" s="9">
+        <v>3</v>
+      </c>
+      <c r="AS15" s="10" t="s">
+        <v>102</v>
       </c>
     </row>
-    <row r="16" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="16" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A16" s="8" t="s">
-        <v>63</v>
+        <v>224</v>
       </c>
       <c r="B16" s="8" t="s">
-        <v>64</v>
+        <v>225</v>
       </c>
       <c r="C16" s="9">
-        <v>137</v>
+        <v>2554</v>
       </c>
       <c r="D16" s="9">
         <v>0</v>
       </c>
       <c r="E16" s="10" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="F16" s="9">
         <v>131</v>
       </c>
       <c r="G16" s="10" t="s">
-        <v>65</v>
+        <v>226</v>
       </c>
       <c r="H16" s="9">
         <v>6</v>
       </c>
       <c r="I16" s="10" t="s">
-        <v>66</v>
+        <v>227</v>
+      </c>
+      <c r="J16" s="9">
+        <v>0</v>
+      </c>
+      <c r="K16" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L16" s="9">
+        <v>460</v>
+      </c>
+      <c r="M16" s="10" t="s">
+        <v>228</v>
+      </c>
+      <c r="N16" s="9">
+        <v>0</v>
+      </c>
+      <c r="O16" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="P16" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q16" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="R16" s="9">
+        <v>30</v>
+      </c>
+      <c r="S16" s="10" t="s">
+        <v>229</v>
+      </c>
+      <c r="T16" s="9">
+        <v>112</v>
+      </c>
+      <c r="U16" s="10" t="s">
+        <v>230</v>
+      </c>
+      <c r="V16" s="9">
+        <v>0</v>
+      </c>
+      <c r="W16" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="X16" s="9">
+        <v>100</v>
+      </c>
+      <c r="Y16" s="10" t="s">
+        <v>231</v>
+      </c>
+      <c r="Z16" s="9">
+        <v>20</v>
+      </c>
+      <c r="AA16" s="10" t="s">
+        <v>119</v>
+      </c>
+      <c r="AB16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC16" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD16" s="9">
+        <v>1116</v>
+      </c>
+      <c r="AE16" s="10" t="s">
+        <v>232</v>
+      </c>
+      <c r="AF16" s="9">
+        <v>35</v>
+      </c>
+      <c r="AG16" s="10" t="s">
+        <v>233</v>
+      </c>
+      <c r="AH16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI16" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ16" s="9">
+        <v>485</v>
+      </c>
+      <c r="AK16" s="10" t="s">
+        <v>234</v>
+      </c>
+      <c r="AL16" s="9">
+        <v>57</v>
+      </c>
+      <c r="AM16" s="10" t="s">
+        <v>235</v>
+      </c>
+      <c r="AN16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO16" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP16" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ16" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR16" s="9">
+        <v>2</v>
+      </c>
+      <c r="AS16" s="10" t="s">
+        <v>120</v>
       </c>
     </row>
-    <row r="17" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="17" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A17" s="8" t="s">
-        <v>67</v>
+        <v>236</v>
       </c>
       <c r="B17" s="8" t="s">
-        <v>68</v>
+        <v>237</v>
       </c>
       <c r="C17" s="9">
-        <v>232</v>
+        <v>4432</v>
       </c>
       <c r="D17" s="9">
         <v>1</v>
       </c>
       <c r="E17" s="10" t="s">
-        <v>69</v>
+        <v>108</v>
       </c>
       <c r="F17" s="9">
         <v>205</v>
       </c>
       <c r="G17" s="10" t="s">
-        <v>70</v>
+        <v>238</v>
       </c>
       <c r="H17" s="9">
         <v>26</v>
       </c>
       <c r="I17" s="10" t="s">
-        <v>71</v>
+        <v>239</v>
+      </c>
+      <c r="J17" s="9">
+        <v>0</v>
+      </c>
+      <c r="K17" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L17" s="9">
+        <v>1043</v>
+      </c>
+      <c r="M17" s="10" t="s">
+        <v>240</v>
+      </c>
+      <c r="N17" s="9">
+        <v>0</v>
+      </c>
+      <c r="O17" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="P17" s="9">
+        <v>22</v>
+      </c>
+      <c r="Q17" s="10" t="s">
+        <v>241</v>
+      </c>
+      <c r="R17" s="9">
+        <v>29</v>
+      </c>
+      <c r="S17" s="10" t="s">
+        <v>242</v>
+      </c>
+      <c r="T17" s="9">
+        <v>30</v>
+      </c>
+      <c r="U17" s="10" t="s">
+        <v>243</v>
+      </c>
+      <c r="V17" s="9">
+        <v>9</v>
+      </c>
+      <c r="W17" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="X17" s="9">
+        <v>77</v>
+      </c>
+      <c r="Y17" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="Z17" s="9">
+        <v>2</v>
+      </c>
+      <c r="AA17" s="10" t="s">
+        <v>99</v>
+      </c>
+      <c r="AB17" s="9">
+        <v>4</v>
+      </c>
+      <c r="AC17" s="10" t="s">
+        <v>246</v>
+      </c>
+      <c r="AD17" s="9">
+        <v>2212</v>
+      </c>
+      <c r="AE17" s="10" t="s">
+        <v>247</v>
+      </c>
+      <c r="AF17" s="9">
+        <v>42</v>
+      </c>
+      <c r="AG17" s="10" t="s">
+        <v>248</v>
+      </c>
+      <c r="AH17" s="9">
+        <v>3</v>
+      </c>
+      <c r="AI17" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="AJ17" s="9">
+        <v>507</v>
+      </c>
+      <c r="AK17" s="10" t="s">
+        <v>249</v>
+      </c>
+      <c r="AL17" s="9">
+        <v>220</v>
+      </c>
+      <c r="AM17" s="10" t="s">
+        <v>250</v>
+      </c>
+      <c r="AN17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO17" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ17" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR17" s="9">
+        <v>0</v>
+      </c>
+      <c r="AS17" s="10" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="18" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="18" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A18" s="8" t="s">
-        <v>72</v>
+        <v>251</v>
       </c>
       <c r="B18" s="8" t="s">
-        <v>73</v>
+        <v>252</v>
       </c>
       <c r="C18" s="9">
-        <v>239</v>
+        <v>5494</v>
       </c>
       <c r="D18" s="9">
         <v>0</v>
       </c>
       <c r="E18" s="10" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="F18" s="9">
         <v>233</v>
       </c>
       <c r="G18" s="10" t="s">
-        <v>74</v>
+        <v>253</v>
       </c>
       <c r="H18" s="9">
         <v>6</v>
       </c>
       <c r="I18" s="10" t="s">
-        <v>75</v>
+        <v>254</v>
+      </c>
+      <c r="J18" s="9">
+        <v>0</v>
+      </c>
+      <c r="K18" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L18" s="9">
+        <v>1308</v>
+      </c>
+      <c r="M18" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="N18" s="9">
+        <v>0</v>
+      </c>
+      <c r="O18" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="P18" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q18" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="R18" s="9">
+        <v>21</v>
+      </c>
+      <c r="S18" s="10" t="s">
+        <v>184</v>
+      </c>
+      <c r="T18" s="9">
+        <v>87</v>
+      </c>
+      <c r="U18" s="10" t="s">
+        <v>256</v>
+      </c>
+      <c r="V18" s="9">
+        <v>0</v>
+      </c>
+      <c r="W18" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="X18" s="9">
+        <v>99</v>
+      </c>
+      <c r="Y18" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="Z18" s="9">
+        <v>15</v>
+      </c>
+      <c r="AA18" s="10" t="s">
+        <v>141</v>
+      </c>
+      <c r="AB18" s="9">
+        <v>8</v>
+      </c>
+      <c r="AC18" s="10" t="s">
+        <v>258</v>
+      </c>
+      <c r="AD18" s="9">
+        <v>2492</v>
+      </c>
+      <c r="AE18" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="AF18" s="9">
+        <v>13</v>
+      </c>
+      <c r="AG18" s="10" t="s">
+        <v>260</v>
+      </c>
+      <c r="AH18" s="9">
+        <v>4</v>
+      </c>
+      <c r="AI18" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="AJ18" s="9">
+        <v>1164</v>
+      </c>
+      <c r="AK18" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="AL18" s="9">
+        <v>44</v>
+      </c>
+      <c r="AM18" s="10" t="s">
+        <v>107</v>
+      </c>
+      <c r="AN18" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO18" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP18" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ18" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR18" s="9">
+        <v>0</v>
+      </c>
+      <c r="AS18" s="10" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="19" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="19" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A19" s="8" t="s">
-        <v>76</v>
+        <v>262</v>
       </c>
       <c r="B19" s="8" t="s">
-        <v>77</v>
+        <v>263</v>
       </c>
       <c r="C19" s="9">
-        <v>712</v>
+        <v>13461</v>
       </c>
       <c r="D19" s="9">
         <v>0</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="F19" s="9">
-        <v>694</v>
+        <v>703</v>
       </c>
       <c r="G19" s="10" t="s">
-        <v>78</v>
+        <v>264</v>
       </c>
       <c r="H19" s="9">
         <v>18</v>
       </c>
       <c r="I19" s="10" t="s">
-        <v>79</v>
+        <v>265</v>
+      </c>
+      <c r="J19" s="9">
+        <v>0</v>
+      </c>
+      <c r="K19" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L19" s="9">
+        <v>4033</v>
+      </c>
+      <c r="M19" s="10" t="s">
+        <v>266</v>
+      </c>
+      <c r="N19" s="9">
+        <v>0</v>
+      </c>
+      <c r="O19" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="P19" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q19" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="R19" s="9">
+        <v>27</v>
+      </c>
+      <c r="S19" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="T19" s="9">
+        <v>17</v>
+      </c>
+      <c r="U19" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="V19" s="9">
+        <v>0</v>
+      </c>
+      <c r="W19" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="X19" s="9">
+        <v>354</v>
+      </c>
+      <c r="Y19" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="Z19" s="9">
+        <v>4</v>
+      </c>
+      <c r="AA19" s="10" t="s">
+        <v>153</v>
+      </c>
+      <c r="AB19" s="9">
+        <v>0</v>
+      </c>
+      <c r="AC19" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AD19" s="9">
+        <v>6097</v>
+      </c>
+      <c r="AE19" s="10" t="s">
+        <v>268</v>
+      </c>
+      <c r="AF19" s="9">
+        <v>26</v>
+      </c>
+      <c r="AG19" s="10" t="s">
+        <v>207</v>
+      </c>
+      <c r="AH19" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI19" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ19" s="9">
+        <v>2032</v>
+      </c>
+      <c r="AK19" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="AL19" s="9">
+        <v>148</v>
+      </c>
+      <c r="AM19" s="10" t="s">
+        <v>270</v>
+      </c>
+      <c r="AN19" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO19" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP19" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ19" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR19" s="9">
+        <v>2</v>
+      </c>
+      <c r="AS19" s="10" t="s">
+        <v>94</v>
       </c>
     </row>
-    <row r="20" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="20" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A20" s="8" t="s">
-        <v>80</v>
+        <v>271</v>
       </c>
       <c r="B20" s="8" t="s">
-        <v>81</v>
+        <v>272</v>
       </c>
       <c r="C20" s="9">
-        <v>62</v>
+        <v>783</v>
       </c>
       <c r="D20" s="9">
         <v>0</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="F20" s="9">
         <v>56</v>
       </c>
       <c r="G20" s="10" t="s">
-        <v>82</v>
+        <v>273</v>
       </c>
       <c r="H20" s="9">
         <v>6</v>
       </c>
       <c r="I20" s="10" t="s">
-        <v>83</v>
+        <v>274</v>
+      </c>
+      <c r="J20" s="9">
+        <v>0</v>
+      </c>
+      <c r="K20" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L20" s="9">
+        <v>87</v>
+      </c>
+      <c r="M20" s="10" t="s">
+        <v>275</v>
+      </c>
+      <c r="N20" s="9">
+        <v>0</v>
+      </c>
+      <c r="O20" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="P20" s="9">
+        <v>1</v>
+      </c>
+      <c r="Q20" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="R20" s="9">
+        <v>4</v>
+      </c>
+      <c r="S20" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="T20" s="9">
+        <v>42</v>
+      </c>
+      <c r="U20" s="10" t="s">
+        <v>277</v>
+      </c>
+      <c r="V20" s="9">
+        <v>4</v>
+      </c>
+      <c r="W20" s="10" t="s">
+        <v>276</v>
+      </c>
+      <c r="X20" s="9">
+        <v>64</v>
+      </c>
+      <c r="Y20" s="10" t="s">
+        <v>278</v>
+      </c>
+      <c r="Z20" s="9">
+        <v>91</v>
+      </c>
+      <c r="AA20" s="10" t="s">
+        <v>279</v>
+      </c>
+      <c r="AB20" s="9">
+        <v>6</v>
+      </c>
+      <c r="AC20" s="10" t="s">
+        <v>274</v>
+      </c>
+      <c r="AD20" s="9">
+        <v>313</v>
+      </c>
+      <c r="AE20" s="10" t="s">
+        <v>280</v>
+      </c>
+      <c r="AF20" s="9">
+        <v>12</v>
+      </c>
+      <c r="AG20" s="10" t="s">
+        <v>281</v>
+      </c>
+      <c r="AH20" s="9">
+        <v>1</v>
+      </c>
+      <c r="AI20" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="AJ20" s="9">
+        <v>75</v>
+      </c>
+      <c r="AK20" s="10" t="s">
+        <v>282</v>
+      </c>
+      <c r="AL20" s="9">
+        <v>19</v>
+      </c>
+      <c r="AM20" s="10" t="s">
+        <v>283</v>
+      </c>
+      <c r="AN20" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO20" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP20" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ20" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR20" s="9">
+        <v>2</v>
+      </c>
+      <c r="AS20" s="10" t="s">
+        <v>161</v>
       </c>
     </row>
-    <row r="21" ht="19" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="21" ht="19" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A21" s="8" t="s">
-        <v>84</v>
+        <v>284</v>
       </c>
       <c r="B21" s="8" t="s">
-        <v>85</v>
+        <v>285</v>
       </c>
       <c r="C21" s="9">
-        <v>49</v>
+        <v>1529</v>
       </c>
       <c r="D21" s="9">
         <v>0</v>
       </c>
       <c r="E21" s="10" t="s">
-        <v>27</v>
+        <v>97</v>
       </c>
       <c r="F21" s="9">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="G21" s="10" t="s">
-        <v>86</v>
+        <v>286</v>
       </c>
       <c r="H21" s="9">
         <v>6</v>
       </c>
       <c r="I21" s="10" t="s">
-        <v>87</v>
+        <v>287</v>
+      </c>
+      <c r="J21" s="9">
+        <v>0</v>
+      </c>
+      <c r="K21" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="L21" s="9">
+        <v>182</v>
+      </c>
+      <c r="M21" s="10" t="s">
+        <v>288</v>
+      </c>
+      <c r="N21" s="9">
+        <v>0</v>
+      </c>
+      <c r="O21" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="P21" s="9">
+        <v>0</v>
+      </c>
+      <c r="Q21" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="R21" s="9">
+        <v>9</v>
+      </c>
+      <c r="S21" s="10" t="s">
+        <v>239</v>
+      </c>
+      <c r="T21" s="9">
+        <v>35</v>
+      </c>
+      <c r="U21" s="10" t="s">
+        <v>289</v>
+      </c>
+      <c r="V21" s="9">
+        <v>1</v>
+      </c>
+      <c r="W21" s="10" t="s">
+        <v>170</v>
+      </c>
+      <c r="X21" s="9">
+        <v>45</v>
+      </c>
+      <c r="Y21" s="10" t="s">
+        <v>148</v>
+      </c>
+      <c r="Z21" s="9">
+        <v>39</v>
+      </c>
+      <c r="AA21" s="10" t="s">
+        <v>290</v>
+      </c>
+      <c r="AB21" s="9">
+        <v>15</v>
+      </c>
+      <c r="AC21" s="10" t="s">
+        <v>291</v>
+      </c>
+      <c r="AD21" s="9">
+        <v>645</v>
+      </c>
+      <c r="AE21" s="10" t="s">
+        <v>292</v>
+      </c>
+      <c r="AF21" s="9">
+        <v>3</v>
+      </c>
+      <c r="AG21" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="AH21" s="9">
+        <v>0</v>
+      </c>
+      <c r="AI21" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AJ21" s="9">
+        <v>121</v>
+      </c>
+      <c r="AK21" s="10" t="s">
+        <v>293</v>
+      </c>
+      <c r="AL21" s="9">
+        <v>384</v>
+      </c>
+      <c r="AM21" s="10" t="s">
+        <v>294</v>
+      </c>
+      <c r="AN21" s="9">
+        <v>0</v>
+      </c>
+      <c r="AO21" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP21" s="9">
+        <v>0</v>
+      </c>
+      <c r="AQ21" s="10" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR21" s="9">
+        <v>0</v>
+      </c>
+      <c r="AS21" s="10" t="s">
+        <v>97</v>
       </c>
     </row>
-    <row r="22" ht="22" customHeight="1" spans="1:9" x14ac:dyDescent="0.25">
+    <row r="22" ht="22" customHeight="1" spans="1:45" x14ac:dyDescent="0.25">
       <c r="A22" s="11" t="s">
-        <v>88</v>
+        <v>295</v>
       </c>
       <c r="B22" s="11" t="s">
-        <v>89</v>
+        <v>296</v>
       </c>
       <c r="C22" s="12">
-        <v>3994</v>
+        <v>82148</v>
       </c>
       <c r="D22" s="12">
         <v>5</v>
       </c>
       <c r="E22" s="13" t="s">
-        <v>22</v>
+        <v>94</v>
       </c>
       <c r="F22" s="12">
-        <v>3594</v>
+        <v>3685</v>
       </c>
       <c r="G22" s="13" t="s">
-        <v>23</v>
+        <v>95</v>
       </c>
       <c r="H22" s="12">
         <v>395</v>
       </c>
       <c r="I22" s="13" t="s">
-        <v>24</v>
+        <v>96</v>
+      </c>
+      <c r="J22" s="12">
+        <v>0</v>
+      </c>
+      <c r="K22" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="L22" s="12">
+        <v>19294</v>
+      </c>
+      <c r="M22" s="13" t="s">
+        <v>98</v>
+      </c>
+      <c r="N22" s="12">
+        <v>3</v>
+      </c>
+      <c r="O22" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="P22" s="12">
+        <v>44</v>
+      </c>
+      <c r="Q22" s="13" t="s">
+        <v>99</v>
+      </c>
+      <c r="R22" s="12">
+        <v>440</v>
+      </c>
+      <c r="S22" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="T22" s="12">
+        <v>1581</v>
+      </c>
+      <c r="U22" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="V22" s="12">
+        <v>34</v>
+      </c>
+      <c r="W22" s="13" t="s">
+        <v>102</v>
+      </c>
+      <c r="X22" s="12">
+        <v>2277</v>
+      </c>
+      <c r="Y22" s="13" t="s">
+        <v>103</v>
+      </c>
+      <c r="Z22" s="12">
+        <v>380</v>
+      </c>
+      <c r="AA22" s="13" t="s">
+        <v>104</v>
+      </c>
+      <c r="AB22" s="12">
+        <v>147</v>
+      </c>
+      <c r="AC22" s="13" t="s">
+        <v>105</v>
+      </c>
+      <c r="AD22" s="12">
+        <v>36071</v>
+      </c>
+      <c r="AE22" s="13" t="s">
+        <v>106</v>
+      </c>
+      <c r="AF22" s="12">
+        <v>654</v>
+      </c>
+      <c r="AG22" s="13" t="s">
+        <v>107</v>
+      </c>
+      <c r="AH22" s="12">
+        <v>15</v>
+      </c>
+      <c r="AI22" s="13" t="s">
+        <v>108</v>
+      </c>
+      <c r="AJ22" s="12">
+        <v>13010</v>
+      </c>
+      <c r="AK22" s="13" t="s">
+        <v>109</v>
+      </c>
+      <c r="AL22" s="12">
+        <v>4082</v>
+      </c>
+      <c r="AM22" s="13" t="s">
+        <v>110</v>
+      </c>
+      <c r="AN22" s="12">
+        <v>1</v>
+      </c>
+      <c r="AO22" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="AP22" s="12">
+        <v>0</v>
+      </c>
+      <c r="AQ22" s="13" t="s">
+        <v>97</v>
+      </c>
+      <c r="AR22" s="12">
+        <v>30</v>
+      </c>
+      <c r="AS22" s="13" t="s">
+        <v>102</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:I21"/>
+  <autoFilter ref="A4:AS21"/>
   <mergeCells count="2">
-    <mergeCell ref="A1:I1"/>
-    <mergeCell ref="A2:I2"/>
+    <mergeCell ref="A1:AS1"/>
+    <mergeCell ref="A2:AS2"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
